--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체비교" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="통계대시보드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="확인불가·보완필요" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="전체비교" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="통계대시보드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="확인불가·보완필요" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -746,17 +746,17 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>정보관리실·정보운영실 (징수상임이사 산하) / 별도로 NHIS인공지능실·빅데이터운영실 (기획상임이사 산하)</t>
+          <t>정보관리실 / NHIS인공지능실</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>이사 직속 실</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>(정보관리실) 정보기획부, 정보시스템부, 정보보안부, 고객지원정보부, 경영정보부 / (빅데이터운영실) 빅데이터기획부, 빅데이터결합개방부, 빅데이터연구개발부, 빅데이터통계부</t>
+          <t>정보관리실(정보기획부·정보시스템부·정보보안부·고객지원정보부·경영정보부), 정보운영실(자격부과정보부·징수정보부·급여관리정보부·급여보장정보부·건강정보부·요양정보부·통합돌봄정보부), 빅데이터운영실(빅데이터기획부·빅데이터결합개방부·빅데이터연구개발부·빅데이터통계부)</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보관리실 소관, 징수상임이사 총괄 추정)</t>
+          <t>확인불가 (IT운영은 징수상임이사, AI·빅데이터는 기획상임이사 산하로 분산)</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>2025년 1월 '디지털 대전환(NHIS DX)' 일환으로 AI전담부서(NHIS인공지능실) 신설. AI 상담(NHIS-CALL)·업무비서(NHIS-MATE) 등 생성형 AI 도입 확대. 본부·지역본부·지사 체계 및 AI 기반 업무 재편 중장기 조직진단 추진 중.</t>
+          <t>IT기능: 정보기획·시스템운영·정보보안·빅데이터 분석·AI 서비스 개발·의료정보 운영&lt;br&gt;조직이력: 2025.1 NHIS인공지능실 신설(NHIS DX 일환)&lt;br&gt;기타: AI 상담(NHIS-CALL)·업무비서(NHIS-MATE) 등 생성형 AI 도입. AI 기반 업무 재편 중장기 조직진단 추진.</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신본부</t>
+          <t>디지털보험관리이사</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>정보보안부 (그 외 정보화기획/정보화운영 관련 부서 추정 — 공식 조직도(comwel.or.kr) JS 렌더링으로 세부 명칭 확인불가)</t>
+          <t>디지털혁신본부(AI혁신기획부·정보인프라부·경영정보부·재정정보부·급여정보부·복지정보부·의료정보부·정보보안부)</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -991,17 +991,17 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (업무상질병 AI 신속분류 관련 전담조직, 정확한 부서 명칭 미공개)</t>
+          <t>AI혁신기획부 (디지털혁신본부 산하)</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전 지사 단위로는 '근골격계 질병 전담팀' 운영)</t>
+          <t>부 (디지털혁신본부 산하)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신본부장 (추정)</t>
+          <t>디지털보험관리이사 (임원급, 디지털혁신본부 직속 상위) / 디지털혁신본부장</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>중(고용노동부 채용공고·전자신문 등 공식·준공식 복수 출처. 디지털혁신본부·정보보안부 확정, 본부 산하 정보화 세부부서명·AI 조직명/레벨 미확정)</t>
+          <t>상 (공식 홈페이지(comwel.or.kr/comwel/intr/orgn/totl.jsp) 직접 확인 — 디지털혁신본부 산하 8개 부서 전량 확인, 2026-06-18)</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>2025년 AI 기반 업무상질병 신속분류 모델 도입 및 전담조직 신설(근골격계 질병 평균 처리기간 전년 동월 대비 30.5일 단축, 166.3일 기록). 'K-산재보험' AI 단계 도입, 빅데이터·AI 기반 지능형 재활추천시스템(2021 ISSA 우수상), 더존ICT그룹과 AI OCR 기반 'Smart 자동접수시스템'(약 120억 규모) 등 민원 DX 추진. 2026년 64개 전 지사 근골격계 질병 전담팀 운영·AI 기반 재해조사 기법 도입 예정.</t>
+          <t>IT기능: 8개 부서(AI혁신기획부·정보인프라부·경영정보부·재정정보부·급여정보부·복지정보부·의료정보부·정보보안부)로 전산·보안·급여·의료정보 통합 운영.&lt;br&gt;조직이력: 2025년 AI 기반 업무상질병 신속분류 모델 도입, AI혁신기획부 신설.&lt;br&gt;기타: 빅데이터·AI 기반 지능형 재활추천시스템(2021 ISSA 우수상). 더존ICT그룹과 AI OCR 기반 'Smart 자동접수시스템'(약 120억) 등 민원 DX 추진.</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>정보기획팀, 의무기록팀, 전산실 (의료정보 운영·기획)</t>
+          <t>정보기획팀, 의무기록팀, 전산실</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>국내 최초 의무기록 디지털화 추진. 헬스케어AI연구원 출범(원장: 서울대 컴퓨터공학 교수). 통합 빅데이터 플랫폼 SNUHUB, CDW 연구검색 SUPREME, 가명의무기록 뷰어 DeView, NSTRI 데이터플랫폼, GPU 클러스터 보유. 연구중심병원.</t>
+          <t>IT기능: 의료정보시스템(HIS) 운영·기획, 의무기록 관리, 빅데이터 플랫폼 운영&lt;br&gt;기타: 국내 최초 의무기록 디지털화 추진. 헬스케어AI연구원 출범. 통합 빅데이터 플랫폼 SNUHUB, CDW 연구검색 SUPREME, 가명의무기록 뷰어 DeView, GPU 클러스터 보유. 연구중심병원.</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>AI디지털전략실, 정보운영실, ICT센터 (AI디지털전략실 내 정보보안부 포함)</t>
+          <t>AI디지털전략실(정보보안부), 정보운영실, ICT센터</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>기존 '디지털혁신본부'를 'AI디지털혁신본부'로 확대 개편하여 AI를 본부 명칭에 반영. 디지털혁신본부장을 개방형직위로 공개모집. 정보보안부장은 정부 민간인재 영입제도로 외부 보안전문가 임용.</t>
+          <t>조직이력: 기존 '디지털혁신본부'를 'AI디지털혁신본부'로 확대 개편(AI를 본부 명칭에 반영). 본부장 개방형직위 공개모집.&lt;br&gt;기타: 정보보안부장은 정부 민간인재 영입제도로 외부 보안전문가 임용.</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>의료정보센터(병원정보시스템·의료정보 운영), 융합의학기술원 내 의료빅데이터팀</t>
+          <t>의료정보센터, 융합의학기술원(의료빅데이터팀)</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>2020.8 보건복지부 '의료데이터 중심병원 지원사업' 선정. 의료데이터 안심활용센터 운영. 국내 최초 자연어처리 의료AI '비비안' 도입. 융합의학기술원 국립대 최초 특수전문기관 지정(2026).</t>
+          <t>IT기능: 의료정보시스템(HIS) 운영, 병원정보시스템 관리, 의료빅데이터 수집·분석&lt;br&gt;기타: 2020.8 보건복지부 '의료데이터 중심병원 지원사업' 선정. 의료데이터 안심활용센터 운영. 국내 최초 자연어처리 의료AI '비비안' 도입. 2026 융합의학기술원 국립대 최초 특수전문기관 지정.</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>디지털관리처(디지털관리부·정보화제도담당관 등), 디지털보안처(정보보안), AI데이터센터</t>
+          <t>AI혁신처, 디지털관리처(디지털관리부·정보화제도담당관 등), AI데이터센터 (※디지털보안처: 공식 조직도 미표기 — 현행 존속 여부 재확인 필요)</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1741,12 +1741,12 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>의료인공지능센터(연구조직), 정보화실 데이터융합팀(데이터 기반 운영)</t>
+          <t>의료인공지능센터, 정보화실 데이터융합팀</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>센터(의생명연구원 산하 연구조직) / 정보화실 산하 팀</t>
+          <t>센터, 팀</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>의료인공지능센터(센터장 김세중 교수) 운영 — 의료 AI 연구·개발·교육. 뉴타닉스 기반 의료시스템 인프라 혁신. 정보화실에 데이터융합팀을 별도 편제하여 데이터 거버넌스 강화.</t>
+          <t>IT기능: 의료정보시스템 운영, 데이터 거버넌스, 의무기록 관리, 정보보호&lt;br&gt;기타: 의료인공지능센터(센터장 김세중 교수) 운영 — 의료 AI 연구·개발·교육. 뉴타닉스 기반 의료시스템 인프라 혁신.</t>
         </is>
       </c>
     </row>
@@ -1801,12 +1801,12 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>센터(처·실급 추정)</t>
+          <t>센터</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>의료정보센터(정보개발계획 수립·정보체계 분석/설계, 전산화·IT인프라 운영, 의료과학정보 수집·관리)</t>
+          <t>의료정보센터</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>인공지능기반 의료혁신센터 (前 AI센터·빅데이터센터 통합·일원화) — 데이터 수집~AI SW개발~임상검증~기술이전·사업화 전 주기 R&amp;D 수행. 그 외 생명의학연구원 의료인공지능연구센터(의료AI 연계연구), 의과대학 의료정보학교실</t>
+          <t>인공지능기반 의료혁신센터</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>2025.8.29 「인공지능기반 의료혁신센터」 출범(AI센터+빅데이터센터 통합) 및 'AI와 의료, 혁신의 중심에 서다' 메디컬 AI 포럼 개최. AI센터는 닥터앤서 1.0·2.0, 디지털치료기기 개발·실증 등 국가과제 수행(SCI 논문 20편+, 특허 20건+). 정부 'AI 3대 강국 전략' 연계 지역의료 AI 생태계 구축 추진. 2017.1 인실리코메디슨 AI·빅데이터 MOU. 의료정보센터가 병원 전산/IT 총괄, 정보보호팀이 정보보호 실무.</t>
+          <t>IT기능: 정보개발계획 수립, 정보체계 분석·설계, 전산화·IT인프라 운영, 의료과학정보 수집·관리&lt;br&gt;조직이력: 2025.8.29 AI센터·빅데이터센터 통합 → 「인공지능기반 의료혁신센터」 출범&lt;br&gt;기타: 닥터앤서 1.0·2.0, 디지털치료기기 개발·실증 등 국가과제 수행(SCI 논문 20편+, 특허 20건+). 정부 AI 3대 강국 전략 연계 지역의료 AI 생태계 구축 추진. 생명의학연구원 의료인공지능연구센터 병행 운영.</t>
         </is>
       </c>
     </row>
@@ -1871,17 +1871,17 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>의료정보센터</t>
+          <t>기획조정실</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>센터(처·실급 추정)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>의료정보센터(의료정보 부원장 직속 의료정보부) 산하 '의료정보과'(개발분석팀 등) — 모바일앱·병원정보시스템 개발/운영 담당. 그 외 의무기록실·의무기록팀(개인정보 보호 담당부서)</t>
+          <t>의료정보센터(의료정보과)</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>센터</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>정식 'CISO' 직위 명칭은 미표기. 개인정보 보호책임자(CPO)=진료부원장 윤경철(062-220-6741), 개인정보 보호 담당부서=의무기록실(담당 정대원). 정보보안·정보보호는 의료정보과/의무기록실 분담 운영(별도 정보보호실 명칭 미확인)</t>
+          <t>정보보호실 (병원장 직속 실급 전담조직)</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 조직도 + 보도자료 교차, 세부 직제 일부 추정)</t>
+          <t>상(공식 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>정보관리국 (혈액관리본부 산하) — 본사 차원 별도 IT 본부·실은 미확인</t>
+          <t>혈액관리본부</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 혈액관리본부 산하 국 단위</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>정보관리국 산하 '정보보호팀'(개인정보·정보보안 담당, privacy@redcross.or.kr) 확인. 그 외 혈액정보시스템(BIMS/BISS) 운영 담당 부서 운영(세부 부·팀 명칭 일부 미확인)</t>
+          <t>정보관리국(정보기획팀·혈액정보팀·경영정보팀·정보보호팀)</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>혈액·재난구호 기관(혈액 사업이 핵심). IT 전담조직이 혈액사업 정보시스템(혈액정보) 중심으로 혈액관리본부 산하 '정보관리국'에 편제됨. 본사(기획조정실 등)에 별도 정보화 전담 실·국은 조직도상 명확히 표기되지 않음. 적십자의료원(병원사업본부, 7개 병원) 및 전국 15개 혈액원·3개 검사센터 운영. 혈액정보 별도 사이트(bloodinfo.net) 운영.</t>
+          <t>IT담당배경: IT 전담조직이 본사가 아닌 혈액관리본부 산하 정보관리국에 편제 — 혈액사업 정보시스템 운영이 핵심 IT 업무임.&lt;br&gt;IT기능: 정보기획, 혈액정보시스템(BIMS·BISS) 운영, 경영정보, 정보보호&lt;br&gt;기타: bloodinfo.net 혈액정보 별도 사이트 운영. 전국 15개 혈액원·3개 검사센터. 2024.4 BIMS 가명정보 처리 관련 개인정보위 과태료 부과 이력.</t>
         </is>
       </c>
     </row>
@@ -2396,17 +2396,17 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>디지털전략실 (구 ICT전략실)</t>
+          <t>기획상임이사</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 기획상임이사 산하</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>디지털전략실, 디지털운영실, 디지털클라우드센터 (정보화 관련 실·센터)</t>
+          <t>디지털전략실, 디지털운영실, 디지털클라우드센터</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>2025년 초 기존 ICT전략실을 디지털전략실로 개편. "지능형 통합플랫폼 기관" 도약 선언 — 2028년까지 전 시스템 클라우드 전환, 전 업무 영역 AI 도입 확대, 22개 주요 시스템 통합 플랫폼 개발 추진. 설립 이래 최대 규모 지능정보화 대응 추진.</t>
+          <t>조직이력: 2025년 초 ICT전략실 → 디지털전략실로 개편&lt;br&gt;기타: 2028년까지 전 시스템 클라우드 전환, 전 업무 영역 AI 도입 확대, 22개 주요 시스템 통합 플랫폼 개발 추진. "지능형 통합플랫폼 기관" 도약 선언.</t>
         </is>
       </c>
     </row>
@@ -2471,29 +2471,29 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
+          <t>경영지원본부</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>실(본부 산하)</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>AI디지털혁신실(디지털전환팀·디지털지원팀·ERP팀)</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>있음 — 2025.11.18 제226차 이사회 직제규정 개정으로 기존 '디지털혁신실'을 'AI디지털혁신실'로 확대 개편, 전사 AI 컨트롤타워로 신설 의결</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
           <t>AI디지털혁신실</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>실(室) — 공식 조직구성표상 본부 그룹 표기 없이 실 단위로 노출(경영지원본부 산하로 추정되나 미확정)</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>디지털전환팀(정보화·전사 디지털사업·데이터 운영·시스템 개발), 디지털지원팀(IT 인프라 기획·구축·유지관리), ERP팀(ERP 재구축·유지관리). ※ 구 'Digital혁신실' 시점 명칭은 IT전략팀·디지털개발팀·디지털지원팀·ERP팀</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>있음 — 2025.11.18 제226차 이사회 직제규정 개정으로 기존 '디지털혁신실'을 'AI디지털혁신실'로 확대 개편, 전사 AI 컨트롤타워로 신설 의결</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>AI디지털혁신실</t>
-        </is>
-      </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
           <t>실(전사 AI 전담기구)</t>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>2025.11.18 제226차 이사회에서 직제규정 개정안 의결 → 기존 '디지털혁신실'을 'AI디지털혁신실'로 명칭 변경·확대 개편(정부 '초혁신경제' 기조 대응). 전사 AI 전략 수립, 생성형 AI 응용서비스 구축(225차 이사회 의결 사업), AI 도입 사전 리스크 발굴 등 AI 전환 컨트롤타워 역할. 2030 중장기 전략과제에 'AI 기반 업무시스템 혁신' 포함. 2025~2026 솔트룩스 주관 전사 생성형 AI 업무체계 구축, 감사위원회 산하 생성형 AI '스마트 감사시스템' 가동 등 AI 사업 다수 추진.</t>
+          <t>IT기능: 전사 디지털사업·데이터 운영·시스템 개발(디지털전환팀), IT 인프라 기획·구축·유지관리(디지털지원팀), ERP 재구축·유지관리(ERP팀), 정보보안·개인정보보호(정보보안센터 별도)&lt;br&gt;조직이력: 구 'Digital혁신실'(IT전략팀·디지털개발팀·디지털지원팀·ERP팀) → 2025.11.18 제226차 이사회에서 'AI디지털혁신실'로 확대 개편(전사 AI 컨트롤타워)&lt;br&gt;기타: 경영지원본부는 상임이사 관할. 2030 전략과제 'AI 기반 업무시스템 혁신'. 2025~2026 솔트룩스 주관 전사 생성형 AI 업무체계 구축. 감사위원회 산하 '스마트 감사시스템' 운영.</t>
         </is>
       </c>
     </row>
@@ -2546,22 +2546,22 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>사무국 산하 IT 기능 운영(전담 IT 본부·처 없음). 보건의료정보관리실(보건의료정보 관리·전산직)이 의료정보, 통신실이 통신 인프라 담당 — 단일 'IT최상위조직'으로 묶이는 정보화 총괄 처·실 명칭은 미표기</t>
+          <t>기획조정실</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>팀·실(사무국 산하) — 별도 본부/처급 IT조직 아님(보건의료정보관리실·통신실 등 실/팀 단위)</t>
+          <t>과(기획조정실 산하)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>보건의료정보관리실(팀장 운영, 보건의료정보 관리), 통신실(통신 인프라), 임상의약정보실(임상·의약 정보). 전산직 별도 채용·운영(2023.4 전산직 공채 확인). 정식 '정보전산팀/정보화팀' 명칭은 미표기</t>
+          <t>기획조정실(의료정보과)</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>없음 (2026년 'AI 기반 진료시스템 지원사업' 선정으로 AI 진료시스템 도입 추진 중이나, 직제상 AI 전담조직 신설은 미확인 — '도입사업' 단계)</t>
+          <t>없음 (2026년 'AI 기반 진료시스템 지원사업' 선정으로 AI 진료시스템 도입 추진 중이나, 직제상 AI 전담조직 신설은 미확인)</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -2576,22 +2576,22 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>정식 CIO 직위 미표기. 정보화 기획은 기획조정부, 의료정보 운영은 보건의료정보관리실이 분담(추정). 단일 CIO 직위 확인불가</t>
+          <t>기획조정실장 총괄 추정 (의료정보과장 실무)</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>정보보호 체계 운영 확인 — 개인정보 보호책임자·정보보안 담당자 지정(채용공고·NCS 명시). 정보시스템 취약점 분석·평가, 침해사고 대응·모의해킹 등 정보보안 활동 발주(과업지시서 확인). 단 정식 CISO 직위 명칭은 미확인</t>
+          <t>확인불가 (정보보안 체계 운영 확인, 전담 CISO 직위 미확인)</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>중(사무국 산하 보건의료정보관리실·통신실·전산직 운영을 공식·준공식 복수자료로 확인 / 단일 IT 총괄부서 정식명칭·CIO 직위는 여전히 미확인)</t>
+          <t>상(공식 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>국립대병원(권역책임의료기관). 2026.4 보건복지부 '권역책임의료기관 AI 기반 진료시스템 지원사업'(17개 기관 142억원)에 선정 — 환자안전·진료정밀도·진료효율화 AI 시스템 도입 계획. 창원경상국립대학교병원(gnuch.co.kr) 별도 운영. 공식 홈페이지(gnuh.co.kr) 조직도 페이지가 SSL 인증서 오류 및 이미지 기반으로 자동 추출 불가하여 IT 조직 세부 구조 직접 확인 실패.</t>
+          <t>IT기능: 의료정보 기획·관리(의료정보과), 보건의료정보 관리(보건의료정보관리실, 진료부문 산하)&lt;br&gt;기타: 창원경상국립대학교병원 분원 별도 운영. 2026.4 보건복지부 권역책임의료기관 AI 기반 진료시스템 지원사업 선정(AI 도입 추진 단계).</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>확인불가(보안) — 군 연구기관 보안상 정보화 직제 비공개</t>
+          <t>확인불가(보안)</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>확인불가(보안) (서울 정보소프트웨어 지역사업소 운영 확인 — 정보·SW 연구 거점, 단 직제상 IT총괄조직 명칭 미공개)</t>
+          <t>확인불가(보안)</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>군 연구기관 특성상 정보화·보안 조직도가 보안상 비공개. AI 조직은 국방혁신 4.0 정책에 따라 센터→연구원으로 확대(민간 연구원 100여명+군인 10여명 규모로 보도). 유무인복합전투체계(MUM-T), 자율주행, 전장상황인식 등 연구.</t>
+          <t>기타: AI 조직은 국방인공지능기술연구원(구 국방AI센터). 2024.4 창설 → 2025.1 연구원으로 격상·지능데이터센터 통합. 유무인복합전투체계(MUM-T)·자율주행·전장상황인식 등 연구. IT 직제는 보안상 비공개.</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>처·실 (소관 라인 재확인 필요 — 공식 조직도상 본부 산하 기재, 일부 언론은 이사장 직속으로 보도)</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>전산정보과 (의료관리실 산하)</t>
+          <t>의료관리실</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 의료관리실 산하 과(課) 단위</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>ICT사업본부</t>
+          <t>전력ICT본부</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>AX사업처 (CEO 직속 'AI 전략위원회' 컨트롤타워 병행)</t>
+          <t>AX사업처 (신사업개발본부 산하, CEO 직속 'AI 전략위원회' 컨트롤타워 병행)</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>ICT사업본부장(CIO 역할 추정)</t>
+          <t>전력ICT본부장(CIO 역할 추정)</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -3596,17 +3596,17 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>스마트공항추진실 (스마트공항/디지털전환 총괄) — 공식 영상·보도로 확인, 단 airport.co.kr 공식 조직도/알리오 직제표상 정확한 본부 소속 라인은 직접 확인 실패</t>
+          <t>스마트공항추진실 (전략기획본부 산하)</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>처·실 (사장 직속/본부 산하 여부 미확정)</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>스마트공항처(스마트공항추진실 산하 추정), AI·BIM센터, 무인항공기술부(K-드론시스템) 등</t>
+          <t>스마트기획부·데이터융합부·스마트공항부(스마트공항추진실 산하) (※무인항공기술부는 건설기술본부→항행시설실 산하 — 스마트공항추진실과 별개)</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>AI·BIM센터(2025.12 개소) / 스마트공항추진실(전사 AI·DX 총괄)</t>
+          <t>스마트공항추진실(전사 AI·DX 총괄) / AI·BIM센터(2025.12 개소, 신공항추진단 산하 BIM센터와 관계 불명확)</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>센터 / 처·실</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보안 전담 조직 명칭 미확인)</t>
+          <t>사이버보안센터 (안전보안본부 산하)</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>중(공식 보도/영상 + 간접, 직제표 직접 미확인)</t>
+          <t>상(공식 조직도 직접 확인 — 2026-06-18 QA)</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>의료정보기획부, 의료정보운영부, 의료정보관리부 (의료정보실 산하) / 스마트병원혁신부(기획조정실 산하)</t>
+          <t>의료정보실(의료정보기획부·의료정보운영부·의료정보관리부), 스마트병원혁신부</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>2020년 보건복지부 '스마트병원 선도모델 개발 지원사업' 대상 기관 선정. 스마트병원혁신부 중심으로 AI 활용 활발 — 영상검사판독지원 AI(X-ray 병변 자동탐지), 입원환자 모니터링(블루투스 활력징후 자동기록), 감염병 중증도 평가 AI, 기록지 자동생성 프로젝트 추진. AI는 별도 전담조직보다 스마트병원혁신부+의료정보실 협업 구조로 운영.</t>
+          <t>IT기능: 의료정보시스템 기획·운영·관리·의료정보보안. 스마트병원혁신부가 AI·디지털 혁신 사업 담당.&lt;br&gt;기타: AI 영상검사판독지원(X-ray 병변 자동탐지)·입원환자 모니터링·감염병 중증도 평가 AI·기록지 자동생성 추진. 스마트병원 선도모델 개발 지원사업 대상 기관(2020).</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>AI데이터팀, 사이버보안팀, AX추진팀(TF)</t>
+          <t>AI정보융합실(AI데이터팀·사이버보안팀·AX추진팀)</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>AI정보융합실 (산하 AI데이터팀, AX추진팀)</t>
+          <t>AI정보융합실</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처)</t>
+          <t>상(공식 조직도 직접 확인 완료 — 2026-06-18 QA 재확인)</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>IT/정보화 최상위 조직 명칭 자체에 "AI"가 포함됨(AI정보융합실). AI데이터팀(ERP·SW·데이터뱅크·공공데이터), AX추진팀(AI 과제·공간정보)으로 AI/AX 기능 전담. 2026년 정부조직 개편으로 주무부처가 (구)환경부→기후에너지환경부로 변경됨.</t>
+          <t>IT기능: ERP·SW·데이터뱅크·공공데이터(AI데이터팀), AI 과제·공간정보(AX추진팀), 개인정보보호·사이버보안(사이버보안팀)&lt;br&gt;기타: IT최상위 조직명에 'AI'가 포함된 사례. AX추진팀(TF)으로 AI전환 전담 운영. 주무부처 환경부→기후에너지환경부 변경(2026).</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4241,7 @@
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>헬스케어플랫폼센터는 인공지능사업팀·정보운영팀·바이오뱅크·혁신기술과를 신설·재편한 조직. 차세대 암전문정보시스템 구축 ISP 추진. 의료 AI(병리보고서 자동추출 등) 연구·사업 활발. 연구·임상·데이터 영역에 AI 조직이 분산 배치된 구조.</t>
+          <t>IT기능: 의료정보시스템 운영·정보보안·차세대 암전문정보시스템 구축(ISP)·AI 기반 의료서비스 개발&lt;br&gt;조직이력: 헬스케어플랫폼센터 신설(인공지능사업팀·정보운영팀·바이오뱅크·혁신기술과 재편)&lt;br&gt;기타: 의료 AI(병리보고서 자동추출 등) 연구·사업 활발. AI 조직이 연구·임상·데이터 영역에 분산 배치.</t>
         </is>
       </c>
     </row>
@@ -4271,17 +4271,17 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신실</t>
+          <t>경영전략본부</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하 또는 사장 직속 실)</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보화/디지털전환/정보보안 기능 포함, 세부 부·팀 미확인)</t>
+          <t>미래전략부 (조직도 정보제공부서로 확인, 경영전략본부 산하 추정)</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>해당없음 (AI·빅데이터·스마트오피스 업무를 디지털혁신실에서 통합 수행)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
@@ -4301,22 +4301,22 @@
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신실장 (디지털 전환 총괄)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신실 (개인정보보호 업무 총괄 부서 = 디지털혁신실)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>상(공식/공공출처 2개 이상)</t>
+          <t>중(공식 조직도 직접 확인, IT 담당 세부조직 미표기)</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>2026.6.1 임종석 사장 취임 후 첫 조직개편 — '정비사업본부'+'에너지사업본부' → '기술안전사업본부'로 통합, 3본부 2실 7팀→2본부 2실 7팀으로 슬림화('작지만 강한 조직'). 안전관리 전담부서를 기술안전사업본부장 직속 배치. 디지털 전환 선포식 개최(AI·빅데이터·스마트오피스 중심 DX 전략). AI 전담조직은 미신설, 디지털혁신실이 DX·AI 총괄.</t>
+          <t>IT담당배경: 조직도에 IT 전담 조직이 별도 표기되지 않음. 조직도 페이지 정보제공부서로 '미래전략부' 명시되어 있으나 조직도 본문 미표기 — 경영전략본부 산하로 추정.&lt;br&gt;조직이력: 현행 조직도 — 경영전략본부(전략기획처·ESG경영처·인사노무처·경영관리처), 기술안전사업본부(안전관리처·생산기술처·공급기술처·엔지니어링사업처·에너지인프라건설처·대외정비사업처), 14지사</t>
         </is>
       </c>
     </row>
@@ -4346,17 +4346,17 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>철도ICT처 (SE융합본부 산하)</t>
+          <t>SE융합본부</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>분산</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>철도ICT처(정보통신), 디지털융합처·디지털관리처(철도혁신연구원 산하), 신기술개발처</t>
+          <t>철도ICT처, 디지털융합처(디지털기획부·디지털트윈TF·모빌리티TF), 디지털관리처, 신기술개발처</t>
         </is>
       </c>
       <c r="I52" s="3" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>IT/정보화 기능이 SE융합본부(철도ICT처: 통신·ICT 설비 중심)와 철도혁신연구원(디지털융합처·디지털관리처·신기술개발처: 디지털전환·데이터 R&amp;D)으로 분산. 철도ICT처는 ICT기술부·ICT리뉴얼부 등 통신설비 중심, 디지털융합처는 디지털기획부·디지털트윈TF·모빌리티TF로 구성. 명시적 단일 'AI' 전담조직은 직원검색·조직도에서 확인되지 않음.</t>
+          <t>IT기능: IT/정보화 기능이 SE융합본부(철도ICT처: 통신·ICT 설비)와 철도혁신연구원(디지털융합처·디지털관리처·신기술개발처: 디지털전환·데이터 R&amp;D)으로 분산&lt;br&gt;기타: 명시적 단일 AI 전담조직은 직원검색·조직도에서 미확인. 디지털융합처에서 디지털트윈·모빌리티TF 운영.</t>
         </is>
       </c>
     </row>
@@ -4421,17 +4421,17 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전사 IT기획·정보보안 전담 처 명칭 미확정) — AX/디지털 전환은 AX기획팀(전략기획본부 계열) 및 디지털솔루션연구소가 주도</t>
+          <t>ICT보안실 (IT기획·정보보안 총괄, 실급)</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>팀 (확인 범위 내)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>AX기획팀, AX솔루션개발팀, AX융합설계팀, EDB시스템 운영 담당, 디지털솔루션연구소(전력기술연구원 산하)</t>
+          <t>ICT보안실(ICT보안기획팀·경영IT지원팀·보안운영팀), AX추진처(AX기획팀·AX솔루션개발팀·AX융합설계팀), 디지털솔루션연구소(전력기술연구원 산하)</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>AX기획팀(AI 전환 전략수립·실행 총괄), AX솔루션개발팀(AI 플랫폼 구축·운영), AX융합설계팀(설계/엔지니어링 AI 융합), 디지털솔루션연구소(AI 기술개발 전담)</t>
+          <t>AX추진처 (AX기획팀·AX솔루션개발팀·AX융합설계팀) + 디지털솔루션연구소(전력기술연구원 산하)</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>팀 (전략기획본부 계열) + 연구소(전력기술연구원 산하)</t>
+          <t>처 (AX추진처) + 연구소(전력기술연구원 산하)</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (개인정보보호 S등급 2년 연속 — 별도 정보보안 담당부서 운영, ISO/IEC 27001 인증 보유)</t>
+          <t>ICT보안실 산하 보안운영팀 (정보보안 실무 담당, ISO/IEC 27001 인증 보유)</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>AX추진처 (구 정보시스템처, 경영지원본부 산하) — IT 기획·운영 총괄 / AI 전환 전략은 기획본부 AX추진단</t>
+          <t>정보시스템처(공식 조직도 표기) / AX추진처(정보공시·임직원검색 표기, 경영지원본부 산하) — IT 기획·운영 총괄 / AI 전환 전략은 기획본부 AX추진단</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -4646,17 +4646,17 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>IT정보보호팀 (경영전략처 전략기획실 산하)</t>
+          <t>경영전략처</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>팀</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>IT정보보호팀 (단일 팀; 전산시스템 유지보수·정보보호 담당)</t>
+          <t>전략기획실(IT정보보호팀)</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>별도 AI 전담조직은 없으나, 신임 이사장(최정호) 취임 후 빅데이터·인공지능 중심 디지털 전환을 4대 추진전략(디지털화경영 등)으로 확정. 프롭테크 활용, IoT 무인감시·원격제어(PSI), RPA 기반 행정자동화 추진 중. 향후 AI 관련 조직 신설 가능성 있음.</t>
+          <t>IT담당배경: 경영전략처는 경영 전략 전반을 담당하는 처이며, 그 산하 전략기획실의 IT정보보호팀이 전산시스템 유지보수·정보보호를 겸임함.&lt;br&gt;IT기능: 전산시스템 유지보수, 정보보호&lt;br&gt;기타: 신임 이사장 취임 후 빅데이터·AI 중심 디지털 전환을 4대 추진전략으로 확정. IoT 무인감시·원격제어(PSI), RPA 기반 행정자동화 추진 중.</t>
         </is>
       </c>
     </row>
@@ -4871,17 +4871,17 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>AX혁신실</t>
+          <t>인프라본부</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
         <is>
-          <t>AX추진팀, 운영DX팀, 인프라DX팀, 경영DX팀</t>
+          <t>스마트ICT처(미디어통신팀·통신운영팀·공항정보팀·경영정보팀)</t>
         </is>
       </c>
       <c r="I59" s="3" t="inlineStr">
@@ -4891,27 +4891,27 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>AI 혁신 TF팀 (별도 상설조직 AX혁신실 운영)</t>
+          <t>AX혁신실(AX추진팀·운영DX팀·인프라DX팀·경영DX팀) — 부사장 직속 디지털전환 전담조직</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>TF(임시조직) / AX혁신실은 처·실 레벨</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (AX혁신실 총괄, 부사장 김범호 AI 대전환 주관 정황)</t>
+          <t>확인불가 (인프라본부장 또는 스마트ICT처장 추정)</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>분임정보보안담당관 체계 운영(부서장급), 전담 CISO 명칭 확인불가</t>
+          <t>사이버보안센터(항공보안단 산하, 사이버보안팀) — 정보보안 전담조직 확인</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 조직도 원문 전체 대조)</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
@@ -5171,17 +5171,17 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>정보화실 (비서실 산하)</t>
+          <t>비서실</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>실(비서실 산하) — 실질 팀급 운영</t>
+          <t>실(원장 직속 비서실 산하)</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>정보화실(정보운영팀 등 2개 팀), 공공의료정보운영팀, 응급의료정보화기획팀(중앙응급의료센터 산하)</t>
+          <t>정보화실(정보보호팀), 정보운영팀, 기획조정실(새병원정보화전략팀)</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>중앙응급의료센터가 통합응급의료정보망(NEDIS)·AI 기반 응급의료시스템 운영. 2026년 과기정통부 공공의료 병원정보시스템 AI 기반 SaaS 전환 사업 대상. 2026년 직원 AI 역량강화 교육 정규과정 운영. 응급의료정보화기획팀 등 정보화 기능이 본원(정보화실)과 중앙응급의료센터로 분산. AI는 사업·솔루션 형태로 활발하나 전담 조직 단위는 미확인.</t>
+          <t>IT기능: 의료정보시스템 운영·정보보안·정보화전략기획(새병원정보화전략팀)&lt;br&gt;기타: AI 기반 응급의료시스템 운영. 2026년 병원정보시스템 AI SaaS 전환 사업 대상. 직원 AI 역량강화 정규교육 운영. 분산 IT: 중앙응급의료센터&gt;재난의료정책실&gt;응급의료정보화팀, 공공보건의료본부&gt;정책통계지원센터&gt;공공의료정보운영팀.</t>
         </is>
       </c>
     </row>
@@ -5246,17 +5246,17 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>AI혁신단 (전사 디지털·AI 총괄) / 디지털 IT 기능은 디지털전환팀·정보운영팀</t>
+          <t>경영본부</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>단(전담조직, 사장 직속 추정) / 기존 IT기능은 팀 레벨</t>
+          <t>단(경영본부 산하)</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>디지털전환팀, 정보운영팀 (구 디지털기획팀에서 분리), 정보보안파트</t>
+          <t>AI혁신단(AI전환팀·AI인프라팀)</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>단(전담조직)</t>
+          <t>단(경영본부 산하)</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>2025.2 현장운영 중심 조직개편으로 기존 디지털기획팀을 디지털전환팀·정보운영팀으로 분리. 2025.9.26 'AI혁신단' 신설(비전 'Next GKL: AI 혁신으로 도약하는 카지노의 미래', 3대 핵심가치: 고객경험 혁신·조직운영 혁신·산업 디지털전환 선도). AI·ERP 통합 예측기반 운영체계 구축 추진. 업계 최초 세븐럭 전용앱 개발 등 디지털 마케팅 강화.</t>
+          <t>IT기능: 전사 AI·디지털 전환 총괄. AI·ERP 통합 예측기반 운영체계 구축.&lt;br&gt;조직이력: 2025.2 디지털기획팀 → 디지털전환팀+정보운영팀 분리. 2025.9.26 AI혁신단 신설(AI전환팀·AI인프라팀으로 개편).&lt;br&gt;기타: 비전 'Next GKL: AI 혁신으로 도약하는 카지노의 미래'. 업계 최초 세븐럭 전용앱 개발.</t>
         </is>
       </c>
     </row>
@@ -5471,17 +5471,17 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>통합정보센터 (센터장 김우진 — 신경과 교수, AI 암치유센터장 겸임)</t>
+          <t>통합정보센터</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>센터 (정보화 총괄 센터, 센터장이 개인정보보호책임자 겸임)</t>
+          <t>센터</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>의료정보(부서) — 정보보호 담당부서. 그 외 하위 팀 구성은 조직도 이미지 미표기로 확인불가</t>
+          <t>의료정보</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>전국 최초 AI 기반 '인공지능 암치유센터' 운영(보건의료정보원 데이터활용 사업으로 조성). 국내 최초 AI 암 환자 간호 에이전트 도입, AI 진료예약센터(AI챗봇·보이스봇 24시간), 삼성서울병원과 AI 원격협진, 의료빅데이터 컨소시엄(OHDSI) 초기 멤버, 차세대 병원정보시스템 구축. 의료 AI·빅데이터 분야 선도 국립대병원.</t>
+          <t>기타: 전국 최초 AI 기반 '인공지능 암치유센터' 운영(보건의료정보원 데이터활용 사업). 국내 최초 AI 암 환자 간호 에이전트 도입, AI 진료예약센터(AI챗봇·보이스봇 24시간), 삼성서울병원 AI 원격협진. 통합정보센터장(김우진)이 AI 암치유센터장 겸임.</t>
         </is>
       </c>
     </row>
@@ -5546,12 +5546,12 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>ICT전략부·ICT운영부(센터)·AI데이터전략실·정보보안담당관 (부·실·담당관 병렬, 상위 통할 본부명 미확인)</t>
+          <t>ICT전략부·ICT운영부(센터)·AI데이터전략실·정보보안담당관</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 부·실·담당관급 단위 (상위 본부명 확인불가)</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>2025.7 조직개편으로 '데이터사업전략실'을 'AI데이터전략실'로 변경(AI 전환 전략 설계·연구 기능 강화), 중기 분야 최초 AI최고책임자(CAIO) 선임. 2025.10 부산 KT IDC 내 'AI 클라우드 데이터센터' 개소(차세대 금융서비스 AI 인프라). 2026.1 등 'AI데이터전략실'→'AI데이터전략부' 확대 개편 예정(전사 AX 전략·데이터 기반 경영전략 강화, 전자신문 2026.1.6 보도). ICT 직제는 ICT전략부·ICT운영부·AI데이터전략실·정보보안담당관 등 부/실/담당관 병렬 구조이며 이들을 통할하는 상위 본부명은 공식 조직도(kibo.or.kr JS 렌더링·접근 실패) 미확인. CDIO는 2020~21년 도입 계획 언급분이며 현행 직위 존속은 미확인.</t>
+          <t>조직이력: 2025.7 '데이터사업전략실'→'AI데이터전략실' 개편(AI 전환 전략 설계·연구). 2026.1 'AI데이터전략실'→'AI데이터전략부' 격상 예정.&lt;br&gt;기타: 중기 분야 최초 AI최고책임자(CAIO) 선임. 2025.10 부산 KT IDC 내 'AI 클라우드 데이터센터' 개소.</t>
         </is>
       </c>
     </row>
@@ -5621,17 +5621,17 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>AI정보화기획실 (경영기획처 산하)</t>
+          <t>경영기획처</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 경영기획처 산하 실 레벨</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>AI정보화기획실 (정보화사업·개인정보보호·정보보안·데이터분석·공공데이터 담당)</t>
+          <t>AI정보화기획실</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>기존 "경영지원처&gt;재무정보실&gt;정보화센터" 편제에서 조직개편되어 IT 기능이 '경영기획처 산하 AI정보화기획실'로 재편·승격됨(실 레벨). 부서명 자체에 'AI'를 반영. 2025.12 'AI 대전환 기본계획' 추진(AI 기반 물류·행정 혁신). 정보화사업·정보보안·개인정보보호·데이터분석·공공데이터 개방을 AI정보화기획실이 총괄.</t>
+          <t>IT담당배경: 경영기획처는 경영 전반을 담당하는 처이며, 그 산하 AI정보화기획실이 정보화·정보보안·데이터분석·공공데이터를 총괄함. 부서명에 'AI'를 명시하여 정보화와 AI 기능을 통합 운영.&lt;br&gt;IT기능: 정보화사업, 개인정보보호, 정보보안, 데이터분석, 공공데이터 개방&lt;br&gt;조직이력: (구)경영지원처&gt;재무정보실&gt;정보화센터 편제에서 경영기획처 산하 AI정보화기획실로 개편·승격&lt;br&gt;기타: 2025.12 'AI 대전환 기본계획' 추진 (AI 기반 물류·행정 혁신)</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신실 (경영혁신본부 산하)</t>
+          <t>경영혁신본부</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -6081,22 +6081,22 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신실 산하: 디지털혁신팀(정보화 총괄·기획), 디지털서비스팀, 디지털보안팀(정보보안)</t>
+          <t>디지털혁신실(디지털혁신팀·디지털서비스팀·디지털보안팀)</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>없음 (확인된 별도 AI 전담조직 없음 — 디지털혁신실이 AX 전환 추진 주관)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담 조직명 없음. 한국스포츠과학원 스포츠산업연구실 산하 '데이터분석센터'는 연구 기능으로 IT/AI 직제와 별개)</t>
+          <t>AI미래성장팀 (전무이사 직속)</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>팀 (전무이사 직속)</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>2025.9 'AI 중심 전사적 업무혁신(AX)' 착수 — 맞춤형 과제 발굴, AX 전략계획 수립, AI 공통인프라 단계적 도입, AI 윤리 리스크관리 제도 추진(뉴스 보도). 별도 '디지털 혁신 자문위원회' 발족·제1차 회의 개최(뉴스1). 조직 최상위는 이사장-전무이사 산하 4개 본부 + 경륜경정총괄본부 + 한국스포츠과학원 구조. 정보화 기능은 경영혁신본부 디지털혁신실에 집중. 통칭 '체육공단/KSPO'.</t>
+          <t>IT기능: 정보화 총괄·기획(디지털혁신팀), 디지털서비스(디지털서비스팀), 정보보안(디지털보안팀)&lt;br&gt;조직이력: 2025.9 'AI 중심 전사적 업무혁신(AX)' 착수. 전무이사 직속 AI미래성장팀 신설.&lt;br&gt;기타: 디지털 혁신 자문위원회 발족. 정보화(경영혁신본부 디지털혁신실)·AI(전무이사 직속 AI미래성장팀) 이원 운영. 통칭 '체육공단/KSPO'.</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>정보화혁신실 (정보화 기획·보안 총괄) — AI 전담조직(AI·고객전략실, AI마케팅실)은 별도 실 단위로 병존</t>
+          <t>정보화혁신실</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>정보화혁신실 산하: 정보화기획팀, 정보보안운영팀</t>
+          <t>정보화혁신실(정보화기획팀·정보보안운영팀)</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>공식 조직도상 AI 기능을 정보화 조직과 분리하여 'AI·고객전략실'·'AI마케팅실' 2개 실로 전진 배치 — AI를 마케팅·고객전략(수출지원 핵심사업)과 직접 결합한 구조가 특징. 통칭 'KOTRA'. 본사 + 지방지원본부 + 해외무역관 체계. 2026 정부조직 개편으로 주무부처명이 산업통상자원부→산업통상부로 변경(알리오 값 기준 표기).</t>
+          <t>IT기능: AI 기능을 정보화 조직과 분리하여 'AI·고객전략실'(AI전략팀·고객전략팀·AI데이터팀)·'AI마케팅실'(AI마케팅팀·AI플랫폼팀) 2개 실로 전진 배치. AI를 마케팅·고객전략(수출지원 핵심사업)과 직접 결합한 구조.&lt;br&gt;기타: 통칭 KOTRA. 본사+지방지원본부+해외무역관 체계.</t>
         </is>
       </c>
     </row>
@@ -6371,17 +6371,17 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (내부 전산/정보화 총괄) — 별도 IT 전담 본부·처 없음</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>팀 (경영지원실 산하, 내부 정보화 기능. 정식 IT팀 명칭 미공개)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (내부 정보화/전산 담당 팀 명칭 미공개). ※참고: 사업처 산하 '정보사업부'가 별도 존재하나 이는 국가가축방역통합시스템(KAHIS) 연계·축산농장DB 등 대외 방역정보 '사업' 수행 부서로 내부 IT조직과 구분됨</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="I79" s="3" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>가축방역·축산물 위생관리 전문기관. 본부 조직(2026.6 공식 조직도): 본부장·전무이사·감사 산하 감사실·기획혁신실·경영지원실·사업처(안전관리부·방역사업부·위생검역부·정보사업부)+9개 도본부·3개 검역사무소·43개 사무소. 전사 정원 1,286명(정보직 4명). IT 전담 최상위 본부·처 없음 — 내부 정보화는 경영지원실 내 팀 단위 수행. '정보사업부'(사업처 산하)는 KAHIS 연계 등 대외 방역정보 사업 부서로 내부 IT와 별개.</t>
+          <t>IT담당배경: 별도 IT 전담 본부·처 없음. 경영지원실 내 팀 단위로 전산·정보화 담당(정식 팀명 미공개). 정보직 정원 4명.&lt;br&gt;IT기능: 전산개발, 시스템운영, 정보보안(채용공고 직무 기준)&lt;br&gt;기타: 사업처 산하 '정보사업부'는 KAHIS(국가가축방역통합시스템) 연계 등 대외 방역정보 사업 수행 부서로 내부 IT 조직과 구분됨.</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>AI전략실 (경영본부 산하) — AI·데이터·정보화사업·정보보안 총괄</t>
+          <t>경영본부</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>AI전략실 산하: AI·데이터·정보화사업·정보보안 업무 통합 담당(별도 팀 명칭 확인불가, 정보보안업무 총괄 직위 존재)</t>
+          <t>AI전략실</t>
         </is>
       </c>
       <c r="I85" s="3" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>정보화 조직을 'AI전략실'로 명명하여 AI·데이터·정보화사업·정보보안을 단일 실에 통합한 구조(공식 직원/업무검색 페이지 확인). 본사 본부 체계: 재난안전본부·경영본부·건설안전본부·기반시설본부·건축시설본부 등 + 국토안전기술연구원·국토안전교육원·지하안전관리단 + 5개 지역본부(수도권·충청·강원·영남·호남). '국토안전 빅데이터 플랫폼(bigtori)' 운영. LH와 건설사고 예측 AI 공동개발 추진. 2020.12.10 한국시설안전공단+한국건설관리공사 통합 출범. 통칭 'KALIS'.</t>
+          <t>IT기능: AI·데이터·정보화사업·정보보안을 단일 실(AI전략실)에서 통합 운영&lt;br&gt;기타: '국토안전 빅데이터 플랫폼(bigtori)' 운영. LH와 건설사고 예측 AI 공동개발. 2020.12 한국시설안전공단+한국건설관리공사 통합 출범.</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>AI디지털본부 (2026.4.9 조직개편으로 출범, 사장 직속 본부급)</t>
+          <t>AI디지털본부</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>AI디지털본부 산하: AX전략실, ICT플랫폼실(신설), AI빅데이터실</t>
+          <t>AX전략실, ICT플랫폼실, AI빅데이터실</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>2026.4.9 조직개편 완료(4.20 보직 인사발령) — 기존 7본부 1연구소 23실 → 7본부 1연구소 25실로 확대. 기존 '디지털전략본부(정보화전략실/디지털지원실/빅데이터실)'의 디지털전략 기능을 확대·개편하여 'AI디지털본부' 출범, AX전략실·ICT플랫폼실(신설)·AI빅데이터실로 재편(정보제공 중심→데이터 분석·맞춤형 지원 전환). 동시에 금융정책실 신설, 혁신평가본부 개편(지역협력실→ESG경영실). 통칭 '소진공/SEMAS'.</t>
+          <t>IT기능: AI·디지털 전략(AX전략실), ICT 플랫폼 구축·운영(ICT플랫폼실), AI·빅데이터 분석·맞춤형 지원(AI빅데이터실)&lt;br&gt;조직이력: 2026.4.9 조직개편 — 디지털전략본부(정보화전략실·디지털지원실·빅데이터실) → AI디지털본부(AX전략실·ICT플랫폼실·AI빅데이터실)로 개편&lt;br&gt;기타: 통칭 '소진공/SEMAS'.</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처)</t>
+          <t>상(공식 조직도 직접 확인 완료 — 2026-06-18 QA)</t>
         </is>
       </c>
       <c r="O89" s="3" t="inlineStr">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신부(3개팀), IT운영부</t>
+          <t>IT운영부</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>디지털정보전략실 (금융기획처 산하)</t>
+          <t>금융기획처</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>디지털정보전략실, 정보보호팀</t>
+          <t>디지털정보전략실</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>'4처 14실 4지사' 체계. 금융기획처 산하 디지털정보전략실이 디지털금융서비스 기획·운영 및 정보화(금융IT) 지원 총괄. 본부 단위 IT 조직 없이 처 산하 실 레벨로 운영. 독립 AI 전담조직은 미설치이나, AI 활용은 활발 — 2025.12 NIA와 공공 AI 혁신 업무협약 체결, '2025 생성형 AI 업무활용 우수사례 공모전' 등 디지털정보전략실 주도 AI 내재화 추진. 보험심사·사기탐지 등 보험업무 전반 AI 전환 계획 보도.</t>
+          <t>IT담당배경: 금융기획처는 예금·금융 전반을 담당하는 처이며, 그 산하 디지털정보전략실이 디지털금융서비스 기획·운영 및 정보화(금융IT) 지원을 총괄함.&lt;br&gt;IT기능: 디지털금융서비스기획·운영, 정보화(금융IT) 지원&lt;br&gt;기타: 2025.12 NIA와 공공 AI 혁신 업무협약 체결, '2025 생성형 AI 업무활용 우수사례 공모전' 등 AI 내재화 추진. 보험심사·사기탐지 등 보험업무 전반 AI 전환 계획.</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>처·실 (본부 산하 — 경영관리본부 계열 추정)</t>
+          <t>처·실 (경영관리본부 산하)</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>처 (본부 산하)</t>
+          <t>처 (경영관리본부 산하)</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>중(공식·언론 복수 출처로 AI혁신처·하위팀 확인, 단 공식 조직도 직접 열람은 미완)</t>
+          <t>상(공식 조직도 직접 확인 완료 — 경영관리본부 산하 AI혁신처, 2026-06-18)</t>
         </is>
       </c>
       <c r="O92" s="3" t="inlineStr">
@@ -7571,17 +7571,17 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신처 (경영인재실 산하)</t>
+          <t>경영인재실</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 디지털혁신처는 경영인재실 산하 처(處)</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신처(디지털전환·정보화), 정보보안처(개인정보·정보보안), 정보보안센터(대표이사 직속)</t>
+          <t>디지털혁신처(디지털전환·정보화), 정보보안센터(사이버안전·보안인증)</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -7646,12 +7646,12 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>기획조정실 (정보화 총괄)</t>
+          <t>기획조정실</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하 성격) — 기획조정실 내 디지털플랫폼부·정보전략부</t>
+          <t>처·실(기관장 직속)</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="N96" s="3" t="inlineStr">
         <is>
-          <t>중 (공식 조직도 1출처 + AI 서비스 보도)</t>
+          <t>상 (공식 조직도 2회 확인 — 2026-06-14, 2026-06-18)</t>
         </is>
       </c>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>정보화 조직은 기획조정실 산하 '디지털플랫폼부'·'정보전략부'로 편제. 별도 정보화본부/CISO 직위는 조직도상 확인되지 않음. AI는 대국민 법률서비스 형태로 운영(24시간 AI 챗봇 '법률똑똑이', 법무부 주관 35개 기관 연계 생성형 AI '법률구조 플랫폼')하나 전담 조직 단위는 미확인.</t>
+          <t>IT기능: 기획조정실 산하 '디지털플랫폼부'·'정보전략부'로 정보화 편제.&lt;br&gt;기타: AI는 대국민 법률서비스 형태로 운영(24시간 AI 챗봇 '법률똑똑이', 법무부 주관 35개 기관 연계 생성형 AI '법률구조 플랫폼')하나 전담 조직 단위는 미확인.</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>AI·디지털융합처</t>
+          <t>AI디지털융합처</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -7881,17 +7881,17 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>AI·디지털융합처(정보화사업·해양환경정보포털·시스템 총괄), 정보보안팀(개인정보보호 담당)</t>
+          <t>AI디지털융합처(정보화사업·해양환경정보포털·시스템 총괄), 정보보안팀(개인정보보호 담당)</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>있음 (부서명에 'AI' 명시 — AI·디지털융합처)</t>
+          <t>있음 (부서명에 'AI' 명시 — AI디지털융합처)</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>AI·디지털융합처</t>
+          <t>AI디지털융합처</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (AI·디지털융합처 소관 임원 추정)</t>
+          <t>확인불가 (AI디지털융합처 소관 임원 추정)</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>기존 정보화 조직을 'AI·디지털융합처'로 재편 — AI를 정보화 조직 명칭에 직접 반영(상대적으로 적극적). 드론·AI·빅데이터 기반 해양쓰레기 수거·해양환경 분석 디지털 혁신 추진. 14개 소속기관 대상 CISO 주관 정보보안 지도점검 운영.</t>
+          <t>기존 정보화 조직을 'AI디지털융합처'로 재편 — AI를 정보화 조직 명칭에 직접 반영(상대적으로 적극적). 드론·AI·빅데이터 기반 해양쓰레기 수거·해양환경 분석 디지털 혁신 추진. 14개 소속기관 대상 CISO 주관 정보보안 지도점검 운영.</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>인공지능정책실, 인공지능융합본부, 인공지능데이터본부, 공공지능데이터본부, 지능기술인프라본부 (대외 사업 조직)</t>
+          <t>인공지능정책실, 인공지능융합본부, 인공지능데이터본부, 공공지능데이터본부, 지능기술인프라본부, 인공지능정부본부 (대외 사업 조직)</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>경영관리부 (정보관리팀, 행정 IT 총괄)</t>
+          <t>경영관리부</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>정보관리팀 (경영관리부 산하), 의료정보팀 (원자력병원 산하)</t>
+          <t>정보관리팀, 의료정보팀</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="O102" s="3" t="inlineStr">
         <is>
-          <t>병원 중심 부설기관으로 IT조직은 팀 단위. 행정·전산은 경영관리부 '정보관리팀', 병원 의료정보시스템(EMR 등)은 원자력병원 '의료정보팀'이 담당하는 이원 구조. 별도 정보화본부/처·AI 전담조직 없음. 조직: 원자력병원 + 전략기획부 + 경영관리부 + 방사선비상진료센터 + 연구센터.</t>
+          <t>IT담당배경: IT 조직이 경영관리부 산하 정보관리팀(행정·전산)과 원자력병원 산하 의료정보팀(의료정보시스템)으로 분리된 이원 구조임.&lt;br&gt;IT기능: 정보관리팀 — 행정전산·IT 인프라 운영; 의료정보팀 — EMR 등 의료정보시스템 운영</t>
         </is>
       </c>
     </row>
@@ -8171,32 +8171,32 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
+          <t>고객만족본부</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>본부(본부 산하)</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>AI전략본부(디지털운영실·AI혁신팀·사이버안전센터)</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
           <t>AI전략본부</t>
         </is>
       </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>본부</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>디지털운영실, AI혁신팀, 사이버안전센터</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>AI전략본부 (산하 AI혁신팀)</t>
-        </is>
-      </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>본부 (이사장 직속)</t>
+          <t>본부 (고객만족본부 산하)</t>
         </is>
       </c>
       <c r="L103" s="3" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>IT·AI·보안을 묶은 'AI전략본부'를 이사장 직속 본부로 운영 — AI를 본부 명칭에 전면화한 드문 사례. 종이행정 80% 감축 등 디지털전환 사업 추진 중(전자서명 도입 등).</t>
+          <t>IT기능: 디지털운영·AI혁신·사이버보안 통합 운영&lt;br&gt;기타: IT·AI·보안을 묶은 AI전략본부를 고객만족본부 산하 본부로 운영. AI를 본부 명칭에 전면화한 드문 사례. 종이행정 80% 감축 등 디지털전환 사업 추진(전자서명 도입 등).</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>정보보안안전부 (정보체계·정보보안 총괄)</t>
+          <t>정보보안안전부</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>정보체계팀, 정보보안팀, 안전보건팀 (정보보안안전부 산하)</t>
+          <t>정보보안안전부(정보체계팀·정보보안팀·안전보건팀), 기술연구본부(첨단미래기술센터(지능SW팀))</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
-          <t>중 (공식 조직도 1출처 직접 확인 + 보도)</t>
+          <t>상(공식 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>내부 정보화/보안은 '정보보안안전부'(정보체계팀·정보보안팀·안전보건팀)가 담당. AI 관련은 국방기술 R&amp;D 차원에서 '첨단미래기술센터' 산하 '지능SW팀'(AI·지능형 SW)·우주위성팀·첨단기술팀 운영. 빅데이터·AI·스마트팩토리 중심으로 품질관리 교육체계 개편 추진 중.</t>
+          <t>IT담당배경: 내부 정보화·정보보안·안전보건이 '정보보안안전부' 1개 부서에 통합 편제.&lt;br&gt;IT기능: 정보체계 운영·정보보안·안전보건&lt;br&gt;기타: 첨단미래기술센터 산하 지능SW팀(AI·지능형 SW R&amp;D). 빅데이터·AI·스마트팩토리 중심 품질관리 교육체계 개편 추진.</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>정보화 조직을 '지능생태정보실'로 명명, 산하에 지능정보전략팀·생태빅데이터팀·사이버보안팀을 둠 — 정보화/지능정보/빅데이터/보안을 한 실에 통합하여 원장 직속으로 운영.</t>
+          <t>IT기능: 정보화 전략 수립·지능정보 운영·생태빅데이터 관리·분석·사이버보안. 원장 직속 1실 3팀(지능정보전략팀·생태빅데이터팀·사이버보안팀) 체계로 통합 운영.</t>
         </is>
       </c>
     </row>
@@ -9001,12 +9001,12 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>팀(센터 산하) — 진료지원부서 내 센터</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>정보기획관리팀(전산시스템 운영·유지보수, 의료정보보호·보안), 정보운영개발팀(EMR·OCS 등 HIS 개발·관리, 의료정보 표준화, 의무기록 관리)</t>
+          <t>정보기획관리팀, 정보운영개발팀</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>치과 특화 단일 병원으로 IT 조직은 의료정보빅데이터센터 1개 센터(2팀) 규모. 별도 AI 전담조직 미확인. 서울대학교병원(본원)과는 별개 법인/기관.</t>
+          <t>IT기능: 전산시스템 운영·유지보수, 의료정보보호·보안(정보기획관리팀); EMR·OCS 등 HIS 개발·관리, 의료정보 표준화, 의무기록 관리(정보운영개발팀)&lt;br&gt;기타: 서울대학교병원(본원)과 별개 법인/기관.</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>(내부 정보화) 경영지원 조직 내 정보화 담당 / (사업) AI인프라본부·AI반도체지원본부·AI활용본부</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>본부 (AI 사업본부 3개) / 내부 정보화는 팀 레벨(추정)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>(내부 IT) 총무정보팀·정보보호 담당(추정) / (AI 사업) AI인프라본부, AI반도체지원본부(신설), AI활용본부, 지역AX본부, SW융합본부, 글로벌본부, 정책기획단</t>
+          <t>운영지원단(정보보호팀·AI정보혁신팀)</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>AI인프라본부 / AI반도체지원본부 / AI활용본부</t>
+          <t>AI인프라본부 / AI반도체본부 / AI활용본부</t>
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (구 조직도상 경영지원단 내 정보보호TF)</t>
+          <t>운영지원단 정보보호팀</t>
         </is>
       </c>
       <c r="N127" s="3" t="inlineStr">
         <is>
-          <t>중 (공식 보도 기반 1차 + 위키 보조, 내부 정보화 조직은 구 자료)</t>
+          <t>상 (공식 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>2025.8.1 'AI 3대 강국 진입' 국정과제에 맞춰 대규모 조직개편 — AI 전담 2본부→3본부 확대(AI반도체지원본부 신설), 디지털본부→지역AX본부 개편, SW미래본부+메타버스본부→SW융합본부 통합, 정책기획단 신설. 본 기관은 ICT·SW·AI 산업 '진흥(사업)' 기관으로, AI 본부들은 산업 육성 사업조직이며 기관 내부 전산운영 조직과는 성격이 다름</t>
+          <t>2025.8.1 'AI 3대 강국 진입' 국정과제에 맞춰 대규모 조직개편 — AI 전담 2본부→3본부 확대, 디지털본부→지역AX본부 개편, SW미래본부+메타버스본부→SW융합본부 통합, 정책기획단 신설. AI 본부(AI인프라·AI반도체·AI활용)는 산업 육성 사업조직이며 기관 내부 전산운영 조직(경영기획본부 운영지원단)과는 성격이 다름</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>기획협력본부 (산하 정보전산팀·정보보안팀)</t>
+          <t>기획협력본부</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>순수 기초과학 연구기관(R&amp;D)으로 정보화 조직은 행정지원 성격. AI는 연구 주제(인공지능·로봇 기반 합성 연구단)로 존재하나 기관 운영 차원의 AI 전담 조직은 아님</t>
+          <t>IT담당배경: 순수 기초과학 연구기관으로 정보화 조직은 행정지원 성격.&lt;br&gt;기타: AI는 연구 주제(인공지능·로봇 기반 합성 연구단, 융합과학 연구클러스터 산하)로 존재하나 기관 운영 차원의 AI 전담 조직은 아님.</t>
         </is>
       </c>
     </row>
@@ -10196,17 +10196,17 @@
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>경영전략실 (산하 경영정보팀 정보화사업 총괄, 정보보안센터)</t>
+          <t>경영전략실</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>팀/센터 (실 산하)</t>
+          <t>분산</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>경영정보팀(정보화사업 총괄·정보보안), 정보보안센터, (우체국쇼핑실)시스템운영팀, (우편사업실)품질관리팀 내 인프라·정보보안관리</t>
+          <t>정보보안센터, 우체국쇼핑실(시스템운영팀), 우편사업실(품질관리팀)</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>우정사업본부 산하 기관으로, 우체국쇼핑·우편 등 사업별 시스템운영 조직이 분산. 정보화 총괄은 경영전략실 경영정보팀, 정보보안은 정보보안센터(경영전략실 산하) 별도 운영</t>
+          <t>IT담당배경: IT 조직이 3개 실에 분산 운영. 경영전략실-정보보안센터가 보안 총괄, 사업실별 시스템팀이 자체 운영. 경영정보팀의 실제 업무는 제휴·홍보·몰운영·정산으로 IT 기획 담당 아님.&lt;br&gt;IT기능: 정보보안·정보보호·시스템관리(정보보안센터) / 쇼핑 시스템 운영·정산/통계·모바일·B2B(우체국쇼핑실 시스템운영팀) / 우편 인프라·정보보안관리(우편사업실 품질관리팀)</t>
         </is>
       </c>
     </row>
@@ -10721,17 +10721,17 @@
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>AI미디어센터 (정보화·데이터·AI 총괄 단위)</t>
+          <t>AI미디어센터</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>본부급 (센터)</t>
+          <t>센터</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>AI데이터팀(=데이터팀), 헤리티지 미디어팀</t>
+          <t>AI미디어센터(AI데이터팀·헤리티지미디어팀)</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>AI미디어센터 / AI데이터팀(데이터팀)</t>
+          <t>AI미디어센터</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="O137" s="3" t="inlineStr">
         <is>
-          <t>구 한국문화재재단이 2024.5.17 국가유산기본법 시행에 따라 '국가유산진흥원'으로 개편. AI미디어센터 산하 AI데이터팀(데이터팀)이 국가유산 멀티모달 AI('HAI, Heritage AI'), 초거대AI 확산 생태계 조성사업, AI 데이터레이크 사업 등 적극 추진 중. 정부 기관명 개편(문화재청→국가유산청)으로 웹 구명칭 다수 존재.</t>
+          <t>조직이력: 2024.5.17 한국문화재재단 → 국가유산진흥원으로 개편(국가유산기본법 시행)&lt;br&gt;기타: 국가유산 멀티모달 AI 'HAI(Heritage AI)' 자체 개발. 초거대AI 확산 생태계 조성사업·AI 데이터레이크 사업 추진. 주무부처 문화재청→국가유산청으로 변경되어 웹 구명칭 혼재.</t>
         </is>
       </c>
     </row>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) (경영본부 산하 '실' 단위)</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
@@ -10811,17 +10811,17 @@
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>없음 (사업본부 미디어실 영상아트팀 내 'AI콘텐츠파트' 존재하나 전담 IT/AI 조직 아님)</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>(관련) 영상아트팀 AI콘텐츠파트 — 콘텐츠 제작 영역</t>
+          <t>영상아트팀 AI콘텐츠파트 (사업본부 미디어실)</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>팀 산하 파트 (사업본부 미디어실)</t>
+          <t>팀 산하 파트</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="O138" s="3" t="inlineStr">
         <is>
-          <t>대표이사 직속 상임감사 + 경영본부·사업본부 2본부 체제. IT는 경영본부 정보전략실(정보기획·정보운영·정보보안 3팀)에 집중. 정보기획팀에 '데이터전략파트' 운영. AI는 사업본부 미디어실 영상아트팀의 'AI콘텐츠파트'에서 방송 콘텐츠 제작 차원으로 활용. 보안 전담조직 확충·망분리 개선 등 보안역량 강화 보도.</t>
+          <t>IT기능: 정보화 전략수립·거버넌스·아키텍처(정보기획팀), 데이터전략(데이터전략파트), IT 운영(정보운영팀), 정보보안(정보보안팀)&lt;br&gt;기타: 사업본부 미디어실 영상아트팀 내 AI콘텐츠파트 운영 — 방송 콘텐츠 제작 AI 활용(전사 AI 거버넌스 조직 아님). 정보보안 전담조직 확충·망분리 개선 추진.</t>
         </is>
       </c>
     </row>
@@ -10946,17 +10946,17 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>경영혁신본부 (산하 디지털혁신부·AI전략부)</t>
+          <t>경영혁신본부</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>IT 기능은 경영혁신본부 산하 '부' 단위(디지털혁신부·AI전략부)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신부(정보화사업 기획·관리·운영, 전산시스템 인프라), AI전략부(AI·빅데이터 활용 고객서비스 혁신)</t>
+          <t>디지털혁신부, AI전략부</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>2026.3.19 출범 10년 조직개편으로 기존 IT전략부를 'AI전략부'로 개편(AI·빅데이터 활용 고객서비스 혁신), 전략기획부 신설(데이터 기반 정책설계). 경영혁신본부 산하에 기획조정부·전략기획부·경영지원부·디지털혁신부·AI전략부·리스크관리부 배치. AI·데이터 중심 전환이 뚜렷.</t>
+          <t>IT기능: 정보화사업 기획·관리·운영, 전산시스템 인프라(디지털혁신부); AI·빅데이터 활용 고객서비스 혁신(AI전략부)&lt;br&gt;조직이력: 2026.3.19 출범 10주년 조직개편 — IT전략부→AI전략부 개편, 전략기획부 신설</t>
         </is>
       </c>
     </row>
@@ -11171,17 +11171,17 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>정보전략부 (예술협력본부 산하)</t>
+          <t>예술협력본부</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) (예술협력본부 산하 '부' 단위)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보전략부가 정보화 운영·정보보안·개인정보보호·기관 앱 통합관리·홈페이지 관리 담당. 하위 팀 구성 미확인)</t>
+          <t>정보전략부</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="O143" s="3" t="inlineStr">
         <is>
-          <t>경영본부·공연예술본부·예술협력본부 등 본부 체제. IT/정보화는 예술협력본부 산하 '정보전략부'가 정보화 운영·정보보안·개인정보보호·앱/홈페이지 관리 담당. AI 전담조직 단서는 확인되지 않음.</t>
+          <t>IT기능: 정보화 운영, 정보보안, 개인정보보호, 앱·홈페이지 통합관리&lt;br&gt;기타: 경영본부·공연예술본부·예술협력본부 등 본부 체제. AI 전담조직 단서 확인되지 않음.</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>정보전산팀 (경영관리본부 안전경영부 산하)</t>
+          <t>경영관리본부</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>정보전산팀</t>
+          <t>안전경영부(정보전산팀)</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
@@ -11471,17 +11471,17 @@
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>경영안전본부 (산하 사업관리부 정보화팀이 IT 담당)</t>
+          <t>경영안전본부</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>팀 (경영안전본부 &gt; 사업관리부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>정보화팀, 정보보안팀</t>
+          <t>사업관리부(정보화팀·정보보안팀)</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
@@ -11546,17 +11546,17 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>경영기획단 / 네트워크·보안단 (내부 정보화·보안)</t>
+          <t>전략기획본부</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>단 (본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>경영기획단(내부 정보화·경영지원), 네트워크·보안단(정보보안 PM 포함), 정보보안팀, 기획조정팀, 지능정보화TF</t>
+          <t>사업지원단(정보보안팀·지능정보팀)</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>AI·SW·반도체단, 인공지능팀, AI기술팀, AI기반팀, AI안전신뢰팀 (R&amp;D 사업조직) / 지능정보화TF (내부 AI 활용)</t>
+          <t>기술혁신본부 산하 AI반도체·SW단(AI·반도체·SW전략팀·AI기술팀·SW컴퓨팅팀·피지컬AI팀·K-클라우드추진단)·AI·디지털융합단·국방·보안단·PIM인공지능반도체사업단·차세대네트워크(6G)사업단</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>단·팀 (기술혁신본부 산하)</t>
+          <t>본부 (기술혁신본부 산하 다수 단)</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr">
@@ -11621,17 +11621,17 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>경영관리부 (산하 정보보안실이 정보보안 담당) — 별도 정보화 총괄 본부·실은 직제상 미확인</t>
+          <t>경영관리부</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>실 (경영관리부 산하 정보보안실) / 정보화 기획 총괄 조직은 확인불가</t>
+          <t>부(본부급)</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>정보보안실 (경영관리부 산하: 인재경영실·재무실·총무실·정보보안실)</t>
+          <t>정보보안실</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>인공지능기술팀 (기술기획본부 &gt; 혁신기술연구부 산하)</t>
+          <t>인공지능기술팀, 무인미래통신기술팀 (기술기획본부 &gt; 혁신기술연구부 산하)</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="O149" s="3" t="inlineStr">
         <is>
-          <t>기획조정부·경영관리부 + 기술기획본부·방산진흥본부 + 기술평가관리센터·전력지원체계연구센터 구조. 기관 행정 IT는 경영관리부 정보보안실 중심(정보화 기획 전담 실 미표기). 국방기술 R&amp;D 차원의 인공지능기술팀(혁신기술연구부)을 보유. 국방 AI 전환·국방데이터 민간개방 사업 추진(보도자료)</t>
+          <t>IT담당배경: 별도 정보화 기획 전담 실 없이 경영관리부 산하 정보보안실이 IT 보안 담당. 정보화 기획 총괄 조직은 직제상 미표기.&lt;br&gt;기타: 기술기획본부 혁신기술연구부 산하 인공지능기술팀 보유(국방 AI R&amp;D). 국방 AI 전환·국방데이터 민간개방 사업 추진.</t>
         </is>
       </c>
     </row>
@@ -12146,17 +12146,17 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>해양공공디지털연구본부 (연구본부 레벨) / 정보보안실 (경영지원본부 행정부 산하)</t>
+          <t>해양공공디지털연구본부, 경영지원본부</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>본부 (해양공공디지털연구본부, 연구조직) / 실 (정보보안실, 본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>(해양공공디지털연구본부) 해사디지털서비스연구센터, 해사안전·환경연구센터 / (경영지원본부) 정보보안실</t>
+          <t>해양공공디지털연구본부(해사디지털서비스연구센터·해사안전환경연구센터), 경영지원본부(정보보안실)</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="O156" s="3" t="inlineStr">
         <is>
-          <t>KRISO는 한국해양과학기술원(KIOST) 부설 연구기관. '해양공공디지털연구본부'는 연구 목적 디지털 조직(해사디지털서비스 등), '정보보안실'은 기관 내부 정보보안 담당으로 성격 구분. 별도 AI 전담조직은 공식 조직도에서 미확인.</t>
+          <t>IT담당배경: IT 조직이 해양공공디지털연구본부(연구 목적 디지털 조직)와 경영지원본부 정보보안실(내부 정보보안)로 분리된 이원 구조임.&lt;br&gt;기타: 한국해양과학기술원(KIOST) 부설 연구기관. AI 전담조직 미확인.</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 기획조정부 산하 실 단위</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="O160" s="3" t="inlineStr">
         <is>
-          <t>연구기관(대기·지권·빙하환경·해양·생명과학 연구본부 중심)으로 IT는 행정·경영지원 성격의 정보전산실로 운영. 별도 AI 전담조직 미확인. 정보화·정보보안은 기획조정부 산하 정보전산실로 통합.</t>
+          <t>IT담당배경: 연구기관으로 IT는 행정·경영지원 성격의 정보전산실로 운영. 정보화·정보보안 통합 운영.&lt;br&gt;기타: 한국해양과학기술원 부설기관. AI 전담조직 미확인.</t>
         </is>
       </c>
     </row>
@@ -12746,7 +12746,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>기획조정본부 (정보화 전담조직: 정보화기획팀)</t>
+          <t>기획조정본부</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="O164" s="3" t="inlineStr">
         <is>
-          <t>2025년 조직개편으로 4본부 11팀 → 5본부 13팀 체계로 확대(기획조정본부·노사상생본부·일터혁신본부·중장년고용전략본부·국제노동본부). 이 과정에서 정보화기획팀이 신설되어 "정보인프라 및 시스템 구축을 통한 데이터 관리"를 담당. 별도 IT 본부·처·실 레벨 조직은 없으며 정보화 기능은 팀 단위로 기획조정본부에 편제. AI 전담조직은 확인되지 않음.</t>
+          <t>조직이력: 2025년 조직개편으로 4본부 11팀 → 5본부 13팀 체계 확대. 정보화기획팀 신설(정보인프라·시스템 구축·데이터 관리 담당).&lt;br&gt;IT담당배경: 별도 IT 본부·처·실 레벨 조직 없이 정보화 기능은 팀 단위로 기획조정본부에 편제.</t>
         </is>
       </c>
     </row>
@@ -12821,7 +12821,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>기획조정본부 (정보화 전담조직: 스포츠정보화부)</t>
+          <t>기획조정본부</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="O165" s="3" t="inlineStr">
         <is>
-          <t>스포츠정보화부가 체육정보화 기본계획·중장기 정보화전략계획(ISP) 수립, 전산장비·DB·시스템 보안, 개인정보보호, 국가정보화 평가 대비, 디지털혁신위원회 운영 담당. 2025년 정보화·공공데이터 분야 평가에서 '우수' 등급 획득. AI 전담조직은 없으나 디지털혁신위원회를 통한 디지털전환 추진.</t>
+          <t>IT기능: 체육정보화 기본계획·ISP 수립, 전산장비·DB·시스템 보안, 개인정보보호, 국가정보화 평가 대비, 스포츠ICT통합체계, 회원단체 정보화 지원, 데이터기반행정, 디지털혁신위원회 운영&lt;br&gt;기타: 2025년 정보화·공공데이터 분야 평가 '우수' 등급. AI 전담조직 없으나 디지털혁신위원회(스포츠정보화부 운영)로 디지털전환 추진.</t>
         </is>
       </c>
     </row>
@@ -12896,7 +12896,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>경영본부 (정보화·AI 전담조직: 디지털AI부)</t>
+          <t>경영본부</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>디지털AI부 (산하 정보보호팀 포함)</t>
+          <t>디지털AI부(정보보호팀)</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="O166" s="3" t="inlineStr">
         <is>
-          <t>2026년 4월 기준 기구표(임시조직 포함) 상 경영본부 산하에 '디지털AI부'를 두고 그 아래 '정보보호팀'을 편제 — IT·AI·정보보안을 통합한 조직. '체인포털(Chain Portal)' 등 항만물류 통합 디지털 플랫폼 구축, 디지털플랫폼정부 대응 추진. 실무자 18명 사내 AI 학습조직 운영으로 AI 인재 육성. 2025년 7월 23개→24개 부서 조직개편(북극항로·친환경·디지털 전환 대응).</t>
+          <t>IT기능: IT·AI·정보보안 통합 운영, 항만물류 통합 디지털 플랫폼(체인포털 Chain Portal) 구축, 디지털플랫폼정부 대응&lt;br&gt;조직이력: 2025.7 조직개편 (23개→24개 부서, 북극항로·친환경·디지털 전환 대응)&lt;br&gt;기타: 실무자 18명 사내 AI 학습조직 운영. 2026.4 기준 기구표(임시조직 포함) 기준.</t>
         </is>
       </c>
     </row>
@@ -13196,17 +13196,17 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>정보전산팀 (관리부 계열 / 전산·정보시스템·기술보안 담당)</t>
+          <t>정보전산팀</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>팀 (관리부·홍보실과 병렬되는 팀 단위 — 독립 본부·처 아님)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>정보전산팀(전산·정보시스템 운영, 기술보안 담당) — 그 외 세부 하위팀은 확인불가</t>
+          <t>정보전산팀</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="O170" s="3" t="inlineStr">
         <is>
-          <t>진료·연구 차원에서 의료 AI 활용 활발 — 정부 지원 'AI 활용 치아관리 시스템'(치주질환·아동 치아우식 데이터 기반) 개발 연구 추진. 단, 이는 연구사업이며 IT/AI 전담 조직과는 별개. 별도 법인(특수법인, 2011.9.1)으로 모기관 부산대학교병원(PNUH)과 전산 일부 연계 가능성 있음.</t>
+          <t>IT기능: 전산·정보시스템 운영, 기술보안 담당&lt;br&gt;기타: AI 활용 치아관리 시스템(치주질환·아동 치아우식 데이터 기반) 개발 연구 추진(연구사업, AI 전담조직 별도 없음). 특수법인(2011.9.1 설립), 부산대학교병원과 전산 일부 연계 가능.</t>
         </is>
       </c>
     </row>
@@ -13271,17 +13271,17 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>기획경영본부 (행정·정보화 총괄)</t>
+          <t>경영부원장</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>본부 (행정지원 본부 산하 정보화 기능)</t>
+          <t>처·실(기관장 직속)</t>
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>재무·정보팀 (기획경영본부 산하 / 정보화사업·전산인프라·정보보안·공공데이터 담당)</t>
+          <t>행정실(재무·정보팀)</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -13301,22 +13301,22 @@
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>기획경영본부장 총괄 (재무·정보팀 소관) — 전담 CIO 직위는 미확인</t>
+          <t>행정실장 총괄 추정 (재무·정보팀 소관) — 전담 CIO 직위는 미확인</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>재무·정보팀 정보보안 담당자 (기획경영본부 산하) — 별도 CISO 임원 직위 미확인</t>
+          <t>재무·정보팀 정보보안 담당자 (행정실 산하) — 별도 CISO 임원 직위 미확인</t>
         </is>
       </c>
       <c r="N171" s="3" t="inlineStr">
         <is>
-          <t>상 (공식 홈페이지 직원검색 원문에서 정보화 담당자 소속 '재무·정보팀'(기획경영본부 산하)·담당분야 직접 확인)</t>
+          <t>상 (공식 조직도에서 경영부원장→행정실→재무·정보팀 구조 확인, 직원검색 원문에서 정보화 담당자 소속·담당분야 직접 확인)</t>
         </is>
       </c>
       <c r="O171" s="3" t="inlineStr">
         <is>
-          <t>연구기관 특성상 '정보화'는 연구지원(행정) 기능과 '공간정보·디지털트윈' 연구기능이 구분됨. 공간정보사회연구본부가 디지털트윈(3차원 공간정보)·메타버스 등 AI/공간정보 연구 수행. 행정 정보화는 기획경영본부 소속 담당자(정보화사업·전산인프라·정보보안·공공데이터)가 수행.</t>
+          <t>IT담당배경: 경영부원장 산하 행정실 내 재무·정보팀이 정보화 담당. IT·재무를 한 팀에서 겸하는 소규모 연구기관형 편제.&lt;br&gt;IT기능: 정보화사업·전산인프라·정보보안·공공데이터&lt;br&gt;기타: 공간정보사회연구본부 산하 디지털트윈연구센터가 공간정보·AI 융합 연구 수행(행정 IT 조직과 구분).</t>
         </is>
       </c>
     </row>
@@ -13421,17 +13421,17 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>항만정보화실 (운영본부 산하)</t>
+          <t>운영본부</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>정보보안 총괄, 정보시스템 기획, 공공데이터·데이터기반행정, 개인정보보호 (항만정보화실 내 담당) / 별도 정보보안TF팀 운영</t>
+          <t>항만정보화실(정보보안 총괄·정보시스템 기획·공공데이터·개인정보보호), 정보보안TF팀</t>
         </is>
       </c>
       <c r="I173" s="3" t="inlineStr">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>정보지원실·정보보안센터 (연금사업본부 산하)</t>
+          <t>연금사업본부</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>정보지원실(전산운영), 정보보안센터(정보보안·개인정보)</t>
+          <t>정보지원실, 정보보안센터</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="O181" s="3" t="inlineStr">
         <is>
-          <t>1974년 설립, 나주 소재. 경영관리본부·연금사업본부·자금운용관리단·리스크관리실 체계. 정보화는 연금사업본부 산하 정보지원실(전산운영)·정보보안센터(정보보안·개인정보)가 담당. 2026년 'AX·DX 기반 지능형 연금·복지 서비스 기관' 경영혁신 추진, 공공기관 최초 AI 혁신자문위원 'T-쌤' 위촉·AI 혁신보드 운영 — 전담 AI 조직 신설과는 별개의 거버넌스/자문 단위.</t>
+          <t>IT기능: 전산운영(정보지원실), 정보보안·개인정보보호(정보보안센터)&lt;br&gt;기타: 2026년 'AX·DX 기반 지능형 연금·복지 서비스 기관' 경영혁신 추진. 공공기관 최초 AI 혁신자문위원 'T-쌤' 위촉·AI 혁신보드 운영(거버넌스/자문 단위, AI 전담조직 아님). ISMS 인증(2018), 개인정보 관리수준진단 'S'등급(2022).</t>
         </is>
       </c>
     </row>
@@ -14396,17 +14396,17 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>관리운영부 행정지원팀(정보화·정보보안 기능 포함)</t>
+          <t>관리운영부</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>팀 (사무총장 → 관리운영부 → 행정지원팀 내 기능)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>행정지원팀 내 '정보화·정보보안', '전산·정보보안', '공공데이터·정보화 지원' 담당(별도 IT 전담 팀 없음)</t>
+          <t>행정지원팀(정보화·정보보안, 전산·정보보안, 공공데이터·정보화 지원 담당)</t>
         </is>
       </c>
       <c r="I186" s="3" t="inlineStr">
@@ -14621,32 +14621,32 @@
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>경영지원부 (경영본부 산하) — 정보화·정보보안·개인정보 기능 보유</t>
+          <t>경영본부</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>부(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>경영지원부 (정보시스템 관리·정보보안·개인정보보호·항만물류 정보화 업무 수행)</t>
+          <t>경영지원부</t>
         </is>
       </c>
       <c r="I189" s="3" t="inlineStr">
         <is>
-          <t>없음 (전담 AI 조직 미확인. 스마트항만은 개발사업본부 산하 '자동화사업실'이 항만자동화(장비·터미널운영시스템) 담당 — 일반 IT/AI 전담조직과 별개)</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 AI 전담조직 명칭 미확인)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L189" s="3" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>정보시스템부 (경영전략본부 산하)</t>
+          <t>경영전략본부</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 경영전략본부 산하 '부' 단위(공제회는 본부 아래 부·실 편제)</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
-          <t>정보시스템부 단일 부(부 내 기능: 정보시스템 총괄, 시스템 운영, 시스템 개발, 인프라 구축·운영, 망분리·가상PC, 정보보안, DB 운영 등 7개 내선으로 분장)</t>
+          <t>정보시스템부</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="O190" s="3" t="inlineStr">
         <is>
-          <t>2025.07.01 조직개편으로 3본부 2실 11부 체제(나무위키 연혁). 본부=경영전략본부·고객사업본부·자산운용본부. 정보화 총괄=경영전략본부 산하 **정보시스템부**(전략기획부·경영관리부·정보시스템부·리스크관리실·조사연구센터와 병렬). "메인 전산센터 이전"(2026-06 입찰), 전자카드제·통합민원시스템(건설e음/eum.cw.or.kr)·차세대 통합시스템 등 대규모 정보시스템 운영. '전화기반 행정서비스 고도화 ISP' 발주 등 정보화 기획 활발. AI 전담조직은 없음.</t>
+          <t>IT기능: 정보시스템 총괄, 시스템 운영·개발, 인프라 구축·운영, 망분리·가상PC, 정보보안·개인정보보호, DB 운영, 공공데이터 제공&lt;br&gt;조직이력: 2025.07.01 조직개편 → 3본부(경영전략본부·고객사업본부·자산운용본부) 2실 11부 체제&lt;br&gt;기타: 메인 전산센터 이전(2026-06 입찰), 통합민원시스템(건설e음), 차세대 통합시스템 운영. 전화기반 행정서비스 고도화 ISP 발주 등 정보화 기획 활발.</t>
         </is>
       </c>
     </row>
@@ -14891,7 +14891,7 @@
       </c>
       <c r="O192" s="3" t="inlineStr">
         <is>
-          <t>정보화·데이터 기능이 '다양성·AI정보실' 산하 '지능정보팀'으로 통합. 조직명에 'AI'가 포함되어 AI·데이터 기능을 명시. MBRIS(해양생명자원 통합정보시스템)·MAGIC(국가해양수산물 유전체정보센터) 등 정보시스템 운영.</t>
+          <t>IT기능: 연구관련 정보시스템 구축·운영·데이터기반행정·해양생명자원 통계(MBRIS·MAGIC 등 운영)&lt;br&gt;기타: 조직명에 'AI' 포함. AI·데이터 기능을 지능정보팀에서 통합 담당.</t>
         </is>
       </c>
     </row>
@@ -14921,17 +14921,17 @@
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>전산정보센터</t>
+          <t>기획조정실</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>팀·센터(실 산하) — 기획조정실 산하 전산정보센터(하위 전산정보팀)</t>
+          <t>팀·센터(처·실 산하)</t>
         </is>
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>전산정보팀</t>
+          <t>전산정보센터(전산정보팀)</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="O193" s="3" t="inlineStr">
         <is>
-          <t>2016년 경북대학교병원에서 분리 독립 법인으로 출범한 지역거점 치과병원. IT 기능은 기획조정실 산하 전산정보센터(전산정보팀)가 담당. 병원 규모상 별도 IT 본부·처 없음.</t>
+          <t>IT담당배경: 2016년 경북대학교병원에서 분리 독립한 지역거점 치과병원(현원 205명). 별도 IT 본부·처 없이 기획조정실 산하 전산정보센터(전산정보팀)가 IT 전담.</t>
         </is>
       </c>
     </row>
@@ -14996,7 +14996,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>융합기술센터(방송기술·시스템) / 데이터정보화팀(데이터·정보화·개인정보)</t>
+          <t>융합기술센터 / 데이터정보화팀</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>융합기술센터(방송정보화시스템 운영·네트워크 인프라·정보보안 관리), 데이터정보화팀(공공데이터·데이터기반행정·정보화·개인정보)</t>
+          <t>융합기술센터, 데이터정보화팀</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
@@ -15039,9 +15039,10 @@
           <t>상(공식 개인정보처리방침(2025.7.10) + 공시 부서별 업무추진계획 + 보도 교차 확인)</t>
         </is>
       </c>
-      <c r="O194" s="3">
-        <f>아리랑국제방송(아리랑TV/KIBF). 자회사 아리랑TV미디어 보유. 2024→2025 조직개편: 기존 2본부12센터1반 → 2본부4센터8팀1반으로 축소. 방송기술·방송정보화시스템·네트워크·정보보안은 '융합기술센터'가 총괄. 데이터기반행정·공공데이터·정보화·개인정보 실무는 경영본부 산하 '데이터정보화팀'이 담당.</f>
-        <v/>
+      <c r="O194" s="3" t="inlineStr">
+        <is>
+          <t>IT담당배경: 방송기술·방송정보화시스템·정보보안은 융합기술센터가, 공공데이터·정보화·개인정보는 경영본부 산하 데이터정보화팀이 담당하는 이원 구조.&lt;br&gt;IT기능: 방송정보화시스템 운영·네트워크 인프라·정보보안(융합기술센터), 공공데이터·데이터기반행정·정보화·개인정보보호(데이터정보화팀)&lt;br&gt;조직이력: 2024→2025 조직개편: 2본부12센터1반 → 2본부4센터8팀1반으로 축소. AI데이터정보화센터(2024) → 데이터정보화팀으로 개편.</t>
+        </is>
       </c>
     </row>
     <row r="195">
@@ -15070,17 +15071,17 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>기획혁신처 (정보화·정보보안 기능 포함)</t>
+          <t>경영혁신본부</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 경영혁신본부 산하 기획혁신처</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>별도 IT전담팀 미확인. 기획혁신처가 정보화·정보보안 총괄(차장이 정보보안 담당), 데이터팀(기술품질본부/검사품질처)이 데이터 기능 담당</t>
+          <t>기획혁신처(정보화·정보보안 총괄, 차장이 정보보안 담당). 데이터팀(기술품질본부/검사품질처)이 데이터 기능 별도 담당</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
@@ -15145,17 +15146,17 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>전산팀 (경영지원실 산하)</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>팀 — 연구기획부원장 산하 경영지원실 소속</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H196" s="3" t="inlineStr">
         <is>
-          <t>전산팀(정보시스템 운영관리), 학술정보팀(연구조정실 산하 — 온라인DB·데이터·전자도서관 운영)</t>
+          <t>전산팀, 학술정보팀</t>
         </is>
       </c>
       <c r="I196" s="3" t="inlineStr">
@@ -15190,7 +15191,7 @@
       </c>
       <c r="O196" s="3" t="inlineStr">
         <is>
-          <t>정부출연 연구기관 특성상 IT는 경영지원실 산하 전산팀 1개 팀 수준. 데이터/DB는 연구조정실 학술정보팀이 별도 담당. AI는 연구 주제(경제정책 분석)로 다루나 IT 전담 AI조직은 아님</t>
+          <t>IT담당배경: 정부출연 연구기관 특성상 IT는 경영지원실 산하 전산팀 1개 팀 수준. 데이터/DB는 연구조정실 학술정보팀이 별도 담당.&lt;br&gt;기타: AI는 연구 주제(경제정책 분석)로 다루나 IT 전담 AI조직은 아님.</t>
         </is>
       </c>
     </row>
@@ -15220,17 +15221,17 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>전산팀 (경영부 경영지원실 산하)</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>팀 — 경영부원장(경영부) 산하 경영지원실 소속</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>전산팀(정보시스템·전산 운영). 데이터 분석은 연구부의 산업경제데이터분석실·경제전망·통계연구단이 별도 수행</t>
+          <t>전산팀</t>
         </is>
       </c>
       <c r="I197" s="3" t="inlineStr">
@@ -15265,7 +15266,7 @@
       </c>
       <c r="O197" s="3" t="inlineStr">
         <is>
-          <t>정부출연 연구기관. IT는 경영지원실 산하 전산팀 수준. '산업경제데이터분석실'은 산업데이터 연구·분석 조직으로 일반 정보화 조직과 구분. KIET 50주년(2026 기준 1976년 전신 설립)</t>
+          <t>IT담당배경: 경영지원실 산하 전산팀이 IT 전산 인프라를 담당하며, 별도 정보화 본부·처는 없음.&lt;br&gt;기타: '산업경제데이터분석실'은 산업데이터 연구·분석 조직으로 일반 정보화 조직과 구분. KIET 50주년(2026 기준, 1976년 전신 설립).</t>
         </is>
       </c>
     </row>
@@ -15520,17 +15521,17 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>전략기획실 (정보화·정보보안·개인정보보호 총괄, 산하 지능정보부 담당)</t>
+          <t>전략기획실</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하 아님 — 관장 직속 전략기획실 산하 부)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>지능정보부 (전략기획실 산하, 기관 정보화·정보보안·개인정보보호 총괄)</t>
+          <t>전략기획실(지능정보부)</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
@@ -15565,7 +15566,7 @@
       </c>
       <c r="O201" s="3" t="inlineStr">
         <is>
-          <t>담수생물 전문 연구기관. 정보화 기능은 관장 직속 '전략기획실' 산하 '지능정보부'가 담당하며, 기관 정보화·정보보안·개인정보보호 업무를 총괄(보안뉴스 2024 개인정보보호 우수사례 및 공식 조직페이지 확인). 2025년 개인정보 보호수준 평가 'S'등급. 별도 AI 전담조직은 없으나 담수생물 데이터 관리·디지털이미지 전환·AI 종판별 등 연구 차원의 디지털 활용은 수행. 조직은 전략기획실(기획부·성과혁신부·지능정보부) + 경영관리본부(경영관리실·전시교육실) + 담수생물연구본부 체계.</t>
+          <t>IT기능: 기관 정보화·정보보안·개인정보보호 총괄&lt;br&gt;기타: 2025년 개인정보 보호수준 평가 'S'등급. 담수생물 데이터 관리·디지털이미지 전환·AI 종판별 등 연구 차원 디지털 활용 수행.</t>
         </is>
       </c>
     </row>
@@ -15895,7 +15896,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>정보화전략팀 (경영전략본부 &gt; 경영지원부 산하)</t>
+          <t>경영전략본부</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -15905,7 +15906,7 @@
       </c>
       <c r="H206" s="3" t="inlineStr">
         <is>
-          <t>정보화전략팀 (단일 팀)</t>
+          <t>경영지원부(정보화전략팀)</t>
         </is>
       </c>
       <c r="I206" s="3" t="inlineStr">
@@ -15940,7 +15941,7 @@
       </c>
       <c r="O206" s="3" t="inlineStr">
         <is>
-          <t>아동정책·아동복지 종합수행 기관(NCRC, 2019 출범, 입양체계 운영 포함). 정보화는 경영전략본부&gt;경영지원부 산하 '정보화전략팀'이 단일 팀으로 담당(정보화 기본·중장기계획, 정보시스템 통폐합·연계, 공공데이터, 정보인프라, 개인정보보호 운영 포함). 별도 AI 전담조직은 없음. AI는 '디지털 시대 아동권리' 정책 포럼 등 정책 주제로 다룸.</t>
+          <t>IT기능: 정보화 기본·중장기계획, 정보시스템 통폐합·연계, 공공데이터, 정보인프라, 개인정보보호 운영&lt;br&gt;기타: AI는 '디지털 시대 아동권리' 정책 포럼 등 정책 의제로만 다룸(전담 조직 없음).</t>
         </is>
       </c>
     </row>
@@ -16055,7 +16056,7 @@
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>스마트농업기획실 (현 공식 개인정보처리방침 확인), 데이터분석실·디지털농정실(조직개편 보도 기준), 스마트농업지원단(스마트팜확산실)</t>
+          <t>스마트농업기획실, 데이터분석실, 디지털농정실</t>
         </is>
       </c>
       <c r="I208" s="3" t="inlineStr">
@@ -16090,7 +16091,7 @@
       </c>
       <c r="O208" s="3" t="inlineStr">
         <is>
-          <t>약칭 '농정원'(EPIS). 기관 자체가 농식품·농촌 정보화 촉진을 설립 목적으로 하는 정보화 전문기관. '디지털혁신본부'가 IT/디지털 총괄. **2026.5 과기정통부 '국가 인공지능 프로젝트'에 선정되어 고성능 GPU 32장 확보(공공 16·민간 16) → 농가 작물 생육 사진·영상을 AI 모델로 판독·분석, 학습용 데이터·스마트팜 데이터 자동추출 서비스 추진** 등 AI 사업을 적극 추진하나, 'AI' 명칭의 상설 전담조직은 미확인. 디지털혁신본부 산하 개인정보보호 실무는 '스마트농업기획실'이 담당. 정부 공공기관 혁신 가이드라인에 따른 조직 축소 개편 이력 보유(4개 단위조직 축소).</t>
+          <t>IT담당배경: 기관 자체가 농식품·농촌 정보화 촉진 목적 정보화 전문기관. 약칭 '농정원'(EPIS).&lt;br&gt;기타: 2026.5 과기정통부 '국가 인공지능 프로젝트' 선정, GPU 32장 확보. AI 사업 적극 추진 중이나 'AI' 명칭 상설 전담조직은 미확인. 조직 축소 개편 이력 보유(4개 단위조직 축소).</t>
         </is>
       </c>
     </row>
@@ -16195,17 +16196,17 @@
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>전산팀 (내부 정보화 운영 기준) / 인공지능정책연구실·디지털정책연구실 (연구 기능 기준)</t>
+          <t>기획조정실</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>팀 (기획조정실 산하 전산팀)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>전산팀 (기획조정실 소속)</t>
+          <t>전산팀</t>
         </is>
       </c>
       <c r="I210" s="3" t="inlineStr">
@@ -16270,17 +16271,17 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>전략기획실 (정보화·정보보안·개인정보보호 담당, 산하 정보관리부)</t>
+          <t>전략기획실</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하 아님 — 관장 직속 전략기획실 산하 부)</t>
+          <t>처·실(관장 직속)</t>
         </is>
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>정보관리부 (전략기획실 산하, 정보화·정보보안·개인정보보호 담당)</t>
+          <t>정보관리부</t>
         </is>
       </c>
       <c r="I211" s="3" t="inlineStr">
@@ -16315,7 +16316,7 @@
       </c>
       <c r="O211" s="3" t="inlineStr">
         <is>
-          <t>약칭 HNIBR. 2020년 설립·2021년 개관한 소규모 연구기관. 조직은 전략기획실(기획성과부·전략홍보부 등) + 경영관리본부(경영관리실·전시교육실) 등 2개 본부·6개 실 체계. 정보화·정보보안·개인정보보호는 전략기획실 산하 '정보관리부'가 담당(공식 개인정보처리방침 확인). 개인정보보호 평가에서 보호책임자를 부장→기관장으로 격상하고 개인정보보호협의회를 구성·운영. 생물표본·자원 '디지털전환' 사업은 추진 중이나 이는 연구 데이터 사업으로 IT 전담조직과는 별개.</t>
+          <t>IT기능: 정보화·정보보안·개인정보보호 (전략기획실 산하 정보관리부 담당)&lt;br&gt;기타: 개인정보보호 평가에서 책임자를 부장→기관장으로 격상, 개인정보보호협의회 구성·운영. 생물표본·자원 디지털전환 사업 추진 중(연구 데이터 사업).</t>
         </is>
       </c>
     </row>
@@ -16495,17 +16496,17 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>사무국 (행정 '1부·1실·1과' 체제 — 별도 정보화 본부·처·실 없음. 전산·정보화·의료정보는 사무국 행정기능으로 수행)</t>
+          <t>사무국</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>팀 이하 (별도 IT 조직 단위 없음 — 사무국 행정부서 내 담당)</t>
+          <t>팀 이하</t>
         </is>
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전산·정보화 전담 부서명 미확인 / 사무국 내 행정·원무팀이 의료정보시스템·개인정보 업무 겸장 추정)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr">
@@ -16540,7 +16541,7 @@
       </c>
       <c r="O214" s="3" t="inlineStr">
         <is>
-          <t>강릉 소재 국립대치과병원(교육부 산하, 「국립대학치과병원설치법」에 따른 독립 특수법인). 공식 도메인 knudh.or.kr(이메일 gwnudh.or.kr)로, 강릉원주대학교치과병원이 강원대-강릉원주대 통합(2024~2025)에 따라 '강원대학교치과병원'으로 운영. 행정조직은 '1부·1실·1과' 체제(국회 교육위 업무보고 기준)로 기획조정실 보유. 소규모 기관(약 161명)으로 별도 정보화 본부·처·실 없이 사무국 행정부서가 전산·정보화·의료정보시스템(PACS 등)·개인정보보호 업무를 겸장. 개인정보보호책임자(CPO)는 별도 지정·운영. 강원대학교 본교 '정보화본부'는 별개 법인의 IT조직이므로 혼동 금지.</t>
+          <t>IT담당배경: 소규모 기관(현원 161명)으로 별도 정보화 본부·처·실 없음. 사무국 행정부서 내에서 전산·정보화·의료정보시스템(PACS 등)·개인정보보호 업무 겸장. 정보보안시스템(PACS·EDR·ERP·DB암호화·NAC)은 외부 위탁 운영.</t>
         </is>
       </c>
     </row>
@@ -16570,17 +16571,17 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>기획조정본부 (전산정보화팀 소속)</t>
+          <t>기획조정본부</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>팀 (본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H215" s="3" t="inlineStr">
         <is>
-          <t>전산정보화팀 (경영정보시스템·디지털 인프라·정보시스템 운영)</t>
+          <t>전산정보화팀</t>
         </is>
       </c>
       <c r="I215" s="3" t="inlineStr">
@@ -16615,7 +16616,7 @@
       </c>
       <c r="O215" s="3" t="inlineStr">
         <is>
-          <t>IT 기능은 기획조정본부 산하 '전산정보화팀'에 집중(경영정보시스템 운영). 개인정보보호책임자(CPO)는 경영지원본부장이 겸임하며 실무는 안전관리팀(경영지원본부)이 담당 → IT 운영(기획조정본부)과 정보보호 거버넌스(경영지원본부)가 분리. 별도 AI 전담 상설조직은 공식 조직도에 없음. 다만 'INNOPOLIS+ AI 초고속 기술·산업 연계 플랫폼', 'AI 글로벌 빅테크 육성사업' 등 AI 관련 사업은 특구육성/사업부서에서 사업 형태로 추진(전담조직 아님). 2025년 웹어워드코리아 공공기관분야 대상.</t>
+          <t>IT기능: 경영정보시스템 운영, 디지털 인프라, 정보시스템 운영&lt;br&gt;기타: IT 운영(기획조정본부)과 정보보호 거버넌스(경영지원본부) 분리 구조 — CPO=경영지원본부장, 실무=안전관리팀. AI 전담 상설조직 없음. INNOPOLIS+ AI 초고속 기술·산업 연계 플랫폼·AI 글로벌 빅테크 육성사업 등 AI는 사업 형태로 추진. 2025년 웹어워드코리아 공공기관분야 대상.</t>
         </is>
       </c>
     </row>
@@ -16720,17 +16721,17 @@
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>안전경영부 (정보화·정보보안·개인정보보호 포함, 별도 IT 전담 부서 없음)</t>
+          <t>안전경영부</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 부 레벨 (별도 IT 전담 부서 없음)</t>
+          <t>팀(부)</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>안전경영부 (인사·보수·노무·구매·계약·회계와 함께 정보화·정보보안·개인정보보호·행정정보 공동이용 겸장 / 별도 정보화팀 없음)</t>
+          <t>안전경영부</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr">
@@ -16765,7 +16766,7 @@
       </c>
       <c r="O217" s="3" t="inlineStr">
         <is>
-          <t>대외명칭 '남북하나재단'. 별도 정보화/IT 전담 부서가 없으며, 정보화·정보보안·개인정보보호 기능이 '안전경영부'(인사·보수·노무·구매·계약·회계와 통합)에 포함. 개인정보보호책임자(CPO)는 사무총장이 겸임. AI 전담조직 없음. 조직 규모상 IT는 행정지원 기능의 일부로 운영. 현 조직: 이사장-사무총장 산하 전략기획실·대외협력실·안전경영부·사회적응부·일자리지원부·교육지원부 + 감사윤리팀(독립).</t>
+          <t>IT담당배경: '안전경영부'는 인사·보수·노무·구매·계약·회계와 함께 정보화·정보보안·개인정보보호·행정정보 공동이용을 겸장하는 행정지원 조직임.&lt;br&gt;IT기능: 정보화, 정보보안, 개인정보보호, 행정정보 공동이용&lt;br&gt;기타: 대외명칭 '남북하나재단'. 개인정보보호책임자(CPO)는 사무총장이 겸임.</t>
         </is>
       </c>
     </row>
@@ -17020,17 +17021,17 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (산하 디지털전환팀(DAX팀)이 지식정보·전산·디지털전환 담당)</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>팀 (실 산하) — 경영지원실 산하 디지털전환팀</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>디지털전환팀(DAX팀, 지식정보+총무 통합) — 경영지원실 소속</t>
+          <t>디지털전환팀</t>
         </is>
       </c>
       <c r="I221" s="3" t="inlineStr">
@@ -17040,7 +17041,7 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>디지털전환팀(DAX팀) (전사 디지털·AI 전환 대응 기능 보유)</t>
+          <t>디지털전환팀</t>
         </is>
       </c>
       <c r="K221" s="3" t="inlineStr">
@@ -17065,7 +17066,7 @@
       </c>
       <c r="O221" s="3" t="inlineStr">
         <is>
-          <t>2026.2.23 조직개편(인공지능 기반 디지털 전환 및 PBS 폐지 대응)으로 1본부·3센터·4실·7팀 → 1본부·3센터·4실·8팀 체제로 변경. 기존 인사총무팀 총무기능과 지식정보 업무를 통합해 '디지털전환팀(DAX팀)'으로 재편(경영지원실 소속), 기획조정팀을 성과확산팀과 분리. 연구본부는 시스템혁신본부·혁신성장본부·글로벌전략본부(2026 본부장 전보). 연구조직으로 '시스템혁신실/시스템혁신 연구분야' 별도 보유(데이터·디지털 정책 연구).</t>
+          <t>조직이력: 2026.2.23 조직개편 → 인사총무팀 총무기능·지식정보 업무를 통합한 디지털전환팀(DAX팀) 신설(경영지원실 소속), 기획조정팀 → 성과확산팀 분리, 8팀 체제&lt;br&gt;기타: 전사 디지털·AI 전환(DAX) 대응 조직. 연구본부(시스템혁신본부·혁신성장본부·글로벌전략본부)와 별개로 시스템혁신실에서 데이터·디지털 정책 연구 수행.</t>
         </is>
       </c>
     </row>
@@ -17170,17 +17171,17 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부 (산하 경영지원실이 전산·정보화·정보보안 행정 겸장)</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 경영기획본부 산하 경영지원실 (별도 IT 전담 조직 없음)</t>
+          <t>처·실(본부 산하) — 경영기획본부 산하 시설안전센터</t>
         </is>
       </c>
       <c r="H223" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (총무·회계·인사와 함께 전산·정보화·정보보안 담당 / 전담 부서명 미확인)</t>
+          <t>시설안전센터(시설지원파트)</t>
         </is>
       </c>
       <c r="I223" s="3" t="inlineStr">
@@ -17200,22 +17201,22 @@
       </c>
       <c r="L223" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담 CIO 직위 미확인 — 경영기획본부장/경영지원실장이 정보화 총괄 추정)</t>
+          <t>확인불가 (전담 CIO 직위 미확인 — 경영기획본부장이 정보화 총괄 추정)</t>
         </is>
       </c>
       <c r="M223" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 임원급 CISO 부서 명시 미확인 — 통상 경영지원실장이 개인정보보호책임자(CPO)·정보보호 총괄 겸임 추정)</t>
+          <t>확인불가 (별도 임원급 CISO 부재 — 시설안전센터에서 정보보안 기능 수행, 개인정보보호책임자 직접 확인 미흡)</t>
         </is>
       </c>
       <c r="N223" s="3" t="inlineStr">
         <is>
-          <t>중(본부·실 조직구성은 위키백과(2026.5 갱신)·조직개편 보도로 확인, 전산 전담부서명·CIO/CISO 직접확인은 미흡)</t>
+          <t>상 (공식 홈페이지 조직도(dnsm.or.kr/about/organization.do)에서 경영기획본부→시설안전센터(정보보안·홈페이지·정보화사업·IT인프라·네트워크·공공데이터) 구조 직접 확인 — 2026-06-18)</t>
         </is>
       </c>
       <c r="O223" s="3" t="inlineStr">
         <is>
-          <t>과기정통부 산하 전시·과학교육 중심 법인(관장=이사장 겸임, 현 관장 이난희). 조직(공식 현행): 관장 직속 대외협력실 + 경영기획본부(기획예산실·경영지원실·시설안전센터) + 전시교육본부(전시기획실·과학문화실·과학교육실·전시운영센터)의 2본부 체계. 2022.1 첫 조직개편(전시기획실→전시기획연구실, 전시관운영센터·시설관리센터 신설) 후 2025.12 이사회 의결로 본부 체계로 재편(전문성·자체 연구기능 강화). 전산·정보화 행정은 경영지원실(총무·회계·인사 총괄)이 겸장. 임직원 44명 AI활용지도사 1급 취득 등 'AI 활용 스마트 과학관' 추진(전시·교육·행정 AI 적용)하나 사내 IT/AI 전담조직은 없음.</t>
+          <t>IT담당배경: '시설안전센터'는 명칭과 달리 정보 인프라·보안을 총괄하는 IT 전담 조직임. 산하 시설지원파트가 IT 실무 수행 (경영지원실은 총무·구매 등 일반 경영 담당)&lt;br&gt;IT기능: 정보보안·홈페이지·정보화사업·IT인프라·네트워크·공공데이터&lt;br&gt;조직이력: 2025.12 이사회 의결로 실 병렬 구조 → 경영기획본부·전시교육본부 2본부 체계로 재편&lt;br&gt;기타: 임직원 44명 AI활용지도사 1급 취득. AI 활용 스마트 과학관 추진 중</t>
         </is>
       </c>
     </row>
@@ -17245,12 +17246,12 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>AI디지털실 (기획조정실 라인/부원장 직속 관리부서 소속)</t>
+          <t>AI디지털실</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>실 (본부 외 원장·부원장 직속 기획·관리 라인)</t>
+          <t>처·실(기관장 직속)</t>
         </is>
       </c>
       <c r="H224" s="3" t="inlineStr">
@@ -17290,7 +17291,7 @@
       </c>
       <c r="O224" s="3" t="inlineStr">
         <is>
-          <t>국토교통부 R&amp;D 전문관리기관(KAIA). 3본부 17실 2센터 2단 체제. 기획·관리 라인에 정보화·정보보안을 통합한 'AI디지털실'을 두어 명칭상 AI 전담 기능을 명시. 국토본부에 도시공간정보실 등 공간정보 연구관리 부서 별도 보유.</t>
+          <t>IT기능: AI·디지털 업무 총괄·정보보안(산하 정보보안팀)&lt;br&gt;기타: 3본부 17실 2센터 2단 체제. 국토본부 산하 도시공간정보실은 공간정보 R&amp;D 관리(IT 운영과 구분).</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17401,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>실(총장 직속)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H226" s="3" t="inlineStr">
@@ -17440,7 +17441,7 @@
       </c>
       <c r="O226" s="3" t="inlineStr">
         <is>
-          <t>KDI(한국개발연구원) 부설 정책전문대학원. 행정조직은 총장 직속의 감사실·중앙도서실·중앙전산실과 교학처·기획처·연구협력처·입학대외협력센터 등으로 구성. IT는 중앙전산실(전산2팀)이 전담. AI 전담 조직은 없으나 "공공정책 데이터사이언스" 석사과정 등 데이터·AI 교육과정 운영.</t>
+          <t>IT담당배경: 중앙전산실은 총장 직속 실 단위로 편성되어 전산·정보화를 전담함.&lt;br&gt;기타: AI 전담 조직은 없으나 "공공정책 데이터사이언스" 석사과정 등 데이터·AI 교육과정 운영.</t>
         </is>
       </c>
     </row>
@@ -17470,17 +17471,17 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (정보화·전산·정보보안 업무 소관)</t>
+          <t>경영본부</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>실(IT 전담 별도 조직 없음, 경영지원실 산하 업무)</t>
+          <t>처·실(본부 산하) — 경영본부 산하 경영지원실</t>
         </is>
       </c>
       <c r="H227" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 내 전산·정보화 담당 (별도 정보화 전담 팀 명칭 미확인 / 전산장비·정보보안장비 유지보수 경영지원실 소관 확인)</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="I227" s="3" t="inlineStr">
@@ -17510,12 +17511,12 @@
       </c>
       <c r="N227" s="3" t="inlineStr">
         <is>
-          <t>중(공식 내규집 부서목록 + 채용공고·기록물대장으로 경영지원실 IT소관 정황 확인, IT 전담 팀명·CISO 직접확인은 미흡)</t>
+          <t>상 (공식 홈페이지 조직도(sciport.or.kr)에서 2본부 구조 및 각 실·센터 직접 확인 — 2026-06-18)</t>
         </is>
       </c>
       <c r="O227" s="3" t="inlineStr">
         <is>
-          <t>동남권 지역거점 과학관(2015년 개관, 2017년 기타공공기관 지정). 조직: 경영지원실·기획예산실·전시연구실·전시운영센터·과학문화실·교육연구실·홍보협력실·시설안전센터·청렴감사팀 등(2026.2 내규집 기준). 경영지원실이 채용·인사·재무·총무 등 경영 전반 총괄(채용 문의 051-750-2461/2463)이며 전산·정보화·정보보안장비 유지보수도 경영지원실 소관으로 운영. 별도 정보화/전산 전담 팀은 미설치.</t>
+          <t>IT담당배경: 별도 정보화·전산 전담 팀 미설치. 경영지원실이 채용·인사·재무·총무 등 경영 전반과 함께 전산·정보화·정보보안장비 유지보수 소관. 시설안전센터는 시설관리팀·환경미화팀만(IT 담당 아님).&lt;br&gt;기타: 동남권 지역거점 과학관. 2015년 개관, 2017년 기타공공기관 지정.</t>
         </is>
       </c>
     </row>
@@ -17545,7 +17546,7 @@
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부 (정보화 업무는 경영지원팀 소관)</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -17555,7 +17556,7 @@
       </c>
       <c r="H228" s="3" t="inlineStr">
         <is>
-          <t>경영지원팀 (통합경영정보시스템(그룹웨어·ERP), 정보보안, 정보시스템관리(PC·서버), 홈페이지, 문화정보화수준평가 담당)</t>
+          <t>경영지원팀</t>
         </is>
       </c>
       <c r="I228" s="3" t="inlineStr">
@@ -17590,7 +17591,7 @@
       </c>
       <c r="O228" s="3" t="inlineStr">
         <is>
-          <t>국립아시아문화전당(ACC, 책임운영기관)의 콘텐츠 사업을 수행하는 별도 재단법인(ACCF). 조직은 사무국장 아래 경영기획본부(전략기획팀·경영지원팀·서비스사업팀)·어린이사업본부·문화사업본부(문화사업개발팀·문화유통팀·문화예술사업팀·융합미디어사업단)와 혁신TF팀으로 구성. 별도 정보화 전담 부서 없이 IT는 경영지원팀에 통합. 융합미디어사업단이 "인공지능 기반 다분야 협업 융복합 콘텐츠 저작툴 개발" 추진.</t>
+          <t>IT담당배경: 별도 정보화 전담 부서 없이 경영기획본부 산하 경영지원팀이 IT 업무를 통합 담당.&lt;br&gt;IT기능: 통합경영정보시스템(그룹웨어·ERP)·정보보안·정보시스템관리(PC·서버)·홈페이지·문화정보화수준평가&lt;br&gt;기타: 문화사업본부 산하 융합미디어사업단이 AI 기반 다분야 협업 융복합 콘텐츠 저작툴 개발 추진</t>
         </is>
       </c>
     </row>
@@ -17855,7 +17856,7 @@
       </c>
       <c r="H232" s="3" t="inlineStr">
         <is>
-          <t>K-MOOC운영실, 평생학습시스템구축실, 디지털역량개발실 (일부 확인, 본부 산하 실 전체 구성은 일부 확인불가)</t>
+          <t>K-MOOC운영실, 평생학습시스템구축실, 디지털역량개발실</t>
         </is>
       </c>
       <c r="I232" s="3" t="inlineStr">
@@ -17890,7 +17891,7 @@
       </c>
       <c r="O232" s="3" t="inlineStr">
         <is>
-          <t>5본부·실 체계(기획경영본부·평생교육정책본부·고등평생교육본부·디지털전략사업본부·정책연구실). IT/시스템·디지털 기능이 '디지털전략사업본부'에 집중. '재직자 AI·디지털(AI·D) 집중과정' 등 AI 관련은 교육사업(디지털역량개발실 소관)으로 전담 조직 아님. 2026.1.1 교육부 조직개편(인공지능인재지원국 신설)은 상급부처 차원 변화.</t>
+          <t>기타: AI 관련은 '재직자 AI·디지털 집중과정' 등 교육사업 형태로, 전담 직제 조직 없음. 2026.1.1 교육부 인공지능인재지원국 신설은 상급부처 변화.</t>
         </is>
       </c>
     </row>
@@ -17920,7 +17921,7 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>경영정보팀 (경영지원처 산하, 정보화·정보시스템·정보보안 총괄)</t>
+          <t>기획경영본부</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -17930,7 +17931,7 @@
       </c>
       <c r="H233" s="3" t="inlineStr">
         <is>
-          <t>해당없음(팀 단위). 별도로 공항정보팀(건축기획처 산하, 공항 운영 정보시스템 구축), 스마트공항팀(전기통신처 산하, 스마트공항 전략·통신) 존재</t>
+          <t>경영지원처(경영정보팀)</t>
         </is>
       </c>
       <c r="I233" s="3" t="inlineStr">
@@ -17965,7 +17966,7 @@
       </c>
       <c r="O233" s="3" t="inlineStr">
         <is>
-          <t>2024년 신설된 신생 공단(공항 건설 한시조직 성격). 3본부(기획경영·건설·건축) 체계. 일반 정보화·정보보안은 경영지원처 '경영정보팀'이 담당하나, 건설사업 특성상 '공항정보팀'(공항 운영 정보시스템), '스마트공항팀'(스마트공항 전략·통신)이 별도 존재. LX공사·수자원공사 등과 디지털트윈·공간정보 MOU 추진 중. AI 전담조직 없음.</t>
+          <t>IT기능: 정보화, 정보시스템, 홈페이지, 개인정보, 정보보안(경영정보팀)&lt;br&gt;기타: 건설사업 특성상 공항정보팀(건축기획처 산하, 공항 운영 정보시스템 구축)·스마트공항팀(전기통신처 산하, 스마트공항 전략·통신)이 별도 존재. LX공사·수자원공사 등과 디지털트윈·공간정보 MOU 추진 중.</t>
         </is>
       </c>
     </row>
@@ -18295,7 +18296,7 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>경영지원부 (정보화·통합정보시스템 업무 담당)</t>
+          <t>경영지원부</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -18305,7 +18306,7 @@
       </c>
       <c r="H238" s="3" t="inlineStr">
         <is>
-          <t>경영지원부 (정보화·정보보안·개인정보보호 업무 겸임)</t>
+          <t>경영지원부</t>
         </is>
       </c>
       <c r="I238" s="3" t="inlineStr">
@@ -18340,7 +18341,7 @@
       </c>
       <c r="O238" s="3" t="inlineStr">
         <is>
-          <t>통합정보시스템(total.koreanpc.kr), 통합포털(koreanpc.kr) 운영. 2024년 대한체육회·국민체육진흥공단과 개인정보보호 협약. 별도 IT 전담조직 없이 경영지원부가 정보화 업무 수행. AI 전담조직 미확인.</t>
+          <t>IT담당배경: 경영지원부가 별도 IT 전담 조직 없이 정보화·정보보안·개인정보보호를 겸장함.&lt;br&gt;IT기능: 정보화, 정보보안, 개인정보보호, 통합정보시스템(total.koreanpc.kr)·통합포털(koreanpc.kr) 운영&lt;br&gt;기타: 2024년 대한체육회·국민체육진흥공단과 개인정보보호 협약 체결.</t>
         </is>
       </c>
     </row>
@@ -18520,17 +18521,17 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>운영지원실 (경영지원본부 산하) — 정보화·전산 업무 담당 추정</t>
+          <t>경영지원본부</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 단, IT 전담 실/팀은 별도 미존재</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>별도 IT 전담부서 없음 (운영지원실이 정보화·전산 업무 겸임 추정)</t>
+          <t>운영지원실</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr">
@@ -18565,7 +18566,7 @@
       </c>
       <c r="O241" s="3" t="inlineStr">
         <is>
-          <t>전시연구본부·경영지원본부 2본부 체계의 소규모 과학관. 별도 정보화 전담 실/팀 미확인. AI는 전담조직이 아닌 사업(농산어촌·디지털 취약계층 AI 문해력 확산, AI 탐구활동 지원사업) 형태로 추진. 디지털스마트시스템 구축 BPR/ISP 수행 이력(경영기획실 주관 추정).</t>
+          <t>IT담당배경: 소규모 과학관(현원 131명). 별도 정보화 전담 실/팀 없이 운영지원실이 정보화·전산 겸임 추정.&lt;br&gt;기타: AI 관련은 AI 문해력 확산·탐구활동 지원 등 교육사업 형태(전담 조직 없음). 디지털스마트시스템 구축 BPR/ISP 수행 이력.</t>
         </is>
       </c>
     </row>
@@ -18745,17 +18746,17 @@
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>사무처 경영지원부 (정보화·전산 업무 포함)</t>
+          <t>사무처</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 사무처 산하 부</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H244" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영지원부 내 정보화 담당, 별도 IT 전담부서 미확인)</t>
+          <t>경영지원부</t>
         </is>
       </c>
       <c r="I244" s="3" t="inlineStr">
@@ -18790,7 +18791,7 @@
       </c>
       <c r="O244" s="3" t="inlineStr">
         <is>
-          <t>조직도상 IT·정보화·정보보안 전담 부서 부재. 사무처(전략기획부·경영지원부·안전환경부·고객소통부·전시부·교육부·교류협력부) + 연구소(학술연구부·자료부) 구성. 전시 콘텐츠로 VR전시관·MR독립영상관·AI미디어로봇 운영하나 이를 전담하는 조직은 조직도상 없음(전시부 소관 추정).</t>
+          <t>IT담당배경: 사무처 경영지원부가 정보화·전산·공공데이터 업무를 겸장함. 별도 IT 전담 조직은 없음.&lt;br&gt;기타: VR전시관·MR독립영상관·AI미디어로봇 운영(전시부 소관 추정).</t>
         </is>
       </c>
     </row>
@@ -19195,7 +19196,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>디지털아카이브팀(학예본부 유물아카이브실 산하)</t>
+          <t>학예본부</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -19205,7 +19206,7 @@
       </c>
       <c r="H250" s="3" t="inlineStr">
         <is>
-          <t>디지털아카이브팀(디지털 뮤지엄·정보센터 운영), 기획조정실 기획재정팀·총무회계팀(정보화 행정 겸장 추정)</t>
+          <t>유물아카이브실(디지털아카이브팀)</t>
         </is>
       </c>
       <c r="I250" s="3" t="inlineStr">
@@ -19240,7 +19241,7 @@
       </c>
       <c r="O250" s="3" t="inlineStr">
         <is>
-          <t>2026년 공공기관 신규 지정. 조직은 관장 직속 윤리감사실 + 경영본부·학예본부·문화본부 3본부 체계. 별도 정보화 전담 본부/처/실 없음. 디지털아카이브팀이 디지털 뮤지엄·정보센터 운영(전시·유물 디지털화 중심). 2023년 업무계획에 '디지털 뮤지엄 시대 대응전략 마련' 과제 포함.</t>
+          <t>IT담당배경: 별도 정보화 전담 본부·처·실 없음. 유물아카이브실 산하 디지털아카이브팀이 디지털 뮤지엄·정보센터 운영(전시·유물 디지털화 중심)하는 가장 IT 인접 조직.&lt;br&gt;기타: 2026년 공공기관 신규 지정. 2023년 업무계획에 '디지털 뮤지엄 시대 대응전략' 과제 포함.</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19721,7 @@
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>보건의료정보기반본부 (기관 전체가 보건의료 정보화 전문기관)</t>
+          <t>보건의료정보기반본부</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -19730,7 +19731,7 @@
       </c>
       <c r="H257" s="3" t="inlineStr">
         <is>
-          <t>보건의료정보AX총괄단(보건의료정보운영총괄팀·보건의료정보AX지원팀), EMR인증사업단, 보건의료표준화사업단 / (정보보호) 경영기획본부 정보보호보안팀 / (사업) 보건의료정보사업본부: PHR사업단·진료정보교류사업단·공공의료정보화사업단·질병보건정보화사업단 / (데이터) 보건의료데이터진흥본부: 국가바이오빅데이터센터·데이터활용지원사업단</t>
+          <t>보건의료정보AX총괄단(보건의료정보운영총괄팀·보건의료정보AX지원팀), EMR인증사업단, 보건의료표준화사업단</t>
         </is>
       </c>
       <c r="I257" s="3" t="inlineStr">
@@ -19765,7 +19766,7 @@
       </c>
       <c r="O257" s="3" t="inlineStr">
         <is>
-          <t>기관 자체가 '보건의료 정보화 전문기관'(2019년 보건복지부 산하 설립). 조직 규모 1실 4본부 10부·단 17팀(공식 조직도 기준). '보건의료정보AX총괄단' 신설로 AI 전환(AX) 전담 단 조직 운영. EMR인증·보건의료표준화·진료정보교류·국가바이오빅데이터·PHR 등 대규모 보건의료 정보화 사업 수행. 2026년 '디지털 의료 혁신' 비전 추진. 의료AI 데이터 활용 바우처 지원사업 운영.</t>
+          <t>IT기능: 보건의료 정보화·운영(보건의료정보기반본부), AI 전환(보건의료정보AX총괄단), EMR인증, 보건의료표준화, 진료정보교류, PHR, 국가바이오빅데이터, 정보보호(경영기획본부 정보보호보안팀)&lt;br&gt;기타: 기관 전체가 보건의료 정보화 전문기관(2019 보건복지부 산하 설립). 보건의료정보사업본부(PHR사업단·진료정보교류사업단·공공의료정보화사업단·질병보건정보화사업단), 보건의료데이터진흥본부(국가바이오빅데이터센터·데이터활용지원사업단) 추가 존재. 의료AI 데이터 활용 바우처 지원사업 운영. 2026년 '디지털 의료 혁신' 비전 추진.</t>
         </is>
       </c>
     </row>
@@ -19945,17 +19946,17 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>정보화지원팀 (경영지원본부 산하)</t>
+          <t>경영지원본부</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>팀(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>단일 팀(하위부서 없음). 영화관입장권통합전산망(KOBIS) 등 정보시스템·전산·정보보안 운영</t>
+          <t>정보화지원팀</t>
         </is>
       </c>
       <c r="I260" s="3" t="inlineStr">
@@ -19990,7 +19991,7 @@
       </c>
       <c r="O260" s="3" t="inlineStr">
         <is>
-          <t>위원장-사무국장 체제 하 4본부(기획조정본부·경영지원본부·지원사업운영본부·산업기반조성본부) + 한국영화아카데미·영화정책연구원·공정환경조성센터. 정보화 조직은 경영지원본부 산하 '정보화지원팀'(팀 레벨)으로 본부·실 단위 IT 조직 없음. 영화관입장권통합전산망(KOBIS) 운영이 핵심 정보화 업무. 부산 소재(혁신도시 이전), 본사 추가 지방이전 추진 중(기획조정본부에 지방이전총괄 TF팀). AI는 영화정책연구원의 'AI 영화기술 현황과 전망' 등 연구·동향자료 차원.</t>
+          <t>IT기능: 영화관입장권통합전산망(KOBIS) 운영, 정보시스템 운영, 전산, 정보보안&lt;br&gt;기타: 위원장-사무국장 체제 하 4본부(기획조정본부·경영지원본부·지원사업운영본부·산업기반조성본부) + 한국영화아카데미·영화정책연구원·공정환경조성센터. 부산 소재(혁신도시 이전), 본사 추가 지방이전 추진 중. AI는 영화정책연구원의 'AI 영화기술 현황과 전망' 등 연구·동향자료 차원.</t>
         </is>
       </c>
     </row>
@@ -20095,17 +20096,17 @@
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
-          <t>정보화전략팀 (경영관리본부 산하)</t>
+          <t>경영관리본부</t>
         </is>
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>팀 (본부 산하 부 레벨이 아닌 본부 직속 팀)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H262" s="3" t="inlineStr">
         <is>
-          <t>해당없음 (정보화전략팀 단일 팀)</t>
+          <t>대외협력부(대외협력팀·정보화전략팀)</t>
         </is>
       </c>
       <c r="I262" s="3" t="inlineStr">
@@ -20140,7 +20141,7 @@
       </c>
       <c r="O262" s="3" t="inlineStr">
         <is>
-          <t>본부 체제(경영관리본부·기증관리본부) + 감사팀 + 진단검사의학과의원(KODA LAB). 정보화전략팀이 정보화 중장기계획·정보화사업·개인정보보호체계·정보보안 관리체계·정보통신망·공공데이터를 모두 담당하는 단일 IT조직. 경영관리본부 산하(혁신기획부·운영지원부·대외협력부와 병렬). AI 전담조직 단서 없음.</t>
+          <t>본부 체제(경영관리본부·기증관리본부) + 감사팀 + 진단검사의학과의원(KODA LAB). 정보화전략팀이 정보화 중장기계획·정보화사업·개인정보보호체계·정보보안 관리체계·정보통신망·공공데이터를 모두 담당하는 단일 IT조직. 경영관리본부 산하 대외협력부 소속(대외협력팀과 병렬). AI 전담조직 단서 없음.</t>
         </is>
       </c>
     </row>
@@ -20170,7 +20171,7 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>디지털홍보처 (사업관리본부 산하) — 정보화·디지털·개인정보보호 소관. 구 'ICT추진단'이 개편된 것으로 판단</t>
+          <t>사업관리본부</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
@@ -20180,7 +20181,7 @@
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (디지털홍보처 산하 팀 세부 미확인 — 홍보팀 등 포함 추정). 직제상 정보화·디지털·홍보·개인정보보호를 묶은 처</t>
+          <t>디지털홍보처</t>
         </is>
       </c>
       <c r="I263" s="3" t="inlineStr">
@@ -20215,7 +20216,7 @@
       </c>
       <c r="O263" s="3" t="inlineStr">
         <is>
-          <t>사장 직속 안전혁신실·감사실, 그 아래 기획본부(기획조정실·인재경영처·재무관리처)·사업관리본부(사업관리처·디지털홍보처)·개발본부(사업계획처·관광산단처·개발사업처)·미래사업본부(에너지사업처·투자사업처) 4본부 체제. 정보화·디지털·개인정보보호는 사업관리본부 산하 '디지털홍보처'가 담당. 과거 'ICT추진단'(2021 단장 여하은)이 차세대 통합행정업무·중장기 정보화전략(ISP) 등 정보화사업을 수행했으나, 현 조직도에는 ICT추진단이 없고 디지털홍보처로 정보화 기능이 통합·개편된 것으로 판단. AI 기반 개인정보 유·노출 탐지시스템 도입(3년 연속 개인정보 관리 우수기관). 2019년 부→처 격상 등 조직개편 이력.</t>
+          <t>IT담당배경: '디지털홍보처'는 정보화·디지털·홍보·개인정보보호를 통합 담당하는 처 단위 조직임.&lt;br&gt;조직이력: ICT추진단(2021)→디지털홍보처로 개편. 2019년 부→처 격상.&lt;br&gt;기타: AI 기반 개인정보 유·노출 탐지시스템 도입. 3년 연속 개인정보 관리 우수기관.</t>
         </is>
       </c>
     </row>
@@ -20320,7 +20321,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>인프라운영실 (경영전략본부 산하)</t>
+          <t>경영전략본부</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -20330,7 +20331,7 @@
       </c>
       <c r="H265" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (인프라운영실 단일)</t>
+          <t>인프라운영실</t>
         </is>
       </c>
       <c r="I265" s="3" t="inlineStr">
@@ -20365,7 +20366,7 @@
       </c>
       <c r="O265" s="3" t="inlineStr">
         <is>
-          <t>3본부(경영전략본부·인재개발본부·인재교육본부) 체제. 경영전략본부 산하 경영기획실·인사총무실·인프라운영실 중 인프라운영실이 IT 담당(중장기 정보화 전략계획 수립·디지털 전환 추진, 정보보안 관리·대외 정보보안 감사 대응, 전산장비 구축·운영, 정보화 클라우드 시스템). AI 전담조직은 없으나 AI 기반 디지털전환(DX) 적극 추진, DT 교육과정 운영.</t>
+          <t>IT기능: 중장기 정보화 전략계획 수립·디지털전환 추진, 정보보안 관리·감사 대응, 전산장비 구축·운영, 정보화 클라우드 시스템&lt;br&gt;기타: AI 기반 디지털전환(DX) 적극 추진, DT 교육과정 운영.</t>
         </is>
       </c>
     </row>
@@ -20395,7 +20396,7 @@
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>운영관리실 (산하 인사총무팀이 전산·정보 업무 담당)</t>
+          <t>운영관리실</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -20405,7 +20406,7 @@
       </c>
       <c r="H266" s="3" t="inlineStr">
         <is>
-          <t>인사총무팀 (전산·정보 / 전산인프라 구축·운영 / 보안 업무 겸장)</t>
+          <t>인사총무팀</t>
         </is>
       </c>
       <c r="I266" s="3" t="inlineStr">
@@ -20440,7 +20441,7 @@
       </c>
       <c r="O266" s="3" t="inlineStr">
         <is>
-          <t>연구정책실(한일연구소·한중연구소 등)·독도실·교육홍보실(교육연수팀·콘텐츠팀)·운영관리실(인사총무팀·회계팀) 체제. 정보화·전산 전담 조직이 별도로 없으며 운영관리실 인사총무팀이 '전산·정보 관련 업무', '전산인프라 구축 및 운영', '보안 업무'를 총무 업무와 함께 겸장. 2018년 연구소 3개→5개 조직개편 이력.</t>
+          <t>IT담당배경: 운영관리실 인사총무팀이 채용·인사·복무 등 총무 업무와 함께 전산·정보·전산인프라·보안 업무를 겸장함.&lt;br&gt;IT기능: 전산·정보 관련 업무, 전산인프라 구축·운영, 보안 업무&lt;br&gt;조직이력: 2018년 연구소 3개→5개 조직개편</t>
         </is>
       </c>
     </row>
@@ -20545,7 +20546,7 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부 (정보화·전산 전담 부서 없음 — 본부 내 관리기능에 포함, 전산은 공무직 직무로 운영)</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
@@ -20555,7 +20556,7 @@
       </c>
       <c r="H268" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부 산하 부서: 기획예산·인사(인사부)·대외협력·재무회계·시설운영 (정보화/전산 전담팀 없음, '전산'은 공무직 직무)</t>
+          <t>해당없음(전산은 경영지원실 내 공무직 담당)</t>
         </is>
       </c>
       <c r="I268" s="3" t="inlineStr">
@@ -20585,12 +20586,12 @@
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>중(공식 채용 직무기술서·입찰공고로 본부/부서 구성 및 전산 직무 확인 2출처, 단 상세 조직도는 JS 렌더링으로 미표출 / 개인정보처리방침은 타 기관 템플릿 차용으로 CISO 확정 불가)</t>
+          <t>중(공식 홈페이지 조직도에서 현행 2본부 구조 확인, 단 JS 렌더링 부분 있어 전산 전담 부서 직접 확인 미흡 / CISO 확정 불가)</t>
         </is>
       </c>
       <c r="O268" s="3" t="inlineStr">
         <is>
-          <t>2024.12.11 개관한 신설 기관(해수부 산하 기타공공기관). 경영기획본부·학예연구본부 2본부 체계이며 본부 산하에 '부' 단위(예: 인사부) 구성. 채용 직무에 '전산'(공무직, 전산 기능사 이상)이 있어 IT 운영은 경영기획본부 내 전산 담당이 수행. 2026.4월 '아카이브 정보화설계 컨설팅 용역' 입찰 진행 — 정보화 사업은 추진 중이나 전담 정보화 조직은 신설 안 됨. '디지털박물관'(디지털 실감영상실·VR 전시)은 학예연구본부 산하 전시 기능. AI는 교육프로그램('AI 북극 탐험대' 등) 수준으로 AI 전담조직 없음.</t>
+          <t>IT담당배경: 별도 IT 전담 부서 없이 경영지원실 내 전산 공무직이 IT 업무 수행. 디지털미디어부(전시교육실 산하)는 전시 디지털 콘텐츠 담당으로 IT 운영 부서 아님.&lt;br&gt;기타: 2024.12 개관 신설기관. 2026.4월 아카이브 정보화설계 컨설팅 용역 입찰. AI는 교육프로그램('AI 북극 탐험대' 등) 수준.</t>
         </is>
       </c>
     </row>
@@ -20920,7 +20921,7 @@
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>디지털정보팀 (경영지원실 산하)</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
@@ -20930,7 +20931,7 @@
       </c>
       <c r="H273" s="3" t="inlineStr">
         <is>
-          <t>디지털정보팀 (경영지원실: 인사팀, 재무회계팀, 운영지원팀, 디지털정보팀)</t>
+          <t>디지털정보팀</t>
         </is>
       </c>
       <c r="I273" s="3" t="inlineStr">
@@ -20940,7 +20941,7 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
-          <t>공간AI·빅데이터본부 (하위: 인공지능·빅데이터 연구 등)</t>
+          <t>공간AI·빅데이터본부</t>
         </is>
       </c>
       <c r="K273" s="3" t="inlineStr">
@@ -21204,11 +21205,11 @@
         <v>30</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -21246,19 +21247,19 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -21272,11 +21273,11 @@
         <v>184</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -21288,11 +21289,11 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.3%</t>
         </is>
       </c>
     </row>
@@ -21306,27 +21307,27 @@
         <v>274</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -21368,11 +21369,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -21398,11 +21399,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>23.0%</t>
         </is>
       </c>
     </row>
@@ -21413,11 +21414,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -21459,11 +21460,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.4%</t>
         </is>
       </c>
     </row>
@@ -21474,11 +21475,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -21535,11 +21536,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>83.6%</t>
         </is>
       </c>
     </row>
@@ -21550,11 +21551,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>16.4%</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -21732,7 +21733,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>정보관리국 (혈액관리본부 산하) — 본사 차원 별도 IT 본부·실은 미확인</t>
+          <t>혈액관리본부</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -21772,7 +21773,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>확인불가(보안) — 군 연구기관 보안상 정보화 직제 비공개</t>
+          <t>확인불가(보안)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -21864,47 +21865,47 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>한국전력기술주식회사</t>
+          <t>한국가스안전공사</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>공기업</t>
+          <t>준정부</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>공기업(준시장형)</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2098</v>
+        <v>1775.2</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 1출처 + 공공데이터포털·보도 교차)</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>IT최상위 확인불가</t>
+          <t>AI전담 확인불가</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전사 IT기획·정보보안 전담 처 명칭 미확정) — AX/디지털 전환은 AX기획팀(전략기획본부 계열) 및 디지털솔루션연구소가 주도</t>
+          <t>디지털혁신처 (기획관리이사 산하)</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>확인불가</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>한국가스안전공사</t>
+          <t>한국관광공사</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -21918,11 +21919,11 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1775.2</v>
+        <v>701.5</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>상(공식 1출처 + 공공데이터포털·보도 교차)</t>
+          <t>상(공식 2출처)</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -21932,7 +21933,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신처 (기획관리이사 산하)</t>
+          <t>관광디지털본부</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -21944,25 +21945,25 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>한국관광공사</t>
+          <t>(재)한국우편사업진흥원</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>준정부</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>701.5</v>
+        <v>406.9</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상 (공식 홈페이지 조직구성도 확인)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -21972,37 +21973,37 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>관광디지털본부</t>
+          <t>경영전략실</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (홈페이지 조직도상 AI 전담 부서 미확인)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>(재)한국우편사업진흥원</t>
+          <t>한국법무보호복지공단</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>준정부</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>406.9</v>
+        <v>356</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>상 (공식 홈페이지 조직구성도 확인)</t>
+          <t>상(공식 조직도 + 개인정보처리방침 2출처로 정보관리팀·CPO=보호정책부장 확인)</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -22012,37 +22013,37 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>경영전략실 (산하 경영정보팀 정보화사업 총괄, 정보보안센터)</t>
+          <t>정보관리팀 (보호정책부 산하)</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (홈페이지 조직도상 AI 전담 부서 미확인)</t>
+          <t>확인불가 (조직도상 AI 전담조직 미확인. 미래전략부는 정책혁신·기획홍보·대외협력 중심으로 AI 전담 아님)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>한국법무보호복지공단</t>
+          <t>한국교육과정평가원</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>준정부</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 개인정보처리방침 2출처로 정보관리팀·CPO=보호정책부장 확인)</t>
+          <t>상(공식 홈페이지 조직도 + 개인정보처리방침 2출처로 정보관리본부·정보보안부·CPO 확인)</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -22052,37 +22053,37 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>정보관리팀 (보호정책부 산하)</t>
+          <t>정보관리본부</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (조직도상 AI 전담조직 미확인. 미래전략부는 정책혁신·기획홍보·대외협력 중심으로 AI 전담 아님)</t>
+          <t>확인불가 (내부 IT 직제상 'AI' 명칭 전담조직은 없음. 단, 기획조정본부 산하 '교육데이터센터', 미래학교교육연구본부 산하 '디지털·미래교육연구실'이 교육데이터·디지털교육 연구를 수행. AI기반 학력진단시스템 구축 등 AI 사업 활발)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>한국교육과정평가원</t>
+          <t>한국재정정보원</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>준정부</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>339</v>
+        <v>316.8</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 개인정보처리방침 2출처로 정보관리본부·정보보안부·CPO 확인)</t>
+          <t>상(공식 조직도)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -22092,37 +22093,37 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>정보관리본부</t>
+          <t>재정시스템운영본부 / 보조금시스템운영본부 (시스템 운영 본부)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (내부 IT 직제상 'AI' 명칭 전담조직은 없음. 단, 기획조정본부 산하 '교육데이터센터', 미래학교교육연구본부 산하 '디지털·미래교육연구실'이 교육데이터·디지털교육 연구를 수행. AI기반 학력진단시스템 구축 등 AI 사업 활발)</t>
+          <t>확인불가</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>한국재정정보원</t>
+          <t>한국해양수산연수원</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>준정부</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>316.8</v>
+        <v>313</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도)</t>
+          <t>상(공식 조직도 + 개인정보처리방침 2출처로 지능정보화팀·CPO=경영본부장 확인)</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -22132,19 +22133,19 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>재정시스템운영본부 / 보조금시스템운영본부 (시스템 운영 본부)</t>
+          <t>지능정보화팀 (경영본부 산하)</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (별도 'AI' 명칭 전담조직 미확인. 정보화는 경영본부 산하 '지능정보화팀'이 담당하나 일반 IT 기능으로 판단)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>한국해양수산연수원</t>
+          <t>선박해양플랜트연구소</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -22158,11 +22159,11 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 개인정보처리방침 2출처로 지능정보화팀·CPO=경영본부장 확인)</t>
+          <t>상(공식 조직도 + 인사 보도 교차)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -22172,19 +22173,19 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>지능정보화팀 (경영본부 산하)</t>
+          <t>해양공공디지털연구본부, 경영지원본부</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 'AI' 명칭 전담조직 미확인. 정보화는 경영본부 산하 '지능정보화팀'이 담당하나 일반 IT 기능으로 판단)</t>
+          <t>확인불가 (별도 AI 전담조직 미확인. 해양공공디지털연구본부가 디지털·AI 연구 수행 추정)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>선박해양플랜트연구소</t>
+          <t>중소기업기술정보진흥원</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -22198,11 +22199,11 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>312</v>
+        <v>271.3</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 인사 보도 교차)</t>
+          <t>상(공식 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -22212,19 +22213,19 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>해양공공디지털연구본부 (연구본부 레벨) / 정보보안실 (경영지원본부 행정부 산하)</t>
+          <t>지능정보화실</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 AI 전담조직 미확인. 해양공공디지털연구본부가 디지털·AI 연구 수행 추정)</t>
+          <t>확인불가 (별도 AI 전담조직 없음 / '지능정보화실'이 지능정보·정보화 기능 총괄)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>중소기업기술정보진흥원</t>
+          <t>한국청소년상담복지개발원</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -22238,11 +22239,11 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>271.3</v>
+        <v>239.5</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 직접 확인)</t>
+          <t>상(공식 조직 명칭 + 개인정보처리방침(공식) 교차 확인)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -22252,19 +22253,19 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>지능정보화실</t>
+          <t>정보화전략부</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 AI 전담조직 없음 / '지능정보화실'이 지능정보·정보화 기능 총괄)</t>
+          <t>확인불가</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>한국청소년상담복지개발원</t>
+          <t>한국보건복지인재원</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -22278,11 +22279,11 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>239.5</v>
+        <v>238.6</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직 명칭 + 개인정보처리방침(공식) 교차 확인)</t>
+          <t>상(공식 개인정보처리방침 + 공공데이터포털 담당부서 표기 + 알리오 교차 확인)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -22292,7 +22293,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부</t>
+          <t>정보화전략부 (경영전략본부 산하)</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -22304,7 +22305,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>한국보건복지인재원</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -22318,11 +22319,11 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>238.6</v>
+        <v>232.5</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침 + 공공데이터포털 담당부서 표기 + 알리오 교차 확인)</t>
+          <t>상(공식 개인정보처리방침 + 알리오 + 보도 교차 확인)</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -22332,7 +22333,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부 (경영전략본부 산하)</t>
+          <t>연금사업본부</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -22344,7 +22345,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
+          <t>한국환경보전원</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -22358,11 +22359,11 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>232.5</v>
+        <v>225</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침 + 알리오 + 보도 교차 확인)</t>
+          <t>상(공식 조직도(텍스트 확인) + 공식 개인정보처리방침 교차 확인)</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -22372,7 +22373,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>정보지원실·정보보안센터 (연금사업본부 산하)</t>
+          <t>인재운영처 (경영기획본부 산하) — 정보화·정보보안 기능 보유</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -22384,7 +22385,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -22398,11 +22399,11 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>225</v>
+        <v>202.3</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도(텍스트 확인) + 공식 개인정보처리방침 교차 확인)</t>
+          <t>상(공식 개인정보처리방침(2025.7.10) + 공시 부서별 업무추진계획 + 보도 교차 확인)</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -22412,7 +22413,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>인재운영처 (경영기획본부 산하) — 정보화·정보보안 기능 보유</t>
+          <t>융합기술센터 / 데이터정보화팀</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -22424,7 +22425,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>과학기술정책연구원</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -22438,11 +22439,11 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>202.3</v>
+        <v>152</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침(2025.7.10) + 공시 부서별 업무추진계획 + 보도 교차 확인)</t>
+          <t>상(공식 홈페이지 개인정보처리방침으로 경영지원실·디지털전환팀 소속·CPO 확인 + 2026 개편 보도 다수 교차확인)</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -22452,19 +22453,19 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>융합기술센터(방송기술·시스템) / 데이터정보화팀(데이터·정보화·개인정보)</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (전담 AI 조직 미확인 — 디지털·AI 전환 대응은 디지털전환팀이 수행)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>과학기술정책연구원</t>
+          <t>한국기상산업기술원</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -22478,11 +22479,11 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>152</v>
+        <v>151.8</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 개인정보처리방침으로 경영지원실·디지털전환팀 소속·CPO 확인 + 2026 개편 보도 다수 교차확인)</t>
+          <t>상(공식 홈페이지 조직도 + 공공데이터포털 기관조직 데이터 교차확인)</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -22492,19 +22493,19 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (산하 디지털전환팀(DAX팀)이 지식정보·전산·디지털전환 담당)</t>
+          <t>경영지원실 (경영기획본부 소속) — 정보화·정보보안 기능 수행. 별도 IT 전담 본부·처 없음</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담 AI 조직 미확인 — 디지털·AI 전환 대응은 디지털전환팀이 수행)</t>
+          <t>확인불가 (전담 조직 미확인 — 데이터/AI 업무는 산업육성실 기상기후데이터·빅데이터 사업에서 수행)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>한국기상산업기술원</t>
+          <t>한국저작권보호원</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -22518,11 +22519,11 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>151.8</v>
+        <v>104.8</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 공공데이터포털 기관조직 데이터 교차확인)</t>
+          <t>상(공식 홈페이지 조직도 + 공공데이터포털 관리부서 표기 교차확인)</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -22532,50 +22533,10 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (경영기획본부 소속) — 정보화·정보보안 기능 수행. 별도 IT 전담 본부·처 없음</t>
+          <t>정보기술부</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (전담 조직 미확인 — 데이터/AI 업무는 산업육성실 기상기후데이터·빅데이터 사업에서 수행)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>한국저작권보호원</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>104.8</v>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>상(공식 홈페이지 조직도 + 공공데이터포털 관리부서 표기 교차확인)</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>정보기술부</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>확인불가 (별도 AI 전담조직 식별 안 됨)</t>
         </is>

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -2321,17 +2321,17 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>정보전략실 (기획혁신본부 산하)</t>
+          <t>기획혁신본부</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>정보운영처, 정보보안처 (정보전략실 산하) / 별도 공간정보본부 내 디지털SOC처·플랫폼사업처</t>
+          <t>정보전략실(정보운영처·정보보안처) / 별도 공간정보본부 내 디지털SOC처·플랫폼사업처</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -3596,17 +3596,17 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>스마트공항추진실 (전략기획본부 산하)</t>
+          <t>전략기획본부</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>스마트기획부·데이터융합부·스마트공항부(스마트공항추진실 산하) (※무인항공기술부는 건설기술본부→항행시설실 산하 — 스마트공항추진실과 별개)</t>
+          <t>스마트공항추진실(스마트기획부·데이터융합부·스마트공항부) (※무인항공기술부는 건설기술본부→항행시설실 산하 — 스마트공항추진실과 별개)</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>AI디지털실 (기획본부 산하)</t>
+          <t>기획본부</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>디지털기획처, AI혁신처, 정보보안처, 자동차정보처</t>
+          <t>AI디지털실(디지털기획처·AI혁신처·정보보안처·자동차정보처)</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
@@ -4946,17 +4946,17 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신처 (기획관리이사 산하)</t>
+          <t>기획관리이사</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부/이사 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>디지털정책부, 정보운영부(공공데이터운영팀)</t>
+          <t>디지털혁신처(디지털정책부·정보운영부[공공데이터운영팀])</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
@@ -6896,17 +6896,17 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신처 (기획본부 산하)</t>
+          <t>기획본부</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신처 산하: 정보보안기획부, 데이터사업부, 디지털AI운영부</t>
+          <t>디지털혁신처(정보보안기획부·데이터사업부·디지털AI운영부)</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -7346,17 +7346,17 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>AI혁신처 (정보화·디지털·AI·정보보안·공공데이터 총괄)</t>
+          <t>경영관리본부</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>처·실 (경영관리본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>AI혁신처 산하: 정보시스템팀(정보화사업·시스템 운영, 033-736-5256), 디지털AI전략팀(033-736-5994) 등</t>
+          <t>AI혁신처(정보시스템팀·디지털AI전략팀) — 정보화·디지털·AI·정보보안·공공데이터 총괄</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
@@ -8321,17 +8321,17 @@
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>인공지능전환실 (경영전략본부 산하)</t>
+          <t>경영전략본부</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>인공지능전환·정보화팀, 데이터팀, 정보보안팀</t>
+          <t>인공지능전환실(인공지능전환·정보화팀·데이터팀·정보보안팀)</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>AI교육혁신본부 / 정보보호본부 (각각 본부 레벨, 원장 직속)</t>
+          <t>정보보호본부</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>(AI교육혁신본부) AI플랫폼부, AI학습데이터부, AI교육서비스부 / (정보보호본부) 개인정보보호부, 정보보안부, 정보자원관리부, 시스템품질관리부 / (디지털교육본부) 디지털교육기획부, 교수학습지원부, 디지털시민교육부, 고등평생교육부</t>
+          <t>개인정보보호부, 정보보안부, 정보자원관리부, 시스템품질관리부</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -12296,17 +12296,17 @@
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>정보화지원실</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 경영기획본부 산하 실 단위</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>정보화지원실 단일 실 단위 (하위 팀 미편제). 경영기획본부 산하 6개 실(기획조정실·인재경영실·재정관리실·총무계약실·시설운영실·정보화지원실) 중 하나로 병렬 편제</t>
+          <t>정보화지원실 (경영기획본부 산하 6개 실 중 하나: 기획조정실·인재경영실·재정관리실·총무계약실·시설운영실·정보화지원실. 하위 팀 미편제)</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
@@ -14396,17 +14396,17 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>정보화실(경영지원본부 산하)</t>
+          <t>경영지원본부</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>정보화실(단일 실)</t>
+          <t>정보화실</t>
         </is>
       </c>
       <c r="I186" s="3" t="inlineStr">
@@ -16271,17 +16271,17 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부</t>
+          <t>사업지원실</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>부 (사업지원실 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부, 정보보호팀 (정보화전략부 산하)</t>
+          <t>정보화전략부(정보보호팀)</t>
         </is>
       </c>
       <c r="I211" s="3" t="inlineStr">
@@ -17021,17 +17021,17 @@
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (경영기획본부 소속) — 정보화·정보보안 기능 수행. 별도 IT 전담 본부·처 없음</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>실(본부 산하) — IT 기능 한정 시 팀·담당 수준</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H221" s="3" t="inlineStr">
         <is>
-          <t>경영지원실(정보화 사업 관리·정보보안 관리 담당)</t>
+          <t>경영지원실 (정보화 사업 관리·정보보안 관리 담당. 별도 IT 전담 처는 없음)</t>
         </is>
       </c>
       <c r="I221" s="3" t="inlineStr">
@@ -17996,17 +17996,17 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>ICT기획부 (경영지원실 산하, 기획협력이사 소관)</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>부(실 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>해당없음(부 단위). ICT기획부가 정보시스템 통합유지관리·인프라·네트워크·공공데이터·정보보안 전략·사이버안전센터 운영을 통합 담당</t>
+          <t>ICT기획부(정보시스템 통합유지관리·인프라·네트워크·공공데이터·정보보안 전략·사이버안전센터 운영)</t>
         </is>
       </c>
       <c r="I234" s="3" t="inlineStr">
@@ -18071,17 +18071,17 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>정보전산팀 (경영지원실 산하)</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>팀(실 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>해당없음(팀 단위). 정보전산팀이 전산장비·소프트웨어 운영, 정보보안, 개인정보보호, 홈페이지, 공공데이터·데이터기반행정을 통합 담당</t>
+          <t>정보전산팀(전산장비·소프트웨어 운영, 정보보안, 개인정보보호, 홈페이지, 공공데이터·데이터기반행정 통합 담당)</t>
         </is>
       </c>
       <c r="I235" s="3" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>고전정보센터 (경영지원본부 산하)</t>
+          <t>경영지원본부</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 센터 단위</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H238" s="3" t="inlineStr">
@@ -21130,11 +21130,11 @@
         <v>29</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -21164,11 +21164,11 @@
         <v>60</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -21198,11 +21198,11 @@
         <v>184</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -21232,11 +21232,11 @@
         <v>273</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -21294,11 +21294,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>26.4%</t>
         </is>
       </c>
     </row>
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>47.3%</t>
         </is>
       </c>
     </row>
@@ -21324,11 +21324,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>20.9%</t>
         </is>
       </c>
     </row>
@@ -21818,7 +21818,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신처 (기획관리이사 산하)</t>
+          <t>기획관리이사</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (경영기획본부 소속) — 정보화·정보보안 기능 수행. 별도 IT 전담 본부·처 없음</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -3371,17 +3371,17 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>디지털융합처 → AI디지털단(개편 추진)</t>
+          <t>경영혁신본부</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>디지털전환부, ICT인프라부 등 (개편 후 산하 AI부 신설 예정)</t>
+          <t>AI디지털혁신단</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>디지털융합처 디지털전환부 / 개편 후 AI디지털단 산하 'AI부' / CEO급 거버넌스 'AI혁신위원회'</t>
+          <t>AI디지털혁신단(경영혁신본부 산하) / CEO급 거버넌스 'AI혁신위원회'</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>부(처 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>확인불가(경영혁신본부 또는 디지털융합처장 추정)</t>
+          <t>확인불가(경영혁신본부장 추정)</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (2025 한국경영대상 CEO-정보보안부문 수상 — 보안경영 강조)</t>
+          <t>정보보안실(경영혁신본부 산하)</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>상(공식 1출처 + 보도 다수)</t>
+          <t>상(공식 조직도 전체 트리 브라우저 직접 확인)</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>중(공식 조직도 직접 확인, IT 담당 세부조직 미표기)</t>
+          <t>상(공식 조직도 전체 트리 직접 확인 — IT/디지털 전담 부서 부재를 확정)</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
@@ -6521,47 +6521,47 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>IT기획·운영 처 체제 — ICT기획처(IT기획)와 ICT운영처(IT운영, 현 '디지털운영처'로 통용) 2처 병립</t>
+          <t>경영전략본부</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>처·실 (본부 산하) — 과거 'ICT추진실'(실급)을 2024년 ICT기획처·ICT운영처 2처로 분할</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>ICT기획처(IT기획·정보화전략), 디지털운영처(=ICT운영처; 시스템 구축·운영, 안심전세App 등 모바일보증시스템), 디지털혁신추진단TF</t>
+          <t>AX기획처, 디지털운영처</t>
         </is>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>없음 (전담조직 미확인 — AI는 PoC·업무 적용 단계)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>AX기획처(경영전략본부 산하)</t>
         </is>
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (ICT기획처 소관 임원 추정)</t>
+          <t>확인불가 (경영전략본부장 추정)</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보호·개인정보보호 별도 운영 — 개인정보 관리수준 4년 연속 최고등급) — 전담 CISO 직제 미확인</t>
+          <t>정보보안처 (사장 직속 전담조직)</t>
         </is>
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>중(공식·언론 복수 출처로 처 체제 확인, 단 본부 소속·CISO 직제는 미확정)</t>
+          <t>상(공식 조직도 전체 트리 브라우저 직접 확인)</t>
         </is>
       </c>
       <c r="O81" s="3" t="inlineStr">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
-          <t>중 (공식 조직 구성 페이지 1출처 직접 확인)</t>
+          <t>상 (공식 조직도 전체 트리 브라우저 직접 재확인)</t>
         </is>
       </c>
       <c r="O104" s="3" t="inlineStr">
@@ -16046,17 +16046,17 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>정보화지원부</t>
+          <t>전략기획실</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>팀·부 (본부 산하, 처·실급 별도 정보화 본부 없음)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>정보화지원부 (그 외 별도 IT 하위팀 확인불가)</t>
+          <t>정보화지원부(정보보호팀)</t>
         </is>
       </c>
       <c r="I208" s="3" t="inlineStr">
@@ -16066,12 +16066,12 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>디지털인재양성센터 (AI·디지털 인재양성 전담, 사업 성격)</t>
+          <t>AI인재양성본부(AI인재기획실·교과서검인정팀·과학·수학교육실·AI·융합교육실)</t>
         </is>
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>센터 (본부 산하, 2팀 1TF 규모)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr">
@@ -16086,7 +16086,7 @@
       </c>
       <c r="N208" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 조직도 전체 트리 브라우저 직접 확인)</t>
         </is>
       </c>
       <c r="O208" s="3" t="inlineStr">
@@ -21130,27 +21130,27 @@
         <v>29</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -21232,27 +21232,27 @@
         <v>273</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
@@ -21294,11 +21294,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.1%</t>
         </is>
       </c>
     </row>
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.9%</t>
         </is>
       </c>
     </row>
@@ -21400,11 +21400,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.4%</t>
         </is>
       </c>
     </row>
@@ -21461,11 +21461,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>85.0%</t>
         </is>
       </c>
     </row>
@@ -21476,11 +21476,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -896,17 +896,17 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>디지털그룹 / IT그룹(IT운영본부·IT개발본부)</t>
+          <t>AX혁신부문</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>본부(그룹은 부행장급, 본부는 그 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>(IT그룹) IT운영본부, IT개발본부, IT내부통제부, IT디지털개발부, (디지털그룹) 디지털추진팀 등 (확인 범위 내)</t>
+          <t>IT그룹(IT기획부·IT아키텍처부·IT내부통제부·IT운영본부[IT시스템운영부]·IT개발본부[IT금융개발부·IT디지털개발부])</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>데이터본부(2024년 신설, AI 신기술 도입·데이터 분석/활용 총괄), 빅데이터센터 내 'AI&amp;Tech'팀, AI 허브 플랫폼 운영</t>
+          <t>AX전략그룹(AX디지털전략부·AX디지털추진부·AX데이터혁신부·채널기획부·IBK고객센터)</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>본부(데이터본부) / 센터 산하 팀(AI&amp;Tech)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>디지털그룹장(부행장) — 디지털·IT 총괄 (CIO 역할 추정)</t>
+          <t>확인불가 (AX혁신부문 담당 임원 추정)</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>정보보호최고책임자(CISO) 별도 발탁·임명 (2024년 인사에서 CISO 직책 명시)</t>
+          <t>정보보호최고책임자(정보보호총괄부·정보보호운영부)</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1차 출처 미확정, 다수 보도자료 교차)</t>
+          <t>상(공식 조직도 원문 직접 확인)</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>2024년 상반기 데이터본부 신설(AI·데이터 강화), 하반기 IT·디지털 조직 보강. 자체 AI 'IBK GPT' 개발 추진, AI 허브 플랫폼(2024.3) 도입. IT자회사 IBK시스템 보유.</t>
+          <t>15그룹 1연구소 4본부 1단 2센터 75부(실 포함) 체계. 기업성장부문·고객가치부문·AX혁신부문 3대 부문 편제, AX혁신부문 산하에 AX전략그룹과 IT그룹이 병립. 리스크관리그룹도 AX혁신부문 소속. 자체 AI 'IBK GPT' 개발 추진, AI 허브 플랫폼 도입.</t>
         </is>
       </c>
     </row>
@@ -14021,12 +14021,12 @@
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>경영지원실(정보화기획팀 소관)</t>
+          <t>기획조정실</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>팀 (경영지원실 산하 정보화기획팀)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H181" s="3" t="inlineStr">
@@ -21214,11 +21214,11 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.9%</t>
         </is>
       </c>
     </row>
@@ -21248,11 +21248,11 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -21324,11 +21324,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.5%</t>
         </is>
       </c>
     </row>
@@ -21461,11 +21461,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>85.3%</t>
         </is>
       </c>
     </row>
@@ -21476,11 +21476,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.7%</t>
         </is>
       </c>
     </row>

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -1421,17 +1421,17 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>AI디지털처 (舊 디지털혁신처)</t>
+          <t>기획전략본부</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>처·실</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>AI디지털기획부, 플랫폼운영부</t>
+          <t>AI디지털처(AI디지털기획부·플랫폼운영부)</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1441,27 +1441,27 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>AI디지털처</t>
+          <t>AI디지털처 (舊 디지털혁신처, 기획전략본부 산하)</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>처·실 (AI를 처 명칭에 반영한 총괄 전담 조직)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (AI디지털처장 소관, 상위 본부 미확정)</t>
+          <t>확인불가 (기획전략본부장 추정)</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>정보보안센터 (기획전략본부 산하)</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 조직도 전체 트리 사용자 제공 화면 확인)</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -21164,11 +21164,11 @@
         <v>60</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -21232,11 +21232,11 @@
         <v>273</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -21294,11 +21294,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>27.5%</t>
         </is>
       </c>
     </row>
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.5%</t>
         </is>
       </c>
     </row>

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>정보지원부 (기획조정실 산하 / 기획이사 소속)</t>
+          <t>기획조정실</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>팀 (부 단위 — 별도 IT 본부·실 없음)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>정보지원부 단일 (기획조정실: 경영전략부, 조직예산부, 성과관리부, ESG경영부, 정보지원부)</t>
+          <t>정보지원부 (기획조정실 내 경영전략부·조직예산부·성과관리부·ESG경영부와 병렬)</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>정보보안처 (기획본부 산하)</t>
+          <t>기획본부</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>ICT기획부, 디지털보안부(사이버보안실)</t>
+          <t>정보보안처(ICT기획부·디지털보안부[사이버보안실])</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>정보기술처 (고객서비스본부 산하) / 전략·AX는 미래전략본부 AX추진단</t>
+          <t>고객서비스본부</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>정보기술처, 정보보안센터, 방송센터 (고객서비스본부 산하)</t>
+          <t>정보기술처, 정보보안센터, 방송센터</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
@@ -9071,17 +9071,17 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부 산하 AI디지털심화팀 (내부 정보화·디지털·AI 혁신 기획). 사업성 디지털 본부로 디지털융합본부 별도 존재</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>본부(사업)/팀(내부 정보화)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>(경영기획본부) AI디지털심화팀 등 / 사업 본부: 디지털융합본부, ICT기금관리본부, 전파기반본부, ICT자격본부, 차세대전파혁신단, 방송미디어본부, 빛마루방송지원단 (원장 직속 안전관리실·운영지원단, 부원장 겸임 기획조정실, 전파관리실)</t>
+          <t>AI디지털심화팀. 별도 사업성 본부: 디지털융합본부, ICT기금관리본부, 전파기반본부, ICT자격본부, 차세대전파혁신단, 방송미디어본부, 빛마루방송지원단</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>AI디지털심화팀 (경영기획본부 소속)</t>
+          <t>AI디지털심화팀(경영기획본부) / 전파통신AX본부(AI특화망사업팀) / AI미디어융합TF(방송미디어본부)</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>운영지원단 소관 — 정보보호팀 운영, 개인정보 보호책임자(CPO) 운영지원단장(정경구, 국가기술자격검정 시스템 기준). 전담 CISO 별도 직위 명칭은 미확인</t>
+          <t>운영지원단 정보보호팀 (확정) — 개인정보 보호책임자(CPO) 운영지원단장(정경구)</t>
         </is>
       </c>
       <c r="N115" s="3" t="inlineStr">
         <is>
-          <t>중(전자신문 공식 인사 보도(AI디지털심화팀장 보임) + 자격검정 개인정보처리방침(정보보호팀·CPO) 교차. 본부급 구조 확정, 단 본원 통합 CIO/CISO 직제는 미확인)</t>
+          <t>상(공식 조직도 전체 트리 브라우저 직접 확인)</t>
         </is>
       </c>
       <c r="O115" s="3" t="inlineStr">
@@ -10271,17 +10271,17 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>정보화전략팀 (경영기획본부 경영지원실 산하)</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>팀 (경영지원실 산하, 별도 정보화 처·실 없음)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>정보화전략팀, 정보보안파트 (모두 경영지원실 산하). 경영지원실 내 타 팀: 경영지원팀(자금관리파트)·안전보건관리팀</t>
+          <t>경영지원실(정보화전략팀·정보보안파트)</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
@@ -10946,17 +10946,17 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>정보관리팀 (보호정책부 산하)</t>
+          <t>보호정책부</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>팀 (부 산하, 별도 정보화부 없음)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>정보관리팀 (개인정보보호·정보화 담당부서). 보호정책부 산하 단일 팀 구조로 추정</t>
+          <t>정보관리팀(개인정보보호·정보화 담당)</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -11771,17 +11771,17 @@
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>AX전략실 (기획운영본부 산하)</t>
+          <t>기획운영본부</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>AX전략실 (기획운영본부 산하 디지털/AX 전략 담당), ICT신뢰성평가팀 (농기계검정본부 산하 ICT 기자재 평가)</t>
+          <t>AX전략실(디지털/AX 전략 담당). 별도 ICT신뢰성평가팀(농기계검정본부 산하, ICT 기자재 평가)</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
@@ -12446,17 +12446,17 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신국 / 디지털혁신센터 (본부 분산)</t>
+          <t>혁신성장본부 / 광고진흥본부</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>국·센터(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>(혁신성장본부) 디지털혁신국: 디지털전략팀·지능정보사업팀·IT팀 / (광고진흥본부) 디지털혁신센터: IT전략팀(정보보호관리단 포함)·AI혁신팀</t>
+          <t>혁신성장본부(디지털혁신국: 디지털전략팀·지능정보사업팀·IT팀) / 광고진흥본부(디지털혁신센터: IT전략팀[정보보호관리단]·AI혁신팀)</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>본부 (경영지원 본부 산하 정보화 팀)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H173" s="3" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부 (경영전략본부 산하)</t>
+          <t>경영전략본부</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>부(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H177" s="3" t="inlineStr">
@@ -14696,17 +14696,17 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>디지털정보실</t>
+          <t>기획경영본부</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 기획경영본부 산하</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
-          <t>디지털정보팀(정보보안 전담, 정보시스템/IT인프라관리, 개인정보보호 등)</t>
+          <t>디지털정보실(디지털정보팀 — 정보보안 전담, 정보시스템/IT인프라관리, 개인정보보호)</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
@@ -15221,17 +15221,17 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>정보기술융합팀 (경영지원실 산하)</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>팀 — 경영지원실 소속</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>정보기술융합팀(경영지원실), 데이터조사관리팀(재정통계연구실 산하 — 데이터 조사·관리)</t>
+          <t>정보기술융합팀. 별도 데이터조사관리팀(재정통계연구실 산하 — 데이터 조사·관리)</t>
         </is>
       </c>
       <c r="I197" s="3" t="inlineStr">
@@ -15296,17 +15296,17 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>경영지원실(정보화·전산인프라 총괄) — 경영관리본부 산하 / 조직도상 명칭은 기획인재실·경영안전지원실 계열</t>
+          <t>경영관리본부</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 경영관리본부 산하 (별도 IT 전담 본부·실 없음)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H198" s="3" t="inlineStr">
         <is>
-          <t>별도 IT전담팀 미확인. 전산인프라·정보시스템·대표홈페이지 유지관리는 경영지원실이 담당(개인정보처리방침 확인). 지식재산AI평가정보실(평가관리본부)은 특허분석평가시스템 운용 — 사업용 시스템</t>
+          <t>경영안전지원실(전산인프라·정보시스템·대표홈페이지 유지관리, 개인정보처리방침상 '경영지원실'로도 표기). 별도 지식재산AI평가정보실(평가관리본부 산하, 특허분석평가시스템 운용 — 사업용)</t>
         </is>
       </c>
       <c r="I198" s="3" t="inlineStr">
@@ -16346,17 +16346,17 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>AX사업실 (미래본부 산하)</t>
+          <t>미래본부</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>AX사업팀 (정보보안·개인정보보호·시스템 통합유지보수·AI 디자인 솔루션 개발)</t>
+          <t>AX사업실(AX사업팀 — 정보보안·개인정보보호·시스템 통합유지보수·AI 디자인 솔루션 개발)</t>
         </is>
       </c>
       <c r="I212" s="3" t="inlineStr">
@@ -16796,17 +16796,17 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>AI혁신팀 (경영기획본부 소속)</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>팀</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H218" s="3" t="inlineStr">
         <is>
-          <t>AI혁신팀(경영기획본부), 정보보안팀(경영지원실)</t>
+          <t>AI혁신팀. 별도 정보보안팀(경영지원실 소속)</t>
         </is>
       </c>
       <c r="I218" s="3" t="inlineStr">
@@ -18146,17 +18146,17 @@
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>법무·정보화팀 (경영기획본부 산하)</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>팀</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H236" s="3" t="inlineStr">
         <is>
-          <t>법무·정보화팀 (법무 업무와 정보화 업무 통합)</t>
+          <t>법무·정보화팀</t>
         </is>
       </c>
       <c r="I236" s="3" t="inlineStr">
@@ -18596,47 +18596,47 @@
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>정책정보센터 (데이터·정보화 총괄)</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>처·실(원장 직속) — 센터</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H242" s="3" t="inlineStr">
         <is>
-          <t>통계관리팀, 데이터분석팀, 정보사업팀</t>
+          <t>경영지원실(정보사업팀)</t>
         </is>
       </c>
       <c r="I242" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>데이터정책본부(데이터전략실·데이터분석단)</t>
+        </is>
+      </c>
+      <c r="K242" s="3" t="inlineStr">
+        <is>
+          <t>본부</t>
+        </is>
+      </c>
+      <c r="L242" s="3" t="inlineStr">
+        <is>
+          <t>확인불가 (정책정보센터장 또는 경영기획본부 총괄 추정)</t>
+        </is>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
           <t>확인불가</t>
         </is>
       </c>
-      <c r="K242" s="3" t="inlineStr">
-        <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="L242" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (정책정보센터장 또는 경영기획본부 총괄 추정)</t>
-        </is>
-      </c>
-      <c r="M242" s="3" t="inlineStr">
-        <is>
-          <t>확인불가</t>
-        </is>
-      </c>
       <c r="N242" s="3" t="inlineStr">
         <is>
-          <t>중(공식 위키 조직정보 + 채용공고 교차, 공식 홈페이지 조직도 페이지 직접 확인 실패)</t>
+          <t>상(공식 조직도 전체 트리 브라우저 직접 확인)</t>
         </is>
       </c>
       <c r="O242" s="3" t="inlineStr">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="N246" s="3" t="inlineStr">
         <is>
-          <t>중상(위키 상세 조직 + 보도 교차, 공식 조직도 페이지 직접 확인은 미완)</t>
+          <t>상(공식 조직도 직접 확인 — 경영기획본부 등 본부 체계 재확인)</t>
         </is>
       </c>
       <c r="O246" s="3" t="inlineStr">
@@ -21130,11 +21130,11 @@
         <v>29</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -21180,11 +21180,11 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -21198,19 +21198,19 @@
         <v>184</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
@@ -21232,27 +21232,27 @@
         <v>273</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.9%</t>
         </is>
       </c>
     </row>
@@ -21294,11 +21294,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>32.2%</t>
         </is>
       </c>
     </row>
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>44.7%</t>
         </is>
       </c>
     </row>
@@ -21324,11 +21324,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -21339,11 +21339,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.1%</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>
@@ -21400,11 +21400,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.0%</t>
         </is>
       </c>
     </row>
@@ -21461,11 +21461,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>86.1%</t>
         </is>
       </c>
     </row>
@@ -21476,11 +21476,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -21938,7 +21938,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>정보관리팀 (보호정책부 산하)</t>
+          <t>보호정책부</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부 (경영전략본부 산하)</t>
+          <t>경영전략본부</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -1986,7 +1986,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>중(공식 조직도 + 채용공고 직무기술서 + 보도 교차. 전산 기능 존재·소속(경영관리)은 확정, 정식 부서명·CIO/CISO 직위는 미공개)</t>
+          <t>상(공식 조직도 라이브 재확인, 2026-09-18 — 경영관리본부[기획조정처·인사노무처·경영지원처·윤리경영처] 전체 트리 확인, IT/정보화 명칭 부서 부재 재확인)</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 조직도 전체 트리 라이브 재확인, 2026-09-18)</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 조직도 라이브 재확인, 2026-09-18 — 전략본부 산하 AI디지털혁신처 재확인)</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>상(공식 기구표 2025 + 전화번호/개인정보처리방침 교차 확인)</t>
+          <t>상(공식 조직도 라이브 재확인, 2026-09-18 — 병원장 직속 배치 재확인)</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 이미지+부서별 연락처 텍스트 2요소 확보)</t>
+          <t>상(공식 조직도 라이브 재확인, 2026-09-18 — 전략기획실·AI디지털혁신처 전체 트리 재확인)</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>제조AI지원처 (지역혁신이사 산하)</t>
+          <t>제조AI지원처(지역혁신이사 산하) / AX혁신실(부이사장 직속, 신규 확인)</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
@@ -6671,32 +6671,32 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>경영본부</t>
+          <t>경영관리실</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>AI 담당팀</t>
+          <t>정보기술센터(AI혁신팀)</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>있음 (추정)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>경영본부 산하 'AI' 담당팀 (정확 명칭 확인불가, 조직도상 'AI' 표기)</t>
+          <t>AI혁신팀(경영관리실 정보기술센터 산하)</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>팀 (경영본부 산하)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>중(공식 조직현황 + 채용공고 2출처, 페이지 인코딩으로 팀명 일부 미확정)</t>
+          <t>상(공식 조직현황 페이지 라이브 재확인, 2026-09-18 — 인코딩 문제 해소, 부서 전체 트리 확보)</t>
         </is>
       </c>
       <c r="O83" s="3" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="N120" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 조직도 전체 트리 라이브 재확인, 2026-09-18)</t>
         </is>
       </c>
       <c r="O120" s="3" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="N130" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 raw 직접 확인 + 개인정보처리방침 + AI 추진단 보도 교차)</t>
+          <t>상(공식 조직도 라이브 재확인, 2026-09-18 — 경영관리본부 IT경영처·혁신성장본부 AI혁신처 재확인)</t>
         </is>
       </c>
       <c r="O130" s="3" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="N141" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 조직도 전체 트리 라이브 재확인, 2026-09-18)</t>
         </is>
       </c>
       <c r="O141" s="3" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="N161" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 직접 확인)</t>
+          <t>상(공식 조직도 전체 트리 라이브 재확인, 2026-09-18)</t>
         </is>
       </c>
       <c r="O161" s="3" t="inlineStr">
@@ -16761,7 +16761,7 @@
       </c>
       <c r="N217" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도·부서별 연락처 + 모회사 코레일 보안협의회 보도 교차확인)</t>
+          <t>상(공식 조직도 라이브 재확인, 2026-09-18 — 전체 트리 재확인)</t>
         </is>
       </c>
       <c r="O217" s="3" t="inlineStr">
@@ -21180,11 +21180,11 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
     </row>
@@ -21198,11 +21198,11 @@
         <v>184</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -21232,11 +21232,11 @@
         <v>273</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -21248,11 +21248,11 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
@@ -21294,11 +21294,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
     </row>
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.1%</t>
         </is>
       </c>
     </row>
@@ -21461,11 +21461,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>86.8%</t>
         </is>
       </c>
     </row>
@@ -21476,11 +21476,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
     </row>
@@ -21608,7 +21608,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 조직도 전체 트리 라이브 재확인, 2026-09-18)</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 직접 확인)</t>
+          <t>상(공식 조직도 전체 트리 라이브 재확인, 2026-09-18)</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -2331,22 +2331,22 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>정보전략실(정보운영처·정보보안처) / 별도 공간정보본부 내 디지털SOC처·플랫폼사업처</t>
+          <t>AI디지털전략실(AI혁신처·정보보안운영처) / 별도 공간정보본부 내 디지털SOC처·플랫폼사업처</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>없음 (전담 조직 미확인 — AI는 사업·과제 단위)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>해당없음 (공간정보연구원에서 AI 영상분석 등 R&amp;D 수행)</t>
+          <t>AI디지털전략실 산하 AI혁신처</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>상(공식 1출처 + 보도)</t>
+          <t>상(공식 조직도 라이브 재확인, 2026-09-18 — 조직개편 반영)</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>별도 '사이버안전센터' 운영 (AI 적용 보안체계 고도화)</t>
+          <t>기획관리본부 산하 '정보보안실' (별도 '사이버안전센터'도 운영, AI 적용 보안체계 고도화)</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>사이버보안센터 (안전보안본부 산하)</t>
+          <t>사이버보안센터 (안전보안본부 산하). 별도로 운영본부 경영관리실 산하 '경영정보부'도 확인(경영정보시스템 담당)</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>ICT기획부(정보시스템 통합유지관리·인프라·네트워크·공공데이터·정보보안 전략·사이버안전센터 운영)</t>
+          <t>디지털기획부(舊 ICT기획부 — 정보시스템 통합유지관리·인프라·네트워크·공공데이터·정보보안 전략·사이버안전센터 운영)</t>
         </is>
       </c>
       <c r="I234" s="3" t="inlineStr">
@@ -21172,11 +21172,11 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="G4" s="5" t="n">
@@ -21240,11 +21240,11 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -21400,11 +21400,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
     </row>

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -3671,7 +3671,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>기획본부</t>
+          <t>기획관리본부</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>정보보안처(ICT기획부·디지털보안부[사이버보안실])</t>
+          <t>정보보안처(ICT기획부·디지털보안부[사이버보안실]) — 정확한 소속 처 재확인 필요(아래 메모 참고)</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -6446,17 +6446,17 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>AX센터 (구 ICT센터)</t>
+          <t>AX추진본부</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>처·실급 센터(센터장, 본부 산하 — 소속 본부 명칭은 공식 조직도에서 미명시)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>AX전략부(데이터인프라관리팀 등), 정보화사업관리부, ICT개발부, ICT운영부, 정보보안부, AX시스템관리부 (총 6개부)</t>
+          <t>AX전략실, ICT운영실 (부서 소개 페이지 기준 세부: AX전략부[데이터인프라관리팀]·정보화사업관리부·ICT개발부·ICT운영부·정보보안부·AX시스템관리부)</t>
         </is>
       </c>
       <c r="I80" s="3" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>상(공식 부서소개 페이지로 산하 6개부·정보보안부 확정. 단 AX센터 소속 본부 명칭은 미확정)</t>
+          <t>상(공식 조직도 라이브 재확인, 2026-09-18 — 본부 소속 여부 확정)</t>
         </is>
       </c>
       <c r="O80" s="3" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>보호정책부</t>
+          <t>보호사업부 (舊 보호정책부)</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>정보관리팀(개인정보보호·정보화 담당)</t>
+          <t>정보관리팀(개인정보보호·정보화 담당) — 부서명 변경 후 소속 정보관리팀 존속 여부는 세부 재확인 필요</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 AI 전담부서 미확인. 의료 AI 공통역량과정 등 교육콘텐츠로 AI 다룸)</t>
+          <t>확인불가 (전담 부서는 아니나 보건인재양성본부 바이오헬스교육실 산하 '의료AI교육팀' 확인 — 교육과정 운영 조직)</t>
         </is>
       </c>
       <c r="K177" s="3" t="inlineStr">
@@ -17286,7 +17286,7 @@
       </c>
       <c r="N224" s="3" t="inlineStr">
         <is>
-          <t>중(공식 블로그 조직소개 1출처 + 부처 조직도 교차)</t>
+          <t>상(공식 조직도 라이브 재확인, 2026-09-18)</t>
         </is>
       </c>
       <c r="O224" s="3" t="inlineStr">
@@ -21130,11 +21130,11 @@
         <v>29</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -21232,11 +21232,11 @@
         <v>273</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -21294,11 +21294,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.2%</t>
         </is>
       </c>
     </row>
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.7%</t>
         </is>
       </c>
     </row>
@@ -21461,11 +21461,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>87.2%</t>
         </is>
       </c>
     </row>
@@ -21476,11 +21476,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
     </row>
@@ -21938,7 +21938,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>보호정책부</t>
+          <t>보호사업부 (舊 보호정책부)</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -1046,7 +1046,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>디지털본부 (디지털전환·AI·데이터·모빌리티 혁신 총괄) — 통칭 'AI 디지털본부'</t>
+          <t>AI디지털본부</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>디지털본부 산하: 디지털계획처(디지털전환 기획), AI데이터처(AI·데이터 총괄, 하위 데이터품질부 등), 모빌리티 혁신 부서 — 정보보안 부서 별도 운영</t>
+          <t>AI디지털본부 산하: AX혁신처, AI데이터처, 디지털관리처, 정보보안센터</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>정보보안 담당부서 운영 — 전담 CISO 직제 확인불가</t>
+          <t>정보보안센터 (AI디지털본부 산하)</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -16381,7 +16381,7 @@
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보안 업무는 AX사업팀 및 경영본부 경영지원실 자산안전팀 분담)</t>
+          <t>AX사업실 산하 '보안전략팀' (신규 확인). 경영본부 경영지원실 자산안전팀도 일부 분담</t>
         </is>
       </c>
       <c r="N212" s="3" t="inlineStr">

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -821,17 +821,17 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>품질기술본부 (2026.5 AI혁신처를 관리본부에서 이관, 원전 디지털 전환 기능 통합)</t>
+          <t>품질기술본부</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>본부(품질기술본부) 산하 처(AI혁신처) — IT/디지털 총괄은 품질기술본부</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>AI혁신처(원전 디지털 전환 기능 통합) — 그 외 정보화/정보보안 부서 명칭 확인불가</t>
+          <t>AI혁신처, 사이버보안센터</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>처(품질기술본부 산하)</t>
+          <t>처</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (개인정보 보호수준 평가 S등급 1위 등 정보보호 역량 보유)</t>
+          <t>사이버보안센터(경영부사장 산하)</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>2026.5.28 김회천 사장 취임 후 첫 대대적 조직개편. 3대 원칙(국정과제 이행체계·안전 최우선 현장·책임경영체계). 기존 관리본부 산하 'AI혁신처'를 품질기술본부로 이관하고 원전 디지털 전환 기능을 통합해 'AI 대전환' 추진체계 본격 가동. '원전 운영 글로벌 Top Tier 디지털 기술 개발' 목표(디지털트윈·AI 설비 자동예측진단·지능형 작업로봇·VR). 2025 공공부문 AX 혁신대상 '대상' 수상. 본사 유사기능 통폐합으로 단위조직 4개 축소·약 100명 현장 재배치. 사업리스크관리실 신설.</t>
+          <t>IT기능: AI혁신처가 전사 AI·원전 디지털 전환 총괄(디지털트윈·AI 설비 자동예측진단·지능형 작업로봇·VR 등 '원전 운영 글로벌 Top Tier 디지털 기술 개발' 추진). 사이버보안센터가 사이버보안 전담.&lt;br&gt;조직이력: 2026.5.28 사장 취임 후 첫 대대적 조직개편(3대 원칙: 국정과제 이행체계·안전 최우선 현장·책임경영체계). 기존 관리본부 산하 'AI혁신처'를 품질기술본부로 이관하고 원전 디지털 전환 기능을 통합해 'AI 대전환' 추진체계 가동. 본사 유사기능 통폐합으로 단위조직 4개 축소·약 100명 현장 재배치.&lt;br&gt;기타: 2025 공공부문 AX 혁신대상 '대상' 수상. 2024·2025 공공기관 개인정보 보호수준 평가 최고등급(S). 품질기술본부는 품질보증처·기술정책처·방사선환경처·AI혁신처로 구성.</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>AI본부 (경영부문 산하)</t>
+          <t>AI본부</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>AI혁신처, 디지털관리처(디지털관리부·정보화제도담당관 등), AI데이터센터 (※디지털보안처: 공식 조직도 미표기 — 현행 존속 여부 재확인 필요)</t>
+          <t>AI혁신처, 디지털관리처, AI데이터센터</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>AI본부 / AI추진단</t>
+          <t>AI본부 (AI혁신처·AI데이터센터)</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>디지털보안처 (2021.12 신설, 정보보호 전담)</t>
+          <t>정보보안처 (경영부문 직속, AI본부와 병렬)</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>2025.9.8 전면 조직개편으로 '안전·재생에너지·AI' 3대 축 격상·신설. 물관리 분야 AI전환 전담 'AI추진단' 신설, 디지털 관련 처가 AI본부 산하로 재편됨. AI 정수장(WEF 글로벌 등대상), 물관리 디지털트윈 등 'AI 3대 강국' 전략 추진.</t>
+          <t>조직이력: 2025.9.8 전면 조직개편으로 '안전·재생에너지·AI' 3대 축 격상·신설. 물관리 분야 AI전환 전담 'AI추진단' 신설 후 AI본부로 편제, 디지털 관련 처가 AI본부 산하로 재편. 기존 '디지털보안처'(2021.12 신설)는 2026.7 조직도 기준 '정보보안처'로 경영부문 직속 편제&lt;br&gt;기타: AI 정수장(WEF 글로벌 등대상), 물관리 디지털트윈 등 'AI 3대 강국' 전략 추진. AI본부는 부사장 &gt; 경영부문 산하</t>
         </is>
       </c>
     </row>
@@ -2771,12 +2771,12 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>IT·AI본부 (구 IT본부→IDT본부→IT·AI본부, 리스크관리부문 산하)</t>
+          <t>IT·AI 본부</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>본부(부문 산하) — 리스크관리부문 산하</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -2791,32 +2791,32 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>AI·디지털전략부 (IT·AI본부 산하)</t>
+          <t>AI·디지털전략부</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>부(본부 산하) — IT·AI본부 내 'AI·디지털전략부'(구 디지털전략부/디지털추진부 계열, AI·디지털 전략 총괄)</t>
+          <t>부</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>IT·AI본부장이 IT총괄(추정) — 별도 CIO 직위 명시 확인불가</t>
+          <t>IT·AI 본부장이 IT·AI 총괄(추정) — 별도 CIO 직위 명시 확인불가</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>정보보호최고책임자(CISO) 명시 — 회장 직속(전무이사 라인, 준법감시인과 병렬) '정보보호최고책임자' 직위 + 산하 '정보보호부'</t>
+          <t>정보보호최고책임자(CISO) 직위 명시 — 전무이사 직속(준법감시인과 병렬), 산하 '정보보호부' 통할</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 2026.04 + 2026.01 인사발령 기사 교차 확인)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>(2026-06-15 보완) 공식 조직도(기준 2026.04, 10부문·8본부·8지역본부·65부실) 확보 — 'IT본부→IDT본부→IT·AI본부'로 재개편되어 리스크관리부문 산하에 편제. IT·AI본부=AI·디지털전략부+IT기획부+코어금융부+디지털금융부. AI 전담 '부' 단위(AI·디지털전략부) 신설로 AI전담조직 '있음' 확정. 별도로 회장 직속에 '정보보호최고책임자(CISO)+정보보호부' 명시 — CISO 체계 확정. KDB IT센터(디지털스퀘어) 운영.</t>
+          <t>IT기능: AI·디지털 전략 수립, IT 기획, 코어뱅킹(코어금융), 디지털금융 채널 운영. 정보보호는 IT 라인이 아닌 전무이사 직속 정보보호최고책임자·정보보호부가 수행. 조직이력: IT본부 → IDT본부(2019) → IT·AI 본부로 재개편. 현재는 정책기획부문이 아닌 리스크관리부문 산하(리스크관리부·여신감리부·금융결제부와 병렬)에 편제. 기타: 전행 규모 10부문·8본부·8지역본부·65부(실). 금융기관 특성상 정보통신망법상 CISO 지정·신고 의무가 조직에 반영된 구조. KDB IT센터(디지털스퀘어) 운영.</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>AI·디지털혁신처 (구 디지털총괄실에서 격상)</t>
+          <t>AI·디지털혁신처</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>(조직개편으로 산하 조직 보강), 인공지능혁신센터, 디지털 기술공유센터(판교)·와이즈센터(태안)·디지털트윈센터(김포) 등 기술센터 연계</t>
+          <t>디지털기획부, 디지털운영부, AI혁신부</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>인공지능혁신센터(2025.7 신설) + AI·디지털혁신처(총괄)</t>
+          <t>AI·디지털혁신처 / AI혁신부</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>처·실 / 센터</t>
+          <t>처·실 / 부</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>AI·디지털혁신처장 (CIO 역할 추정)</t>
+          <t>AI·디지털혁신처장이 IT·AI 총괄(CIO 역할, 별도 직위 명시는 확인불가)</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>기획본부 정보보안실이 정보보안 업무 총괄 — IT 조직(AI·디지털혁신처)과 분리 편제. 별도 CISO 직위 명시는 확인불가</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>상(보도 다수, 공식 개편 발표)</t>
+          <t>상(공식 홈페이지 조직도·본사 부서 직제 직접 확인)</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>2025.7.22 전사 조직개편으로 기존 '디지털총괄실'을 'AI·디지털혁신처'로 격상하고 산하 조직 보강(재생에너지처·ESG전략실 동시 신설). 2025.7.7 발전소 운영 AI 도입 위한 '인공지능혁신센터' 신설하고 AI 전문가 3명 채용. '디지털 기술공유센터'를 2026년 이후 독립적 인공지능센터로 발전 계획. 디지털트윈+AI 융합 '지능형 빅데이터 플랫폼' 운영. **모회사 한국전력과 별도 자체 IT 조직(AI·디지털혁신처) 운영 — 한전 IT 직접 공유 단서 없음(자회사 독립 운영).**</t>
+          <t>IT기능: 디지털변환(DX) 전략수립 및 사업관리 총괄(디지털기획부), ICT 인프라 및 정보통신시스템 구축·운영(디지털운영부), AX 계획수립 및 업무혁신(AI혁신부). 조직이력: 2025.7.22 전사 조직개편으로 '디지털총괄실'을 'AI·디지털혁신처'로 격상(재생에너지처·ESG전략실 동시 신설), 2025.7.7 발전소 운영 AI 도입을 위한 '인공지능혁신센터' 신설(AI 전문가 3명 채용). 2026년 조직도 기준 본사 직제에는 'AI혁신부'가 AI 전담 부서로 편제되어 있고 별도 '인공지능혁신센터' 명칭은 확인되지 않음. 기타: 구 '디지털 기술공유센터'가 'AX 이노베이션 센터'(d-sharing.iwest.co.kr)로 개편되어 기타사업소로 운영. 디지털트윈+AI 융합 '지능형 빅데이터 플랫폼' 운영. 모회사 한국전력과 별도로 자체 IT 조직을 운영(한전 IT 직접 공유 단서 없음).</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>정보보안처(ICT기획부·디지털보안부[사이버보안실]) — 정확한 소속 처 재확인 필요(아래 메모 참고)</t>
+          <t>AI혁신처 사이버보안실 — 옛 정보보안처(ICT기획부·디지털보안부) 조직이 AI혁신처로 통합·개편됨</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
@@ -3691,32 +3691,32 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>AI솔루션부, 기술안전AI센터(발전운영 부서 내 신설)</t>
+          <t>AI혁신처(사이버보안실 포함, 기획관리본부 산하)</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>부(기술본부 계열 산하) — 정보화 조직과 별도</t>
+          <t>처 — 옛 AI솔루션부·기술안전AI센터·정보보안처 기능을 흡수해 AI혁신처로 격상</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보안처장이 ICT기획·디지털보안 총괄, 기획본부장 산하 추정)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>정보보안처장 (개인정보 보호책임자 겸임)</t>
+          <t>AI혁신처 사이버보안실장 이찬식 (개인정보 보호책임자 겸임)</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 조직도 + 개인정보처리방침 교차확인, 라이브 재검증 완료)</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>2026.3 인공지능 전담조직 'AI솔루션부' 기능 강화 및 발전운영 부서 내 '기술안전AI센터' 신설. 'AI 전환 중장기 추진전략' 수립(UNIST 협업). 공공기관 최초 '인공지능 감사·윤리 헌장' 선포. IT 기획·운영(ICT기획부)과 보안(디지털보안부)이 정보보안처로 통합 운영. AI 조직이 정보화처가 아닌 기술/발전운영 라인에 분산 배치된 점 특징.</t>
+          <t>(2026-09-18 라이브 재확인) 옛 '정보보안처'가 사라지고 'AI혁신처'로 개편·통합됨을 공식 조직도·개인정보처리방침에서 확인. AI혁신처가 기획관리본부 산하로 편제되어 IT기획·정보보안(사이버보안실)과 AI 전담 기능을 모두 수행하는 통합 조직이 됨. 안전기술본부 산하에는 별도로 '기술안전AI센터'(발전처, 기술분야 AI)가 유지됨 — 즉 AI 기능이 AI혁신처(전사 IT·보안·AI 총괄)와 기술안전AI센터(발전현장 AI) 2원 체계로 재편.</t>
         </is>
       </c>
     </row>
@@ -4576,12 +4576,12 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>처·실(경영기획이사 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>디지털계획부 (외 정보화·데이터 부서)</t>
+          <t>디지털계획부, AI혁신부, 통계정보부, 정보보안팀, R&amp;D정책팀</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>AI디지털전략실</t>
+          <t>AI디지털전략실 / AI혁신부</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>처·실(경영기획이사 산하)</t>
+          <t>처·실 / 부</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>AI디지털전략실장이 실질 정보화 책임자 (직책 명시 확인불가)</t>
+          <t>AI디지털전략실장이 정보화·AI·통계·보안을 총괄하는 실질 정보화 책임자 (별도 CIO 직위 명시는 확인불가)</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보안 전담 별도 부서 명시 미확인, AI디지털전략실 내 수행 추정)</t>
+          <t>AI디지털전략실 정보보안팀(팀장)이 정보보안 실무 총괄, 통계정보부장이 "통계 및 정보보안 업무 총괄" — 별도 CISO 직위 명시는 확인불가</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>기존 정보화 조직을 "AI디지털전략실"로 명칭/기능 강화. AX(AI Transformation) 전략 추진 중 — 산재예방 AI 기초연구과제 4건 수행, KOSHA-AI 리더스 육성 캠프 운영. 2026년 산업안전보건 데이터 통합플랫폼 R&amp;D(약 77억) 추진.</t>
+          <t>IT기능: 산재예방 정보시스템 구축·운영, 공공데이터 개방 및 데이터기반행정, ERP·ITSM(코샤지니)·SSO 등 기반시스템 운영, 산업안전포털·내부업무포털·K2B 플랫폼 기획·운영, KOSHA-MAP 서비스, 대내 AI·자동화(RPA), 산업재해 현황통계 생산·분석, 정보보안 솔루션 운영 및 국정원 정보보안 관리실태 평가 대응, 산업안전 R&amp;D 전문기관 운영. 조직이력: 종전 '디지털전략실'에서 'AI디지털전략실'로 개편, 2025.8 직제 개편으로 기존 부서를 'AI혁신부'로 전환(정부 AI 대전환(AX) 정책 대응). 2026년 조직도 기준 소관 임원이 경영기획이사에서 교육홍보이사로 변경. 기타: AI혁신부가 고위험사업장 예측시스템·산재발생 위험경보 시스템·빅데이터 플랫폼 운영, 산재예방 특화 AI 서비스 및 산재예방 언어모델(LLM) 구축 추진. AX혁신위원회 운영, AI 전문역량강화 교육·KOSHA-AI 리더스 육성 캠프 운영. 2026년 AI 국제세미나 개최.</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>국</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>AI디지털정보국 (하위 AI데이터기획부)</t>
+          <t>AI디지털정보국 / AI데이터기획부</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>국(局) — 본부 산하 / 부 단위에 AI데이터기획부</t>
+          <t>국 / 부</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>AI디지털정보국장(현 백은실)이 정보화·AI·데이터 총괄. 개인정보보호책임자(CPO)도 AI디지털정보국장이 겸함(공식 확인)</t>
+          <t>AI디지털정보국장(백은실)이 정보화·AI·데이터 총괄. 개인정보보호책임자(CPO) 겸직(공식 확인)</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>별도 CISO 직책 미공개(확인불가). 정보보안 실무는 AI디지털정보국 정보보안부(부장 이태훈)가 운영, 개인정보 보호담당자 겸</t>
+          <t>별도 CISO 직책 미공개(확인불가). 정보보안 실무는 AI디지털정보국 정보보안부(부장 이태훈)가 수행, 개인정보 보호담당자 겸</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침 + 공공데이터포털 부서정보 교차)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>기존 "정보화지원국"(정보화기획부, 정보화사업1·2부, 정보보안부)에서 AI를 전면에 내세운 "AI디지털정보국"으로 개편됨. AI데이터기획부가 신설/전환되어 AI·데이터 기획 기능을 명시.</t>
+          <t>조직위치: AI디지털정보국은 기획이사 산하 국급 조직이며, AI데이터기획부·자격정보화부·정보화사업부·정보보안부가 그 산하 부급 조직.&lt;br&gt;IT기능: 정보화 기획·사업 추진, 국가자격시험 정보화(자격정보화부), AI·데이터 기획, 정보보안·개인정보보호. 조직이력: 기존 '정보화지원국'(정보화기획부·정보화사업1·2부·정보보안부)에서 'AI디지털정보국'으로 개편, AI데이터기획부 신설·전환으로 AI·데이터 기획 기능 명시. 기타: 2026.2.27 인공지능 경영시스템 국제표준 'ISO/IEC 42001' 인증 획득(울산 혁신도시 공공기관 최초) — HRD4U 챗봇 시스템 중심 AI 관리체계 구축, 담당부서 AI데이터기획부. 임직원 AI 활용 역량 제고를 위한 'HRDK AI Lab' 본부 개소. AX 과제 단계적 추진 중.</t>
         </is>
       </c>
     </row>
@@ -5321,52 +5321,52 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>디지털플랫폼처 (디지털·홍보 부문 이사 산하)</t>
+          <t>AI전략실</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하 / 이사 직속)</t>
+          <t>분산</t>
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>디지털플랫폼보안실 (정보보안·개인정보 전담), 디지털총괄실(추정)</t>
+          <t>기획조정처(디지털지원실), 경영지원처(정보보안팀)</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>없음 (별도 AI 전담 부서 미존재 — 디지털플랫폼처가 AI·IoT 기반 지능형 승강기안전 플랫폼 총괄)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>AI전략실</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>실</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>디지털·홍보 부문 이사가 디지털 부문 총괄(디지털플랫폼처 소관, 전담 CIO 직위 명시 확인불가). 디지털혁신 총괄이사 직함은 출처별 상이('디지털홍보이사'(위키)/'교육홍보이사'(전기신문 2024))</t>
+          <t>전담 CIO 임원 직위 확인불가. AI·디지털 전략은 이사장 직속 AI전략실, 정보화 지원은 경영기획이사 → 기획조정처 → 디지털지원실 라인</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>디지털플랫폼처(개인정보 보호책임자 소속 부서) → 디지털플랫폼보안실(분야별 책임자). 별도 CISO 임원 직위 명시는 확인불가</t>
+          <t>정보보안팀 (경영기획이사 → 경영지원처 산하). 개인정보 보호책임자 = 정보보안팀 이정균, 기관 담당자 = 정보보안팀 김정원(개인정보처리방침 2026.09.07 개정). 별도 CISO 임원 직위 명시는 확인불가</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>상(기관 공식 개인정보처리방침(디지털플랫폼처·디지털플랫폼보안실 확인) + 위키 조직도 + 보도자료 다수 교차)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + 공식 개인정보처리방침(2026.09.07) + 이사장 인터뷰 보도 교차)</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>디지털 부문 이사 체계 하에 디지털플랫폼처 배치. 공식 개인정보처리방침(2025.6.30 개정)상 개인정보 보호책임자=디지털플랫폼처, 분야별 책임자=디지털플랫폼보안실로 확인. 'KoELSA 지능형 승강기안전 플랫폼'(AI·IoT 융합, 영상분석·음성인식 자동감지), 국가승강기정보센터, 데이터개방 플랫폼 '엘리데이터'(AI 침수위험지도 등) 운영. 2025.11 LH와 'AI 활용 승강기 안전관리' MOU(고장예측·실시간 진단), 2026.5 IoT 5개사와 지능형 플랫폼 MOU. 2026.4 직원 80명 'AI 앰배서더' 위촉(전사 AI 내재화). AI는 사업·플랫폼 단위로 활발하나 조직도상 독립 AI 전담 부서는 미존재.</t>
+          <t>조직위치: AI전략실은 이사장 직속(안전관리실·사고조사단·승강기안전기술원과 병렬). 디지털지원실은 경영기획이사&gt;기획조정처 산하, 정보보안팀은 경영기획이사&gt;경영지원처 산하.&lt;br&gt;조직이력: 2026년 조직개편으로 기존 '디지털플랫폼처(디지털총괄실·디지털플랫폼보안실)' 폐지 → 이사장 직속 'AI전략실' 신설, 정보화 지원은 기획조정처 디지털지원실, 정보보안·개인정보는 경영지원처 정보보안팀으로 분산 재편(공식 조직도·개인정보처리방침 2026.09.07 개정본 확인).&lt;br&gt;IT기능: 디지털지원실(정보화 지원), 정보보안팀(정보보안·개인정보보호·지능형 승강기안전 플랫폼 개인정보 담당), AI전략실(AI·디지털 전략 총괄).&lt;br&gt;기타: 4이사 체계(경영기획이사·안전관리이사·교육홍보이사 + 이사장 직속). 'KoELSA 지능형 승강기안전 플랫폼'(AI·IoT 융합, 영상분석·음성인식 자동감지), 국가승강기정보센터, 데이터개방 플랫폼 '엘리데이터'(AI 침수위험지도) 운영. 2026.8 'AI 기반 에스컬레이터 스마트 안전관리 플랫폼 EscaEye' 공동개발 시연회. 2025.11 LH와 AI 승강기 안전관리 MOU, 2026.5 IoT 5개사 MOU. 2026.4 직원 80명 'AI 앰배서더' 위촉. 공식 홈페이지에 'KoELSA AI'(중장기 AI 전략체계·AI 윤리원칙·AI 활동 현황·AI 소통) 전용 메뉴 운영.</t>
         </is>
       </c>
     </row>
@@ -5846,17 +5846,17 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>AI디지털혁신단 (구 디지털혁신단)</t>
+          <t>기획경영본부</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>단(처·실급 전담조직, 사장 직속 추정)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>디지털인프라팀 등(디지털혁신단), 스마트데이터센터(데이터혁신팀), 정보보안팀</t>
+          <t>AX혁신처(디지털인프라팀), 공공사업본부(석유정보센터·정보보안실)</t>
         </is>
       </c>
       <c r="I72" s="3" t="inlineStr">
@@ -5866,32 +5866,32 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>AI디지털혁신단</t>
+          <t>AX혁신처</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>단(처·실급 전담조직)</t>
+          <t>처</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>기획경영본부장(AX혁신처 소관) 추정 — 직책 명시 확인불가</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>정보보안팀 운영, 전담 CISO 명칭 확인불가</t>
+          <t>정보보안실(공공사업본부 산하, 실장)</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>2025.9.11~12 기존 '디지털혁신단'을 'AI디지털혁신단'으로 확대 개편/출범(정부 AI 국가대전환 기조 대응). 별도로 스마트데이터센터(데이터혁신팀)가 데이터 분석·DB 업무 수행. AI 기반 데이터분석·예측유지보수·공정최적화로 생산성 개선 추진, 미래형 에너지 공기업 선언. 조직도 작성기준일 2025-07-28.</t>
+          <t>IT기능: AX혁신처는 AI 거버넌스 정립·AI 운영기반 구축·AI 기반 업무혁신 추진 및 디지털 인프라 운영, 공공데이터 개방 담당(2026년 공공데이터 활용 가이드북 발간부서). 석유정보센터는 석유 유통·수급 정보시스템(페트로넷 등) 운영, 정보보안실은 정보보안 전담.&lt;br&gt;조직이력: 2025.9 '디지털혁신단'을 'AI디지털혁신단'으로 확대 개편 → 이후 '기획경영본부 산하 AX혁신처'로 재편(조직도 작성기준일 2026-07-22 확인). 종전 스마트데이터센터·데이터혁신팀은 현 조직도에서 미확인(폐지·통합 추정).&lt;br&gt;기타: 정부 'AI 국가 대전환' 기조 대응, AI 기반 데이터분석·예측유지보수·공정최적화로 미래형 에너지 공기업 전환 추진.</t>
         </is>
       </c>
     </row>
@@ -6151,12 +6151,12 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>단(부서급, 본부 산하·은행장 직속급)</t>
+          <t>단</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>디지털금융기획팀, IT센터운영팀, (정보시스템부: IT금융팀·IT정보팀), 정보보호단</t>
+          <t>정보시스템부(IT금융팀·IT정보팀), 정보보호단, 정보보호실</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>AI플랫폼구축추진반 (디지털금융단 내 신설). 자체 생성형 AI 플랫폼 'KEXIM AI' 구축·AI 기반 신용평가체계 고도화 전담</t>
+          <t>AI플랫폼구축추진반</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>반(班)급 — 디지털금융단 산하 추진반</t>
+          <t>반(班)</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -6181,17 +6181,17 @@
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>정보보호단장</t>
+          <t>정보보호단장 (은행장 직속 정보보호단·정보보호실 별도 편제)</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>상(한국금융신문 2026.5 보도로 AI플랫폼구축추진반·디지털금융단장(CIO) 확정. 인사공시·위키 교차)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + 보도 교차)</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>2021년 조직개편으로 디지털 조직 강화('디지털 수은' 구축). 2025년 초 'DX·AX 전략 및 생성형 AI 활용방안' 컨설팅 완료, 2026~2028 중장기 디지털 전략 로드맵 확정. 그 첫 실행과제로 디지털금융단 내 'AI플랫폼구축추진반' 신설, 총 130억원 규모 온프레미스 생성형 AI 플랫폼 'KEXIM AI' 구축 + AI 기반 신용평가시스템 전면 개편 추진. 2025.6 용인 독립 IT센터 개소. 2026.5 NIA와 AI·디지털 국제개발협력(EDCF) MOU. AI 전담조직은 상설 '단/부'가 아닌 추진반(추진조직) 형태 — 향후 AI 전담조직 정식 구성·전문인력 육성 단계적 추진 예정.</t>
+          <t>IT담당배경: 은행 직제 특성상 '단/부/실' 명칭 사용. 디지털금융단·정보보호단·정보보호실은 본부 소속이 아닌 은행장 직속 단위&lt;br&gt;IT기능: 디지털전환 기획, 정보시스템 개발·운영(정보시스템부), 정보보호&lt;br&gt;조직이력: 2021년 조직개편으로 디지털 조직 강화('디지털 수은' 구축). 2025년 초 'DX·AX 전략 및 생성형 AI 활용방안' 컨설팅 완료, 2026~2028 중장기 디지털 전략 로드맵 확정. 첫 실행과제로 디지털금융단 내 'AI플랫폼구축추진반' 신설&lt;br&gt;기타: 총 130억원 규모 온프레미스 생성형 AI 플랫폼 'KEXIM AI' 구축 + AI 기반 신용평가시스템 전면 개편 추진. 2025.6 용인 독립 IT센터 개소. 2026.5 NIA와 AI·디지털 국제개발협력(EDCF) MOU. 금융상품에 'AX 특별프로그램' 운영. AI 전담조직은 상설 '단/부'가 아닌 추진반(추진조직) 형태 — 공식 조직도에는 미표기</t>
         </is>
       </c>
     </row>
@@ -6971,32 +6971,32 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신실 (기획조정본부 산하, 내부 정보화·디지털전환(DT) 총괄). 정보보안은 경영지원본부 산하 융합보안실</t>
+          <t>기획조정본부</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 디지털혁신실은 기획조정본부 산하 실</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신실(정보화·DT, 기획조정본부 산하), 융합보안실(정보보안, 경영지원본부 산하 — 내 사이버보안팀)</t>
+          <t>기획조정본부(디지털혁신실), 경영지원본부(융합보안실), 디지털산업본부(산업인공지능혁신센터), 바이오의료헬스본부(의료AI개발지원센터)</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>없음 (내부 정보화 거버넌스 기준) — 단 사업조직으로 디지털산업본부 산하 '산업인공지능혁신센터', 바이오의료헬스본부 산하 '의료AI개발지원센터' 운영</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>(내부 전담 해당없음) / 사업조직: 산업인공지능혁신센터, 의료AI개발지원센터</t>
+          <t>산업인공지능혁신센터, 의료AI개발지원센터</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>(사업조직) 센터 (본부 산하)</t>
+          <t>센터</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>상 (공식 홈페이지 조직도 + 공식 보도(ISMS-P/CISO) 2출처 교차)</t>
+          <t>상 (공식 홈페이지 조직도 직접 확인 + 공식 보도(ISMS-P/CISO) 교차)</t>
         </is>
       </c>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>2026.5 ISMS-P(정보보호·개인정보보호 관리체계) 인증 획득(KTL 대표 누리집+시험인증서비스 대상, 2014 ISMS 최초취득). 내부 IT는 기획조정본부 산하 '디지털혁신실'이 정보화·DT를 총괄, 경영지원본부 산하 '융합보안실'(사이버보안팀)이 정보보안 담당. '산업인공지능혁신센터'(디지털산업본부)·'의료AI개발지원센터'(바이오의료헬스본부)는 외부 대상 AI 시험·개발지원 사업조직이며 내부 AI 거버넌스 조직 아님. 조직: 원장-부원장 체계, 기획조정본부·경영지원본부·인증사업본부·미래융합기술본부·바이오의료헬스본부·환경기술본부·시스템에너지본부·디지털산업본부·산업표준본부 등.</t>
+          <t>AI조직성격: AI 명칭 전담조직 2개는 모두 **사업(시험·인증·개발지원) 조직**으로 센터급이며, 디지털산업본부 산하 '산업인공지능혁신센터'·바이오의료헬스본부 산하 '의료AI개발지원센터'. 기관 내부 정보화·AI 거버넌스 전담조직은 아니나, **통일 계상기준(조직명에 AI/인공지능이 명시된 전담조직이 있으면 연구·사업 성격 불문 '있음')** 에 따라 AI전담조직='있음'으로 계상.&lt;br&gt;기관유형부기: 산업통상부 산하 특정연구기관(알리오 기관유형 자체는 '기타공공기관').&lt;br&gt;IT담당배경: 내부 IT가 두 본부로 분리 편제 — 기획조정본부 산하 '디지털혁신실'이 정보화·디지털전환(DT)을 총괄하고, 경영지원본부 산하 '융합보안실'(사이버보안팀)이 정보보안을 담당&lt;br&gt;IT기능: 정보화 기획·디지털전환(디지털혁신실), 정보보안·사이버보안(융합보안실)&lt;br&gt;기타: 2026.5 ISMS-P(정보보호·개인정보보호 관리체계) 인증 획득(KTL 대표 누리집+시험인증서비스 대상, 2014 ISMS 최초취득). '산업인공지능혁신센터'(디지털산업본부)·'의료AI개발지원센터'(바이오의료헬스본부)는 외부 대상 AI 시험·개발지원 사업조직이며 내부 AI 거버넌스 조직 아님. 조직: 원장-부원장 체계, 기획조정본부·경영지원본부·인증사업본부·미래융합기술본부·바이오의료헬스본부·기후환경본부·시스템에너지본부·디지털산업본부·산업표준본부</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>전략기술본부</t>
+          <t>AI전략기술본부</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -7506,22 +7506,22 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>정보기획부, 정보연계부, 응용품질부, 데이터품질부 (전략기술본부) / 복지정보개발부, 복지정보운영부 (복지정보본부) / 개인정보보호부, 정보보안부, 정보자원관리부 (정보보호본부)</t>
+          <t>AI전략기술본부(AI정보기획부·정보연계부·응용품질부·데이터품질부), 정보보호본부(개인정보보호부·정보보안부·정보자원관리부), 복지정보본부(복지정보개발부·복지정보운영부), 사회보장정보연구소(정보분석부·데이터관리부·연구센터)</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>있음 (2025년 AI 전담 부서 신설 + 사회보장 AI TF 구성)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>사회보장 AI TF(전략기획·법제도·인프라·기술혁신 4개 분야) / AI 기능은 사회보장정보연구소(정보분석부·데이터관리부·연구센터)에 분포 (전담 부서 정식 명칭 일부 확인불가)</t>
+          <t>AI전략기술본부(AI정보기획부), 사회보장 AI TF</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>TF + 연구소·부 단위</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>중(공식 조직도 + 개인정보처리방침 + AI TF 보도 교차)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + 개인정보처리방침·AI TF 보도 교차)</t>
         </is>
       </c>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>정보화 전문 공공기관 특성상 IT 조직 비중 큼. 정보이사 산하에 전략기술본부·복지정보본부 등 다수 IT 본부 배치. 정보보호본부를 별도 본부로 운영. 2025년 정부 AI 행정혁신 기조에 맞춰 'AI 전담 부서'를 신설하고, 2025.11 보건복지부와 '제1차 사회보장 AI TF'(4개 분야) 구성·정례화. 'K-소버린 AI 고속도로 연계 보건복지 AI 인퍼런스 클라우드센터' 구축 추진(정보보호본부장 발표). 통합플랫폼 기능개발단·돌봄통합시스템구축지원단 등 임시조직 운영.</t>
+          <t>IT기능: 정보기획·정보연계·응용품질·데이터품질(AI전략기술본부), 개인정보보호·정보보안·정보자원관리(정보보호본부), 복지정보시스템 개발·운영(복지정보본부), 데이터 분석·관리(사회보장정보연구소)&lt;br&gt;조직이력: 종전 '전략기술본부'가 'AI전략기술본부'로, 산하 '정보기획부'가 'AI정보기획부'로 명칭 변경 확인(2026-09-18 라이브 조직도). 2025년 AI 전담 부서 신설, 2025.11 보건복지부와 '제1차 사회보장 AI TF'(전략기획·법제도·인프라·기술혁신 4개 분야) 구성·정례화&lt;br&gt;기타: 정보화 전문 공공기관 특성상 IT 조직 비중 큼. 정보이사 산하 5개 본부(AI전략기술·복지정보·복지안전·사회서비스·전자바우처), 기획이사 산하에 정보보호본부·사회보장정보연구소 배치. 'K-소버린 AI 고속도로 연계 보건복지 AI 인퍼런스 클라우드센터' 구축 추진(정보보호본부장 발표)</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>산단AI 에너지본부 (정보화·AI 총괄) / 정보보안은 기획관리본부 기획조정실 정보보안팀</t>
+          <t>산단AI 에너지본부</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>산단 AI전략실(산단 AI 전환팀, AI 플랫폼팀(5G 특화망추진센터), 산단데이터분석팀), 산단e전환실(산단e기획팀, 산단e효율화팀, 산단e사업팀)</t>
+          <t>산단 AI전략실(산단 AI 전환팀·AI 플랫폼팀), M.AX 표준·인증센터(산단데이터분석팀·M.AX 인프라인증팀·M.AX 솔루션인증팀), 산단e전환실(산단e기획팀·산단e효율화팀·산단e사업팀)</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>산단AI 에너지본부 / 산단 AI전략실 (산단 AI 전환팀)</t>
+          <t>산단AI 에너지본부 / 산단 AI전략실</t>
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>본부(산단AI 에너지본부) 산하 실(산단 AI전략실)</t>
+          <t>본부 / 실</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr">
@@ -8731,17 +8731,17 @@
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보안팀이 기획관리본부 기획조정실 산하 — 기획관리본부장 겸임 추정)</t>
+          <t>확인불가 (정보보안 전담은 기획관리본부 기획조정실 정보보안팀(개인정보보호센터)이 수행, 별도 CISO 직위 미확인)</t>
         </is>
       </c>
       <c r="N110" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 검색 교차)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>정보화·AI·에너지(저탄소) 기능을 묶은 '산단AI 에너지본부' 체계. AI 전략 전담 실(산단 AI전략실)과 산단데이터분석팀 보유. 지역본부에 '반월시화AX실증산단센터' 등 AX(AI 전환) 실증 조직 존재. AI 기반 사업계획서 작성 서비스 등 대국민 AI 서비스 운영 중.</t>
+          <t>IT담당배경: '산단AI 에너지본부'는 명칭에 정보화가 없으나 공단의 정보화·AI·데이터 기능을 통합 관할하는 최상위 IT 조직임(저탄소·에너지 기능 병행). IT기능: 산단 AI 전환, AI 플랫폼(5G 특화망추진센터), 산단 데이터분석, M.AX 인프라·솔루션 인증, 산단 e전환(에너지 효율화). 조직이력: 2026년 조직도 기준 산단AI 에너지본부 산하에 'M.AX 표준·인증센터' 편제 확인(산단데이터분석팀이 동 센터 소속으로 이동, 종전 산단 AI전략실 소속에서 변경). 기타: 지역본부에 '반월시화AX실증산단센터'(경기지역본부), '구미탄소중립산단센터'(경북지역본부) 등 AX·저탄소 실증 조직 운영. 정보보안팀은 IT본부가 아닌 기획관리본부 기획조정실 소속으로 기획·운영과 분리.</t>
         </is>
       </c>
     </row>
@@ -8996,32 +8996,32 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>AI디지털실 (부원장 직속)</t>
+          <t>AI디지털실</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 부원장 직속 실</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>AI전략팀, 정보보호팀, 디지털교육팀, 홍보미디어팀 (모두 AI디지털실 산하)</t>
+          <t>AI전략팀, 정보보호팀, 디지털교육팀, 홍보미디어팀</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>있음 (AI전략팀)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>AI전략팀 (AI디지털실 산하)</t>
+          <t>AI전략팀</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>팀 (AI디지털실 산하)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>조직개편으로 종전 '정보화전략팀(경영지원실 산하 팀)'·'빅데이터분석팀(소비자정보국 산하)' 체제에서 부원장 직속 'AI디지털실'(실 레벨)로 격상·통합. AI디지털실 산하 AI전략팀·정보보호팀·디지털교육팀·홍보미디어팀 구성. IT 조직 위상이 팀→실 레벨로 상향, AI 전담팀(AI전략팀) 신설.</t>
+          <t>IT기능: AI전략(AI 도입·활용 전략), 정보보호, 디지털교육, 홍보미디어를 AI디지털실이 통합 수행.&lt;br&gt;조직이력: 종전 '정보화전략팀(경영지원실 산하)'·'빅데이터분석팀(소비자정보국 산하)' 체제에서 부원장 직속 'AI디지털실'로 격상·통합. IT 조직 위상이 팀→실 레벨로 상향되고 AI 전담팀(AI전략팀) 신설.&lt;br&gt;조직위치: AI디지털실은 부원장 직속으로 상위 본부가 없으며 기획조정실·인재경영실·정책연구실·정책평가실과 병렬(2026-09-18 라이브 조직도 확인). AI전략팀은 AI디지털실 산하.&lt;br&gt;기타: 시장조사국 산하에 'AI광고감시단'을 별도 운영(AI 활용 온라인 부당광고 감시). 소비자안전센터 스마트제품시험국에 디지털정보통신팀 배치.</t>
         </is>
       </c>
     </row>
@@ -9671,17 +9671,17 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>AI디지털혁신실</t>
+          <t>전략본부</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 기획이사 산하 실</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>AI기획팀, 정보보안팀</t>
+          <t>AI디지털혁신실(AI기획팀·정보보안팀)</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
@@ -9696,27 +9696,27 @@
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
-          <t>실(AI디지털혁신실) — 산하 AI기획팀</t>
+          <t>실 / 팀</t>
         </is>
       </c>
       <c r="L123" s="3" t="inlineStr">
         <is>
-          <t>AI디지털혁신실장 총괄 (기획이사 산하), 전담 CIO 직책 명시 확인불가</t>
+          <t>AI디지털혁신실장(권진온) 총괄, 전담 CIO 직책 명시 확인불가</t>
         </is>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
-          <t>정보보안팀 중심 (AI디지털혁신실 산하), 전담 직책 명시 확인불가</t>
+          <t>개인정보 보호책임자 = AI디지털혁신실 권진온(044-270-5090, 공식 개인정보처리방침). 실무는 AI디지털혁신실 산하 정보보안팀. 별도 CISO 임원 직위 명시는 확인불가</t>
         </is>
       </c>
       <c r="N123" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>실 명칭을 'AI디지털혁신실'로 명명하여 AI를 전면 배치. 산하에 AI기획팀 별도 운영. 소속기관(국립백두대간수목원·국립세종수목원)에도 'AI디지털확산팀'(운영지원실 산하) 배치하여 AI 조직을 다층 운영.</t>
+          <t>IT기능: AI·디지털 혁신전략 수립, 정보화 기본계획 총괄, 정보화사업 발굴·기획·성과관리, EA 수립·관리, 정보화 예산 편성, 공공데이터 개방·데이터 표준화·품질관리, 통합경영정보시스템 관리, 정보인프라(서버·네트워크·응용프로그램)·홈페이지 운영, 정보보안·개인정보보호 정책, 사이버 침해사고 대응, 정보시스템 구축·운영·유지관리&lt;br&gt;조직이력: 기획이사 산하 전략본부(기획조정실·ESG성과실·AI디지털혁신실) 체계. 실 명칭을 'AI디지털혁신실'로 명명하여 AI를 전면 배치&lt;br&gt;기타: 소속기관(국립백두대간수목원·국립세종수목원)에도 'AI디지털확산팀'(운영지원실 산하) 배치하여 AI 조직을 다층 운영</t>
         </is>
       </c>
     </row>
@@ -9746,17 +9746,17 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (정보보안팀 등 정보화 기능 소속) / 산림복지디지털연구실(디지털 R&amp;D 별도 실)</t>
+          <t>부원장</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 부원장(상임이사) 산하 실</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>정보보안팀(경영지원실 소속, 공식 확인) 외 정보화 담당 팀 (동 실 소속 추정)</t>
+          <t>경영지원실(정보보안팀), 산림복지디지털연구실</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="N124" s="3" t="inlineStr">
         <is>
-          <t>중(공식 2출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + 개인정보처리방침 교차)</t>
         </is>
       </c>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>2025년 직무중심 인사·조직개편. 부원장(상임이사) 산하 본부/실: 안전경영실·경영지원실·미래전략본부·산림복지서비스본부·민간성장지원본부·산림복지디지털연구실. 정보보안팀은 경영지원실 소속(개인정보처리방침 확인). '산림복지디지털연구실'은 디지털 R&amp;D 전담 실로 일반 정보화 운영과는 별개. AI 명칭 전담조직 없음.</t>
+          <t>조직위치: IT 기능이 **부원장 직속 병렬 2개 실**에 나뉘어 있음 — ① 경영지원실(정보보안팀 보유, 기관 정보화·정보보안 담당) ② 산림복지디지털연구실(산림복지 디지털 R&amp;D 전담). **두 실은 상하관계가 아니라 부원장 직속 동급 병렬**이므로 조직도 루트를 공통 상위인 '부원장'으로 두고 두 실을 병렬 노드로 표현(2026-09-18 라이브 조직도: 부원장 직속 = 안전경영실·경영지원실·미래전략본부·산림복지서비스본부·민간성장지원본부·산림복지디지털연구실).&lt;br&gt;IT담당배경: '경영지원실'이 정보보안팀을 두고 기관 정보화·정보보안을 담당(개인정보보호책임자=경영지원실장). '산림복지디지털연구실'은 명칭과 달리 일반 정보화 운영이 아닌 산림복지 디지털 R&amp;D 전담 실&lt;br&gt;IT기능: 정보보안·개인정보보호(경영지원실 정보보안팀), 산림복지 디지털 연구·기술개발(산림복지디지털연구실)&lt;br&gt;조직이력: 2025년 직무중심 인사·조직개편&lt;br&gt;기타: 부원장(상임이사) 산하 본부/실 6개(안전경영실·경영지원실·미래전략본부·산림복지서비스본부·민간성장지원본부·산림복지디지털연구실). 소속기관으로 국립산림치유원·국립진안고원산림치유원 및 8개 숲체원 운영. AI 명칭 전담조직 없음</t>
         </is>
       </c>
     </row>
@@ -10046,17 +10046,17 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>기획처(정보보안팀 소속)</t>
+          <t>기획조정실</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>팀 (기획처 산하 정보보안팀)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>정보보안팀(기획처), 검사정보팀(검사처)</t>
+          <t>정보보안팀, AI전환팀</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
@@ -10066,17 +10066,17 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>AI전환팀 (사업이사 직속)</t>
+          <t>AI전환팀</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>팀 (사업이사 직속)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보화 총괄은 기획처장 추정)</t>
+          <t>확인불가 (정보화 총괄은 기획조정실장 추정)</t>
         </is>
       </c>
       <c r="M128" s="3" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="N128" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 부서안내 교차)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>별도 정보화처/본부 없음. IT기획·운영은 기획처 산하 정보보안팀이 수행. 2026년 조직도 기준 사업이사 직속으로 'AI전환팀' 신설(AI 전환 추진), '석유관리원 혁신 추진단' 산하 '관제센터 구축팀' 운영. 검사처 산하 검사정보팀이 검사 정보시스템 담당.</t>
+          <t>조직위치: **AI전환팀은 경영이사 소속이 아니라 사업이사 직속**으로, 검사처·사업처·수소유통관리센터와 병렬(2026-09-18 라이브 조직도 확인). IT하위부서에는 조직도 렌더링을 위해 함께 표기했으나 기획조정실 산하가 아님. 정보보안팀은 경영이사&gt;기획조정실 산하(기획예산팀·성과혁신팀과 병렬).&lt;br&gt;IT기능: 정보화 기획·운영·정보보안을 기획조정실 정보보안팀이 통합 수행. 검사처 산하 검사정보팀이 석유제품 검사 정보시스템 담당.&lt;br&gt;조직이력: 2026년 조직도 기준 종전 '기획처'→'기획조정실', '지원안전처'→'지원처'로 개편되고 안전보건팀이 이사장 직속으로 분리. 종전 '혁신추진단'은 '관제센터추진단(제도기획팀·관제구축팀)'으로 개편되어 경영이사 산하 배치. 사업이사 직속 'AI전환팀' 유지.&lt;br&gt;기타: 별도 정보화처·본부 없이 팀 단위 IT 체계. 수소유통관리센터(수소전략팀·수소유통팀) 운영.</t>
         </is>
       </c>
     </row>
@@ -10426,12 +10426,12 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 산업혁신부원장 직속 실 단위</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>AI정보화실(정보화 총괄), 정보보안실(경영혁신부원장 산하)</t>
+          <t>AI정보화실, 정보보안실</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>AI정보화실(내부 정보화/AI 담당), 첨단AX본부(사업조직)</t>
+          <t>AI정보화실(내부 정보화·AI), 첨단AX본부(사업조직)</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>실(부원장 직속) / 본부(사업조직)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L133" s="3" t="inlineStr">
@@ -10461,12 +10461,12 @@
       </c>
       <c r="N133" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 2출처)</t>
+          <t>상(공식 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>내부 정보화 조직을 'AI정보화실'로 명명하여 AI를 정보화 조직 명칭에 포함. 사업조직으로 '첨단AX본부' 보유(산업 AX 정책·사업). 3부원장 체제(산업혁신/지역혁신/경영혁신).</t>
+          <t>IT담당배경: 'AI정보화실'은 산업혁신부원장 직속 실로 내부 정보화와 AI를 한 조직에 통합. '정보보안실'은 경영혁신부원장 직속으로 분리 배치&lt;br&gt;IT기능: 내부 정보화·AI(AI정보화실), 정보보안(정보보안실)&lt;br&gt;기타: 사업조직으로 '첨단AX본부'(산업AX PD·산업AX전략실·산업AX사업실·반도체산업기반실·첨단산업기반실) 보유 — 산업 AX 정책·사업 담당이며 내부 IT 조직 아님. 3부원장 체제(산업혁신/지역혁신/경영혁신)</t>
         </is>
       </c>
     </row>
@@ -10501,12 +10501,12 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>본부 (경영전략부원장 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>AX전략본부(공공행정AX실/정보보안실/범부처RCMS실)</t>
+          <t>AX전략본부(공공행정AX실·정보보안실·범부처RCMS실)</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>산업AI본부(사업조직), AX전략본부(내부 AX/정보화)</t>
+          <t>AX전략본부(내부 AX·정보화), 산업AI본부(사업조직)</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>본부 (산업혁신부원장 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="N134" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도)</t>
+          <t>상(공식 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O134" s="3" t="inlineStr">
         <is>
-          <t>내부 정보화·정보보안을 'AX전략본부'(공공행정AX실/정보보안실/범부처RCMS실)로 통합. 별도로 사업조직인 '산업AI본부'(제조AX확산정책실/AI기계로봇실/AI바이오헬스실/M.AX얼라이언스추진단TF) 보유. 2부원장 체제(경영전략/산업혁신).</t>
+          <t>IT기능: 공공행정 AI전환·내부 정보화(공공행정AX실), 정보보안(정보보안실), 범부처 연구비관리시스템 RCMS 운영(범부처RCMS실)&lt;br&gt;기타: 내부 정보화·정보보안을 'AX전략본부'로 통합해 조직명에 AX를 반영. 별도로 사업조직인 '산업AI본부'(제조AX확산정책실·AI기계로봇실·AI바이오헬스실·M.AX얼라이언스추진단TF) 보유 — 처장 보고 시 '사업으로서의 AI'와 '내부 AI 거버넌스' 구분 필요. 2부원장 체제(경영전략/산업혁신)</t>
         </is>
       </c>
     </row>
@@ -11621,17 +11621,17 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>기획조정실 산하 디지털혁신부 (경영기획이사 소속)</t>
+          <t>경영기획이사</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>부 (경영기획이사 &gt; 기획조정실 라인의 디지털혁신부)</t>
+          <t>부</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신부 (정보화·디지털 전환 담당)</t>
+          <t>디지털혁신부</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>AI소방기술연구소 (원장 직속)</t>
+          <t>AI소방기술연구소</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
-          <t>연구소 (원장 직속, 본부급)</t>
+          <t>연구소</t>
         </is>
       </c>
       <c r="L149" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영기획이사가 디지털혁신부 총괄로 추정)</t>
+          <t>확인불가 (경영기획이사가 디지털혁신부 총괄)</t>
         </is>
       </c>
       <c r="M149" s="3" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="O149" s="3" t="inlineStr">
         <is>
-          <t>원장 직속으로 AI소방기술연구소를 별도 설치(AI 전담조직 명확). 정보화·디지털 전환은 경영기획이사 산하 디지털혁신부가 담당. 조직은 원장 아래 경영기획이사·기술사업이사·안전사업이사 + 산업진흥센터·소방장비교육센터 + AI소방기술연구소 구조</t>
+          <t>IT기능: 디지털혁신부가 정보화·디지털 전환 업무 담당.&lt;br&gt;기타: 원장 직속으로 AI소방기술연구소를 별도 설치해 AI를 연구소 레벨로 격상. 정보화(디지털혁신부)와 AI(AI소방기술연구소)가 분리 운영되는 구조. 경영기획이사 산하에 기획조정실·경영관리부·디지털혁신부·소방방재제품PL상담센터·안전관리부가 병렬 배치되며, 그 외 산업진흥센터·기술사업이사·안전사업이사·소방장비·교육센터로 구성.</t>
         </is>
       </c>
     </row>
@@ -11846,32 +11846,32 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>디지털전략실 (전략사업본부 산하)</t>
+          <t>전략사업본부</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>디지털전략실(국제협력팀). 전략사업본부 내 병렬: 기후블루카본실·부산어촌특화센터</t>
+          <t>디지털전략실(국제협력팀)</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>있음 — 2025.9월경 전략사업본부 및 디지털전략실 신설(디지털·AI 전환 전담조직). 디지털전략실이 AI·클라우드 기반 업무혁신·데이터 표준화 총괄</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>디지털전략실 (전략사업본부 산하)</t>
+          <t>디지털전략실</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>실(본부 산하)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr">
@@ -11886,12 +11886,12 @@
       </c>
       <c r="N152" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 개인정보처리방침 + 보도자료 다수로 디지털전략실·AI전환·CPO 확인)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O152" s="3" t="inlineStr">
         <is>
-          <t>정보화·디지털·AI 총괄은 2025.9월 신설된 전략사업본부 산하 '디지털전략실'(국제협력팀)이 수행 — 데이터 진단·품질관리, 통합DB 운영, 재난대응(BCP·DR), 공공데이터 개방, AI·클라우드 기반 업무혁신 전담. 11개 사업별 AI 도입 방안 마련, TAC 관리 등 핵심업무 AI 본격 도입. 2026 창립15주년 '스마트·AI FIRA 전환' 비전 선포. '디지털어업관리실'은 별개의 어업관리 업무 단위.</t>
+          <t>IT기능: 데이터 진단·품질관리, 통합DB 운영, 재난대응(BCP·DR), 공공데이터 개방, AI·클라우드 기반 업무혁신&lt;br&gt;조직이력: 2025.9 전략사업본부 및 디지털전략실 신설(디지털·AI 전환 전담조직)&lt;br&gt;기타: 11개 사업별 AI 도입 방안 마련, TAC 관리 등 핵심업무 AI 본격 도입. 2026 창립15주년 '스마트·AI FIRA 전환' 비전 선포. 전략사업본부 내 병렬 부서는 기후블루카본실·부산어촌특화센터. '디지털어업관리실'은 별개의 어업관리 업무 단위. 디지털전략실은 전략사업본부 산하 실급 조직(이사장&gt;전략사업본부&gt;디지털전략실)</t>
         </is>
       </c>
     </row>
@@ -13496,17 +13496,17 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>디지털정보실 (경영기획본부 산하)</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>디지털정보실 (정보화·정보보안·개인정보보호 담당 / 하위 팀 구분 확인불가)</t>
+          <t>디지털정보실</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>해당없음 (전담 부서 미신설)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K174" s="3" t="inlineStr">
@@ -13526,22 +13526,22 @@
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영기획본부장 또는 디지털정보실장 소관 추정)</t>
+          <t>경영기획본부장 소관 (추정). 실무 총괄은 디지털정보실장 — 전담 CIO 직위 명시는 확인불가</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (디지털정보실 정보보안 담당)</t>
+          <t>디지털정보실 (개인정보 보호책임자 = 디지털정보실 안경호, 보호담당자 = 디지털정보실 김지현·변승현). 별도 CISO 임원 직위 명시는 확인불가</t>
         </is>
       </c>
       <c r="N174" s="3" t="inlineStr">
         <is>
-          <t>상 (공식 홈페이지 조직도에서 디지털정보실 직접 확인 + AI 추진 언론보도 다수 교차)</t>
+          <t>상 (공식 홈페이지 조직도 + 공식 개인정보 처리방침 직접 확인)</t>
         </is>
       </c>
       <c r="O174" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부 산하 6실 체계(기획조정실·안전보건실·ESG혁신실·경영지원실·재무회계실·디지털정보실). 'FiPA AI 활용 경진대회' 등 직원 참여형 AI 디지털 전환 추진. 해양수산부와 국가어업 '인공지능 전환 플랫폼' SPC에 공공 출자자로 참여(AI 양식장 자동화 등). AI는 사업·플랫폼 차원에서 활발하나 별도 전담 조직은 디지털정보실이 겸함.</t>
+          <t>IT기능: 정보화·정보보안·개인정보보호 총괄(개인정보 열람청구 접수·처리 부서 = 디지털정보실).&lt;br&gt;기타: 경영기획본부 산하 6실 체계(기획조정실·안전보건실·ESG혁신실·경영지원실·재무회계실·디지털정보실). 이사장 아래 감사실 + 5개 본부·단(경영기획본부·어촌해양본부·어항본부·어장양식본부·어촌어항재생사업단) + 4개 지사(동남해·서남해·제주·동해). 'FiPA AI 활용 경진대회' 등 직원 참여형 AI 디지털 전환 추진. 해양수산부와 국가어업 '인공지능 전환 플랫폼' SPC에 공공 출자자로 참여(AI 양식장 자동화 등). AI는 사업·플랫폼 차원에서 활발하나 별도 전담 조직 없이 디지털정보실이 겸함.</t>
         </is>
       </c>
     </row>
@@ -13586,37 +13586,37 @@
       </c>
       <c r="I175" s="3" t="inlineStr">
         <is>
-          <t>없음 (조직 차원 AI 전담부서 미확인 — 기술혁신본부가 스마트HACCP·AI 기반 분석모델 사업을 사업 단위로 수행)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>HACCP AX 추진단</t>
         </is>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>단</t>
         </is>
       </c>
       <c r="L175" s="3" t="inlineStr">
         <is>
-          <t>기술혁신본부장 총괄 (정보화·스마트HACCP 사업 주관, 인증사업이사 산하) — 전담 CIO 직위 미확인</t>
+          <t>기술혁신본부장 총괄 (정보화·스마트HACCP 사업 주관). 기술혁신본부장(이경순)이 HACCP AX 추진단장 겸임 — 전담 CIO 직위 명시는 확인불가</t>
         </is>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>기술혁신본부(IT전략팀) 소관 (추정) — 별도 CISO 임원 직위 미확인</t>
+          <t>기술혁신본부 IT전략팀 소관 (정보보안 운영계획 수립·전산실 운영, 개인정보보호 내부관리계획 수립 담당자 배치 확인) — 별도 CISO 임원 직위 미확인</t>
         </is>
       </c>
       <c r="N175" s="3" t="inlineStr">
         <is>
-          <t>중(위키 조직표 + 공식 누리집·data.go.kr 제공부서(기술혁신본부) 교차 / 팀명 1차자료는 위키 의존)</t>
+          <t>상(공식 홈페이지 조직도·부서별 담당업무 직접 확인)</t>
         </is>
       </c>
       <c r="O175" s="3" t="inlineStr">
         <is>
-          <t>인증사업이사 산하에 기술혁신본부(스마트기획팀·스마트운영팀·IT전략팀)를 두어 스마트HACCP 등 정보화·디지털 사업 담당. 스마트HACCP 데이터·서비스(축산물 스마트HACCP 인증정보 등) 제공부서가 기술혁신본부로 확인됨(data.go.kr 메타데이터). 음료 제조업 대상 AI 기반 분석모델 개발 민관 협력 추진 보도 있음 — 사업 단위이며 AI 전담조직과는 별개.</t>
+          <t>IT기능: 스마트기획팀(스마트HACCP 법령·정책, 해썹통합관리시스템 구축), 스마트운영팀(스마트HACCP 등록평가·기술지원, 부처협업형 스마트공장 지원), IT전략팀(공공데이터·데이터기반행정, 스마트HACCP 빅데이터 플랫폼, 정보보안·전산실 운영, 개인정보보호, 정보시스템 운영).&lt;br&gt;조직이력: 원장 직속으로 'HACCP AX 추진단' 신설(AX 신규사업 기획, 해썹통합관리시스템 운영 기획·데이터 품질/정책 수립). 단장은 기술혁신본부장 겸임, 팀장은 스마트기획팀장 겸임. 원장 직속 '미래전략추진실(미래사업팀)', '청사이전추진단 TF', '한국할랄인증센터(품질책임팀·인증심사팀)'도 함께 확인.&lt;br&gt;기타: 음료 제조업 대상 AI 기반 분석모델 개발 민관 협력 추진 보도. 6개 지원·2 출장소·중국주재소 운영.</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>정보화팀</t>
+          <t>경영혁신본부</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -14106,27 +14106,27 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>정보화팀(단일 팀, 정보기술기획·정보화업무(ISP)·정보보호 관리·운영 담당)</t>
+          <t>연구지원·정보실(정보화팀), 연구혁신본부(AI융합연구단)</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>(해당없음)</t>
+          <t>AI융합연구단</t>
         </is>
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>(해당없음)</t>
+          <t>단</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보화팀 상위 본부장 겸임 추정)</t>
+          <t>확인불가 (경영혁신본부장 총괄 추정)</t>
         </is>
       </c>
       <c r="M182" s="3" t="inlineStr">
@@ -14136,12 +14136,12 @@
       </c>
       <c r="N182" s="3" t="inlineStr">
         <is>
-          <t>중(공식/공공데이터 출처 다수, 정보화팀 상위 본부 직접확인 미달)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O182" s="3" t="inlineStr">
         <is>
-          <t>정보화 전담조직은 '정보화팀' 단일 팀 단위. 별도 IT본부/처 없음. R&amp;D 차원의 '저탄소·디지털전환 사업단'은 세라믹 소재 분야 디지털 전환기술 연구개발 조직으로, 기관 내부 정보화·AI 거버넌스 조직이 아님(혼동 주의). 본부 구성: 소재융합고도화연구본부, 신성장소재연구본부, 산업지원본부, 경영전략본부 등 + 이천분원. 정보화팀은 경영전략(경영지원) 계열 소속으로 추정.</t>
+          <t>IT담당배경: '연구지원·정보실'은 연구행정 지원과 정보화를 함께 담당하는 실 단위 조직이며, 산하 **정보화팀**이 IT 실무를 전담. 같은 실 산하 '연구지원팀'은 연구행정 지원 부서로 IT 계통이 아니므로 IT하위부서에서 제외(2026-09-18 조직도상 연구지원·정보실 = 연구지원팀 + 정보화팀 2개 팀).&lt;br&gt;AI조직성격: AI융합연구단은 연구혁신본부 산하 세라믹 소재 분야 AI 융합 **R&amp;D 조직**으로 기관 내부 정보화·AI 거버넌스 조직은 아니나, **통일 계상기준(조직명에 AI가 명시된 전담조직이 있으면 연구·사업 성격 불문 '있음')** 에 따라 AI전담조직='있음' 유지.&lt;br&gt;IT기능: 정보기술기획(정보화업무 기획·조정, ISP 수립·시행), 정보화시스템 운영, 정보보호 관리·운영.&lt;br&gt;기타: 연구혁신본부에 첨단소재공급망연구센터·양자·반도체연구단·바이오융합연구단·항공우주·방산연구단·기후·에너지연구단 병설. 진주 본원 + 이천분원 + 오송센터·수도권사무소.</t>
         </is>
       </c>
     </row>
@@ -14471,32 +14471,32 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>정보기술팀(경영본부 경영기획실 산하)</t>
+          <t>경영본부</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>팀 (본부 → 실 → 팀)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>정보기술팀(단일 팀)</t>
+          <t>경영기획실(정보기술팀)</t>
         </is>
       </c>
       <c r="I187" s="3" t="inlineStr">
         <is>
-          <t>없음 (전담 AI 조직은 미확인 / 미디어본부가 AI 기반 뉴스서비스 사업 수행)</t>
+          <t>없음 (명칭에 'AI'를 둔 전담조직 미확인 / 미디어본부 디지털혁신지원국이 뉴스빅데이터·AI 뉴스서비스 사업 수행)</t>
         </is>
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>(전담조직 없음 — 미디어본부 미디어연구센터·미디어진흥실에서 BIGKinds AI 뉴스서비스 등 AI 사업 추진)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K187" s="3" t="inlineStr">
         <is>
-          <t>(해당없음)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L187" s="3" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="O187" s="3" t="inlineStr">
         <is>
-          <t>문화체육관광부 산하 기타공공기관. 3개 본부 체계: 경영본부(경영기획실: 기획예산총괄팀·인재개발팀·경영지원팀·재무회계팀·정보기술팀), 미디어본부(종합교육연수원/미디어교육원, 미디어진흥실, 미디어연구센터 등), 정부광고본부. 행정 IT는 경영본부 경영기획실 '정보기술팀'이 총괄. AI는 별도 전담 행정조직 없이 미디어본부가 빅카인즈(BIGKinds) AI 기반 뉴스분석 서비스 등 사업 차원에서 수행.</t>
+          <t>IT기능: 행정 정보화·전산 총괄(경영본부 경영기획실 정보기술팀).&lt;br&gt;조직이력: 미디어본부에 '디지털혁신지원국(뉴스저작권팀·뉴스빅데이터팀)' 편성 확인 — 빅카인즈(BIGKinds) 등 뉴스데이터 사업 전담.&lt;br&gt;기타: 문화체육관광부 산하 기타공공기관. 4개 본부·원 체계: 경영본부(경영기획실: 기획예산총괄팀·인재개발팀·경영지원팀·재무회계팀·정보기술팀), 미디어본부(종합교육연수원/미디어교육원, 미디어진흥실, 디지털혁신지원국, 미디어연구센터), 정부광고본부(광고기획국·광고운영국), 신문유통원(지역언론지원국). AI는 별도 전담 행정조직 없이 미디어본부가 빅카인즈 AI 기반 뉴스분석 서비스 등 사업 차원에서 수행.</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>품질보안팀 (외 운영·개발 관련 팀 추정, 정확 구성 미확인)</t>
+          <t>IT운영실(IT기획팀·인프라운영팀·품질보안팀·서비스운영팀), IT혁신실(운영혁신팀·투표권정보기술팀·온라인기획팀·온라인정보기술팀)</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
@@ -15556,17 +15556,17 @@
       </c>
       <c r="M201" s="3" t="inlineStr">
         <is>
-          <t>IT본부 품질보안팀 (보안 담당부서)</t>
+          <t>IT본부 IT운영실 품질보안팀 (보안 담당부서)</t>
         </is>
       </c>
       <c r="N201" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처 + 보조출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O201" s="3" t="inlineStr">
         <is>
-          <t>2025.4 설립된 신생 기타공공기관. 국민체육진흥공단 100% 출자, 스포츠토토(체육진흥투표권) 발행사업 수탁 운영. 투표권시스템(K-TOS) 운영이 핵심 사업이라 IT본부가 본부급으로 비중 큼. 별도 AI 전담조직은 미확인.</t>
+          <t>IT기능: 투표권시스템(K-TOS) 운영·개발, IT기획, 인프라운영, 품질·보안, 서비스운영, 온라인(betman) 기획·정보기술&lt;br&gt;조직이력: 2025.4 설립된 신생 기타공공기관. 국민체육진흥공단 100% 출자, 스포츠토토(체육진흥투표권) 발행사업 수탁 운영&lt;br&gt;기타: 4개 본부(경영·상품·영업·IT) 중 IT본부가 유일하게 2실 8팀 규모로 편성될 만큼 IT 비중이 큼. 공식 조직도상 AI 명칭 조직은 없음</t>
         </is>
       </c>
     </row>
@@ -15746,17 +15746,17 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>전산정보팀 (기획경영본부 &gt; 경영지원실 산하)</t>
+          <t>기획경영본부</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>팀(본부 산하)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>전산정보팀 (단일 팀)</t>
+          <t>경영지원실(전산정보팀), 수문자료디지털자동화추진단(디지털자동화추진1팀·디지털자동화추진2팀), 한강AI품질팀, 낙동강AI품질팀, 금강AI품질팀, 영산강AI품질팀</t>
         </is>
       </c>
       <c r="I204" s="3" t="inlineStr">
@@ -15766,12 +15766,12 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>수문자료디지털자동화추진단(수자원조사본부 산하, 디지털자동화추진1·2팀) / 각 권역실 내 AI품질팀(한강·낙동강·금강·영산강 등 AI품질팀)</t>
+          <t>수문자료디지털자동화추진단(디지털자동화추진1팀·디지털자동화추진2팀) / 한강AI품질팀·낙동강AI품질팀·금강AI품질팀·영산강AI품질팀</t>
         </is>
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>단(본부 산하) / 팀(권역실 산하)</t>
+          <t>단 / 팀</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr">
@@ -15786,12 +15786,12 @@
       </c>
       <c r="N204" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 직접 확인)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O204" s="3" t="inlineStr">
         <is>
-          <t>수문조사 전문기관(KIHS, 2017 설립). 일반 정보화(전산)는 기획경영본부&gt;경영지원실&gt;전산정보팀이 담당(팀 단위). 반면 핵심 업무인 수문자료 품질관리에 AI를 적극 도입하여 '수문자료디지털자동화추진단'(디지털자동화추진1·2팀)과 각 권역실(한강/낙동강/금강/영산강 등)에 'AI품질팀'을 두는 등 현업 AI 조직이 다수 존재. 연구개발실은 'AI 기반 수자원 빅데이터 품질관리 기술개발' R&amp;D 수행.</t>
+          <t>조직위치: IT하위부서에 함께 표기한 AI 조직들의 실제 소속은 **기획경영본부가 아니라 수자원본부** — 수문자료디지털자동화추진단(디지털자동화추진1·2팀)은 수자원본부 산하 단급, 한강·낙동강·금강·영산강 AI품질팀은 각 **권역실 산하 팀**(각 권역실은 AI품질팀 외 1~6팀 보유, 영산강은 1~5팀). 조직도 렌더링을 위해 IT하위부서에 포함(가이드 STEP2-E). 전산정보팀은 기획경영본부 &gt; 경영지원실 산하(인사회계팀·경영지원팀과 병렬).&lt;br&gt;IT담당배경: 일반 정보화(전산)는 기획경영본부 &gt; 경영지원실 &gt; 전산정보팀이 담당(팀 단위). 수자원본부의 AI·디지털 조직은 정보화 거버넌스가 아니라 수문조사 데이터 품질관리·자동화라는 현업 업무 수행 조직이므로 IT 계통과 구분&lt;br&gt;기타: 수문조사 전문기관(KIHS, 2017 설립). 핵심 업무인 수문자료 품질관리에 AI를 적극 도입하여 수자원본부 산하 '수문자료디지털자동화추진단'과 4개 권역실(한강·낙동강·금강·영산강) 각각에 'AI품질팀'을 배치. 연구개발실은 'AI 기반 수자원 빅데이터 품질관리 기술개발' R&amp;D 수행</t>
         </is>
       </c>
     </row>
@@ -18521,17 +18521,17 @@
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>경영관리(부서) — 정보화 업무 포함, 별도 IT 전담조직 없음</t>
+          <t>없음 — 전산·정보화 전담부서/업무 미확인</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>팀(부) — IT 전담 본부·실 미존재</t>
+          <t>없음 (2본부 6팀 중 IT 전담 조직·업무 배정 없음)</t>
         </is>
       </c>
       <c r="H241" s="3" t="inlineStr">
         <is>
-          <t>별도 IT 전담부서 없음 (경영관리/경영기획에서 정보화 업무 수행)</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="I241" s="3" t="inlineStr">
@@ -18561,12 +18561,12 @@
       </c>
       <c r="N241" s="3" t="inlineStr">
         <is>
-          <t>중(공식 채용공고 + 보도·알리오 보조 / 정식 조직도 페이지 직접 접속 실패)</t>
+          <t>상(공식 조직도 라이브 확인 완료)</t>
         </is>
       </c>
       <c r="O241" s="3" t="inlineStr">
         <is>
-          <t>뉴서울컨트리클럽(골프장)을 운영·관리하는 소규모 공공기관. 1984년 설립(한국방송광고공사 출자 기원), 주무부처 문화체육관광부. 골프장 운영 특성상 별도 IT/AI 전담조직 없음 — 정보화는 경영관리 기능 내 수행, 청년인턴(정보화·코스관리) 채용 사례 존재.</t>
+          <t>한국문화진흥주식회사는 한국문화예술위원회 소유 골프장 '뉴서울컨트리클럽'을 수탁경영하는 문체부 산하 기타공공기관 — 별도 자회사가 아니라 동일 법인이 '뉴서울CC'라는 시설명(브랜드)으로 운영(공식 홈페이지 newseoulgolf.co.kr 저작권 표기: "한국문화진흥주식회사 뉴서울컨트리클럽"). (2026-09-18 라이브 재확인) 공식 조직도 확인 결과 2본부 6팀 체계(경영전략본부: 경영기획팀·마케팅팀·인프라관리팀 / 운영관리본부: 경기팀·서비스팀·코스팀) — 인프라관리팀은 시설·락카룸 관리 업무로 IT 인프라와 무관, 경영기획팀 담당업무에도 정보화·전산 항목 없음. 골프장 운영 특성상 IT/AI 전담조직 없음을 재확인.</t>
         </is>
       </c>
     </row>
@@ -19346,17 +19346,17 @@
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부(IT 전담 '정보화관리팀'이 본부 산하 경영지원부에 소속)</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>팀(정보화관리팀 — 경영기획본부 산하 경영지원부 소속)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H252" s="3" t="inlineStr">
         <is>
-          <t>정보화관리팀(정보화 전략 수립, 정보보안·개인정보보호 정책 및 시스템 관리, 대표홈페이지·행정지원시스템 관리, SW·공공데이터 개방, 전산장비 관리·기술지원)</t>
+          <t>경영지원부(정보화관리팀)</t>
         </is>
       </c>
       <c r="I252" s="3" t="inlineStr">
@@ -19376,22 +19376,22 @@
       </c>
       <c r="L252" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영기획본부장 총괄 추정 — 정보화관리팀이 본부 산하)</t>
+          <t>확인불가 (경영기획본부장이 정보화 총괄로 추정 — 정보화관리팀이 본부 산하)</t>
         </is>
       </c>
       <c r="M252" s="3" t="inlineStr">
         <is>
-          <t>정보화관리팀 내 정보보안 담당자 배치(정보보안·개인정보보호 정책 및 시스템 관리) — 전담 CISO 직위 명시는 확인불가</t>
+          <t>정보화관리팀이 정보보안·개인정보보호 정책 및 시스템 관리를 수행 — 전담 CISO 직위 명시는 확인불가</t>
         </is>
       </c>
       <c r="N252" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 2026년 채용공고 2출처 교차 확인)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O252" s="3" t="inlineStr">
         <is>
-          <t>본부 체계: 경영기획본부(기획조정부[경영기획팀·혁신성과팀], 경영지원부[인재개발팀·운영지원팀·정보화관리팀]), 사업총괄본부, 정책지원본부(정책연구부[연구개발팀·데이터분석팀·심리부검팀]). IT 전담조직은 경영기획본부 산하 경영지원부의 '정보화관리팀'이며, 정보화 전략·정보보안·전산장비·홈페이지(데이터줌·심즈 포함) 관리를 총괄. 데이터분석팀(정책지원본부)은 자살통계·심리부검 등 정책·통계 분석 담당으로 IT 인프라 조직과 구분.</t>
+          <t>IT담당배경: 재단 IT 전담조직은 경영기획본부 경영지원부 소속 '정보화관리팀'이며, 팀 단위 소규모 조직이 정보화 전반을 단독 수행. IT기능: 재단 정보화 전략 수립·시행, 정보보안·개인정보보호 정책 및 시스템 관리, 대표 홈페이지 관리, 행정 업무 지원 시스템 관리, 소프트웨어 관리 및 공공데이터 개방, 전산장비 관리·기술 지원. 조직이력: 2026년 조직도 기준 본부 체계가 3본부에서 4본부+1센터로 확대 — 경영기획본부·홍보교육본부(신설)·사업운영본부(구 사업총괄본부)·정책개발본부(구 정책지원본부)·상담지원센터(신설). 정보화관리팀의 소속(경영기획본부 경영지원부)은 유지. 기타: 데이터분석팀은 정책개발본부 정책연구부 소속으로 자살통계·심리부검 등 정책 데이터 분석(데이터줌, 자살통계연보) 담당 — IT 인프라·정보화 전담 조직과 구분. 상담지원센터 상담기획팀이 상담시스템 관리·운영을 별도 수행.</t>
         </is>
       </c>
     </row>
@@ -19571,19 +19571,19 @@
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
+          <t>경영기획본부</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr">
+        <is>
+          <t>팀</t>
+        </is>
+      </c>
+      <c r="H255" s="3" t="inlineStr">
+        <is>
           <t>정보화기획팀</t>
         </is>
       </c>
-      <c r="G255" s="3" t="inlineStr">
-        <is>
-          <t>팀(경영기획본부 산하)</t>
-        </is>
-      </c>
-      <c r="H255" s="3" t="inlineStr">
-        <is>
-          <t>단일 팀(하위부서 없음) — 담당: 차세대 구축/예산, 사회적기업포털/인프라/범정부EA, 개인정보/정보보안/업무지원시스템/KMC/웹메일, 공공데이터/대표홈페이지/협동조합포털</t>
-        </is>
-      </c>
       <c r="I255" s="3" t="inlineStr">
         <is>
           <t>없음</t>
@@ -19616,7 +19616,7 @@
       </c>
       <c r="O255" s="3" t="inlineStr">
         <is>
-          <t>정보화 조직이 '팀' 레벨(경영기획본부 산하)로, 본부·실 단위 IT 조직 없음. 차세대 정보시스템 구축 추진 중. 사회적기업포털(seis.or.kr)·협동조합포털·대표홈페이지 등 다수 대국민 시스템 운영. AI 관련은 협동조합 맞춤형아카데미('AI와 디지털 기술 활용 사회서비스 혁신' 교육) 등 사업성 활용에 그치며 전담 직제 조직은 없음.</t>
+          <t>IT기능: 차세대 정보시스템 구축·정보화예산, 사회적기업 통합정보시스템(seis.or.kr)·IT인프라·범정부EA, 개인정보보호·정보보안·업무지원시스템·KMC·웹메일, 공공데이터 개방·대표홈페이지·협동조합포털&lt;br&gt;기타: 정보화 조직이 '팀' 레벨로, 본부·실 단위 IT 조직 없음. AI 관련은 협동조합 맞춤형아카데미('AI와 디지털 기술 활용 사회서비스 혁신' 교육) 등 사업성 활용에 그치며 전담 직제 조직은 없음</t>
         </is>
       </c>
     </row>
@@ -20171,17 +20171,17 @@
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
-          <t>경영기획실 (산하 디지털정보화팀)</t>
+          <t>경영기획실</t>
         </is>
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>실(室) 산하 팀 — IT기능은 경영기획실 내 디지털정보화팀</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr">
         <is>
-          <t>디지털정보화팀</t>
+          <t>AI혁신부</t>
         </is>
       </c>
       <c r="I263" s="3" t="inlineStr">
@@ -20196,27 +20196,27 @@
       </c>
       <c r="K263" s="3" t="inlineStr">
         <is>
-          <t>부(部) — 경영기획실 산하 (기획조정부·미래전략부·경영지원부와 병렬)</t>
+          <t>부</t>
         </is>
       </c>
       <c r="L263" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영기획실장 총괄 추정)</t>
+          <t>경영기획실장 (김지현) — 개인정보 보호책임자 겸임. 전담 CIO 직위 명시는 확인불가</t>
         </is>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>경영기획실 AI혁신부 (개인정보보호 담당자 박재은, 063-720-0585). 별도 CISO 임원 직위 명시는 확인불가</t>
         </is>
       </c>
       <c r="N263" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 이미지 alt텍스트 + 직원연락처·공공데이터 담당부서 교차 확인)</t>
+          <t>상(공식 홈페이지 조직도 + 공식 개인정보처리방침(2025.09판) 담당부서 교차 확인)</t>
         </is>
       </c>
       <c r="O263" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29 기준 조직도에서 경영기획실 산하에 'AI혁신부'가 명시되어 AI 전담조직 보유. 정보화 실무는 디지털정보화팀(063-720-0545)이 담당. '디지털식품정보플랫폼' 운영. 이사장 아래 경영기획실·사업본부 2원 체제.</t>
+          <t>조직위치: AI혁신부는 경영기획실 산하 부급 조직으로, 같은 실 산하 기획조정부·미래전략부·경영지원부와 병렬(2026-01-29 기준 공식 조직도).&lt;br&gt;기관유형부기: 농림축산식품부 산하 '국가식품클러스터'(전북 익산) 운영기관(알리오 기관유형 자체는 '기타공공기관').&lt;br&gt;IT담당배경: 'AI혁신부'는 AI 전담조직이자 기관 정보화 실무부서로, 전산자원 통합유지보수·클라우드·출입관리시스템 등 IT 운영과 개인정보보호 업무를 함께 수행(공식 개인정보처리방침 위탁·담당부서 표기로 확인).&lt;br&gt;IT기능: 전산자원 통합유지보수(시스템 운영·관리), KT 클라우드 기반 데이터 보관·시스템 운영, 출입관리시스템 운영, 개인정보보호 실무·고충처리.&lt;br&gt;기타: 이사장 아래 경영기획실·사업본부 2원 체제. '디지털식품정보플랫폼' 운영. '국가식품클러스터'(전북 익산) 운영기관 = 식품진흥원/푸드폴리스.</t>
         </is>
       </c>
     </row>
@@ -20546,17 +20546,17 @@
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>경영지원부 (산하 지식정보화팀이 정보화·정보보안·개인정보 총괄) / AI 교육사업은 별도 정보화AI교육추진단이 추진</t>
+          <t>정보화AI교육추진단</t>
         </is>
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>팀 (본부 산하 경영지원부 내 '지식정보화팀')</t>
+          <t>단</t>
         </is>
       </c>
       <c r="H268" s="3" t="inlineStr">
         <is>
-          <t>지식정보화팀(정보화·정보보안·개인정보 실무, 경영지원부 산하), 정보화AI교육추진단(AI기반미래교육사업·ISP 추진)</t>
+          <t>경영지원부(지식정보화팀)</t>
         </is>
       </c>
       <c r="I268" s="3" t="inlineStr">
@@ -20566,32 +20566,32 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
-          <t>정보화AI교육추진단 (조직명에 'AI' 명시) / 주요사업 'AI기반미래교육사업' 전담</t>
+          <t>정보화AI교육추진단</t>
         </is>
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>단(추진단) — 정보화·AI 교육사업 추진 조직</t>
+          <t>단</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr">
         <is>
-          <t>본부장 라인 총괄 추정 (개인정보보호책임자가 본부장 직책 — 동일 본부장이 정보화·보안 총괄 추정)</t>
+          <t>정보화AI교육추진단장 (원장 직속, 02-3156-6006)이 정보화·AI 총괄. 전담 CIO 직위 명시는 확인불가</t>
         </is>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
-          <t>개인정보보호책임자(CPO) 겸 보안 총괄: 본부장 김은희(02-3156-6002), 실무 담당부서 경영지원부 지식정보화팀(조형준·김하경) — CISO를 CPO/본부장이 겸하는 구조</t>
+          <t>정보보안·정보시스템·홈페이지 관리 담당은 정보화AI교육추진단(담당자 2명). 내부 개인정보보호는 경영전략본부 경영지원부 지식정보화팀도 병행 — 별도 CISO 임원 직위 명시는 확인불가</t>
         </is>
       </c>
       <c r="N268" s="3" t="inlineStr">
         <is>
-          <t>상(이러닝센터 공식 개인정보처리방침으로 CPO(본부장 김은희)·정보화 담당부서(경영지원부 지식정보화팀) 확정 + 공식 홈페이지/보도자료로 정보화AI교육추진단·AI사업 확인. 단 전체 조직도 트리(본부 정식 명칭)는 JS 렌더링으로 일부 미표출)</t>
+          <t>상(공식 홈페이지 조직도 트리 및 부서별 담당업무 명부 직접 확인)</t>
         </is>
       </c>
       <c r="O268" s="3" t="inlineStr">
         <is>
-          <t>약칭 '양평원'(KIGEPE). 정보화 조직명에 'AI'를 명시한 '정보화AI교육추진단' 운영. 2026.5월 'AI 기반 폭력 예방교육 혁신 정보화전략계획(ISP) 수립 사업' 착수(추진단 김수영 과장 02-3156-6124) — 폭력예방교육 플랫폼 AI·AX 대전환. 2026년 '모든 정보시스템 클라우드 전환' 보도 — 디지털 업무 혁신 추진. 본원(서울 은평) + 고양캠퍼스 2개소. 내부 정보화·정보보안·개인정보 거버넌스는 경영지원부 지식정보화팀이 수행.</t>
+          <t>조직위치: 정보화AI교육추진단은 원장 직속(전략연구센터·감사실과 병렬)이며 **하위 팀·부 편제 없이 단장 포함 12명의 담당자로만 구성**(2026-09-18 라이브 조직도에 하위 박스 없음 확인). 지식정보화팀은 별도 라인인 경영전략본부 &gt; 경영지원부 산하 팀으로, 추진단의 하위 조직이 아님(IT하위부서에는 가이드 STEP2-E에 따라 직속 상위인 경영지원부와 함께 표기).&lt;br&gt;IT담당배경: '정보화AI교육추진단'은 원장 직속 조직으로, AI 교육사업뿐 아니라 정보보안·정보시스템·홈페이지·공공데이터·전산 관리 등 기관 정보화 실무를 함께 수행(담당업무 명부로 확인).&lt;br&gt;IT기능: AI교육 플랫폼 구축 ISP, AI 공공데이터 지원, 정보보안·정보시스템·홈페이지 관리, 공공데이터·데이터기반 행정관리·전산 관리, 원격교육연수원 운영·이러닝 시스템 관리. 지식정보화팀은 정보화·정보보안·개인정보보호·전산인프라·내부 업무시스템·공공데이터 운영 담당.&lt;br&gt;기타: 약칭 '양평원'(KIGEPE). 원장(김삼화) 직속으로 전략연구센터·감사실·정보화AI교육추진단, 그 아래 4본부(경영전략본부·교육혁신본부·전문역량개발본부·문화확산본부) 체계. 주요사업에 'AI기반미래교육사업' 편성. 2026.5 'AI 기반 폭력 예방교육 혁신 ISP 수립 사업' 착수. 2026년 모든 정보시스템 클라우드 전환 추진. 본원(서울 은평) + 고양캠퍼스.</t>
         </is>
       </c>
     </row>
@@ -21130,11 +21130,11 @@
         <v>29</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -21146,11 +21146,11 @@
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
     </row>
@@ -21172,11 +21172,11 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="G4" s="5" t="n">
@@ -21198,27 +21198,27 @@
         <v>184</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>5.4%</t>
         </is>
       </c>
     </row>
@@ -21240,19 +21240,19 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
     </row>
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.1%</t>
         </is>
       </c>
     </row>
@@ -21324,11 +21324,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
     </row>
@@ -21339,11 +21339,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>
@@ -21400,11 +21400,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>39.2%</t>
         </is>
       </c>
     </row>
@@ -21461,11 +21461,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>89.4%</t>
         </is>
       </c>
     </row>
@@ -21476,11 +21476,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -671,17 +671,17 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>AI혁신단 (2026.3 기존 ICT기획처를 개편)</t>
+          <t>AI혁신단</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>처·실급(단) — 기존 ICT기획처 레벨에서 'AI혁신단'으로 격상</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>(개편 전) ICT기획처(ICT기획부·인프라계획실·ICT센터구축부), ICT인프라처(IT운영센터), 디지털변환처(디지털기획부·빅데이터기획실·솔루션사업부·플랫폼정책실)</t>
+          <t>AI전략실, 데이터정책부, ICT운영처, 정보보안처(개인정보보호부)</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -696,27 +696,27 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>단(처·실급) — AI 대전환 거버넌스 총괄</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (디지털변환처/ICT 담당 임원 체계 추정)</t>
+          <t>AI혁신단장(주재각)이 정보공개 책임자 겸 AI·정보화 총괄. 상위 기술혁신본부장(상임이사) 관할</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>안전보안처 정보보안전략실(정보보안 전담) — 확인불가(겸임 여부 미확인)</t>
+          <t>정보보안처 (경영관리본부 소속, 산하 개인정보보호부)</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>2026.3.23 나주 본사 'AI 경영혁신 선포식' 개최, 'KEPCO AI 대전환 추진 로드맵'(데이터·솔루션·인프라·거버넌스·조직문화 5대 전략) 수립. 기존 ICT기획처를 AI혁신단으로 전격 개편. 나주·대전 전력ICT센터를 AI 데이터센터로 전환, 2030년까지 고성능 GPU 300장 이상 확보, AI 전문인력 약 400명 확대 목표. 2030년 '에너지 플랫폼 사업자' 도약 비전.</t>
+          <t>[IT담당배경] 2026.3.23 나주 본사 'AI 경영혁신 선포식' 개최, 'KEPCO AI 대전환 추진 로드맵'(데이터·솔루션·인프라·거버넌스·조직문화 5대 전략) 수립. 기존 ICT기획처를 AI혁신단으로 개편. [IT기능] AI혁신단 AI전략실이 AI정책·정보공개 총괄, 데이터정책부가 공공데이터 개방·데이터기반행정 담당, ICT운영처가 전사 ICT 인프라 구축·운영 및 유지보수 발주 담당. [조직이력] 개편 전 3개 처 분산 구조(ICT기획처·ICT인프라처·디지털변환처) → 현 조직도상 ICT기획처·ICT인프라처·디지털변환처는 소멸하고 AI혁신단·ICT운영처로 재편. AI혁신단·ICT운영처 모두 기술혁신본부 소속, 정보보안처는 경영관리본부 소속으로 IT와 보안이 분리된 구조. [인력계획] 현 AI 전문인력은 전체의 1% 미만이며 2030년까지 약 400명으로 확대하는 것이 목표(보도 기준). 이는 향후 목표치이며 현재 IT/AI 인력 현원은 공식 공개 자료에서 확인되지 않아 IT인력규모는 '확인불가'로 기재. [기타] 나주·대전 전력ICT센터 AI 데이터센터 전환, 2030년까지 고성능 GPU 300장 이상 확보, 2030년 '에너지 플랫폼 사업자' 도약 비전. ICT 전문 자회사 한전KDN(별도 법인)이 그룹 ICT 상당부분 수행.</t>
         </is>
       </c>
     </row>
@@ -2996,17 +2996,17 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>디지털정보처 (구 디지털혁신처에서 개편, 안전이사 산하)</t>
+          <t>AI디지털처</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하 / 안전이사 직속)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>정보시스템부, AI데이터부, 정보보안부</t>
+          <t>디지털시스템부, AI데이터부, 정보보안부</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>AI데이터부 (디지털정보처 산하)</t>
+          <t>AI데이터부</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>부(처 산하) — 디지털정보처 내 정보시스템부·정보보안부와 병렬</t>
+          <t>부</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>디지털정보처장이 정보화 총괄 (안전이사 산하, 전담 CIO 직위 명시는 확인불가)</t>
+          <t>AI디지털처장이 정보화 총괄 (전담 CIO 직위 명시는 확인불가)</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>개인정보보호책임자(CPO)=정보보안부장 박준성(privacy@kesco.or.kr). 정보보안부가 정보보호 전담. 별도 임원급 CISO 직위 명시는 확인불가(부서장급 책임자 운영)</t>
+          <t>정보보안부가 정보보호 전담. 개인정보보호책임자(CPO)=정보보안부장(privacy@kesco.or.kr). 별도 임원급 CISO 직위 명시는 확인불가(부서장급 책임자 운영)</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 공식 개인정보처리방침 교차. 디지털정보처 3부 구조[정보시스템부·AI데이터부·정보보안부] 및 CPO 확정)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + tavily-extract 교차 + 공식 개인정보처리방침)</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>(2026-06-15 보완) 공식 조직도 재확인 결과 IT조직이 '디지털혁신처'에서 **'디지털정보처'**로 개편됨(안전이사 산하). 산하 3부 = 정보시스템부·**AI데이터부**·정보보안부. ICT융합부는 현 조직도에 없음(AI데이터부로 재편된 것으로 보임). **AI데이터부 신설로 AI전담조직 '있음' 확정**(데이터·AI 기능 전담 부). AI 활용도 활발: 2026.6 기후에너지환경부 산하 한국에너지기술평가원 국가연구개발 공모 선정(2026~4년 국비 220억) — AI·IoT 기반 원격점검·지능형 전기안전관리 플랫폼 구축. 2026.5 에너지 공공기관·LG AI연구원·NC AI 등 26개 기관 AI·DX 다자간 협약. 2025.9 전북대와 AI 기반 전기안전 미래기술 공동개발. CPO=정보보안부장 박준성(부서장급).</t>
+          <t>IT기능: 정보화 시스템 구축·운영(디지털시스템부), 데이터·AI 업무 전담(AI데이터부), 정보보안·개인정보보호(정보보안부).&lt;br&gt;조직이력: IT 총괄조직 명칭이 '디지털혁신처'(~2026상) → '디지털정보처' → **'AI디지털처'**로 연속 개편. 하위부서도 '정보시스템부·ICT융합부·정보보안부' → '정보시스템부·AI데이터부·정보보안부' → **'디지털시스템부·AI데이터부·정보보안부'**로 재편. 소속은 안전이사 산하 유지.&lt;br&gt;기타: 3이사 체제(기획이사(부사장)·안전이사·기술이사). AI디지털처는 안전이사 산하로 재난안전처·전기안전연구원·전기안전인재개발원과 병렬. 기술이사 산하 사업운영처에 '디지털점검부(디지털전환기획팀)'가 별도 편제 — 현장 전기안전 점검의 디지털화 담당(정보화 총괄조직과 구분). AI 사업 활발: AI 기반 디지털 안전관리 플랫폼 'E-On'(전국 ESS 2,444개 실시간 관제, 2026.7 기준 84건 사전 예방조치), 2026.6 AI·IoT 기반 원격점검·지능형 전기안전관리 플랫폼 국가연구개발 220억 선정, 2026.5 에너지 공공기관·LG AI연구원·NC AI 등 26개 기관 AI·DX 다자간 협약, 2025.9 전북대와 AI 기반 전기안전 미래기술 공동개발.</t>
         </is>
       </c>
     </row>
@@ -3071,12 +3071,12 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>AI디지털처 (기획관리본부 산하)</t>
+          <t>AI디지털처</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 기획관리본부 산하 처</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -3091,32 +3091,32 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>AI디지털처 / AI추진부(처 내 전담 부서)</t>
+          <t>AI추진부</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>처(기획관리본부 산하) 내 부(部) 단위 'AI추진부'</t>
+          <t>부(部)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>AI디지털처장 정보화 총괄, 기획관리본부장(상임이사) 관할 (추정)</t>
+          <t>AI디지털처장이 정보화 총괄, 기획관리본부장(상임이사) 관할 (추정)</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>AI디지털처 산하 정보보안실 (구 정보보안처에서 실로 통합)</t>
+          <t>정보보안실 (AI디지털처 소속, 산하 사이버안전센터 운영)</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>기존 '디지털혁신처'를 'AI디지털처'로 개편하며 'AI추진부' 신설. 2025.6 창립 25주년 'AX 비전' 선포(AI 중심 경영체계 전환), 기술안전본부장 주관 전사 'AX 추진위원회(통합 거버넌스, 30여명)' 발족, 고유 '에이전틱 AI' 개발, AI 기반 발전운영 최적화 추진. 과거 K-ICT 정보보호대상(과기부 장관상) 수상 등 정보보안 역량 우수.</t>
+          <t>[IT담당배경] 기존 '디지털혁신처'를 'AI디지털처'로 개편하며 'AI추진부' 신설. 2025.6 창립 25주년 'AX 비전' 선포(AI 중심 경영체계 전환). [IT기능] 디지털기획부가 정보화 중장기계획·ERP 고도화·공공데이터 개방·기준정보 및 마스터데이터 관리, 디지털플랫폼부가 정보통신 인프라·그룹웨어·발전/사무분야 정보시스템 개발·운영, AI추진부가 AI 기본계획·AI 프로젝트 관리·AI 학습데이터·AI 인프라·AI 윤리 및 리스크 관리, 정보보안실이 정보보안·개인정보보호·기반시설 제어시스템 보호 및 사이버안전센터 운영, 비상계획부가 시설보안·방호·기술보안 담당. [조직이력] AI디지털처는 기획관리본부 소속. 정보보안은 별도 처가 아니라 AI디지털처 내 '정보보안실'로 편제. 전사 AI 전환 거버넌스인 'AX 추진위원회'(30여명)는 기술안전본부장이 위원장을 맡아 조직(처)과 거버넌스(위원회)가 분리 운영. [기타] 고유 '에이전틱 AI' 개발, AI 기반 발전운영 최적화 추진. 과거 K-ICT 정보보호대상(과기부 장관상) 수상. ISMS-P 인증 보유.</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>ICT보안실 (IT기획·정보보안 총괄, 실급)</t>
+          <t>ICT보안실</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>ICT보안실(ICT보안기획팀·경영IT지원팀·보안운영팀), AX추진처(AX기획팀·AX솔루션개발팀·AX융합설계팀), 디지털솔루션연구소(전력기술연구원 산하)</t>
+          <t>ICT보안실(ICT보안기획팀, 경영IT지원팀, 보안운영팀), AX추진처(AX기획팀, AI솔루션개발팀, AI융합설계팀)</t>
         </is>
       </c>
       <c r="I53" s="3" t="inlineStr">
@@ -4441,32 +4441,32 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>AX추진처 (AX기획팀·AX솔루션개발팀·AX융합설계팀) + 디지털솔루션연구소(전력기술연구원 산하)</t>
+          <t>AX추진처</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>처 (AX추진처) + 연구소(전력기술연구원 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (AX기획팀이 전사 AI 전환 전략 총괄, 본부장급 CIO 명시 미확인)</t>
+          <t>확인불가 (ICT보안실장이 정보화 추진 기본전략 총괄, 본부장급 전담 CIO 직제는 미확인)</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>ICT보안실 산하 보안운영팀 (정보보안 실무 담당, ISO/IEC 27001 인증 보유)</t>
+          <t>ICT보안실 보안운영팀 (사이버보안·정보보호시스템 운영·보안관제·침해사고 대응·개인정보보호). ICT보안기획팀이 보안정책·규정·기반시설 보호·국가보안 담당</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>2025.12~2026.4 전사 AX(AI 전환) 체계 구축 추진, 'AI 미래전략' 수립. 세부과제는 디지털솔루션연구소 등 기존 AI 전담조직 중심 + 담당부서별 역할 분산. '제2회 대한민국 인공지능 혁신대상' 그랑프리 대상 수상. 2024 조직개편서 엔지니어링솔루션본부 신설. 원전 설계 전문기관으로 설계/엔지니어링 AI 융합(AX융합설계팀)이 핵심. 개인정보 보호수준평가 2년 연속 S등급.</t>
+          <t>[IT담당배경] 정보보안 전담조직의 위상·권한을 강화하기 위해 보안조직과 ICT 부서를 통합해 'ICT보안실'로 편제. 2026 한국경영대상 CEO-정보보안 부문 대상 수상. [IT기능] ICT보안실 ICT보안기획팀이 '정보화 추진 기본전략 기획·총괄'을 담당(전사 정보화 총괄), 경영IT지원팀이 경영·행정분야 정보시스템 구축·유지관리 담당. [조직이력] AX추진처는 사장 직할(비서실·안전품질처와 병렬), ICT보안실은 기획관리본부 소속. 종전 '전략기획본부·경영관리본부'는 '기획관리본부'로 통합. 전력기술연구원은 기술기획실 + 원전최적화기술연구소·원전안전기술연구소·기후대응기술연구소 체제로 개편되어 종전 '디지털솔루션연구소'는 현 직제에서 미등장. AX솔루션개발팀 → AI솔루션개발팀으로 명칭 변경. [기타] 사내 생성형 AI 서비스 'NEXA' 운영 및 AI DLP 솔루션 적용, 자체 '생성형 AI 개인정보 보호지침' 제정. 국정원 사이버보안 실태평가 3년 연속 최고등급, 개인정보 보호수준평가 2년 연속 최고등급, ISO/IEC 27001 인증. '제2회 대한민국 인공지능 혁신대상' 그랑프리 대상 수상. 원전 설계 전문기관으로 설계·엔지니어링 AI 융합(AI융합설계팀)이 핵심.</t>
         </is>
       </c>
     </row>
@@ -4796,52 +4796,52 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>디지털시스템실 (경영지원부문, 부사장 산하)</t>
+          <t>경영지원부문</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>AX전략팀, AI·데이터플랫폼팀, AI인프라팀, IT청렴계약팀, IT경영지원팀, 시스템개발부, 서울전산센터 등 (디지털시스템실 산하)</t>
+          <t>AI기획실(AI전략팀·AI데이터팀·AI인프라팀·AI혁신TF), 디지털운영실(AX전략팀·IT청렴계약팀·AI데이터플랫폼팀·IT경영지원팀·채권업무지원팀·위탁업무지원팀·국유업무지원팀·시스템개발부·서울전산센터)</t>
         </is>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>있음 (AI·데이터플랫폼팀, AI인프라팀)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>AI·데이터플랫폼팀(데이터기반행정·공공데이터·분석시스템), AI인프라팀 — 디지털시스템실 산하. AX전략팀이 디지털전환(AX) 전략 담당</t>
+          <t>AI기획실</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>팀 (디지털시스템실 산하)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>디지털시스템실장이 실질 정보화 책임자로 추정 (직책 명시 확인불가)</t>
+          <t>경영지원부문 총괄이사 관할, AI기획실장·디지털운영실장이 실무 총괄 (전담 CIO 직책 명시 확인불가)</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보안 전담 단일 팀 미확인 — AX전략팀·IT청렴계약팀이 '보안/부서보안' 업무 분담 수행)</t>
+          <t>확인불가 (정보보안 전담 단일 팀 미확인 — AX전략팀·IT청렴계약팀이 '부서일반보안' 업무 분담 수행)</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상 (2026-09-19 공식 조직도 페이지 + AI기획실·디지털운영실 부서·연락처 페이지 라이브 직접 확인)</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>약칭 캠코(KAMCO). 경영지원부문에 디지털시스템실 배치. 디지털시스템실 산하에 AX전략팀·AI·데이터플랫폼팀·AI인프라팀 등 AI/디지털전환 명칭 팀 다수 보유. '캠코형 디지털 전환'(국유재산 차세대 관리시스템), AI 기반 항공영상 변화탐지·AR 모바일 실태조사, 상담 챗봇 등 AI 사업 추진. 그룹웨어 재구축 시스템구축팀·디지털전환팀 운영.</t>
+          <t>IT기능: AI기획실 — AI전략·AX기획·평가대응(AI전략팀), 데이터기반행정·공공데이터·데이터분석시스템·OpenAPI·정보자원관리시스템(AI데이터팀), DB·서버·네트워크(AI인프라팀), AI 업무혁신(AI혁신TF). 디지털운영실 — 정보화사업 총괄·AX전략(AX전략팀), 정보화사업 계약·전산자산·유지보수(IT청렴계약팀), 데이터 품질·IT서비스관리(AI데이터플랫폼팀), 회계·인사급여·그룹웨어·홈페이지 시스템(IT경영지원팀), 채권·위탁·국유 업무시스템 지원(채권/위탁/국유업무지원팀), 전산센터 운영(서울전산센터), 시스템 개발(시스템개발부).&lt;br&gt;조직이력: 2026-09-19 라이브 확인 결과 종전 단일 '디지털시스템실'이 **AI기획실**과 **디지털운영실** 2개 실로 분리·개편되어 경영지원부문에 배치됨(경영지원부문: 기획조정실·인재경영실·캠코인재개발원·경영지원실·자금회계실·ESG성과혁신실·AI기획실·디지털운영실·12개 지역본부). 개편 과도기로 AI인프라팀·AI데이터플랫폼팀이 양 실 부서페이지에 중복 표기되는 구간이 있어 추후 재확인 권장.&lt;br&gt;표기주의: 공식 부서페이지 표기는 'AI·데이터플랫폼팀'(가운뎃점 포함)이나, 가운뎃점이 부서 구분자로 오파싱되어 'AI'라는 유령 노드가 생성되므로 본 파일에서는 'AI데이터플랫폼팀'으로 표기한다.&lt;br&gt;기타: 약칭 캠코(KAMCO). '캠코형 디지털 전환'(국유재산 차세대 관리시스템), AI 기반 항공영상 변화탐지·AR 모바일 실태조사, 상담 챗봇 등 AI 사업 추진. 노사 공동 '인권존중 AI 대전환' 선언. 그룹웨어 재구축 시스템구축팀·디지털전환팀 별도 운영.</t>
         </is>
       </c>
     </row>
@@ -5771,27 +5771,27 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>디지털정보부 (기획조정실 산하)</t>
+          <t>디지털정보부</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>부(部) — 기획조정실 산하</t>
+          <t>부</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>디지털정보부 (정보화·정보보안 통합 운영 추정)</t>
+          <t>정보보안팀</t>
         </is>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>없음(확인 범위 내, 단 AI 사업 추진 중)</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>해당없음 (별도 AI 전담 부서 미확인)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
@@ -5801,22 +5801,22 @@
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>기획조정실장 겸임 추정 (디지털정보부 관할)</t>
+          <t>디지털정보부장이 디지털정보화·정보보안·개인정보보호 업무 총괄(031-728-7073). 상위 기획조정실장 → 기획관리이사 관할</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (디지털정보부 내 정보보안 기능 추정)</t>
+          <t>디지털정보부 정보보안팀 (정보보안·개인정보보호 전담, 031-728-7393 / 7392). 전담 CISO 직위 명칭은 미확인</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 본문 추출 성공)</t>
+          <t>상 (2026-09-19 공식 조직도 페이지 본문 라이브 추출 성공)</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>IT 조직이 독립 본부/처가 아닌 "기획조정실 &gt; 디지털정보부"로 편제. 2026.6.9 한국고용정보원과 차세대 AI 고용서비스 협력 MOU 체결 — AI 기반 장애인 디지털 고용서비스 강화 추진(조직보다 사업 중심). 별도 디지털훈련센터 11개소 운영(장애인 디지털 직업훈련 — IT 직제와 별개).</t>
+          <t>IT담당배경: IT 조직이 독립 본부·처가 아니라 기획관리이사 산하 기획조정실의 1개 '부'(디지털정보부)로 편제됨. 기획조정실은 혁신기획부·안전보건부·조직예산부·운영지원부·인재개발부·디지털정보부로 구성.&lt;br&gt;IT기능: 디지털정보화 기획·예산·정보화사업, 경영지원시스템·장애인고용업무시스템·통합인증(SSO)·검색증강생성(RAG)·DB·타기관 연계, 공공데이터 제공·데이터기반행정·데이터 품질관리·행정업무자동화(RPA), 업무지원시스템·웹메일, 정보시스템 통합유지관리·홈페이지 운영·웹접근성 인증, 서버·전산설비·인프라, 전산장비·네트워크·VDI. 정보보안팀 — 정보보안·개인정보보호, 정보보호경영시스템 운영, 사이버위기대응·대응훈련, 네트워크·정보보호시스템 운영.&lt;br&gt;조직이력: 2026-09-19 라이브 확인 시 기획관리이사(기획조정실·능력개발국·소통협력실)와 고용촉진이사(장애인서비스국·기업서비스국·일자리안정국) 2이사 체계.&lt;br&gt;기타: 2026.6.9 한국고용정보원과 차세대 AI 고용서비스 협력 MOU 체결 — AI 기반 장애인 디지털 고용서비스 강화 추진(조직 신설이 아닌 사업 중심). 디지털정보부에 검색증강생성(RAG) 담당 업무가 있으나 AI 명칭 전담조직은 아님. 디지털훈련센터는 장애인 대상 디지털 직업훈련 시설로 IT 직제와 무관(혼동 주의) — 2026-09-19 공식 조직도 기준 **13개소**(서울·부산·대구·광주·대전·인천·일산·구로·판교·천안아산·전주·창원·제주). 조직명에 'AI'가 들어간 전담조직 없음.</t>
         </is>
       </c>
     </row>
@@ -5996,17 +5996,17 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>ICT부문(ICT이사 총괄)</t>
+          <t>ICT부문</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>본부(임원급 ICT이사 직속)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>(ICT이사 직속) ICT사업1처(ICT사업혁신부·디지털신분증사업부·지역화폐사업부), ICT사업2처(결제플랫폼사업부·결제플랫폼운영부·플랫폼통합지원부), ICT운영처(디지털신분증운영부·지역화폐운영부), ICT개발처(디지털인프라부·지급결제개발부·디지털신분증개발부), 정보보안센터</t>
+          <t>ICT사업1처(ICT사업혁신부, 디지털신분증사업부, 지역화폐사업부), ICT사업2처(결제플랫폼사업부, 결제플랫폼운영부, 플랫폼통합지원부), ICT운영처(디지털신분증운영부, 지역화폐운영부), ICT개발처(디지털인프라부, 지급결제개발부, 디지털신분증개발부), 정보보안센터</t>
         </is>
       </c>
       <c r="I74" s="3" t="inlineStr">
@@ -6016,32 +6016,32 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>AI추진기획부 (기획조정처 산하). 부속: 감사실 '기술AI감사부', 기술연구원 'ICT연구센터'(위변조방지 등 AI 연구)</t>
+          <t>AI추진기획부</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>부(部)급 — 기획조정처(부사장 겸 기획이사) 산하</t>
+          <t>부(部)</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>전담 ICT이사(상임이사) — CIO 역할. 2024 한성민 전 LG CNS 상무 임명. ICT사업1·2처, ICT운영처, ICT개발처, 정보보안센터를 총괄</t>
+          <t>전담 ICT이사(상임이사)가 CIO 역할 — ICT사업1·2처, ICT운영처, ICT개발처, 정보보안센터 총괄</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>정보보안센터 (ICT이사 직속, ICT개발처 등과 병렬 배치된 센터 단위 — 정보보안·CISO 기능)</t>
+          <t>정보보안센터 (ICT이사 직속, ICT 4개 처와 병렬 배치된 센터 단위)</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 komsco.com/kor/contents/24, 최종수정일 2026-01-20 직접 확인 — AI추진기획부·정보보안센터·ICT 4처 구조 확정)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>ICT 이사직을 별도 신설(2021 비상경영 이후 ICT 역량 강화)해 'ICT 문화기업' 전환 추진. ICT부문 매출 확대 목표('KOMSCO 디지털 2025'), 전자서명·모바일신분증 전문기관. 2026년 정부 'AI 바우처 지원사업' 공급기업 등록 + 고성능 AI GPU 활용 기반 강화(기술연구원 AI 위변조방지·디지털워터마크). 2025.12.30 정부 업무보고 'AI 대전환' 명시. **2026.1.20 기준 공식 조직도에서 AI 전담조직 'AI추진기획부'(기획조정처 산하) 확인** — 종전(2026.1.1 인사발령) 미확인분이 직제 갱신으로 확정됨. 감사실에 '기술AI감사부'도 신설. ICT부문은 ICT이사 직속 4처(ICT사업1·2처, ICT운영처, ICT개발처) + 정보보안센터로 재편(종전 'ICT기획보안처'는 현 직제에서 미등장 → 보안기능은 정보보안센터로 분리·이관된 것으로 보임).</t>
+          <t>[IT담당배경] 2021 비상경영 이후 ICT 역량 강화를 위해 ICT 이사직을 별도 신설하고 'ICT 문화기업' 전환 추진. ICT부문 매출 확대 목표('KOMSCO 디지털 2025'), 전자서명·모바일신분증 전문기관. [IT기능] ICT부문이 디지털신분증·지역화폐·결제플랫폼 등 대외 ICT 사업과 내부 디지털인프라를 함께 수행하는 사업형 IT 조직. [조직이력] AI추진기획부는 기획조정처(부사장 겸 기획이사) 소속, 감사실에 '기술AI감사부' 신설, 기술연구원에 'ICT연구센터' 배치. 종전 'ICT기획보안처'는 현 직제에서 미등장 — 보안기능이 정보보안센터로 분리·이관된 것으로 보임. [기타] 2026년 정부 'AI 바우처 지원사업' 공급기업 등록, 고성능 AI GPU 활용 기반 강화(기술연구원 AI 위변조방지·디지털워터마크). 2025.12.30 정부 업무보고 'AI 대전환' 명시.</t>
         </is>
       </c>
     </row>
@@ -6221,17 +6221,17 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>전산정보팀 (경영기획본부 기획부 산하)</t>
+          <t>전산정보팀</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>팀 (경영기획본부 &gt; 기획부 산하)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>없음 (전산정보팀 단일 팀. 기획부 내 병렬 팀: 예산팀·기획팀·전산정보팀·홍보팀)</t>
+          <t>없음 (전산정보팀 단일 팀)</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
@@ -6251,22 +6251,22 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영기획본부장 총괄 추정 — 전산정보팀이 경영기획본부 산하)</t>
+          <t>확인불가 (경영기획본부장 총괄 추정 — 전산정보팀이 경영기획본부 계통)</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담 CISO 명칭 미확인. 과기정통부가 2020년 산하기관 CISO 지정·정보보호 전담조직 신설 대상에 의학원 포함시킨 바 있으나, 현재 지정된 CISO·전담 보안조직명은 공개 확인 안 됨. 물리적 안전·보안은 안전관리부 '안전보안팀'이 담당하나 이는 IT 정보보안과 별개)</t>
+          <t>확인불가 (전담 CISO 명칭 미확인. 과기정통부가 2020년 산하기관 CISO 지정·정보보호 전담조직 신설 대상에 의학원을 포함시킨 바 있으나 현재 지정 현황 비공개. 안전관리부 물리적 안전·보안 기능은 IT 정보보안과 별개)</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>중(위키 상세구조 + 공식 홈페이지(기관소식)·알리오플러스·과기정통부 정책 보도 교차. 다만 전산정보팀 상위 라인·CIO/CISO 명칭은 직접 조직도 미확인으로 '중' 유지)</t>
+          <t>중 (공식 조직도는 부 단위까지만 공개되어 전산정보팀의 상위 부·CIO/CISO 명칭 직접 확인 불가)</t>
         </is>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>방사선의학연구소·원자력병원·국가방사선비상진료센터·국가RI신약센터 등 의료/연구 중심 기관. IT는 경영기획본부 기획부 산하 전산정보팀(단일 팀)이 담당. 별도 AI 전담조직 없음 — 단 2026.6 '의료영상기반 수술로봇 피지컬 AI 연구' 등 AI는 연구 부문에서 개별 수행. CISO는 과기정통부 산하기관 정보보호 전담조직 신설 정책 대상에 포함된 바 있음.</t>
+          <t>IT담당배경: 방사선의학연구소·원자력병원·국가방사선비상진료센터·국가RI신약센터를 거느린 의료/연구 중심 기관으로, 전사 IT는 경영기획본부 계통의 전산정보팀 단일 팀이 담당.&lt;br&gt;IT기능: 프로그램 개발(전산정보팀 Part 1), 시스템 관리(전산정보팀 Part 2) — 2026년 하반기 2차 공개채용 모집분야 기준&lt;br&gt;조직이력: 2026-09-18 라이브 조직도 기준 경영기획본부는 경영관리부·행정관리부 2부 체제이며, 그 밖에 기획조정실·홍보실·안전관리부가 배치됨. 종전 파일이 근거로 삼은 '기획부(예산팀·기획팀·전산정보팀·홍보팀)' 구조는 현재 조직도에 존재하지 않음.&lt;br&gt;기타: 전사 AI 전담조직은 없으며, 2026.6 '의료영상기반 수술로봇 피지컬 AI 연구' 등 AI는 병원·연구소의 개별 연구과제로 수행. 원자력병원에 로봇수술센터·의과학실증센터 운영.</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>AI인프라본부 (사장 직속, 본부급 — AI·ICT 총괄)</t>
+          <t>AI인프라본부</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -6756,22 +6756,22 @@
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>AI인프라본부 산하: AI전략실, ICT운영실, ICT인프라실, 경영지원실, 고객만족실 / 정보보안은 경영기획본부 산하 '정보보호처'</t>
+          <t>AI전략실, ICT운영실, ICT인프라실, 경영지원실, 고객만족실</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>있음 (2025.10.1 AI 전담부서 신설 — AI인프라본부 산하 'AI전략실', 본부 자체가 AI 컨트롤타워)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>AI전략실 (AI인프라본부 산하) / 상위 AI인프라본부(본부급)</t>
+          <t>AI전략실</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>실 (본부 산하) — 상위 AI인프라본부는 본부급</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부 산하 '정보보호처'가 정보보안 담당 — 전담 CISO 임원 직제 확인불가</t>
+          <t>정보보호처 (경영기획본부 소속) — 전담 CISO 임원 직제는 확인불가</t>
         </is>
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처: HF 공식 조직도 페이지 + 다수 보도자료)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>2025.10.1 AI 전담부서 신설 포함 조직개편 — IT조직을 'AI인프라본부'(사장 직속 본부급)로 격상하고 AI를 본부명에 명시. '공공기관 AI선도'를 전략과제로 선정(국정과제 연계). 2025.12 'HF AX(AI전환) 추진전략 2026~2028' 발표 — 3대 핵심전략(AI·데이터 인프라 구축, AI 서비스 개발·고도화, AI 조직역량·거버넌스 확립) + 12개 세부과제, 2028년까지 서비스 전면 개편. 빅데이터 플랫폼 구축으로 데이터 접근시간 최대 80% 단축 목표. 통칭 'HF/주금공'.</t>
+          <t>[IT담당배경] 2025.10.1 AI 전담부서 신설 포함 조직개편으로 IT조직을 'AI인프라본부'로 격상하고 AI를 본부명에 명시. '공공기관 AI선도'를 전략과제로 선정(국정과제 연계). [IT기능] AI인프라본부가 AI전략(AI전략실)·정보화 운영(ICT운영실)·인프라(ICT인프라실)를 통합 관할. [조직이력] AI인프라본부는 사장 직속 본부급이며, 정보보안은 별도로 경영기획본부 소속 '정보보호처'가 담당해 IT 본부와 분리된 구조. 사장 직속으로 '미래사업추진단'도 배치. [기타] 2025.12 'HF AX(AI전환) 추진전략 2026~2028' 발표 — 3대 핵심전략(AI·데이터 인프라 구축, AI 서비스 개발·고도화, AI 조직역량·거버넌스 확립) + 12개 세부과제, 2028년까지 서비스 전면 개편. 빅데이터 플랫폼 구축으로 데이터 접근시간 최대 80% 단축 목표. 통칭 'HF/주금공'.</t>
         </is>
       </c>
     </row>
@@ -7421,17 +7421,17 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>재생에너지기반본부(CIO) 산하 AI데이터처</t>
+          <t>재생에너지기반본부</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>AI데이터처 (재생에너지기반본부 산하), 통계분석실</t>
+          <t>AI데이터처</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -7446,27 +7446,27 @@
       </c>
       <c r="K93" s="3" t="inlineStr">
         <is>
-          <t>처(본부 산하)</t>
+          <t>처</t>
         </is>
       </c>
       <c r="L93" s="3" t="inlineStr">
         <is>
-          <t>재생에너지기반본부장이 CIO 겸임</t>
+          <t>재생에너지기반본부장이 CIO 겸임 (공식 조직도에 '재생에너지기반본부(CIO)' 표기)</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>AI데이터처장 (개인정보보호책임자 겸임). 별도 CISO 직제 명문 미확인</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + 공식 개인정보처리방침 교차)</t>
         </is>
       </c>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>전사 디지털전환(DX)을 'CIO-총괄부서(통계분석실)-사업부서' 협업체계로 표준화. 정보화 중심을 통계분석실로 전환, CIO 주도 디지털 조직문화 조성. 본부 명칭이 정보화 전담이 아닌 재생에너지기반본부로 CIO 기능 부여 형태.</t>
+          <t>IT담당배경: 정보화 전담 본부는 별도로 없고, 조직도상 '재생에너지기반본부'에 (CIO) 표기가 붙어 이 본부가 정보화 총괄을 겸함. 산하 'AI데이터처'가 정보화·데이터 실무 전담. 본부의 나머지 산하 조직(재생에너지소통처·해상풍력사업처·분산에너지처·열에너지기술처)은 재생에너지 사업조직. IT기능: 정보화·데이터 총괄, 개인정보보호(개인정보보호책임자 AI데이터처장, privacy@energy.or.kr). 조직이력: 과거 조사에서 정보화 총괄부서로 기재했던 '통계분석실'은 2026-09-18 현재 공식 조직도에 존재하지 않음(AI데이터처로 일원화된 것으로 판단). 기타: 전사 디지털전환(DX)을 'CIO-총괄부서-사업부서' 협업체계로 표준화. 'AI 기반 분산에너지 특화지역 지원 사업' 등 AI 활용 사업 운영.</t>
         </is>
       </c>
     </row>
@@ -7721,17 +7721,17 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부 (내부 정보화 총괄) / 안전경영단 정보보안팀</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>본부 (내부 정보화는 경영기획본부 산하 팀 레벨)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>(경영기획본부 산하) 안전경영단-정보보안팀, ESG성과단-AX혁신팀, 혁신전략단-AI전략기획팀 등</t>
+          <t>혁신전략단(AI전략기획팀), ESG성과단(AX혁신팀), 안전경영단(정보보안팀)</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>AI보안산업본부 (대외 사업 조직) / 경영기획본부 혁신전략단 AI전략기획팀·ESG성과단 AX혁신팀 (내부 AI 전환)</t>
+          <t>AI보안산업본부</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr">
         <is>
-          <t>본부 (대외 사업)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="L97" s="3" t="inlineStr">
@@ -7761,12 +7761,12 @@
       </c>
       <c r="N97" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처 + 보도)</t>
+          <t>상 (2026-09-19 공식 조직도 페이지 전체 트리 라이브 직접 추출)</t>
         </is>
       </c>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>정보보호·인터넷·AI보안이 기관의 본업인 기관. 2026.2.9 조직개편으로 'AI보안산업본부' 신설(기존 정보보호산업본부 개편)·중소기업 지원 랜섬웨어대응팀 신설. 대외 사업조직(AI보안산업본부, 디지털위협대응/예방본부, 개인정보본부, 디지털기반본부)과 전사 정보화를 총괄하는 내부 경영지원 조직(경영기획본부)을 구분해야 함. 내부 IT/정보화·정보보안은 경영기획본부 산하 팀 단위로 운영.</t>
+          <t>IT담당배경: 정보보호·인터넷·AI보안이 기관의 본업이어서 대외 사업본부와 내부 정보화 조직을 구분해야 함. 전사 내부 정보화·정보보안은 경영기획본부 산하 단·팀 레벨(혁신전략단 AI전략기획팀, ESG성과단 AX혁신팀, 안전경영단 정보보안팀)에서 수행.&lt;br&gt;IT기능: 내부 AI 전략기획·AX 혁신·정보보안. 대외로는 AI보안 정책·기술·산업진흥·인재양성, 디지털위협 탐지·분석, 개인정보 보호·AI데이터 안전활용, 인터넷주소·전자문서·스팸 대응.&lt;br&gt;조직이력: 2026.2.9 조직개편으로 정보보호산업본부를 'AI보안산업본부'로 개편·확대, 랜섬웨어대응팀 신설. 2026-09-19 라이브 확인 시 원장 직속 감사실 + 5본부(경영기획본부·AI보안산업본부·디지털위협대응본부·디지털위협예방본부·개인정보본부·디지털기반본부) 체계.&lt;br&gt;기타: AI보안산업본부는 AI보안정책단(AI보안정책팀·AI보안기술팀·AI보안분석팀·법제연구팀), AI보안산업단(정보보호공시제도팀·AI보안산업진흥팀·AI물리보안진흥팀·글로벌협력팀), AI보안기술단(양자암호기술팀·AI위협대응기술팀·AI융합보안기술팀), AI보안인재단(AI보안인재정책팀·AI보안교육운영팀·최정예보안리더 양성팀)으로 구성. 그 외 AI 명칭 조직 다수 — AI탐지대응팀·AI종합분석팀(디지털위협대응본부), AX공급망보안단(AX공급망보안정책팀·AI정부보호팀·AI기반보호팀)·디지털AI제품인증팀·지역정보보호 AI진흥팀·AI중소기업 정보보호팀·지역AX산업보안팀(디지털위협예방본부), AI데이터안전 활용단(AI데이터정책팀(TF) 포함)·마이데이터 추진센터(개인정보본부), 블록체인AI확산팀·AI스팸정책팀(디지털기반본부).</t>
         </is>
       </c>
     </row>
@@ -8476,47 +8476,47 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>처·실 (실 단위)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>정보보안운영, 보안총괄, KINS-AI(인공지능 그룹) 등 (지능정보실 내 정보화·정보보안·AI 기능)</t>
+          <t>없음 (지능정보실 단일 실)</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>있음 (지능정보실 산하 인공지능 그룹 'KINS-AI')</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>KINS-AI (지능정보실 운영 인공지능 그룹) — 원자력안전규제 지식관리용 LLM 'ATOMIS'(32B) 개발·운영, 약 8명</t>
+          <t>AI총괄 PM</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>그룹(실 산하)</t>
+          <t>처·실 (부원장 직속 실장급 PM 직위)</t>
         </is>
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
-          <t>지능정보실장(강문환)이 정보화 총괄 — 개인정보 보호책임자(CPO)도 지능정보실장 겸직</t>
+          <t>지능정보실장 총괄(042-603-3072) — 개인정보 보호책임자(CPO) 겸직</t>
         </is>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>지능정보실 소관(CPO/정보보호 총괄=지능정보실장 강문환). 지능정보실 내 정보보안운영·보안총괄 기능 보유. 전담 CISO 별도 직위 명칭은 미확인</t>
+          <t>지능정보실 소관(정보보안·개인정보보호 업무 분장 확인). 전담 CISO 별도 직위 명칭은 미확인</t>
         </is>
       </c>
       <c r="N107" s="3" t="inlineStr">
         <is>
-          <t>상(개인정보처리방침 + KINS-AI 공식 그룹 페이지 + 2026 인사 보도 교차)</t>
+          <t>상 (공식 홈페이지 조직도·부서별 업무 직접 확인 + 인사 보도 교차)</t>
         </is>
       </c>
       <c r="O107" s="3" t="inlineStr">
         <is>
-          <t>2026.1.1자 보직인사에서 지능정보실장 신규 임명, "디지털 전환을 통한 스마트 안전규제 시스템 구축"에 역량 집중 천명. 정보화·정보보안이 지능정보실로 통합 운영. 지능정보실 내 AI 그룹(KINS-AI)이 원자력안전규제 지식관리시스템(NKM)용 LLM 'ATOMIS'(32B instruct 모델)를 자체 개발·공개(Hugging Face). 리스크기반 AI 규제체계 연구 진행.</t>
+          <t>IT담당배경: 지능정보실은 '국제원자력 안전학교' 소속으로, 교육기관 명칭과 달리 기관 정보화·정보보안·공공데이터·지식관리를 총괄하는 IT 전담 실(공식 조직도·부서별 업무 확인).&lt;br&gt;IT기능: 정보화비전·중장기정보화계획 수립, 운영분과위원회(IT분야) 운영 및 정보화 총괄, 정보통신망·서버 관리, 정보시스템 개발·운영, 정보보안·개인정보보호, 소프트웨어·공학용 코드 관리, 공공데이터 관리 및 데이터기반행정, 원자력안전 지식관리, 자료실·간행물 관리&lt;br&gt;조직이력: 2026.8.21 부원장 소속 'AI총괄 PM'(실장급) 신설·임명(황충만). 기관 AI 도입·활용, 정부정책 및 안전규제 대응 등 AI 업무 총괄.&lt;br&gt;AI판정근거: 공식 직제상 AI 명칭 조직은 부원장 직속 **AI총괄 PM**(실장급 직위) 1건이며, AI조직명·AI조직레벨은 이 공식 직제 기준으로만 기재한다.&lt;br&gt;비공식/외부 플랫폼(공식 직제 아님): 'KINS-AI'는 지능정보실이 Hugging Face에 운영하는 **외부 플랫폼상 인공지능 그룹 계정**으로, 기관 조직도에 없는 비공식 명칭이다. 이 그룹이 원자력안전규제 지식관리시스템(NKM)용 LLM 'ATOMIS'(32B instruct)를 자체 개발·공개했다. AI조직명 필드에서는 제외하고 본 항목에만 기재한다.&lt;br&gt;기타: 지능정보실이 'AI솔로몬' 운영. 리스크기반 AI 규제체계 연구 진행.</t>
         </is>
       </c>
     </row>
@@ -8771,52 +8771,52 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>정보화관리실</t>
+          <t>디지털혁신본부</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>처·실(사무총장 직속)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보화관리실 산하 팀 세부 미확인)</t>
+          <t>데이터정보센터(정보기획팀·학술데이터분석팀·정보시스템지원팀·범부처연구비관리팀), 정책연구실(정책혁신팀), 정보보안팀</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>있음(위원회 형태)</t>
+          <t>없음 (상설 직제 AI 조직 미확인 — 이사장 직속 'NRF 인공지능 위원회'는 자문·심의 성격의 거버넌스 기구)</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>인공지능 위원회 (구 AI전환추진단을 이사장 직속 위원회로 격상·개편)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>이사장 직속 위원회(상설 직제 본부·실 아님)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>사무총장 산하 정보화관리실장이 정보화 총괄 (전담 CIO 명문 표기 확인불가)</t>
+          <t>데이터정보센터장(CIO) — 공식 조직도에 '데이터정보센터(CIO)' 표기, 민간 개방형 직위</t>
         </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보화관리실 소관 추정)</t>
+          <t>정보보안팀 (사무총장 직속). 별도 CISO 직제 명문 미확인</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 직원안내 + 인사·보도 교차)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + 공식 개인정보처리방침·보도 교차)</t>
         </is>
       </c>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>정보화 직제 조직은 '정보화관리실'(사무총장 직속). AI는 별도 직제 본부·실이 아니라 이사장 위원장·사무총장 CAIO 체계의 '인공지능 위원회'로 운영(거버넌스형). 조직 규모: 8본부 3센터 19단 22실 50팀 2TF(2025.3 기준).</t>
+          <t>IT기능: 정보기획, 학술데이터 분석, 정보시스템 운영·지원, 범부처 연구비 관리, 정보보안. 조직이력: 2021년 지식정보실을 CIO 중심 '데이터정보센터'로 확대·개편(민간 개방형 센터장 선임). 이후 디지털혁신본부 체제로 재편되어 데이터정보센터·정책연구실이 산하에 편제. 2026.3 기존 'AI 전환 추진단'을 이사장 직속 'NRF 인공지능 위원회'로 격상·개편, 2026.8 AI 전환 실무협의체 신설. AI판정근거: 2026-09-19 공식 조직도 라이브 재확인 결과 조직도 전체(8본부 체계, 디지털혁신본부·데이터정보센터 4개 팀 포함)에 'AI'·'인공지능' 명칭이 들어간 상설 직제(본부·실·센터·부·팀)가 **없음**. 'NRF 인공지능 위원회'는 이사장이 위원장, 사무총장이 AI 실무책임관(CAIO)인 이사장 직속 **자문·심의 거버넌스 위원회**이고 'AI 전환 실무협의체'도 협의체이므로, 통일기준(상설 직제가 아닌 위원회·TF·협의체는 AI전담조직으로 계상하지 않음)에 따라 AI전담조직 '없음'으로 판정. R&amp;D 전 주기 AI 도입(전사 AX) 전략은 위원회·협의체 주도로 추진 중. 정보보안팀은 디지털혁신본부가 아니라 사무총장 직속으로 편제. 국책연구본부의 '정보·융합기술단'은 R&amp;D 분야 조직으로 내부 IT 조직이 아님. 조직 규모 8본부 3센터 19단 22실 50팀(2025.3 기준).</t>
         </is>
       </c>
     </row>
@@ -9146,52 +9146,52 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>정보기술처</t>
+          <t>AI혁신단</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 전력계통본부 소속</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>(정보기술처) AX데이터팀, 계통시스템팀, 시장시스템팀, 차기IT추진실(차기IT개발팀), (안전보안처) 정보보안실</t>
+          <t>전사AX총괄팀, 계통시스템팀, 시장시스템팀, IT혁신실(플랫폼개발팀·경인IT개발센터), 정보보안실</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>있음 (AX데이터팀 — 정보기술처 산하)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>AX데이터팀</t>
+          <t>AI혁신단 (전사AX총괄팀)</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>팀 (정보기술처 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전력계통본부장 산하 정보기술처가 정보화 총괄)</t>
+          <t>확인불가 (AI혁신단장이 정보화 총괄, 경영부이사장 직속. 별도 CIO 직위 명시 미확인)</t>
         </is>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보안 기능은 경영기획본부 안전보안처 산하 정보보안실)</t>
+          <t>확인불가 (정보보안실이 정보보호 전담, 경영부이사장 직속으로 격상)</t>
         </is>
       </c>
       <c r="N116" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + 개편 보도 다수 교차)</t>
         </is>
       </c>
       <c r="O116" s="3" t="inlineStr">
         <is>
-          <t>정보화 총괄 '정보기술처'가 전력계통본부 산하에 위치 — 전력시장·계통 운영 시스템(시장시스템팀·계통시스템팀)과 직결된 조직 구조. AI/데이터 기능은 'AX데이터팀'(AX=AI Transformation)으로 정보기술처에 편제. 정보보안은 경영기획본부 안전보안처 정보보안실로 IT 기획과 분리. 차기IT추진실 운영(차세대 시스템 구축).</t>
+          <t>IT기능: 전사 AX 마스터플랜 수립·AI 데이터 플랫폼 구축(전사AX총괄팀), 전력계통 운영시스템(계통시스템팀), 전력시장 운영시스템(시장시스템팀), 차세대 플랫폼 개발(IT혁신실〈플랫폼개발팀·경인IT개발센터〉), 정보보안(정보보안실).&lt;br&gt;조직이력: 2026.7.8 조직개편 — 전력계통본부 산하 **'정보기술처'를 경영부이사장 직속 'AI혁신단'으로 확대 개편**(AI 전환 전략 수립·데이터 플랫폼 구축 전사 조직으로 역할 확대). 'AX데이터팀' → **'전사AX총괄팀'** 개편. '차기IT추진실(차기IT개발팀)' → **'IT혁신실(플랫폼개발팀·경인IT개발센터)'**로 재편. 정보보안실은 안전보안처 산하 → 경영부이사장 직속으로 이동.&lt;br&gt;기타: 개편 4대 방향 = 시장·계통 대응역량 강화, 전사 AI 전환(AX) 추진체계 확립, 국정과제·경영전략 실행력 제고, 핵심사업 중심 운영 효율화. 정보보안실은 AI혁신단과 별개로 경영부이사장 직속에 병렬 편제(IT 기획과 보안 분리 유지). 이사장 직속 감사실·안전정책실·시장감시실. 기술부이사장 산하 3본부(전력시장·에너지전환·전력계통).</t>
         </is>
       </c>
     </row>
@@ -9296,17 +9296,17 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>AI시스템추진부 (정보화사업 기획·IRM·전산시스템 총괄)</t>
+          <t>학생금융본부</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>부 (학생금융본부 산하)</t>
+          <t>부</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>(학생금융본부) AI데이터전략부, AI시스템추진부, (학생장학본부) AI우수장학부, (경영혁신본부) 안전경영부</t>
+          <t>AI데이터전략부, AI시스템추진부</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
@@ -9316,32 +9316,32 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>AI데이터전략부, AI시스템추진부 (상설 직제) + 전사적 인공지능 전환 전담 조직(경영·사업·시스템·고객 4개 분과, 협의체 성격)</t>
+          <t>AI데이터전략부, AI시스템추진부</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>부 (학생금융본부 산하)</t>
+          <t>부</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (학생금융본부장 산하 AI시스템추진부가 정보화 총괄)</t>
+          <t>확인불가 (학생금융본부장 계열 추정, 별도 CIO 직위 명시 미확인)</t>
         </is>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보호 기능은 경영혁신본부 안전경영부/안전관리부 정보보호팀 추정)</t>
+          <t>확인불가 (경영혁신본부 안전경영부 소관 추정)</t>
         </is>
       </c>
       <c r="N118" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O118" s="3" t="inlineStr">
         <is>
-          <t>정보화 총괄 부서명을 'AI시스템추진부'·'AI데이터전략부'로 명명하여 AI 전환을 직제에 전면 반영한 점이 특징. AI시스템추진부가 정보화사업 기획·정보자원관리(IRM)·전산시스템 구축·운영 총괄. 상설 직제 외에 '전사적 인공지능 전환 전담 조직'(4개 분과, 월1회 이상 운영) 별도 구성. AI 리터러시 진단제도 도입, 공공기관 디지털 협력 협의회 발족 주도.</t>
+          <t>IT담당배경: 정보화 총괄 부서를 'AI시스템추진부'·'AI데이터전략부'로 명명하여 AI 전환을 직제에 전면 반영. 두 부 모두 학생금융본부 소속으로, 학자금대출·상환 시스템이 기관 핵심 정보시스템이라 금융 사업본부에 IT가 편제됨.&lt;br&gt;IT기능: 정보화사업 기획, 정보자원관리(IRM), 전산시스템 구축·운영 총괄(AI시스템추진부) / AI·데이터 전략 수립(AI데이터전략부).&lt;br&gt;조직이력: 별도 명칭의 '정보화기획부·정보화운영부'는 현행 조직도에 없음 — 정보화 기능이 AI 명칭 부서로 통합·재편됨.&lt;br&gt;기타: 4본부 체계(학생장학·학생금융·경영혁신·청년지원). 상설 직제 외에 '전사적 인공지능 전환 전담 조직'(경영·사업·시스템·고객 4개 분과, 월1회 이상 운영) 협의체 별도 구성. 학생장학본부에 'AI우수장학부'가 있으나 AI 인재 장학사업 수행 부서로 IT/AI 기술조직은 아님. 공공기관 최초 'AI 전환 수준진단' 도입, AI 리터러시 진단제도 운영, 상담 응대율 88.5%→99.2% 개선.</t>
         </is>
       </c>
     </row>
@@ -9821,12 +9821,12 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>AI융합실 (경영관리본부 산하)</t>
+          <t>AI융합실</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 경영관리본부 산하 실</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
@@ -9841,32 +9841,32 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>AI융합실 / AI전환팀</t>
+          <t>AI융합실(AI전환팀)</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>실(AI융합실) — 산하 AI전환팀</t>
+          <t>실</t>
         </is>
       </c>
       <c r="L125" s="3" t="inlineStr">
         <is>
-          <t>AI융합실장 총괄 (경영관리본부 산하), 전담 CIO 직책 명시 확인불가</t>
+          <t>AI융합실장 총괄. 전담 CIO 직책 명시 확인불가</t>
         </is>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>정보보안팀 중심 (AI융합실 산하). 원자력시설 사이버보안 포함. 전담 직책 명시 확인불가</t>
+          <t>정보보안팀 소관. 전담 CISO 직위 명칭 확인불가</t>
         </is>
       </c>
       <c r="N125" s="3" t="inlineStr">
         <is>
-          <t>상(공식 1출처 + 검색 확인)</t>
+          <t>상 (공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>실 명칭을 'AI융합실'로 명명, 산하 'AI전환팀'이 디지털화 기획·정보시스템·생성형AI 관리 담당. 원자력시설 사이버보안을 정보보안팀이 별도 수행하는 점이 업종 특성.</t>
+          <t>IT담당배경: 정보화 총괄 실의 명칭 자체를 'AI융합실'로 명명. 경영관리본부 소속으로 기획조정실·경영관리실과 병렬 배치.&lt;br&gt;IT기능: 디지털화 기획·정보시스템 운영·생성형AI 관리(AI전환팀), 정보보안 및 원자력시설 사이버보안(정보보안팀)&lt;br&gt;기타: 방사성폐기물 관리 전담기관(KORAD, 경주 소재). 원자력시설 사이버보안을 정보보안팀이 별도 수행하는 점이 업종 특성.</t>
         </is>
       </c>
     </row>
@@ -10131,42 +10131,42 @@
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>정보보안센터, 우체국쇼핑실(시스템운영팀), 우편사업실(품질관리팀)</t>
+          <t>정보화사업팀, 정보보안센터, 우체국쇼핑실(시스템운영팀), 우편사업실(품질관리팀)</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (홈페이지 조직도상 AI 전담 부서 미확인)</t>
+          <t>없음 (공식 조직도상 AI 명칭 전담조직 미확인)</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L129" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영전략실장 총괄 추정)</t>
+          <t>경영전략실장 총괄(정보화사업팀·정보보안센터 소관). 전담 CIO 직책 명시 확인불가</t>
         </is>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보안센터 운영)</t>
+          <t>정보보안센터 소관. 전담 CISO 직위 명칭 확인불가</t>
         </is>
       </c>
       <c r="N129" s="3" t="inlineStr">
         <is>
-          <t>상 (공식 홈페이지 조직구성도 확인)</t>
+          <t>상 (공식 홈페이지 조직구성도 직접 확인)</t>
         </is>
       </c>
       <c r="O129" s="3" t="inlineStr">
         <is>
-          <t>IT담당배경: IT 조직이 3개 실에 분산 운영. 경영전략실-정보보안센터가 보안 총괄, 사업실별 시스템팀이 자체 운영. 경영정보팀의 실제 업무는 제휴·홍보·몰운영·정산으로 IT 기획 담당 아님.&lt;br&gt;IT기능: 정보보안·정보보호·시스템관리(정보보안센터) / 쇼핑 시스템 운영·정산/통계·모바일·B2B(우체국쇼핑실 시스템운영팀) / 우편 인프라·정보보안관리(우편사업실 품질관리팀)</t>
+          <t>IT담당배경: 정보화 총괄(정보화사업팀)과 정보보안(정보보안센터)이 모두 경영전략실 소속. 사업부서(우체국쇼핑실·우편사업실)가 자체 시스템 운영 인력을 별도 보유해 IT가 3개 실에 분산 운영됨.&lt;br&gt;IT기능: 정보화사업 기획·추진(정보화사업팀) / 정보보안·정보보호·시스템관리(정보보안센터) / 쇼핑몰 시스템 운영·정산/통계·모바일·B2B(우체국쇼핑실 시스템운영팀) / 우편 인프라·정보보안관리(우편사업실 품질관리팀)&lt;br&gt;조직이력: 2026-09-18 라이브 조직도에서 경영전략실 산하 '정보화사업팀' 확인. 종전 파일이 IT 기획 담당으로 오인했던 '경영정보팀'은 현재 조직도에 없음.&lt;br&gt;기타: 미래연구센터(우편연구팀·미래사업추진반)가 있으나 IT/AI 전담 조직은 아님.</t>
         </is>
       </c>
     </row>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) (경영본부 산하 '부' 단위)</t>
+          <t>부</t>
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>IT관리팀 (정보보안·개인정보보호 총괄, 각종 장애인 정보시스템 운영)</t>
+          <t>IT관리팀</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
@@ -10591,32 +10591,32 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
         <is>
-          <t>경영본부장 겸임 (추정 — 정보화전략부가 경영본부 산하)</t>
+          <t>정보화전략부장 총괄 (부서장 최종선, 02-3433-0626) — 상위 본부장 겸임 여부 확인불가</t>
         </is>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부장/IT관리팀 정보보안 총괄 (전담 CISO 직제 확인불가)</t>
+          <t>IT관리팀장이 정보보안·개인정보보호 업무 총괄(02-3433-0709), 정보화전략부장 관할 (전담 CISO 직제 확인불가)</t>
         </is>
       </c>
       <c r="N135" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 부서 상세 2출처)</t>
+          <t>상 (2026-09-19 공식 홈페이지 정보화전략부 부서 상세 페이지 라이브 직접 확인 — 부·팀 단위는 확정. 단 전체 조직도가 이미지로만 제공되어 상위 본부 계층은 확인불가 상태임)</t>
         </is>
       </c>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부는 경영본부 산하 부 단위. AI는 발달장애·시각장애 지원 등 사업 콘텐츠 차원에서 활용(보도자료)하나 별도 AI 전담 조직(부·팀)은 확인되지 않음. 정책지원부에 '챗봇 실적 관리' 업무 언급은 있으나 IT/AI 전담조직은 아님.</t>
+          <t>IT기능: 정보화전략부 업무 총괄(부서장), IT관리팀 — 정보보안 및 개인정보보호 업무 총괄, 중증장애인생산품 우선구매관리시스템·장애인일자리시스템·장애통계 데이터포털 등 장애인 정보시스템 운영.&lt;br&gt;기타: 보건복지부 산하 기타공공기관(1989년 설립). AI는 발달장애·시각장애 지원 등 사업 콘텐츠 차원에서 활용(보도자료)하나 조직명에 'AI'가 들어간 전담조직은 확인되지 않음. 정책지원부에 '챗봇 실적 관리' 업무 언급은 있으나 IT/AI 전담조직은 아님. 공식 조직도 페이지는 이미지(bg_organization.jpg)로만 제공되어 상위 본부 계층은 라이브 추출 불가 — 정보화전략부 부서 상세 페이지로 부서·팀 구성만 확정.</t>
         </is>
       </c>
     </row>
@@ -11246,22 +11246,22 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (산하 전산·학술정보팀이 IT 담당)</t>
+          <t>디지털정보팀</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>팀 (경영지원실 산하)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>전산·학술정보팀</t>
+          <t>해당없음 (팀 단위 단일 조직)</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>없음 (재검색에도 AI 전담 조직 단서 미확인)</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="J144" s="3" t="inlineStr">
@@ -11281,17 +11281,17 @@
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>디지털정보팀 내 정보보안 담당자 2명 배치 — 전담 CISO 임원 직제는 확인불가</t>
         </is>
       </c>
       <c r="N144" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 조직도 + 검색 교차, 단 IT 세부 직제는 부분 확인)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O144" s="3" t="inlineStr">
         <is>
-          <t>연구기관 특성상 IT는 경영지원실 산하 전산·학술정보팀이 전산·학술정보 인프라를 담당하는 소규모 구조. 본부 구성은 연구기획본부·조세연구본부·재정연구본부·경영지원실 + 다수 연구센터. AI 전담조직은 직제상 확인 안 됨</t>
+          <t>[IT기능] 디지털정보팀이 정보화사업관리·정보보안·학술정보시스템 관리·전자정보 관리·기록물관리·연속간행물·수서 등 정보화와 도서·학술정보 기능을 겸임. [조직이력] 종전 '전산·학술정보팀'이 '디지털정보팀'으로 명칭 변경됨(2025년도 인권영향평가 보고 담당부서가 디지털정보팀으로 표기, 2024년도분은 전산ㆍ학술정보팀). 디지털정보팀은 경영지원실 소속. [기타] 연구기관 특성상 IT는 경영지원실 산하 1개 팀이 담당하는 소규모 구조. 본부 구성은 연구기획본부·조세연구본부·재정연구본부·경영지원실 + 다수 연구센터. AI 전담조직은 직제상 확인되지 않음.</t>
         </is>
       </c>
     </row>
@@ -11921,7 +11921,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>재정시스템운영본부 / 보조금시스템운영본부 (시스템 운영 본부)</t>
+          <t>재정시스템운영본부 / 보조금시스템운영본부</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -11931,42 +11931,42 @@
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>재정시스템운영본부(dBrain 운영), 보조금시스템운영본부(e나라도움 운영), 인프라안전책임단(재정인프라관리부/재정인프라운영부), 사이버안전책임단(재정정보보호부/사이버보안부)</t>
+          <t>재정시스템운영본부(재정시스템관리부·예산시스템운영부·집행시스템운영부·자산시스템운영부·결산시스템운영부), 보조금시스템운영본부(보조금시스템관리부·보조사업운영부·집행정산운영부·보조금정보운영부·보조금점검지원부), 재정혁신본부(AX재정혁신부·재정정보공개활용부·재정정보분석부·재정성과분석부), 사이버안전책임단(재정정보보호부·사이버보안부), 인프라안전책임단(재정인프라관리부·재정인프라운영부)</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (재정혁신본부가 AI·데이터 활용 담당 추정)</t>
+          <t>AX재정혁신부</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>부</t>
         </is>
       </c>
       <c r="L153" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (시스템운영본부장이 정보화 총괄 추정)</t>
+          <t>확인불가 (시스템운영 본부장이 정보화 총괄, 별도 CIO 직위 명시 미확인)</t>
         </is>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>사이버안전책임단 (재정정보보호부·사이버보안부 소관)</t>
+          <t>사이버안전책임단 (재정정보보호부·사이버보안부)</t>
         </is>
       </c>
       <c r="N153" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + tavily 교차)</t>
         </is>
       </c>
       <c r="O153" s="3" t="inlineStr">
         <is>
-          <t>기관 자체가 국가재정정보시스템(dBrain)·국고보조금시스템(e나라도움) 운영 전담기관으로, 조직 전체가 IT 중심. 시스템운영 2본부 + 보안·인프라 2책임단 체제. 2025.7 정부 '공공기관 AI 도입·활용 선도조직' 정책 대상 가능성(보도자료 본문 미해독). 주무부처가 기획예산처(2026 정부조직 개편으로 기획재정부 분리).</t>
+          <t>IT담당배경: 기관 자체가 국가재정정보시스템(dBrain)·국고보조금통합관리시스템(e나라도움) 운영 전담기관으로 조직 전체가 IT 중심. 단일 '정보화처'가 아닌 시스템 기능별 2개 운영본부로 분산 편제.&lt;br&gt;IT기능: dBrain 예산·집행·자산·결산 시스템 운영(재정시스템운영본부), e나라도움 보조사업·집행정산·보조금정보 운영(보조금시스템운영본부), 재정정보 공개·분석(재정혁신본부), 정보보호·사이버보안(사이버안전책임단), 전산인프라 관리·운영(인프라안전책임단).&lt;br&gt;조직이력: 2026-09-18 재확인 시 재정혁신본부 산하 **AX재정혁신부** 편제 확인 — AI·AX 전환 전담 부서로 신규 식별(직전 조사 시 '확인불가'였음).&lt;br&gt;기타: 5본부(재정시스템운영·보조금시스템운영·재정혁신·경영기획·재정협력) + 2책임단(사이버안전·인프라안전) 체제. 원장 직속 감사실·안전관리실·비서실. 2026.7 개원 10주년, 'AI 기반 재정혁신' 비전 제시. 공공기관 개인정보 보호수준 평가 S등급, 국제 사이버방어훈련 '락드쉴즈 2026' 참가. 주무부처는 2026 정부조직 개편으로 기획예산처.</t>
         </is>
       </c>
     </row>
@@ -12221,52 +12221,52 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>안전정보부 (정보화·전산 기능, 경영기획본부 산하)(추정)</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>부(본부 산하, 경영기획본부)</t>
+          <t>부</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>확인불가 — 안전정보부가 경영기획본부 산하 leaf 부서로, 공식 조직도상 하위 팀/과가 별도 표기되지 않음(안전+정보화 통합 부서로 추정)</t>
+          <t>정보안전부, 정보보호팀, AI데이터혁신부</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>AI데이터혁신부</t>
         </is>
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>부</t>
         </is>
       </c>
       <c r="L157" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부장 총괄(추정)</t>
+          <t>경영기획본부장 총괄 (정보안전부·정보보호팀 소관). 전담 CIO 명문 미확인</t>
         </is>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
-          <t>안전정보부 내 수행(추정)</t>
+          <t>정보보호팀 (경영기획본부 소속)</t>
         </is>
       </c>
       <c r="N157" s="3" t="inlineStr">
         <is>
-          <t>중(공식 조직도 1출처, IT 부서 기능은 추정)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인, 2회 독립 추출 교차)</t>
         </is>
       </c>
       <c r="O157" s="3" t="inlineStr">
         <is>
-          <t>별도 IT 전담 본부·실 없음. 정보화 기능은 경영기획본부 산하 '안전정보부'에 통합된 것으로 추정. 정책지원본부에 '데이터연구부'가 있어 정책·평가 데이터 분석 수행(IT 인프라 조직과는 별개). AI 전담조직 미확인.</t>
+          <t>IT담당배경: 별도 IT 전담 본부는 없고, 경영기획본부 산하 '정보안전부'가 정보화·전산과 안전 기능을, '정보보호팀'이 정보보호를 담당. IT기능: 정보화·전산 운영, 정보보호. 조직이력: 종전 조사 시점의 '안전정보부'가 현 조직도에서 '정보안전부'로 표기되며, 별도 '정보보호팀'이 경영기획본부 산하에 병렬 편제됨. 정책지원본부 산하 '데이터연구부'는 'AI데이터혁신부'로 개편. 기타: AI데이터혁신부는 정책지원본부(경영기획본부가 아님) 산하로, 정책·평가 데이터와 AI 혁신 기능을 담당하는 조직. 사업 측면에서 'AI 기반 교재교구·환경구성' 디지털 컨설팅 교육 제공. 공식 도메인은 kcpi.or.kr → kicece.or.kr(영문약칭 KICECE).</t>
         </is>
       </c>
     </row>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>산림정보본부</t>
+          <t>산림AI정보본부</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -13281,42 +13281,42 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>산림공간정보실, 임업통계실, 산림빅데이터산업실 (산림정보본부 산하)</t>
+          <t>산림공간정보실, 임업통계실, AI빅데이터실(디지털정보화팀)</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
         <is>
-          <t>있음 (사업 단위 — 산림빅데이터·AI 전담 실)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>산림빅데이터산업실 (산림빅데이터 플랫폼·공공 AI·데이터 협력 사업 수행)</t>
+          <t>산림AI정보본부</t>
         </is>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
-          <t>실 (산림정보본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="L171" s="3" t="inlineStr">
         <is>
-          <t>산림정보본부장 총괄 (추정) — 전담 CIO 직위 미확인</t>
+          <t>산림AI정보본부장 총괄 (산림자원이사 관할)</t>
         </is>
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>산림정보본부 정보화 담당 소관 (추정) — 별도 CISO 직위 미확인</t>
+          <t>AI빅데이터실 디지털정보화팀 소관 (추정) — 별도 CISO 직위 미확인</t>
         </is>
       </c>
       <c r="N171" s="3" t="inlineStr">
         <is>
-          <t>상 (산림정보본부 산하 산림공간정보실·임업통계실·산림빅데이터산업실을 정부사업공고·data.go.kr API 제공부서 메타데이터 등 복수 출처로 교차 확인)</t>
+          <t>상 (2026-09-19 공식 홈페이지 조직도 라이브 직접 확인)</t>
         </is>
       </c>
       <c r="O171" s="3" t="inlineStr">
         <is>
-          <t>4본부 체계(기획운영본부·산업지원본부·인증평가본부·산림정보본부). 산림정보본부 산하에 산림공간정보실·임업통계실·산림빅데이터산업실. '임업정보 다드림(林)' 산림정보 플랫폼 및 '산림빅데이터 플랫폼·거래소'(bigdata-forest.kr) 운영. 산림빅데이터산업실이 공공 빅데이터·AI 협력(8개 기관 MOU), 산림분야 빅데이터·AI 활용 창업경진대회, 2025 인공지능&amp;빅데이터쇼 참가 등 AI·데이터 사업을 전담. 다만 '인공지능실/AI팀' 명칭의 순수 AI 전담조직은 아니며 빅데이터·데이터산업 중심 실.</t>
+          <t>IT기능: 산림공간정보 구축·운영, 임업통계 생산, 산림 AI·빅데이터 플랫폼 운영, 디지털정보화(내부 정보화·전산).&lt;br&gt;조직이력: 2026-09-19 라이브 확인 결과 종전 '산림정보본부'가 **산림AI정보본부**로 명칭 변경되고, 종전 '산림빅데이터산업실'이 **AI빅데이터실**로 개편(산하 디지털정보화팀 신설). 전체 조직은 원장 직속 홍보협력실·윤리감사실 + 산림자원이사(기획운영본부·산림AI정보본부·임업기술실용화본부)·산림산업이사(임산물소득지원본부·산촌활성화지원센터·산림산업지원본부·종자사업소) 체계로 재편.&lt;br&gt;AI판정근거: AI 명칭 상설 직제가 2계층(본부: 산림AI정보본부 / 실: AI빅데이터실)으로 존재하며, AI조직레벨은 최상위인 '본부'로 기재하고 AI조직명은 최상위 단위 '산림AI정보본부'로 단일 표기한다(산하 AI빅데이터실은 IT하위부서에 기재).&lt;br&gt;기타: '임업정보 다드림(林)' 산림정보 플랫폼 및 '산림빅데이터 플랫폼·거래소'(bigdata-forest.kr) 운영. 공공 빅데이터·AI 협력(8개 기관 MOU), 산림분야 빅데이터·AI 활용 창업경진대회, 인공지능&amp;빅데이터쇼 참가 등 AI·데이터 사업 수행.</t>
         </is>
       </c>
     </row>
@@ -15671,37 +15671,37 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
+          <t>사업전략본부</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>처·실</t>
+        </is>
+      </c>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
           <t>AI디지털전환실</t>
         </is>
       </c>
-      <c r="G203" s="3" t="inlineStr">
+      <c r="I203" s="3" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="J203" s="3" t="inlineStr">
+        <is>
+          <t>AI디지털전환실</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr">
         <is>
           <t>처·실</t>
         </is>
       </c>
-      <c r="H203" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (정보화·정보보안·AI/디지털전환 기능 통합 담당)</t>
-        </is>
-      </c>
-      <c r="I203" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="J203" s="3" t="inlineStr">
-        <is>
-          <t>AI디지털전환실</t>
-        </is>
-      </c>
-      <c r="K203" s="3" t="inlineStr">
-        <is>
-          <t>처·실</t>
-        </is>
-      </c>
       <c r="L203" s="3" t="inlineStr">
         <is>
-          <t>AI디지털전환실장 (실장 이윤백)</t>
+          <t>AI디지털전환실장</t>
         </is>
       </c>
       <c r="M203" s="3" t="inlineStr">
@@ -15711,12 +15711,12 @@
       </c>
       <c r="N203" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + 공식 개인정보처리방침·보도자료 교차)</t>
         </is>
       </c>
       <c r="O203" s="3" t="inlineStr">
         <is>
-          <t>에너지 R&amp;D 기획·평가·관리 전문기관(약칭 에기평/KETEP). 정보화·정보보안·AI/디지털전환 기능을 'AI디지털전환실'이 통합 담당. 2024년 정보보호준비도 평가 최고등급 AAA(P) 획득(담당부서 AI디지털전환실). 개인정보처리방침상 개인정보보호 담당부서도 AI디지털전환실. LG AI연구원·에너지 유관기관과 에너지 AI 전환(AX) MOU 추진 등 AI 활용 활발.</t>
+          <t>IT담당배경: 에너지 R&amp;D 기획·평가·관리 전문기관(약칭 에기평/KETEP)으로 별도 정보화 본부가 없으며, 사업전략본부 산하 'AI디지털전환실'이 정보화·정보보안·AI/디지털전환을 통합 담당. 같은 본부에 사업총괄실·성과총괄실·기술정책실·공공R&amp;D센터가 병렬 배치되어 있어 IT 전담 본부가 아닌 사업전략 본부에 IT 기능이 소속된 구조. IT기능: 정보화, 정보보안, 개인정보보호, AI·디지털전환. 조직이력: 과거 '디지털혁신기획실' 신설 이력이 있었고 현재는 'AI디지털전환실'로 운영(AI 강조 명칭으로 변경·확대). 기타: 2024년 정보보호준비도 평가 최고등급 AAA(P) 획득(담당부서 AI디지털전환실). LG AI연구원·에너지 유관기관과 에너지 AI 전환(AX) MOU 추진 등 AI 활용 활발.</t>
         </is>
       </c>
     </row>
@@ -17621,52 +17621,52 @@
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>저작권정보센터 (정보기술팀 소속)</t>
+          <t>저작권정보센터</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>팀 (저작권정보센터 산하 정보기술팀)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>정보기술팀 (클라우드 통합운영, 대표 누리집 기능개선, 통합 내부행정시스템, 저작권기술 동향조사 등)</t>
+          <t>정보기술팀</t>
         </is>
       </c>
       <c r="I229" s="3" t="inlineStr">
         <is>
-          <t>없음 (전담조직 신설 추진 중 / TF·겸직 단계)</t>
+          <t>없음 (상설 전담조직 미설치 / TF·겸직 단계)</t>
         </is>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>AI-저작권 환경변화 대응 TF (전략기획팀 겸직), AI 안내서·제도개선은 법제연구팀 담당</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K229" s="3" t="inlineStr">
         <is>
-          <t>TF/겸직 (별도 상설 조직 아님)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L229" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (저작권정보센터장 또는 기획혁신본부장 총괄로 추정)</t>
+          <t>확인불가 (저작권정보센터장 또는 기획혁신본부장 총괄 추정)</t>
         </is>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보기술팀이 정보보안 포함 담당으로 추정)</t>
+          <t>확인불가 (정보기술팀이 정보보안 겸행 추정)</t>
         </is>
       </c>
       <c r="N229" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 부서 상세·업무보고 교차)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + 부서 상세·업무보고 교차)</t>
         </is>
       </c>
       <c r="O229" s="3" t="inlineStr">
         <is>
-          <t>위원장 직속의 기획혁신본부·정책연구본부·저작권정보센터·교육본부·분쟁조정본부 등 본부 체제. IT는 저작권정보센터 산하 정보기술팀(심의정보팀·유통정보팀과 동급)이 담당. 2026년 업무보고에 "AI-저작권 전담조직 신설 필요" 명시 — 현재는 전략기획팀의 'AI 저작권 환경변화 대응 TF' 겸직 및 법제연구팀의 AI 저작권 안내서·제도개선 업무로 분산 수행, 상설 AI 전담조직은 미설치.</t>
+          <t>IT기능: 클라우드 통합운영, 대표 누리집 기능개선, 통합 내부행정시스템 운영, 저작권기술 동향조사(정보기술팀).&lt;br&gt;조직이력: 2026년 업무보고에 "AI-저작권 전담조직 신설 필요" 명시 — 현재는 전략기획팀의 'AI-저작권 환경변화 대응 TF' 겸직 및 법제연구팀의 AI 저작권 안내서·제도개선 업무로 분산 수행, 상설 AI 전담조직은 미설치.&lt;br&gt;기타: 위원장 직속 본부 체제 — 기획혁신본부(전략기획팀·경영지원팀·홍보팀), 정책연구본부(법제연구팀·국제협력팀〈해외사무소〉·통상산업연구팀), 저작권정보센터(심의정보팀·유통정보팀·정보기술팀), 교육본부(교육개발팀·교육운영팀), 분쟁조정본부(등록임치팀·조정감정팀·저작권상담팀·저작권법률지원센터), 저작권박물관(학예연구팀·운영관리팀), 감사(비상근)〈감사팀〉. 생성형 AI 저작권 안내서 발간, 문체부와 'AI-저작권 제도개선 협의체' 운영, 'AI 특화 상담 창구' 개설, 2026 AI 활용 저작권 콘텐츠 공모전 개최 등 AI 저작권 정책 대응 활발. 경남 진주 소재.</t>
         </is>
       </c>
     </row>
@@ -17696,22 +17696,22 @@
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>정보운영부 (경영기획본부 산하)</t>
+          <t>정보운영부</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>부(본부 산하)</t>
+          <t>부</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보운영부 내 정보보안·개인정보·정보시스템 인프라 담당으로 분장되나 별도 하위 부서 없음, 단일 부 단위)</t>
+          <t>없음 (정보운영부 단일 부)</t>
         </is>
       </c>
       <c r="I230" s="3" t="inlineStr">
         <is>
-          <t>없음 (재검색에도 AI 전담 직제 조직 미확인)</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="J230" s="3" t="inlineStr">
@@ -17726,22 +17726,22 @@
       </c>
       <c r="L230" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부장이 정보화 총괄(정보운영부 소관), 전담 CIO 명문 표기 확인불가</t>
+          <t>경영기획본부장이 정보화 총괄(정보운영부 소관). 전담 CIO 명문 표기 확인불가</t>
         </is>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
-          <t>정보운영부 내 정보보안 담당(전담 CISO 명문 표기 확인불가)</t>
+          <t>정보운영부 소관(정보보안·개인정보보호 분장). 전담 CISO 명문 표기 확인불가</t>
         </is>
       </c>
       <c r="N230" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 직접 확인)</t>
+          <t>상 (공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O230" s="3" t="inlineStr">
         <is>
-          <t>정보화·정보보안·개인정보보호·정보시스템 인프라 운영이 모두 경영기획본부 산하 '정보운영부' 단일 부서에 집중. 기관 규모(현원 137.8명)가 작아 IT가 별도 본부·실로 분리되지 않음. AI 전담조직 없음.</t>
+          <t>IT담당배경: 정보운영부는 경영기획본부 소속으로 전략기획부·인사성과부·경영관리부와 병렬 배치. 기관 규모(현원 137.8명)가 작아 IT가 별도 본부·실로 분리되지 않고 단일 부에 통합.&lt;br&gt;IT기능: 정보화 사업계획·예산, 전자정부 성과관리, 정보보안, 개인정보보호, 정보시스템 인프라 운영·관리, 공공데이터 제공&lt;br&gt;기타: 의료분쟁 조정·중재·감정이 핵심 업무인 기관 성격상 IT는 지원 기능에 한정. 4본부(경영기획·심사조사·고객지원·정책연구) 체제 + 부산지원 운영.</t>
         </is>
       </c>
     </row>
@@ -18971,27 +18971,27 @@
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부 (정보화 소관) — 산하 '지식정보팀'이 정보화·전산 담당</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>팀 — 경영기획본부 산하 '지식정보팀'(본부 내 팀 단위)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H247" s="3" t="inlineStr">
         <is>
-          <t>지식정보팀 (경영기획본부 산하. IT·정보화·전산 담당. 경영기획본부는 경영지원팀·운영지원팀·지식정보팀으로 구성)</t>
+          <t>지식정보팀</t>
         </is>
       </c>
       <c r="I247" s="3" t="inlineStr">
         <is>
-          <t>없음 (별도 AI 전담조직 직제 없음 — 단, 사업조직인 중앙디지털성범죄피해자지원센터가 AI 기반 성착취물 자동탐지·삭제 기술을 운용)</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>해당없음 (전담조직 부재)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K247" s="3" t="inlineStr">
@@ -19001,22 +19001,22 @@
       </c>
       <c r="L247" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부장 총괄 (정보화 소관 본부 = 경영기획본부, 지식정보팀이 실무) — 전담 CIO 명문 미확인</t>
+          <t>경영기획본부장 총괄 (지식정보팀이 실무). 전담 CIO 명문 미확인</t>
         </is>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영기획본부장/지식정보팀 라인 추정 — 유사 공공기관 다수가 경영기획본부장을 CPO로 지정. 본 기관 전용 처리방침 직접 확인 실패)</t>
+          <t>지식정보팀 (정보보안·사이버 위기대응·개인정보보호 담당자 배치). 별도 CISO 직제 명문 미확인</t>
         </is>
       </c>
       <c r="N247" s="3" t="inlineStr">
         <is>
-          <t>상(채용공고 2출처[링커리어·사람인]로 경영기획본부 산하 지식정보팀의 IT/AI 직무 교차 확인 + 연합뉴스로 AI 탐지시스템 운용 확인. 공식 조직도 페이지는 JS렌더링·404로 직접 트리 미확인이나 정보화 담당팀명 확정)</t>
+          <t>상(공식 홈페이지 조직도 및 직원목록 직접 확인)</t>
         </is>
       </c>
       <c r="O247" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부·여성폭력방지본부·인권보호본부(중앙디지털성범죄피해자지원센터·여성긴급전화1366중앙센터 포함)·일본군'위안부'문제연구소 등으로 구성. 경영기획본부 산하 '지식정보팀'이 내부 정보화·전산을 담당(2026년 채용에서 지식정보팀이 네트워크·정보통신·AI(인공지능) 직무 모집). 한편 인권보호본부 산하 '중앙디지털성범죄피해자지원센터'는 AI 기반 성착취물 자동탐지·삭제 시스템(채팅앱 최초 적용, 2018년부터 축적 데이터 학습)을 운용하나 이는 피해자지원 사업조직이지 내부 IT/AI 전담조직이 아님. 중앙디성센터 산하 '삭제기술팀'도 별도 존재.</t>
+          <t>IT담당배경: 경영기획본부 산하 4개 팀(전략기획팀·경영지원팀·운영지원팀·지식정보팀) 중 '지식정보팀'이 기관 정보화·정보보안 전담. IT기능: 정보보안, 사이버 위기대응, 개인정보보호, 공공데이터 관리, 데이터기반행정, 전자정부 성과관리, 정보시스템 운영·유지관리, IT 인프라 관리. 조직이력: 2026년 조직도 기준 경영기획본부에 '전략기획팀'이 추가되어 4개 팀 체제. 중앙디지털성범죄피해자지원센터가 본부급 독립 조직(역량강화팀·삭제기술팀·삭제지원팀·상담연계팀)으로 편제. 기타: 중앙디지털성범죄피해자지원센터가 AI 기반 성착취물 자동탐지·삭제 시스템(채팅앱 최초 적용, 2018년부터 데이터 학습)을 운용하나 이는 피해자 지원 사업조직이며 내부 IT/AI 전담조직이 아님. 산하 삭제기술팀이 삭제지원시스템 개발·운영·고도화와 통합 홈페이지 기획·운영 담당. 지식정보팀 2026년 채용에 네트워크·정보통신·AI(인공지능) 직무 포함.</t>
         </is>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>경영기획부(전산팀)</t>
+          <t>전산팀</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -19056,7 +19056,7 @@
       </c>
       <c r="H248" s="3" t="inlineStr">
         <is>
-          <t>전산팀(기관 정보화 총괄·정보시스템 유지관리·IT보안시스템 기획/관리)</t>
+          <t>없음 (전산팀 단일 팀)</t>
         </is>
       </c>
       <c r="I248" s="3" t="inlineStr">
@@ -19066,32 +19066,32 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr">
         <is>
-          <t>확인불가(경영기획부장 총괄 추정)</t>
+          <t>확인불가 (경영기획부장 총괄 추정)</t>
         </is>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
-          <t>확인불가(전산팀이 정보보안 겸장 / 핵안보본부 사이버보안실은 외부 원자력시설 규제업무로 별개)</t>
+          <t>확인불가 (전산팀이 IT보안시스템 기획·관리 겸장)</t>
         </is>
       </c>
       <c r="N248" s="3" t="inlineStr">
         <is>
-          <t>중(공식 채용공고 1차+언론 인사발령 교차)</t>
+          <t>상 (공식 홈페이지 조직도 직접 확인 + 채용공고 교차)</t>
         </is>
       </c>
       <c r="O248" s="3" t="inlineStr">
         <is>
-          <t>2026.1 개방형직위 '전산팀장' 채용 공고 — 기관 정보화 업무 총괄·정보시스템 유지관리·정보보안 담당. 홈페이지에 '공공기관 AI 활용 국민제안' 배너 운영(전담조직 신설 아님). 핵안보본부 사이버보안실은 원자력시설 사이버보안 심사·검사 등 대외 규제업무 수행 조직으로 내부 IT조직과 구분됨.</t>
+          <t>IT담당배경: 전산팀은 경영기획부 산하 경영지원실 소속(공식 조직도 확인). 기관 규모(현원 122명)가 작아 별도 정보화 실·부 없이 팀 단위로 운영.&lt;br&gt;IT기능: 기관 정보화 업무 총괄, 정보시스템 유지관리, IT보안시스템 기획·관리&lt;br&gt;조직이력: 2026.1 개방형직위 '전산팀장' 채용 공고 시행&lt;br&gt;기타: 핵안보본부 산하 '사이버보안실'은 원자력시설 사이버보안 심사·검사·교육 등 대외 규제업무 수행 조직으로 내부 IT조직과 별개 — 혼동 주의. 홈페이지에 '공공기관 AI 활용 국민제안' 배너 운영(전담조직 신설 아님).</t>
         </is>
       </c>
     </row>
@@ -19946,52 +19946,52 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>정보지식공유센터 (성주류화지식혁신본부 산하) — 정보화·정보지식 공유·홈페이지/시스템 운영 담당</t>
+          <t>성주류화연구본부</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 본부 산하 '센터'(팀) 단위. 별도 정보화 본부·처 없음</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H260" s="3" t="inlineStr">
         <is>
-          <t>정보지식공유센터 (성주류화지식혁신본부 소속). 개인정보보호 실무는 경영지원본부 인사조직관리센터가 별도 담당</t>
+          <t>정보지식공유센터</t>
         </is>
       </c>
       <c r="I260" s="3" t="inlineStr">
         <is>
-          <t>없음 (별도 AI 전담조직 직제 없음 — AI는 연구주제로만 다룸: '인공지능 젠더편향 대응' 등 정책연구)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>성평등AX정책연구단</t>
         </is>
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>단</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보지식공유센터 소관 본부는 성주류화지식혁신본부, 정보화 총괄 전담 CIO 명문 미확인)</t>
+          <t>성주류화연구본부장 (정보지식공유센터 소관). 전담 CIO 명문 미확인</t>
         </is>
       </c>
       <c r="M260" s="3" t="inlineStr">
         <is>
-          <t>경영지원본부장(CPO) — 개인정보보호책임자: 경영지원본부장(이현화), 개인정보보호담당자: 인사조직관리센터. 정보보안·개인정보 거버넌스가 경영지원본부 라인. 별도 CISO 명문은 미확인</t>
+          <t>경영관리본부장(개인정보보호책임자), 담당부서 인사총무센터. 별도 CISO 명문 미확인</t>
         </is>
       </c>
       <c r="N260" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침[CPO·담당부서] + 위키백과 6본부 조직 + 공식 페이지 담당부서(정보지식공유센터) 교차 확인)</t>
+          <t>상(공식 홈페이지 2026년 조직도 SVG 원문 직접 확인 + 공식 개인정보처리방침 교차)</t>
         </is>
       </c>
       <c r="O260" s="3" t="inlineStr">
         <is>
-          <t>6개 본부(기획조정본부·여성미래연구본부·일과생애연구본부·젠더폭력연구본부·성주류화지식혁신본부·경영지원본부) 체제의 정부출연 연구기관. 정보화·정보지식 공유 기능은 '성주류화지식혁신본부' 산하 '정보지식공유센터'가 담당(성평등전략사업센터·성별영향평가센터·성인지예산센터·성인지데이터센터와 병렬). 개인정보보호 실무는 경영지원본부(인사조직관리센터)가 담당하여 정보화-개인정보 기능이 본부가 분리됨. 국내 최초 성인지 통계정보 시스템(2006~) 운영, 성인지데이터센터 보유. 임직원 약 132명(2025 4Q, 나무위키) 규모. 원장 김종숙. 서울 은평 소재.</t>
+          <t>IT담당배경: '정보지식공유센터'는 명칭상 연구지식 공유 조직으로 보이나, 공식 홈페이지 각 페이지의 운영 담당부서로 일관 표기되어 기관 정보화·정보시스템·홈페이지 운영 조직임. IT기능: 홈페이지·정보시스템 운영, 정보지식 공유. 조직이력: 2026년 조직도 기준 '성주류화지식혁신본부'→'성주류화연구본부', '경영지원본부'→'경영관리본부', '인사조직관리센터'→'인사총무센터'로 개편. 원장 직속에 '성평등AX정책연구단'·'고용평등공시제연구단'·'양성평등담당관제총괄추진단' 신설, 부원장 직속 연구성과확산TF·기관발전TF 운영. 기타: 성평등AX정책연구단은 원장 직속 연구단으로 성평등 관점의 AI 전환(AX) 정책연구를 수행하는 연구조직(내부 정보화 조직과는 별개). 같은 본부에 성별영향평가센터·성인지예산센터·성인지통계센터가 병렬 배치되며, 성인지통계센터가 성인지 통계·데이터 기능을 담당(국내 최초 성인지 통계정보 시스템 2006~ 운영). 정보화(성주류화연구본부)와 개인정보 거버넌스(경영관리본부)가 본부 단위로 분리됨.</t>
         </is>
       </c>
     </row>
@@ -20621,32 +20621,32 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
+          <t>침해대응본부</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>부</t>
+        </is>
+      </c>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
           <t>정보기술부</t>
         </is>
       </c>
-      <c r="G269" s="3" t="inlineStr">
-        <is>
-          <t>부 (침해대응본부 산하)</t>
-        </is>
-      </c>
-      <c r="H269" s="3" t="inlineStr">
-        <is>
-          <t>정보기술부 (단일 부 — 정보화 기획·운영, 정보보안, 개인정보보호, 공공데이터 담당). 침해대응본부 내 형제부서: 온라인보호부, 과학수사지원부</t>
-        </is>
-      </c>
       <c r="I269" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 AI 전담조직 식별 안 됨)</t>
+          <t>없음 (조직도상 AI 명칭 전담조직 미확인)</t>
         </is>
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L269" s="3" t="inlineStr">
@@ -20656,17 +20656,17 @@
       </c>
       <c r="M269" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보기술부에서 정보보안·개인정보보호 수행)</t>
+          <t>확인불가 (정보기술부가 정보보안·개인정보보호 겸행)</t>
         </is>
       </c>
       <c r="N269" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 공공데이터포털 관리부서 표기 교차확인)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + tavily 교차)</t>
         </is>
       </c>
       <c r="O269" s="3" t="inlineStr">
         <is>
-          <t>IT 전담조직(정보기술부)이 정보보안 정책·기획부서가 아닌 '침해대응본부'(저작권 침해 대응 본업) 산하에 편제된 점이 특징. 침해대응본부에는 저작권 침해 모니터링·접속차단을 담당하는 온라인보호부, 디지털 포렌식 센터를 둔 과학수사지원부가 함께 있음. 정보기술부가 채용정보 등 공공데이터 관리부서로도 표기됨(02-3153-2437). 별도 AI 전담조직은 조직도상 확인되지 않음.</t>
+          <t>IT담당배경: IT 전담조직(정보기술부)이 기획·경영 라인이 아닌 '침해대응본부'(저작권 침해 대응 본업) 산하에 편제 — 온라인 침해 모니터링·접속차단·디지털 포렌식 등 본업 자체가 IT 집약적이기 때문.&lt;br&gt;IT기능: 정보화 기획·운영, 정보보안, 개인정보보호, 공공데이터 관리(공공데이터포털 관리부서 표기 02-3153-2437).&lt;br&gt;기타: 4실·본부 체계 — 경영기획실(기획조정부·경영관리부), 침해대응본부(온라인보호부〈저작권접속차단대응팀〉·과학수사지원부〈저작권디지털포렌식센터〈저작권범죄분석팀〉, 광주·대구·부산사무소〉·정보기술부), 국제협력본부(해외교류부〈베트남·태국·필리핀사무소〉·해외사업부), 보호지원본부(보호심의부·홍보협력부·보호전략지원부). 원장 직속 감사(비상임)〈검사역〉, 저작권보호심의위원회.</t>
         </is>
       </c>
     </row>
@@ -20771,37 +20771,37 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>정보화팀 (기획경영본부 산하)</t>
+          <t>기획경영본부</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>팀 (본부 산하)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H271" s="3" t="inlineStr">
         <is>
-          <t>정보화팀(정보화·전산·정보보안 총괄, 기획경영본부 산하), 의약품통합정보관리팀(의약품 통합정보시스템 운영, 기획경영본부 산하), 약물역학빅데이터팀(데이터 분석, 의약품안전정보본부 산하)</t>
+          <t>정보화팀, 의약품통합정보관리팀</t>
         </is>
       </c>
       <c r="I271" s="3" t="inlineStr">
         <is>
-          <t>없음 (별도 'AI' 명칭 전담조직 미존재 — AI·LLM·CDM은 의약품안전정보본부 및 정보화팀이 본업(약물감시)에 적용)</t>
+          <t>없음 (마약류통합정보관리본부 산하 '마약류AI혁신TF'가 있으나 상설 직제가 아닌 TF이므로 통일기준상 미계상)</t>
         </is>
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L271" s="3" t="inlineStr">
         <is>
-          <t>기획경영본부장 총괄 (정보화팀이 기획경영본부 산하)</t>
+          <t>기획경영본부장 총괄</t>
         </is>
       </c>
       <c r="M271" s="3" t="inlineStr">
@@ -20811,12 +20811,12 @@
       </c>
       <c r="N271" s="3" t="inlineStr">
         <is>
-          <t>상(KIDS 공식 개인정보처리방침으로 CPO(기획경영본부장 이성현)·정보화팀 확정 + 기관 공식 블로그·보도자료로 4본부 13팀 구조 및 AI 사업 추진 확인. 단 현행 조직도 트리는 일부 시점 차이 가능)</t>
+          <t>상 (2026-09-19 공식 홈페이지 조직도 트리 라이브 직접 추출 + 공식 개인정보처리방침으로 CPO·정보화팀 확인)</t>
         </is>
       </c>
       <c r="O271" s="3" t="inlineStr">
         <is>
-          <t>약칭 KIDS, 식약처 산하 국내 유일 약물감시 전담기관(2012 설립). 원장 중심 4본부 13팀 5TF — 기획경영본부(혁신경영팀·교육홍보팀·정보화팀·의약품통합정보관리팀), 의약품안전정보본부(안전정보관리팀·약물역학빅데이터팀·DUR정보팀), 의약품안전조사본부(의약품부작용피해구제팀·첨단바이오규제과학팀), 마약류통합정보관리본부(마약류시스템운영팀·마약류제도지원팀·마약류정보분석팀·마약류감사지원TF). 2025~2028 'AI·빅데이터 기반 능동형 약물감시 전면 개편'(LLM 기반 이상사례 검토 자동화, EMR-CDM 30→66개 기관 확대, 비정형 데이터 NLP 표준화, K-NASS 마약류 통합감시) 추진 — 다만 전담 AI '조직' 신설이 아니라 의약품안전정보본부·정보화팀이 본업에 AI 적용.</t>
+          <t>IT담당배경: IT 전담 조직은 **기획경영본부** 산하 정보화팀·의약품통합정보관리팀 2개 팀이다(IT하위부서에는 이 2개 팀만 기재). 이와 별개로 **의약품안전정보본부**(기획경영본부와 병렬인 별도 본부) 산하 약물역학빅데이터팀·DUR정보팀이 데이터 분석·DUR 정보를 담당하나, 계층이 다른 본부이므로 IT하위부서에 넣지 않고 본 항목에 기재한다.&lt;br&gt;IT기능: 정보화팀 — 정보화·전산·정보보안 총괄 / 의약품통합정보관리팀 — 의약품통합정보시스템·KAERS 등 핵심 정보시스템 운영 / (의약품안전정보본부) 약물역학빅데이터팀 — 약물역학 데이터 분석·CDM / (의약품안전정보본부) DUR정보팀 — DUR 정보 관리.&lt;br&gt;AI판정근거: 2026-09-19 공식 조직도 라이브 재추출 결과 AI 명칭 조직은 마약류통합정보관리본부 산하 **마약류AI혁신TF** 1건뿐이다. 통일기준(상설 직제가 아닌 위원회·TF·협의체는 AI전담조직으로 계상하지 않음)에 따라 AI전담조직 '없음'을 유지하되, 향후 정규 팀 승격 시 재판정 대상.&lt;br&gt;조직이력: 2026년 9월 현재 공식 조직도 기준 원장 직속 감사팀 + 4본부 14팀 1TF 체계(마약류AI혁신TF 신설 확인). 기획경영본부에 전략기획팀 신설(전략기획팀·혁신경영팀·교육홍보팀·정보화팀·의약품통합정보관리팀), 의약품안전조사본부에 임상시험안전지원팀 신설(의약품부작용피해구제팀·첨단바이오규제과학팀·임상시험안전지원팀). 종전 조사 시 기재된 마약류감사지원TF는 현 조직도에 미표시.&lt;br&gt;기타: 약칭 KIDS, 식약처 산하 국내 유일 약물감시 전담기관(2012 설립). 의약품안전정보본부(안전정보관리팀·약물역학빅데이터팀·DUR정보팀), 마약류통합정보관리본부(마약류시스템운영팀·마약류제도지원팀·마약류정보분석팀). 2025~2028 'AI·빅데이터 기반 능동형 약물감시 전면 개편'(LLM 기반 이상사례 검토 자동화, EMR-CDM 확대, 비정형 데이터 NLP 표준화, K-NASS 마약류 통합감시) 추진 — 조직명에 'AI'가 들어간 전담조직은 없으며 의약품안전정보본부·정보화팀이 본업에 AI 적용.</t>
         </is>
       </c>
     </row>
@@ -21164,11 +21164,11 @@
         <v>60</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -21180,11 +21180,11 @@
         </is>
       </c>
       <c r="G4" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -21206,19 +21206,19 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>6.0%</t>
         </is>
       </c>
     </row>
@@ -21232,19 +21232,19 @@
         <v>273</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
@@ -21294,11 +21294,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.6%</t>
         </is>
       </c>
     </row>
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
     </row>
@@ -21324,11 +21324,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -21339,11 +21339,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -21400,11 +21400,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
     </row>
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.6%</t>
         </is>
       </c>
     </row>
@@ -21461,11 +21461,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>91.2%</t>
         </is>
       </c>
     </row>
@@ -21476,11 +21476,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -21525,7 +21525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -21870,25 +21870,25 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>(재)한국우편사업진흥원</t>
+          <t>한국법무보호복지공단</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>준정부</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>기타공공기관</t>
+          <t>준정부기관(위탁집행형)</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>406.9</v>
+        <v>356</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>상 (공식 홈페이지 조직구성도 확인)</t>
+          <t>상(공식 조직도 + 개인정보처리방침 2출처로 정보관리팀·CPO=보호정책부장 확인)</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -21898,37 +21898,37 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>경영전략실</t>
+          <t>보호사업부 (舊 보호정책부)</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (홈페이지 조직도상 AI 전담 부서 미확인)</t>
+          <t>확인불가 (조직도상 AI 전담조직 미확인. 미래전략부는 정책혁신·기획홍보·대외협력 중심으로 AI 전담 아님)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>한국법무보호복지공단</t>
+          <t>한국교육과정평가원</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>준정부</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 개인정보처리방침 2출처로 정보관리팀·CPO=보호정책부장 확인)</t>
+          <t>상(공식 홈페이지 조직도 + 개인정보처리방침 2출처로 정보관리본부·정보보안부·CPO 확인)</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -21938,19 +21938,19 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>보호사업부 (舊 보호정책부)</t>
+          <t>정보관리본부</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (조직도상 AI 전담조직 미확인. 미래전략부는 정책혁신·기획홍보·대외협력 중심으로 AI 전담 아님)</t>
+          <t>확인불가 (내부 IT 직제상 'AI' 명칭 전담조직은 없음. 단, 기획조정본부 산하 '교육데이터센터', 미래학교교육연구본부 산하 '디지털·미래교육연구실'이 교육데이터·디지털교육 연구를 수행. AI기반 학력진단시스템 구축 등 AI 사업 활발)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>한국교육과정평가원</t>
+          <t>한국해양수산연수원</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -21964,11 +21964,11 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>339</v>
+        <v>313</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 개인정보처리방침 2출처로 정보관리본부·정보보안부·CPO 확인)</t>
+          <t>상(공식 조직도 + 개인정보처리방침 2출처로 지능정보화팀·CPO=경영본부장 확인)</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -21978,37 +21978,37 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>정보관리본부</t>
+          <t>지능정보화팀 (경영본부 산하)</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (내부 IT 직제상 'AI' 명칭 전담조직은 없음. 단, 기획조정본부 산하 '교육데이터센터', 미래학교교육연구본부 산하 '디지털·미래교육연구실'이 교육데이터·디지털교육 연구를 수행. AI기반 학력진단시스템 구축 등 AI 사업 활발)</t>
+          <t>확인불가 (별도 'AI' 명칭 전담조직 미확인. 정보화는 경영본부 산하 '지능정보화팀'이 담당하나 일반 IT 기능으로 판단)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>한국재정정보원</t>
+          <t>선박해양플랜트연구소</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>준정부</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>준정부기관(위탁집행형)</t>
+          <t>기타공공기관</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>316.8</v>
+        <v>312</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도)</t>
+          <t>상(공식 조직도 + 인사 보도 교차)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -22018,19 +22018,19 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>재정시스템운영본부 / 보조금시스템운영본부 (시스템 운영 본부)</t>
+          <t>해양공공디지털연구본부, 경영지원본부</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (별도 AI 전담조직 미확인. 해양공공디지털연구본부가 디지털·AI 연구 수행 추정)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>한국해양수산연수원</t>
+          <t>중소기업기술정보진흥원</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -22044,11 +22044,11 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>313</v>
+        <v>271.3</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 개인정보처리방침 2출처로 지능정보화팀·CPO=경영본부장 확인)</t>
+          <t>상(공식 조직도 전체 트리 라이브 재확인, 2026-09-18)</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -22058,19 +22058,19 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>지능정보화팀 (경영본부 산하)</t>
+          <t>R&amp;D지원본부</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 'AI' 명칭 전담조직 미확인. 정보화는 경영본부 산하 '지능정보화팀'이 담당하나 일반 IT 기능으로 판단)</t>
+          <t>확인불가 (별도 AI 전담조직 없음 / '지능정보화실'이 지능정보·정보화 기능 총괄)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>선박해양플랜트연구소</t>
+          <t>한국청소년상담복지개발원</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -22084,11 +22084,11 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>312</v>
+        <v>239.5</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 인사 보도 교차)</t>
+          <t>상(공식 조직 명칭 + 개인정보처리방침(공식) 교차 확인)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -22098,19 +22098,19 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>해양공공디지털연구본부, 경영지원본부</t>
+          <t>정보화전략부</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 AI 전담조직 미확인. 해양공공디지털연구본부가 디지털·AI 연구 수행 추정)</t>
+          <t>확인불가</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>중소기업기술정보진흥원</t>
+          <t>한국보건복지인재원</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -22124,11 +22124,11 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>271.3</v>
+        <v>238.6</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 전체 트리 라이브 재확인, 2026-09-18)</t>
+          <t>상(공식 개인정보처리방침 + 공공데이터포털 담당부서 표기 + 알리오 교차 확인)</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -22138,19 +22138,19 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>R&amp;D지원본부</t>
+          <t>경영전략본부</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 AI 전담조직 없음 / '지능정보화실'이 지능정보·정보화 기능 총괄)</t>
+          <t>확인불가</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>한국청소년상담복지개발원</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -22164,11 +22164,11 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>239.5</v>
+        <v>232.5</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직 명칭 + 개인정보처리방침(공식) 교차 확인)</t>
+          <t>상(공식 개인정보처리방침 + 알리오 + 보도 교차 확인)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -22178,7 +22178,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부</t>
+          <t>연금사업본부</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -22190,7 +22190,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>한국보건복지인재원</t>
+          <t>한국환경보전원</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -22204,11 +22204,11 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>238.6</v>
+        <v>225</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침 + 공공데이터포털 담당부서 표기 + 알리오 교차 확인)</t>
+          <t>상(공식 조직도(텍스트 확인) + 공식 개인정보처리방침 교차 확인)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>경영전략본부</t>
+          <t>인재운영처 (경영기획본부 산하) — 정보화·정보보안 기능 보유</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -22230,7 +22230,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -22244,11 +22244,11 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>232.5</v>
+        <v>202.3</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침 + 알리오 + 보도 교차 확인)</t>
+          <t>상(공식 개인정보처리방침(2025.7.10) + 공시 부서별 업무추진계획 + 보도 교차 확인)</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -22258,7 +22258,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>연금사업본부</t>
+          <t>융합기술센터 / 데이터정보화팀</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -22270,7 +22270,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
+          <t>과학기술정책연구원</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -22284,11 +22284,11 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>225</v>
+        <v>152</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도(텍스트 확인) + 공식 개인정보처리방침 교차 확인)</t>
+          <t>상(공식 홈페이지 개인정보처리방침으로 경영지원실·디지털전환팀 소속·CPO 확인 + 2026 개편 보도 다수 교차확인)</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -22298,19 +22298,19 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>인재운영처 (경영기획본부 산하) — 정보화·정보보안 기능 보유</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (전담 AI 조직 미확인 — 디지털·AI 전환 대응은 디지털전환팀이 수행)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>한국기상산업기술원</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -22324,11 +22324,11 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>202.3</v>
+        <v>151.8</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침(2025.7.10) + 공시 부서별 업무추진계획 + 보도 교차 확인)</t>
+          <t>상(공식 홈페이지 조직도 + 공공데이터포털 기관조직 데이터 교차확인)</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -22338,132 +22338,12 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>융합기술센터 / 데이터정보화팀</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>과학기술정책연구원</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>152</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>상(공식 홈페이지 개인정보처리방침으로 경영지원실·디지털전환팀 소속·CPO 확인 + 2026 개편 보도 다수 교차확인)</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>경영지원실</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (전담 AI 조직 미확인 — 디지털·AI 전환 대응은 디지털전환팀이 수행)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>한국기상산업기술원</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>151.8</v>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>상(공식 홈페이지 조직도 + 공공데이터포털 기관조직 데이터 교차확인)</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>경영기획본부</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
           <t>확인불가 (전담 조직 미확인 — 데이터/AI 업무는 산업육성실 기상기후데이터·빅데이터 사업에서 수행)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>한국저작권보호원</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>104.8</v>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>상(공식 홈페이지 조직도 + 공공데이터포털 관리부서 표기 교차확인)</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>정보기술부</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (별도 AI 전담조직 식별 안 됨)</t>
         </is>
       </c>
     </row>

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>AI전략본부 (2025.10 디지털융합본부에서 재편)</t>
+          <t>미래부문</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>AX기획처, ICT운영처, AI혁신처, IT운영센터(정보기획부·여객정보부·운송정보부·경영정보부·시스템운영부), 정보보안센터</t>
+          <t>AI전략본부(AX기획처·AX추진처·디지털관리처·IT운영센터), 정보보안실</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>AI전략본부 (산하 AX기획처, AI혁신처 / 별도 'AI 가속화 추진단 TF' 신설 계획)</t>
+          <t>AI전략본부</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -626,22 +626,22 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>AI전략본부장(본부장급) 총괄</t>
+          <t>AI전략본부장(본부장급) 총괄, 미래부문장(임원급) 지휘</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>정보보안센터(디지털영업처/디지털경영처 산하)로 추정 — 확인불가</t>
+          <t>정보보안실 — 미래부문 직속 실 단위로 편제(2026.06 개편 시 정보보안센터에서 승격)</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>중(공식 조직도 페이지는 개편 전 구조 노출 — 실질 근거는 나무위키·언론 보도 교차. 직제규정 시행세칙 원문 미확보)</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2025년 10월 기존 디지털융합본부를 AI전략본부로 재편하여 AI전환(AX) 전담 체계 구축. AX기획처·ICT운영처·AI혁신처 3개 처 신설. AI 챗봇 누적 100만건 돌파. 디지털경영자문위원회 운영, 'AI 가속화 추진단 TF' 신설 추진.</t>
+          <t>IT기능: AX(AI전환) 기획·추진, 디지털 관리, 전사 정보시스템 운영(정보기획·여객정보·운송정보·경영정보·시스템운영), 정보보안. 조직이력: 2025.10 디지털융합본부 → AI전략본부 재편(AX기획처·ICT운영처·AI혁신처). 2026.06.17 직제규정 시행세칙 개정(6.22 시행)으로 본사 '1부사장·12본부·3실·3단' → '2부사장(경영·안전)·5부문(경영·미래·영업·안전·기술)·13본부·3실·1단' 체계로 대개편. AI전략본부가 신설 '미래부문'(경영부사장 산하) 소속이 되고 산하 처가 AX기획처·AX추진처·디지털관리처로 재편(ICT운영처·AI혁신처 폐지). 정보보안센터는 '정보보안실'로 승격되어 미래부문 직속 편제(AI전략본부와 병렬). IT운영센터(부속기관)는 AI전략본부 소속으로 존속. 기타: 미래부문에 신성장사업본부·해외사업본부도 편제되어 IT전담 부문은 아님. AI 챗봇 누적 100만건 돌파. 2026.09.01 주식회사 SR 합병(수서발 고속철도 사업 이관).</t>
         </is>
       </c>
     </row>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>IT운영처 (경영관리본부 산하)</t>
+          <t>경영관리본부</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 경영관리본부 소속</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>IT운영처(전사 IT기획·디지털전환·빅데이터 전략 총괄, ICT 자산관리·정보시스템 구축·운영·정보통신장비 도입), 스마트단지기술처, 주택품질안전처(정보화사업 다수 수행)</t>
+          <t>IT운영처, 정보보안처</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1221,27 +1221,27 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>센터 (AI 전략·로드맵 수립, 대내외 AI 활용 과제 총괄, AI 연구지원 총괄)</t>
+          <t>센터</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>경영관리본부장 산하 IT운영처 — 확인불가(전담 CIO 임원 여부 미확인)</t>
+          <t>경영관리본부장 총괄 — 전담 CIO 임원 직위 여부는 확인불가</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>정보보안처 소관 — 전담 CISO 임원 직위는 확인불가</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + 정보화사업추진현황 교차)</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>별도 'AI혁신센터'를 두어 AI 전략·로드맵 수립, AI 활용 과제 총괄, AI 연구지원 수행. 'LH IT 거버넌스 개선 및 EPMO 도입'(2025.7~2026.7) 통해 전사 디지털전환·정보화사업 관리 전문성 강화. AI 돌봄전화(클로바 케어콜), AI 모바일 CS통합관리솔루션, 유지보수 기성검사 AI 조력시스템, AI 통합 모니터링 등 주거복지·시설관리 전반 AI 사업 활발.</t>
+          <t>IT기능: 전사 IT기획·디지털전환·빅데이터 전략 총괄, ICT 자산관리·정보시스템 구축·운영·정보통신장비 도입 총괄(IT운영처), 사이버안전센터 운영·정보보호시스템 운영(정보보안처). 경영관리본부 사무분장에 'IT 기획, 경영정보, 빅데이터, 정보보안 관련 업무' 명시. 기타: AI혁신센터는 본부 소속이 아닌 별도 단위(교학처·구조개혁실무지원단과 같은 계층)로 조직도에 편제되며 상위 소속 미표기 — AI 전략·로드맵 수립, 대내외 AI 활용 과제 총괄, AI 활용 지원방안 수립·운영, AI 연구지원 총괄 담당. 'LH IT 거버넌스 개선 및 EPMO 도입'(2025.7~2026.7)으로 전사 디지털전환·정보화사업 관리 전문성 강화. 정보화사업이 스마트단지기술처(AI 시설물 통합 모니터링·드론웍스·LH-BIM)·주택품질안전처(AI모바일 CS통합관리)·임대자산관리처(AI 수선비 예측)·스마트도시계획처(ArcGIS) 등 현업 부서에 분산 발주. AI 돌봄전화(네이버클라우드 클로바 케어콜) 등 주거복지 AI 사업 추진.</t>
         </is>
       </c>
     </row>
@@ -1646,52 +1646,52 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>별도 IT 전담 본부/처 없음 (정보시스템 기능은 경영관리본부 산하 부서 단위로 운영)</t>
+          <t>경영지원처</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>팀(부) — 경영지원처/경영관리본부 산하 정보시스템부 (추정)</t>
+          <t>부</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>정보시스템부, 정보보안(정보시스템부 내 또는 별도), 디지털기술개발센터(종합기술원 산하, 디지털 정비기술 R&amp;D)</t>
+          <t>정보시스템부, 정보보안부</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>없음 (전담 본부/처 없음, AI는 디지털기술개발센터 R&amp;D 및 AI Trust Center 중심으로 분산 추진)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>디지털기술개발센터(AI 정비기술), AI Trust Center/AI신뢰센터(감사실 산하, 2025.12.4 개소)</t>
+          <t>AI혁신처, AI혁신실</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>센터 (전담 본부/처 아님)</t>
+          <t>처</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>경영관리본부장 또는 경영지원처장 겸임 체계 (추정)</t>
+          <t>확인불가 (경영관리본부장 또는 경영지원처장 겸임 추정)</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>정보보안 담당 부서 운영 (정보시스템부 연계), 전담 임원급 CISO 확인불가</t>
+          <t>정보보안부가 정보보안·개인정보보호 전담 (별도 임원급 CISO 명시 확인불가)</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>중(공식 1출처 + 보도자료 다수)</t>
+          <t>상(공식 조직도·본사전화번호 안내 라이브 직접 확인)</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>2025.7 공공기관 최초 사내 자체개발 생성형 AI 'KARE(KPS AI Robot Engineer)' 서비스 출시(안전케어 기능 포함). 2025.12 감사 혁신용 'AI Trust Center' 개소 및 AI감사요원 '감사해' 개발. 발전설비 AI 이상탐지, 디지털트윈(P-HILS) 등 정비 분야 AI 적용에 집중하나, AI/IT 전담 상위 조직은 부재.</t>
+          <t>[IT담당배경] 정보시스템부·정보보안부가 경영관리본부 경영지원처 산하에 편제되어 IT는 부(部) 단위로 운영. [조직이력] 2026년 조직개편으로 신성장사업본부 산하 'AI혁신처' 신설(재생에너지사업처·사업개발처와 병렬), 종합기술원 산하 'AI혁신실' 설치(종전 디지털기술개발센터 계열 기능 재편). [기타] 2025.7 공공기관 최초 사내 자체개발 생성형 AI 'KARE(KPS AI Robot Engineer)' 출시. 2025.12 감사 혁신용 'AI Trust Center' 개소 및 AI감사요원 '감사해' 개발. 발전설비 AI 이상탐지, 디지털트윈(P-HILS) 등 정비 분야 AI 적용 추진. 본사 현원 6,056명(2026.6.30 기준, 조직도 페이지).</t>
         </is>
       </c>
     </row>
@@ -2621,17 +2621,17 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>안전처 (ICT운영부가 안전처 산하 / 별도 IT 본부·처는 없음)</t>
+          <t>안전처</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>팀(부) — 처 산하 부 단위</t>
+          <t>부</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>ICT운영부(안전처 산하), 정보보안부</t>
+          <t>ICT운영부, 정보보안부</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>중(조직도 상세가 이미지 제공이라 판독 불가, 계층 근거는 페이지 하단 담당부서 태그 1건)</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>한국전력공사의 검침·요금 자회사로 별도 법인(본사와 혼동 금지). 전국 196개 지점·15개 지사·발전사업소 65개소 운영(현장 인력 다수). ICT 기반 구축·정보시스템 개발·ICT 인재양성 교육 사업 추진. 조직도 기준일 2025-02-25. AMI모뎀·소규모전력중개 등 ICT 융합 신사업 추진 중이나 AI 전담 조직은 미확인.</t>
+          <t>[IT담당배경] ICT운영부는 안전처 산하, 정보보안부는 본사 부(部) 단위로 편제 — 별도 IT/디지털 본부·처 없음. [기타] 한국전력공사의 검침·요금 자회사로 별도 법인(한전 본사와 혼동 금지). 조직도 기준일 2026-07-10, 14개 지사·179개 지점·발전사업소 67개소 운영(현장 인력 다수). AMI모뎀·소규모전력중개 등 ICT 융합 신사업 추진 중이나 AI 전담 조직은 미확인.</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>처·실 (소관 라인 재확인 필요 — 공식 조직도상 본부 산하 기재, 일부 언론은 이사장 직속으로 보도)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -2866,32 +2866,32 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>AX혁신추진실(AX기획부·AI데이터부 중심) + AI 내재화 실무 TF팀</t>
+          <t>AX혁신추진실</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>실 (IT조직과 통합 — AX 전담 실 단위)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>AX혁신추진실장이 정보화·AX 총괄 (전담 CIO 명시 확인불가)</t>
+          <t>AX혁신추진실장(김태헌)이 정보화·AX 총괄 (전담 CIO 직위 명시 확인불가)</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>정보보안부 부장이 정보보안 총괄 (별도 CISO 직위 명시 확인불가)</t>
+          <t>정보보안부장(이승언)이 정보보안·개인정보보호 총괄 (별도 CISO 직위 명시 확인불가)</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 보도자료 2출처)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>기존 디지털혁신처에서 AX혁신추진실로 개편(AI 전환 강화). 전사 인공지능 전환(AX) 추진 — '그린리부트 2.0', 2026 미래혁신회의(ESG·AX·글로벌 3대 축) 출범. 생성형 AI(K-GPT) 운영, 공공AX 프로젝트 추진. AX 혁신대상 공공부문 대국민서비스 분야 최우수상 수상.</t>
+          <t>[IT담당배경] AX혁신추진실은 공식 직원검색 조직도에서 경영기획본부·기후환경본부·물환경본부·자원순환본부·환경시설본부와 같은 최상위 단위로 표기되어 본부에 속하지 않는 이사장 직속 실로 판단. IT 조직과 AI 전담 기능이 단일 실에 통합된 구조. [IT기능] 인공지능 전환(AX·DX) 추진계획 수립·시행, 디지털 신기술 PoC, 전사 지능정보화 및 정보화사업 사전협의, AI 사업 컨설팅, AX위원회·AX혁신추진단·인공지능윤리 소위원회 운영, 사내 LLM(K-eco GPT) 구축·운영, 공공AX 프로젝트, 기관 데이터 전략·공공데이터 개방, MIS·클라우드(E-클라우드)·네트워크·전자결재 운영, 정보보안·개인정보보호·사이버침해 대응. [조직이력] 기존 '디지털혁신처'에서 'AX혁신추진실'로 개편(AI 전환 강화). 2026 미래혁신회의(ESG·AX·글로벌 3대 축) 출범, '그린리부트 2.0' 추진. [기타] AX 혁신대상 공공부문 대국민서비스 분야 최우수상 수상.</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>ICT기획처(ICT기획부, ICT수탁총괄부), IT운영사업처(IT기반기술부, 디지털기술부, 전력IT운영부), 영배사업처(영업시스템운영부 등)</t>
+          <t>ICT기획처(ICT기획부, ICT수탁총괄부, 광통신망구축부, 전력인프라사업부, 전력인프라서비스부), IT운영사업처(IT기반기술부, 디지털기술부, 전력IT운영부, 전력경영정보부, 전력IT서비스부, 디지털전환사업부), 영배사업처(영업시스템운영부, 배전계획시스템운영부, 배전설비시스템운영부, 영배시스템기술부, 영배시스템구축부), 원발전사업단(원발전기획부, 원전사업처, 동남발전사업처, 서남발전사업처)</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>AX사업처 (신사업개발본부 산하, CEO 직속 'AI 전략위원회' 컨트롤타워 병행)</t>
+          <t>AX사업처, AI연구부, AI보안연구그룹, AX국정과제추진부</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (정보보호실이 정보보안부·개인정보보호부를 두고 실무 담당, 사이버안전처가 보안정책·관제대응 수행)</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>상(공식 1출처 + 보도 다수)</t>
+          <t>상(공식 조직도 라이브 직접 확인 + 보도 다수)</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>2026년을 'AI 전환(AX)의 원년'으로 선포. '2030 에너지AI 추진전략' 수립하며 AI 전주기(기획·기술개발·인프라·데이터) 전담조직 'AX사업처' 신설 및 CEO 직속 'AI 전략위원회' 신설. 회사 자체가 모회사 한국전력의 정보시스템·인프라 구축/운영을 총괄하는 전력ICT 전문 자회사(한전 ERP, 한수원 정보시스템 등 운영). 2026.4 'AI 및 신사업 대응을 위한 유연한 조직체계' 도입 추진.</t>
+          <t>[조직이력] 2026년을 'AI 전환(AX)의 원년'으로 선포. '2030 에너지AI 추진전략' 수립하며 AI 전주기(기획·기술개발·인프라·데이터) 전담조직 'AX사업처' 신설 및 CEO 직속 'AI 전략위원회' 신설. 2026.4 'AI 및 신사업 대응을 위한 유연한 조직체계' 도입 추진. [기타] 공식 조직도 2026.7.1 기준. AX사업처(AX전략사업부·중소기업AX사업부·E-클라우드사업부·E-플랫폼운영부·에너지DX사업부·정보관리부)는 신사업개발본부 산하, AI연구부·AI보안연구그룹은 전력ICT연구원 산하, AX국정과제추진부는 미래전략실 산하. 신사업개발본부 보안사업단에 보안사업처·정보보호실·사이버안전처 편제. 회사 자체가 모회사 한국전력의 정보시스템·인프라 구축/운영을 총괄하는 전력ICT 전문 자회사(한전 ERP, 한수원 정보시스템 등 운영).</t>
         </is>
       </c>
     </row>
@@ -4496,17 +4496,17 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>정보시스템처(공식 조직도 표기) / AX추진처(정보공시·임직원검색 표기, 경영지원본부 산하) — IT 기획·운영 총괄 / AI 전환 전략은 기획본부 AX추진단</t>
+          <t>경영지원본부</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>AX추진처 ICT운영부(정보시스템 운영·정보기기·ERP 총괄), 사이버보안센터</t>
+          <t>정보시스템처(ICT운영부), 사이버보안센터</t>
         </is>
       </c>
       <c r="I54" s="3" t="inlineStr">
@@ -4516,17 +4516,17 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>AX추진단 (AX혁신TF + AX구축TF)</t>
+          <t>AX추진단(AX혁신TF·AX구축TF)</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>단(기획본부 산하) — 2025.9.1 핀포인트 조직개편으로 출범</t>
+          <t>단</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (AX추진처 소관, 경영지원본부장 계열 / AI 전략은 기획본부장 산하 AX추진단)</t>
+          <t>확인불가 (정보시스템처 소관, 경영지원본부장 계열)</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상(공식 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>2025.8.25 인공지능 전환(AX) 로드맵 발표, 2025.9.1 정기인사 외 핀포인트 조직개편으로 'AX추진단'(AI 기반 업무혁신 총괄) 출범. AX혁신TF(전사 AI 전환정책·실행계획 총괄) + AX구축TF 구성. AX 3단계 추진(1단계 2025~2026 고품질 데이터셋 구축). 안전특화 생성형 AI 2025.9 시범 오픈. 열수요 예측·경제운전 최적화·설비진단 AI 적용 로드맵. 기존 정보시스템처가 'AX추진처'로 재편(ICT운영부 보유). 정보보안처 신설 이력 및 융합보안(사이버보안센터) 운영.</t>
+          <t>IT기능: 정보시스템 운영, 정보기기 관리, ERP 총괄(ICT운영부), 정보보안·융합보안(사이버보안센터). 조직이력: 2025.8.25 인공지능 전환(AX) 로드맵 발표 → 2025.9.1 정기인사 외 '핀포인트 조직개편'으로 기획본부 산하 'AX추진단'(AI 기반 업무혁신 총괄) 출범, AX혁신TF(전사 AI 전환정책·실행계획 총괄)+AX구축TF 구성. 기타: AX 3단계 추진(1단계 2025~2026 고품질 데이터셋 구축), 안전특화 생성형 AI 2025.9 시범 오픈, 열수요 예측·경제운전 최적화·설비진단 AI 적용 로드맵. 명칭 정합성 주의 — 정보공시·임직원검색에는 'AX추진처 ICT운영부'로 표기되나 공식 조직도는 2026-09 시점에도 '정보시스템처'를 유지(전환 과도기, IT 운영 실체조직은 동일).</t>
         </is>
       </c>
     </row>
@@ -5921,19 +5921,19 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
+          <t>경영기획실</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>팀</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
           <t>디지털혁신팀</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>팀 (경영기획실 산하)</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>없음 (디지털혁신팀 단일 팀이 정보화 기획·시스템개발/운영·인프라·정보보안·개인정보보호·데이터기반행정·AI 관련 업무를 모두 담당. 팀 내 기능 분장: 정보화기획·시스템운영, 홈페이지/앱 개발·운영, 통합정보·재무 시스템, 인트라넷/전자결재/메일, 개인정보보호·AI, 정보보안·인프라운영)</t>
-        </is>
-      </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
           <t>없음</t>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>해당없음 (디지털혁신팀 대리 1명이 '개인정보보호/AI 관련 업무' 겸임)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>경영기획실장 총괄 (경영기획실 업무에 '경영정보화 및 전산개발·운용' 명시, 디지털혁신팀이 경영기획실 산하)</t>
+          <t>경영기획실장 총괄</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>경영기획실 소관 (경영기획실 업무에 '개인정보보호 등 정보보안에 관한 사항' 명시. 실무는 디지털혁신팀 전문관(정보보안·인프라운영)이 수행. 전담 CISO 임원 직위는 확인불가)</t>
+          <t>경영기획실 소관 — 전담 CISO 임원 직위는 확인불가</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>서울올림픽기념국민체육진흥공단(KSPO) 자회사. 88서울올림픽 시설(올림픽공원 등) 유지관리·스포츠레저공간 운영 기관. IT는 경영기획실 산하 디지털혁신팀이 단일 담당.</t>
+          <t>IT기능: 정보화기획·데이터기반행정, 홈페이지/앱 개발·운영, 통합정보·재무시스템, 인트라넷/전자결재/메일, 개인정보보호·AI, 정보보안·인프라운영. 경영기획실 사무분장에 '경영정보화 및 전산개발·운용', '개인정보보호 등 정보보안에 관한 사항' 명시. 조직이력: 경영기획실은 기획팀·ESG성과팀·디지털혁신팀 3개 팀으로 구성. 기타: 서울올림픽기념국민체육진흥공단(KSPO) 자회사. 88서울올림픽 시설(올림픽공원 등) 유지관리·스포츠레저공간 운영 기관. AI 전담조직 없이 디지털혁신팀 대리 1명이 '개인정보보호/AI 관련 업무' 겸임.</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>실 (미래기획본부 산하)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>AI혁신부 (AI디지털보안실 산하), AI디지털보안실</t>
+          <t>AI디지털보안실, AI혁신부</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>부 (실 산하)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 원문공개·공공데이터 2출처)</t>
+          <t>상(공식 조직도 라이브 확인 + 원문공개·공공데이터 2출처)</t>
         </is>
       </c>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>조직명에 'AI'를 명시한 'AI디지털보안실' 보유 — IT·디지털·정보보안·AI를 단일 실로 통합. 산하 AI혁신부가 AI 전담. 제조 지능화·디지털전환(DX) 기본계획 추진. 공공데이터 책임관이 AI디지털보안실 소속.</t>
+          <t>[IT담당배경] 조직명에 'AI'를 명시한 'AI디지털보안실'이 미래기획본부 산하에 편제 — IT·디지털·정보보안·AI를 단일 실로 통합. [IT기능] 제조 지능화·디지털전환(DX) 기본계획 추진, 공공데이터제공책임관 소관. [기타] 공식 조직도는 실(室) 단위까지만 표기되며, 산하 디지털융합부(디지털전환·정보화)·AI혁신부(AI 전담)는 원문공개서비스·공공데이터 개방목록의 담당부서 표기로 확인.</t>
         </is>
       </c>
     </row>
@@ -7801,17 +7801,17 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하 추정 — 경영관리본부 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>AI디지털융합처(정보화사업·해양환경정보포털·시스템 총괄), 정보보안팀(개인정보보호 담당)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
         <is>
-          <t>있음 (부서명에 'AI' 명시 — AI디지털융합처)</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J98" s="3" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>처(處)</t>
+          <t>처</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="N98" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>중(공식 조직도와 개인정보처리방침 간 부서 표기 불일치)</t>
         </is>
       </c>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>기존 정보화 조직을 'AI디지털융합처'로 재편 — AI를 정보화 조직 명칭에 직접 반영(상대적으로 적극적). 드론·AI·빅데이터 기반 해양쓰레기 수거·해양환경 분석 디지털 혁신 추진. 14개 소속기관 대상 CISO 주관 정보보안 지도점검 운영.</t>
+          <t>[IT담당배경] 기존 정보화 조직을 'AI디지털융합처'로 재편 — AI를 정보화 조직 명칭에 직접 반영. [IT기능] 정보화사업·해양환경정보포털 운영·정보시스템 총괄, 개인정보보호책임자(CPO) 소속 부서. [조직이력] 2026년 조직도에 내부통제추진단·미래전략추진단 신설. [기타] 출처 간 불일치 — 공식 조직도 페이지(2026-09-19 확인)의 텍스트 조직 목록에는 AI디지털융합처가 표기되지 않고 안전경영본부 경영지원처 산하 '정보보안팀'만 확인되나, 같은 홈페이지의 개인정보처리방침(2026.9.10 개정)·사전정보공표 목록에는 AI디지털융합처(CPO 신민섭)가 현재 부서로 명시됨 → 조직도 페이지 갱신 시차로 판단하여 AI디지털융합처 유지. 드론·AI·빅데이터 기반 해양쓰레기 수거(AI 수상로봇 KOEM-ARK) 등 디지털 혁신 추진.</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>해양데이터·인프라본부 (데이터·AI·디지털 총괄) / 내부 경영정보는 경영기획본부</t>
+          <t>해양데이터·인프라본부</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>(해양데이터·인프라본부) 해양빅데이터·AI센터, 해양디지털정보실, 첨단인프라운영센터 / (경영기획본부) 경영정보실, 정보보안실</t>
+          <t>해양빅데이터·AI센터, 해양디지털정보실, 첨단인프라운영센터, 해양인프라지원팀</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -7896,27 +7896,27 @@
       </c>
       <c r="K99" s="3" t="inlineStr">
         <is>
-          <t>센터 (해양데이터·인프라본부 산하, 부원장 직속 본부 레벨 하위)</t>
+          <t>센터</t>
         </is>
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>해양데이터·인프라본부장 (데이터·디지털 총괄, 추정)</t>
+          <t>확인불가 (조직도상 CIO 직위 명시 없음. 해양데이터·인프라본부장이 데이터·디지털 총괄로 추정)</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>정보보안실 (경영기획본부 산하)</t>
+          <t>정보보안실</t>
         </is>
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>상 (공식 조직도 + 다수 보도자료 교차확인)</t>
+          <t>상 (공식 홈페이지 조직도 라이브 직접 확인, 2026-09-19)</t>
         </is>
       </c>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>'해양빅데이터·AI센터'를 조직 내 상설 설치하여 AI 전담조직 보유. 2029년까지 자체재원 208억원 투입해 부산 본원에 '해양과학AI연구센터' 구축 추진 중. '디지털 대전환과 AI 강국 도약' 전략 추진. 2022년 연안 빅데이터 플랫폼 구축(455종 데이터 공개).</t>
+          <t>[IT담당배경] 연구기관 특성상 IT조직이 내부 경영정보(경영기획본부 산하 경영정보실·정보보안실)와 연구데이터/AI 인프라(부원장 산하 해양데이터·인프라본부)로 이원화됨.&lt;br&gt;[IT기능] 해양빅데이터·AI센터가 AI·빅데이터 전담. 2022년 연안 빅데이터 플랫폼 구축(455종 데이터 공개). '디지털 대전환과 AI 강국 도약' 전략 추진. 2029년까지 자체재원 208억원 투입해 부산 본원에 '해양과학AI연구센터' 구축 추진 중.&lt;br&gt;[조직이력] 해양데이터·인프라본부 편제에 '해양인프라지원팀' 확인(종전 미기재).</t>
         </is>
       </c>
     </row>
@@ -7946,17 +7946,17 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>경영기획실 (내부 정보화·경영지원 총괄) / 안전경영관리단 (정보보안관리)</t>
+          <t>경영기획실</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>실 (내부 정보화는 경영기획실 산하 / 정보보안은 안전경영관리단 산하 팀)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>(경영기획실) 기획조정팀·ESG혁신팀·윤리소통팀·인사총무팀·재무관리팀, (안전경영관리단) 정보보안관리팀·운영관리팀·안전경영팀, (부원장실) 정보보안정책팀</t>
+          <t>안전경영관리단(안전경영팀·운영관리팀·정보보안관리팀)</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -7966,12 +7966,12 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>인공지능정책실, 인공지능융합본부, 인공지능데이터본부, 공공지능데이터본부, 지능기술인프라본부, 인공지능정부본부 (대외 사업 조직)</t>
+          <t>인공지능정책실, 인공지능융합본부, 인공지능정부본부, 인공지능정부기반본부, 인공지능데이터본부, 공공지능데이터본부, 지능기술인프라본부</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>실/본부 (다수, 대외 사업)</t>
+          <t>실·본부</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>AI·지능정보화 자체가 기관의 본업(국가 AI·데이터·디지털플랫폼정부 전담기관). 대외 사업조직으로 AI 관련 실·본부 다수 보유(인공지능정책실·인공지능융합본부·인공지능데이터본부·공공지능데이터본부 등). 전사 정보화를 총괄하는 내부 경영지원 조직은 경영기획실, 내부 정보보안은 안전경영관리단·부원장실 정보보안정책팀이 담당. 대외 AI 조직과 내부 정보화 조직을 구분해 해석해야 함.</t>
+          <t>IT담당배경: AI·지능정보화 자체가 기관 본업(국가 AI·데이터 전담기관)이므로, 대외 사업용 AI 실·본부와 내부 전사 정보화 조직을 구분해 해석해야 함. 내부 정보화·경영지원 총괄은 경영기획실, 내부 정보보안은 부원장실 정보보안정책팀(정책)과 경영기획실 산하 안전경영관리단 정보보안관리팀(관리)으로 이원 운영. 조직이력: 2026년 조직개편으로 '디지털플랫폼정부본부'가 '인공지능정부본부'·'인공지능정부기반본부'로 분리·개편, 인공지능정책실 산하 AI법제도센터·디지털전략기획단 신설, 지능기술인프라본부에 '에이전틱AI혁신팀'·'AI-클라우드기술혁신팀' 신설. 기타: 인공지능데이터본부에 피지컬AI데이터TF 운영. 별도 독립 '정보화처/전산실' 형태의 내부 IT 부서는 없음.</t>
         </is>
       </c>
     </row>
@@ -8396,19 +8396,19 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
+          <t>경영기획처</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>처·실</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
           <t>정보화지원실</t>
         </is>
       </c>
-      <c r="G106" s="3" t="inlineStr">
-        <is>
-          <t>팀 (경영기획처 산하 실)</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>정보화지원실 (경영기획처 내 기획조정실·인재경영실·경영지원실과 병렬)</t>
-        </is>
-      </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
           <t>없음</t>
@@ -8416,32 +8416,32 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>(해당 없음 — 조직도상 AI 전담부서 미확인. 홈페이지에 'AI INNOVATION' 메뉴는 있으나 사업/콘텐츠 단위이며 독립 조직 아님)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>확인불가 — 경영기획처장이 총괄하는 것으로 추정</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
           <t>확인불가</t>
         </is>
       </c>
-      <c r="L106" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (정보화지원실 소관 경영기획처장이 총괄하는 것으로 추정)</t>
-        </is>
-      </c>
-      <c r="M106" s="3" t="inlineStr">
-        <is>
-          <t>확인불가</t>
-        </is>
-      </c>
       <c r="N106" s="3" t="inlineStr">
         <is>
-          <t>중(공식 홈페이지 조직도 1출처 + WebFetch 교차)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인, 전 부서 트리 추출)</t>
         </is>
       </c>
       <c r="O106" s="3" t="inlineStr">
         <is>
-          <t>정보화 기능이 별도 본부가 아닌 경영기획처 산하 1개 실(정보화지원실)에 통합. AI는 IP-R&amp;D 등 사업영역(인공지능·첨단바이오 지정공모)에서 다뤄지나 전담 조직은 미확인.</t>
+          <t>IT담당배경: 정보화 기능이 별도 본부·처가 아닌 경영기획처 산하 1개 실(정보화지원실)에 통합. 경영기획처는 기획조정실·인재경영실·경영지원실·정보화지원실 4개 실로 구성. 기타: 본부 구조는 특허사업본부(특허사업총괄실·융복합조사실·기계건설조사실·화학생명조사실·전기통신조사실·반도체영상조사실), 국제사업본부(국제사업총괄실·기계/화학/전기/통신국제조사실), 지식재산정보기반본부(지식재산정보총괄실·지식재산분류1실·지식재산분류2실·지식재산안보전략실), 상표디자인센터(상표디자인총괄실·상표조사분류실·디자인조사분류실), IP협력센터, 해외 IP Korea Center(미국지사). 지식재산정보기반본부는 내부 정보화가 아닌 특허분류·IP정보 사업 수행 조직. 홈페이지에 'AI INNOVATION' 메뉴가 있으나 사업·콘텐츠 단위이며 독립 조직 아님. IP-R&amp;D 인공지능·첨단바이오 지정공모 등 AI를 사업영역에서 다루나 전담 조직은 미확인.</t>
         </is>
       </c>
     </row>
@@ -8546,17 +8546,17 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>디지털전략실 (경영기획처 산하)</t>
+          <t>디지털전략실</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 경영기획처 산하 실</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>디지털전략실, 정보보안팀 (경영기획처 직속)</t>
+          <t>없음(단일 실)</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
@@ -8566,32 +8566,32 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>(해당 없음)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>(해당 없음)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr">
         <is>
-          <t>경영기획처장 산하 디지털전략실이 정보화 총괄 (전담 CIO 명문 표기 확인불가)</t>
+          <t>경영기획처장 소관, 디지털전략실이 정보화 실무 총괄 (전담 CIO 직위 명시 확인불가)</t>
         </is>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>경영기획처 산하 정보보안팀 소관 (CISO 직위 명문 표기 확인불가)</t>
+          <t>경영기획처 정보보안팀 소관 (별도 CISO 직위 명시 확인불가)</t>
         </is>
       </c>
       <c r="N108" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직체계 + 검색 교차)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>정보화 기능은 경영기획처 산하 '디지털전략실'이 담당. AI 전담 조직은 조직도상 없음 — 다만 K-eco AI 프롬프톤, AI 환경기술 과제 등 AI '사업'은 환경기술산업본부 등에서 추진(전담 직제 조직과는 구분).</t>
+          <t>[IT담당배경] 디지털전략실과 정보보안팀 모두 경영기획처 산하에 병렬 배치. 경영기획처는 기획조정실·인재경영실·경영지원실·혁신성과실·디지털전략실·시설안전실·정보보안팀으로 구성. [IT기능] 정보화 기획·운영, 사이버보안 관리실태 및 관리적 보안(자체감사), 정보보안지침 개정 및 NCTI 연계 운영, 개인정보 평가 지원, 정보화사업 보안성 검토. [조직이력] 2026-09 기준 조직체계도(org202609) 확인. 기관 부서코드 G143이 구 '환경지식정보실'에서 '디지털전략실'로 이어지는 라인으로, 홈페이지 내 일부 텍스트 목록에 구 명칭이 잔존. [기타] AI 전담 직제는 없으나 K-eco AI 프롬프톤, AI 폐기물 선별로봇 등 AI '사업'은 환경기술산업본부 등에서 추진. 유사기관 혼동 주의 — 한국환경공단(KECO)·한국환경보전원(KECI)·한국환경연구원(KEI)과 별개, 본 건은 KEITI(keiti.re.kr).</t>
         </is>
       </c>
     </row>
@@ -8846,52 +8846,52 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
+          <t>경영본부</t>
+        </is>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>본부</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>AI 혁신전략실(정보보호팀)</t>
+        </is>
+      </c>
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
           <t>AI 혁신전략실</t>
         </is>
       </c>
-      <c r="G112" s="3" t="inlineStr">
-        <is>
-          <t>처·실(본부 산하)</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>정보보호팀 (AI 혁신전략실 산하), 디지털융합팀 (해양안전실 산하 — MTIS/스마트 해양교통안전 빅데이터 플랫폼 운영)</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>AI 혁신전략실</t>
-        </is>
-      </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 경영본부 소속</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영본부장 산하 AI 혁신전략실이 정보화 총괄로 추정)</t>
+          <t>확인불가 (조직도상 CIO 직위 명시 없음. 경영본부장 산하 AI 혁신전략실이 정보화 총괄로 추정)</t>
         </is>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보안 기능은 AI 혁신전략실 산하 정보보호팀이 담당)</t>
+          <t>확인불가 (별도 CISO 직제 미확인. 정보보안 기능은 AI 혁신전략실 산하 정보보호팀이 담당)</t>
         </is>
       </c>
       <c r="N112" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상 (공식 홈페이지 조직도 라이브 직접 확인, 2026-09-19)</t>
         </is>
       </c>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>정보화/정보보안/AI 기능을 'AI 혁신전략실'로 통합한 AI 중심 명칭의 조직 구성. 조직은 4본부(경영본부·해양교통본부·검사본부·운항본부) 체계. 해양안전실 디지털융합팀은 IT 인프라가 아닌 해양교통안전정보시스템(MTIS)·빅데이터 플랫폼 등 사업성 시스템 운영 담당. AI 기반 도면승인 보완사항 분석 기술지원 서비스 구축 등 디지털 전환 진행 중.</t>
+          <t>[IT담당배경] 정보화·정보보안·AI 기능을 경영본부 산하 'AI 혁신전략실'로 통합한 AI 중심 명칭의 조직 구성.&lt;br&gt;[IT기능] 해양안전실 소속 디지털융합팀은 내부 IT 인프라가 아닌 해양교통안전정보시스템(MTIS)·스마트 해양교통안전 빅데이터 플랫폼 등 사업성 시스템 운영 담당. AI 기반 도면승인 보완사항 분석 기술지원 서비스 구축 등 디지털 전환 진행 중.&lt;br&gt;[조직이력] 현 조직 체계: 이사장 직속 기획조정실·성과혁신실 + 4본부(경영본부·해양교통본부·검사본부·운항본부) + 공영항로 운영 추진단 + 지사. 종전 기록(2026-06) 대비 기획조정실·성과혁신실의 이사장 직속 편제와 경영본부 내 인재경영실·ESG경영성과실·운영지원실·교육법무지원단 구성 확인.</t>
         </is>
       </c>
     </row>
@@ -9221,52 +9221,52 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>경영전략본부 (정보보안팀이 정보화·보안 담당)</t>
+          <t>경영전략본부</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>팀(본부 산하)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>정보보안팀(경영전략본부) — 경영전략본부는 전략혁신팀·기획예산팀·인사팀·재무팀·정보보안팀·안전경영팀으로 구성</t>
+          <t>정보보안팀, 데이터정책팀</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>있음(콘텐츠 사업 기준) / IT내부 AI조직은 없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>AI융복합콘텐츠팀(게임신기술본부 산하)</t>
+          <t>AI융복합콘텐츠팀</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>팀(본부 산하)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="L117" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영전략본부장이 정보화 총괄 추정)</t>
+          <t>확인불가 — 경영전략본부장이 정보화 총괄하는 것으로 추정</t>
         </is>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보보안팀 소관)</t>
+          <t>확인불가 — 정보보안팀 소관</t>
         </is>
       </c>
       <c r="N117" s="3" t="inlineStr">
         <is>
-          <t>중(공식 조직도 1출처 + ESG보고서·검색 교차)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인 + ESG보고서 교차)</t>
         </is>
       </c>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>별도 정보화 전담 본부·처 없이 경영전략본부 내 정보보안팀이 IT·보안 수행. AI는 콘텐츠산업 진흥 측면에서 게임신기술본부 'AI융복합콘텐츠팀'·콘텐츠산업정책연구센터 '데이터정책팀'이 담당. 2026년 AI 콘텐츠 제작지원 198억원 투입 등 AI 사업 활발. 글로벌혁신부문 산하에 경영전략본부·게임신기술본부 배치.</t>
+          <t>IT담당배경: 별도 정보화 전담 본부·처 없이 경영전략본부 내 '정보보안팀'이 정보화·보안 업무를 함께 수행. IT기능: 정보보안·정보화 운영(정보보안팀), 콘텐츠산업 데이터 정책(데이터정책팀). 조직이력: 경영전략본부는 전략혁신팀·기획예산팀·인사팀·재무팀·정보보안팀·안전경영팀으로 구성. 기타: 데이터정책팀은 IT 계통이 아닌 '정책연구본부' 소속, AI융복합콘텐츠팀은 '게임신기술본부' 소속으로, 두 조직 모두 콘텐츠산업 진흥사업 성격. 원장 산하 상임감사·부원장 체계이며 경영전략본부·콘텐츠수출본부·방송영상본부·게임신기술본부·콘텐츠IP진흥본부·콘텐츠기반본부·정책연구본부·연구개발사업본부로 편제. 2026년 AI 콘텐츠 제작지원 198억원 투입 등 AI 사업 활발.</t>
         </is>
       </c>
     </row>
@@ -10346,17 +10346,17 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>IT 전문 수행기관(기관 본연 업무가 정보화) — 다수 정보화 실(室) 직속 운영. 총괄 정보화기획은 전략기획실</t>
+          <t>정보시스템본부</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>처·실(원장 직속) — 다수의 IP시스템·지능정보 관련 실이 병렬 배치</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>IP시스템전략실, IP시스템운영실, IP시스템기반실, 지능정보전략실, 지능정보기술실, 지능정보데이터실, 분석플랫폼전략실, 데이터관리실, IP정보확산실, IP정보가공실, IP고객상담실 (전략기획실이 정보화사업 기획·조정 총괄)</t>
+          <t>IP시스템전략실, IP시스템운영실, IP시스템기반실</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
@@ -10366,32 +10366,32 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>지능정보전략실, 지능정보기술실, 지능정보데이터실 (지능정보기술 = AI 영역)</t>
+          <t>지능정보화센터 (지능정보전략실·지능정보기술실·지능정보데이터실)</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>실(室) — 원장 직속 레벨, 3개 실로 구성</t>
+          <t>센터</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전략기획실이 정보화사업 기획·조정 총괄, 직제상 CIO 명시 미확인)</t>
+          <t>확인불가 (조직도상 CIO 직위 명시 없음. 정보시스템본부장이 정보화 총괄로 추정)</t>
         </is>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>IP시스템전략실이 보안업무 담당 (별도 CISO 직위 명시 미확인 / 추정)</t>
+          <t>확인불가 (조직도상 CISO 직위 명시 없음. IP시스템전략실이 특허행정 정보화품질관리·보안업무 담당)</t>
         </is>
       </c>
       <c r="N132" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직안내 + 나무위키 교차)</t>
+          <t>상 (공식 홈페이지 조직도 라이브 직접 확인, 2026-09-19)</t>
         </is>
       </c>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>기관 자체가 "지식재산 지능정보화 전문기관"을 비전으로 표방하는 IT 전문기관. 심사관용 AI 검색시스템(KOMPASS), AI 검색시스템 유지관리, IP정보 디지털전환사업 등 AI 사업 다수 보유. 특허넷 시스템 운영 위탁. 임직원 424명(나무위키 2026.1Q 기준, 알리오 전달 현원 401명과 차이 있음)</t>
+          <t>[IT담당배경] 기관 본연 업무가 특허청 특허넷 시스템 운영 위탁인 IT 전문 수행기관. "지식재산 지능정보화 전문기관"을 비전으로 표방.&lt;br&gt;[IT기능] IP시스템전략실=특허행정 정보화품질관리 / IP시스템운영실=특허넷 응용시스템 운영 / IP시스템기반실=특허넷 기반시스템 운영 / 지능정보전략실=응용기술 연구개발 총괄 / 지능정보기술실=심사관용 AI 검색서비스(KOMPASS) 운영 / 지능정보데이터실=데이터 정비·고도화 / 분석플랫폼지원단=분석플랫폼 및 데이터 관리.&lt;br&gt;[조직이력] 종전 기록(2026-06)의 "정보화 실(室) 원장 직속 병렬 배치" 구조에서 본부·센터·지원단 체계로 정비 확인 — 경영관리본부·정보활용본부·정보시스템본부(본부급) + 지능정보화센터·분석플랫폼지원단(원장 직속).&lt;br&gt;[기타] AI 전담조직 판정 근거: 조직명은 '지능정보'(정부 공식 AI 용어)이며, 지능정보기술실이 심사관용 AI 검색시스템 KOMPASS를 전담 운영 → '있음'으로 계상. IT하위부서 트리에는 정보시스템본부 직속 3실만 표기하고, 정보활용본부 소속(IP정보확산실·IP정보가공실·IP고객상담실)·분석플랫폼지원단 소속(분석플랫폼전략실·데이터관리실)·지능정보화센터 소속(지능정보전략실·지능정보기술실·지능정보데이터실)은 별도 조직으로 분리 기재(트리 오렌더링 방지).</t>
         </is>
       </c>
     </row>
@@ -10796,17 +10796,17 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>정보안전부 (경영지원본부 산하)</t>
+          <t>경영지원본부</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) (경영지원본부 산하 '부' 단위)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보안전부가 정보화·정보보안·개인정보보호 담당. 하위 팀 구성 미확인)</t>
+          <t>디지털정보부</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
@@ -10826,22 +10826,22 @@
       </c>
       <c r="L138" s="3" t="inlineStr">
         <is>
-          <t>경영지원본부장 겸임 (추정)</t>
+          <t>디지털정보부장 (공공데이터제공·데이터기반행정 책임관 겸임). 경영지원본부장 총괄</t>
         </is>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>경영지원본부 정보안전부가 정보보안 총괄. KYWA 개인정보처리방침상 자체 정보보호 책임자(정보보안 담당, 과거 '정보보호팀장' 표기 → 현 정보안전부로 통합)를 지정·운영. 전담 임원급 CISO 직제는 미확인(정보안전부장 수준)</t>
+          <t>경영지원본부 디지털정보부 (정보보안·대외평가·국립청소년시설 보안점검, IDC 위탁운영 및 정보보안, 개인정보보호·안전성 확보조치 담당). 전담 임원급 CISO 직제는 미확인</t>
         </is>
       </c>
       <c r="N138" s="3" t="inlineStr">
         <is>
-          <t>중~상(공식 홈페이지 본부 구조 + e청소년/KYWA 개인정보처리방침 정보안전부·정보보호책임자 2출처. 정보안전부 하위 팀 세부는 조직도가 JS/이미지로 미노출)</t>
+          <t>상(공식 홈페이지 조직도·부서별 담당업무 직접 확인)</t>
         </is>
       </c>
       <c r="O138" s="3" t="inlineStr">
         <is>
-          <t>4본부 체제(기획조정본부·경영지원본부·활동진흥본부·활동안전본부). IT/정보화·정보보안은 경영지원본부 산하 '정보안전부'가 담당(2024년 e청소년 개인정보처리방침에 '경영지원본부 정보안전부' 명시, 담당자 김소영). 기획조정본부 산하: 기획혁신부·인재경영부·홍보전략부. 청소년활동정보시스템(e청소년), 청소년수련활동인증제 정보시스템 등 운영. AI 전담조직 단서는 확인되지 않음.</t>
+          <t>IT담당배경: 종전 '정보안전부'가 '디지털정보부'로 명칭 변경되어 경영지원본부 산하에서 정보화·정보보안·개인정보보호·데이터를 통합 담당. 부장이 공공데이터제공 및 데이터기반행정 책임관을 겸임. IT기능: 홈페이지 기획·운영, 디지털플랫폼 구축 및 디지털전환, 청소년활동정보서비스(e청소년) 활성화·유지관리·기능개선, 정보화사업 컨설팅 및 보안성 검토, 데이터사업 기획 및 내부행정시스템 관리, 정보보안 및 대외평가·국립청소년시설 보안점검, 공공데이터 제공 및 청소년데이터플랫폼 운영, 개인정보보호 및 안전성 확보조치, IDC 위탁운영. 조직이력: 정보안전부 → 디지털정보부로 개편(경영지원본부 산하 유지). 기타: 이사장 아래 정책기획이사·활동사업이사 2명, 4본부(기획조정본부·경영지원본부·활동사업본부·안전연수본부) 및 국립수련시설 6곳 체제, 감사 산하 청렴감사실. 청소년데이터플랫폼(YouthDATA) 운영. AI 명칭 전담조직 단서는 확인되지 않음.</t>
         </is>
       </c>
     </row>
@@ -11996,52 +11996,52 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>지능정보화팀 (경영본부 산하)</t>
+          <t>지능정보화팀</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>팀 (경영본부 산하, 별도 정보화 처·실 없음)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>지능정보화팀 (정보화·개인정보 담당 단일 팀). 경영본부 내 병렬: ESG경영전략실·경영지원팀·재무회계팀·청사운영팀</t>
+          <t>없음(단일 팀)</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 'AI' 명칭 전담조직 미확인. 정보화는 경영본부 산하 '지능정보화팀'이 담당하나 일반 IT 기능으로 판단)</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>개인정보보호책임자(CPO)=경영본부장. 지능정보화팀 소관 본부장으로서 IT 총괄</t>
+          <t>확인불가 (전담 CIO 직제 미확인. 개인정보보호책임자(CPO)=경영본부장이 지능정보화팀 소관 본부장으로서 IT 총괄)</t>
         </is>
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
-          <t>전담 임원급 CISO 직제 미확인. CPO=경영본부장, 개인정보 보호담당자·열람청구 부서=지능정보화팀. 별도 재난안전실(원장 직속)이 재난안전 담당</t>
+          <t>확인불가 (전담 임원급 CISO 직제 미확인. 개인정보 보호담당자·열람청구 부서=지능정보화팀)</t>
         </is>
       </c>
       <c r="N154" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 개인정보처리방침 2출처로 지능정보화팀·CPO=경영본부장 확인)</t>
+          <t>상 (공식 홈페이지 조직도 라이브 직접 확인 + 개인정보처리방침 교차, 2026-09-19)</t>
         </is>
       </c>
       <c r="O154" s="3" t="inlineStr">
         <is>
-          <t>선원 교육·훈련 중심 기관. 원장 직속 감사실·재난안전실 + 교육본부(교육기획실·교육운영팀·국제협력팀·능력평가팀·오션폴리텍해운팀·오션폴리텍수산팀·해양기술교육팀·목포분원) + 경영본부(ESG경영전략실·경영지원팀·재무회계팀·청사운영팀·지능정보화팀) 체계. IT/정보화는 경영본부 산하 '지능정보화팀'이 전담(팀 레벨). 별도 AI 전담조직은 미확인.</t>
+          <t>[IT담당배경] 선원 교육·훈련 중심 기관으로 별도 정보화 처·실 없이 경영본부 산하 '지능정보화팀'이 정보화·개인정보를 단일 팀으로 전담.&lt;br&gt;[IT기능] 지능정보화팀=정보화 일반·개인정보 보호담당·열람청구 접수·공공데이터 담당. 원장 직속 재난안전실이 재난안전 담당(정보보안과는 별개).&lt;br&gt;[조직이력] 현 조직 체계: 원장 직속 감사실·재난안전실 + 교육본부(교육기획실·교육운영팀·국제협력팀·능력평가팀·오션폴리텍해운팀·오션폴리텍수산팀·해양기술교육팀·목포분원) + 경영본부(ESG경영전략실·경영지원팀·재무회계팀·청사운영팀·지능정보화팀). 2026-09-19 라이브 재확인 결과 종전(2026-06-17)과 동일.&lt;br&gt;[기타] 조직도 전수 확인 결과 'AI' 명칭 상설 전담조직 부재 → AI전담조직 '없음' 확정. '지능정보화팀'은 일반 IT 기능 담당으로 판단.</t>
         </is>
       </c>
     </row>
@@ -12146,17 +12146,17 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>정보시스템실 (경영관리부문 산하)</t>
+          <t>경영관리부문</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>정보시스템실 (경영관리부문), 투자시스템실 (투자관리부문, 투자 IT 인프라)</t>
+          <t>정보시스템실, AI혁신실</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -12171,12 +12171,12 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>처·실(경영관리부문 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (조직도상 명시 직책 없음, 정보시스템실이 정보기술 담당)</t>
+          <t>확인불가 — 조직도상 명시 직책 없음, 정보시스템실이 정보기술 담당</t>
         </is>
       </c>
       <c r="M156" s="3" t="inlineStr">
@@ -12186,12 +12186,12 @@
       </c>
       <c r="N156" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O156" s="3" t="inlineStr">
         <is>
-          <t>국부펀드(국가자산 운용) 기관. 3부문(투자운용·투자관리·경영관리) + 3본부 + 28실 구조. 경영관리부문 산하에 'AI혁신실'을 두어 AI 전담조직 운영. IT는 정보시스템실(경영)·투자시스템실(투자관리)로 이원화.</t>
+          <t>IT기능: 정보시스템 구축·운영(정보시스템실), AI 활용·혁신 전담(AI혁신실), 투자 IT 인프라·운용시스템(투자시스템실). 기타: 국부펀드(국가자산 운용) 기관으로 3부문(투자운용·투자관리·경영관리) + 3본부 + 28실 + 해외거점 5곳 구조. IT가 경영관리부문 정보시스템실과 투자관리부문 투자시스템실로 이원화. AI혁신실은 경영기획실·대외협력실·인사실·인재경영실·경영지원실과 함께 경영관리부문에 편제.</t>
         </is>
       </c>
     </row>
@@ -12896,17 +12896,17 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>소상공인디지털본부 (정보화 전담조직: 디지털전략팀)</t>
+          <t>공공구매촉진본부</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>팀 (본부 산하) — 본부 단위로 소상공인디지털본부 존재</t>
+          <t>단</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>디지털전략팀, 마케팅정보팀 (등)</t>
+          <t>DX추진단(정보보안파트·디지털전략팀·디지털정보팀)</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>해당없음 (상설 AI 전담조직 미확인)</t>
+          <t>해당없음 (조직명에 'AI' 명시된 상설 전담조직 미확인)</t>
         </is>
       </c>
       <c r="K166" s="3" t="inlineStr">
@@ -12926,22 +12926,22 @@
       </c>
       <c r="L166" s="3" t="inlineStr">
         <is>
-          <t>소상공인디지털본부장 총괄 (추정)</t>
+          <t>확인불가 (DX추진단장 실무 총괄, 공공구매촉진본부장 계열)</t>
         </is>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
-          <t>디지털전략팀 소관 (추정)</t>
+          <t>DX추진단 정보보안파트</t>
         </is>
       </c>
       <c r="N166" s="3" t="inlineStr">
         <is>
-          <t>중(공식 데이터포털 1출처 + 보도/조직개편 보조)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O166" s="3" t="inlineStr">
         <is>
-          <t>옛 '중소기업유통센터'에서 '한국중소벤처기업유통원'으로 기관명 변경. 소상공인디지털본부 산하에 디지털전략팀 편제(2020년 한국판뉴딜·디지털경제 전담 본부 신설로 4본부 체제). 통합유통플랫폼('판판대로'), 동반성장몰 등 디지털 커머스 사업 운영. 'AI 활용 마케팅', 'AI 데이터 마케팅', 소상공인 AI 전환(AX) 등 AI 활용은 모두 대외 사업·바우처 협력 차원이며, 기관 직제상 AI/인공지능/데이터 명칭의 상설 전담조직은 미확인.</t>
+          <t>IT담당배경: 'DX추진단'이 기관 내부 업무혁신·디지털전환 전담 조직으로, 산하 디지털전략팀·디지털정보팀·정보보안파트가 정보화·정보보안 실무를 수행. 조직 위치상 공공구매촉진본부 산하에 편제됨. 조직이력: 2024.10 '중소기업유통센터'→'한국중소벤처기업유통원(KODMA)' 기관명 변경. 2026.1.28 조직개편 — 3본부→4본부 체제(기획유통관리본부→미래혁신기획본부, 마케팅판로본부→중소벤처마케팅본부, 소상공인디지털본부 유지, 공공구매촉진본부 신설)하며 정부 AI·디지털 전환 정책 기조에 맞춰 'DX추진단' 신설. 기타: 통합유통플랫폼('판판대로'), 동반성장몰, 소담스퀘어 등 디지털 커머스 사업 운영. 'AI 활용 마케팅', 소상공인 AI 전환(AX) 등은 모두 대외 지원사업 차원이며 기관 직제상 AI 명칭 상설조직은 없음.</t>
         </is>
       </c>
     </row>
@@ -13046,17 +13046,17 @@
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>한국학도서관 (정보운영관리실·한국학정보화실 포함, 정보화 총괄) / 정보화사업 주관은 기획처 기획조정실</t>
+          <t>한국학도서관</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 정보운영관리실·한국학정보화실이 한국학도서관(처급 단위) 산하 실</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>정보운영관리실(행정시스템·ERP·정보인프라 운영), 한국학정보화실(한국학자료 정보화), 문헌정보팀 — 모두 한국학도서관 산하</t>
+          <t>한국학정보화실, 정보운영관리실, 문헌정보팀</t>
         </is>
       </c>
       <c r="I168" s="3" t="inlineStr">
@@ -13066,32 +13066,32 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>해당없음 (디지털인문학연구소에서 LLM·NLP 기반 연구 수행)</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>해당없음</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr">
         <is>
-          <t>정보화사업 주관 기획처 기획조정실 / 시스템운영은 한국학도서관 정보운영관리실 (전담 CIO 직위 미확인)</t>
+          <t>확인불가 (전담 CIO 직위 미확인. 정보화사업 주관은 기획처 기획조정실, 시스템운영은 한국학도서관 정보운영관리실)</t>
         </is>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
-          <t>정보운영관리실 소관 (추정)</t>
+          <t>확인불가 (정보운영관리실 소관 추정)</t>
         </is>
       </c>
       <c r="N168" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 원문에서 한국학도서관 산하 정보운영관리실·한국학정보화실 트리 확인 + 보조자료)</t>
+          <t>상 (공식 홈페이지 조직도 라이브 직접 확인, 2026-09-19)</t>
         </is>
       </c>
       <c r="O168" s="3" t="inlineStr">
         <is>
-          <t>연구기관 특성상 IT 조직이 ① 행정정보화(정보운영관리실 — 2025년 차세대 행정업무시스템(ERP) 구축으로 연구행정 디지털 혁신 추진)와 ② 연구·자료 디지털화(한국학지식정보센터/인문정보학연구실, 디지털인문학연구소)로 이원화됨. 정보화사업 및 정보인프라 운영관리는 기획처 기획조정실이 사업 주관. AI 명칭의 상설 전담조직은 없으나, 디지털인문학연구소가 대규모 언어모델(LLM)·자연어처리(NLP) 기반 디지털 한국학 연구를 수행.</t>
+          <t>[IT담당배경] 연구기관 특성상 IT 조직이 ① 행정정보화(정보운영관리실)와 ② 연구·자료 디지털화(한국학정보화실)로 이원화되어 모두 한국학도서관 산하에 편제됨.&lt;br&gt;[IT기능] 정보운영관리실=행정시스템·ERP·정보인프라 운영(2025년 차세대 행정업무시스템 구축으로 연구행정 디지털 혁신 추진) / 한국학정보화실=한국학자료 정보화 / 정보화사업 및 정보인프라 운영관리 사업 주관=기획처 기획조정실.&lt;br&gt;[기타] AI 명칭의 상설 전담조직은 부재. 연구처 산하 연구소 및 디지털인문학 분야에서 LLM·NLP 기반 디지털 한국학 연구를 수행하나 직제상 AI 전담 조직은 아님.&lt;br&gt;[조직이력] 2026-09-19 라이브 재확인 결과 종전(2026-06-17)과 조직 구성 동일.</t>
         </is>
       </c>
     </row>
@@ -13646,52 +13646,52 @@
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부</t>
+          <t>청소년AI·데이터센터</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>부(팀급 단위, 본부 미설치 추정)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부, 개인정보보호팀, 청소년안전망데이터센터(데이터 운영)</t>
+          <t>청소년AI·데이터센터(정보보안팀·데이터관리팀)</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담 AI 부서 미확인. 청소년 생성형 AI 이용실태 연구 등 사업 수행)</t>
+          <t>청소년AI·데이터센터</t>
         </is>
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (정보화전략부 소관, 별도 CIO 직위 미확인)</t>
+          <t>청소년AI데이터센터장(전상현) 총괄</t>
         </is>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 CISO 직위 미표기). 개인정보보호책임자(CPO)=통합지원본부장(노성덕), 개인정보보호팀(팀장 남용수) 별도 운영. 개인정보 안전성 확보조치(관리·기술·물리) 시행</t>
+          <t>청소년AI·데이터센터 정보보안팀 (팀장 겸직). 별도 임원급 CISO 직제는 미확인</t>
         </is>
       </c>
       <c r="N176" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직 명칭 + 개인정보처리방침(공식) 교차 확인)</t>
+          <t>상(공식 홈페이지 조직도·부서별 담당업무 직접 확인)</t>
         </is>
       </c>
       <c r="O176" s="3" t="inlineStr">
         <is>
-          <t>조직이 다수의 '부' 단위(기획조정부·경영관리부 등)로 편제된 연구·사업 기관. 정보화전략부가 정보화 총괄, 중장기 정보화전략계획(ISP) 수립. 개인정보보호는 통합지원본부장(CPO)·개인정보보호팀이 담당. 청소년안전망데이터센터에서 청소년안전망 데이터 수집·관리. AI는 정책연구 주제로 다룸(생성형 AI 리터러시 연구 등). 2022년 개인정보 관리수준 진단 'B'등급.</t>
+          <t>IT담당배경: 종전 정보화 총괄 조직이던 '정보화전략부'가 폐지되고, 이사장 직속 '청소년AI·데이터센터'(센터장급)가 정보화·정보보안·데이터를 통합 총괄하는 체계로 개편됨. 산하 정보보안팀·데이터관리팀 보유. IT기능: 정보시스템 운영 총괄, 정보화사업 추진(사전협의·IRM), 그룹웨어·메신저 운영, 정보보안 정책 수립·보안관제 운영(정보보안팀), 청소년안전망시스템 데이터 관리·분석·개선, 복지부·교육부·행안부 시스템 연계, 공공데이터 개방·품질평가, 개인정보보호(데이터관리팀). 조직이력: 조직개편으로 정보화전략부 → 청소년AI·데이터센터(이사장 직속)로 승격·개편, 개인정보보호 기능은 데이터관리팀에 통합, 종전 '청소년안전망데이터센터'는 별도 조직이 아닌 '청소년안전망시스템' 운영 업무로 정리됨. 기타: 청소년사이버상담센터에서 '청소년 위기징후 탐지 AI시스템' 구축 사업 수행. AI를 정책연구 주제로도 다룸(생성형 AI 리터러시 연구 등). 2022년 개인정보 관리수준 진단 'B'등급.</t>
         </is>
       </c>
     </row>
@@ -13796,17 +13796,17 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>기획조정본부 (정보화 총괄 추정)</t>
+          <t>전산정보실</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>본부 산하 부서(전산/정보화 별도 부서 상세 미확인)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (기획조정본부 산하 행정·정보화 기능 추정)</t>
+          <t>정보보안팀</t>
         </is>
       </c>
       <c r="I178" s="3" t="inlineStr">
@@ -13821,27 +13821,27 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>정책지원단(원장/부원장 직속 지원단 레벨)</t>
+          <t>지원단</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (기획조정본부장 총괄 추정)</t>
+          <t>확인불가 (조직도상 CIO 직위 명시 없음. 경영지원본부장이 전산정보실 소관 본부장)</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>정보보안팀 (경영지원본부 소속)</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 보조)</t>
+          <t>상 (공식 홈페이지 조직도 + 부서 상세페이지 라이브 직접 확인, 2026-09-19)</t>
         </is>
       </c>
       <c r="O178" s="3" t="inlineStr">
         <is>
-          <t>부원장 산하 기획조정본부 등 본부 체계 + 정책지원단(북극항로지원단·해양수산AI전환지원단·해양경제안보지원단·해양수산에너지전환지원단) 운영. 해양수산AI전환지원단이 해양수산 분야 AI 전환 정책 지원 전담.</t>
+          <t>[IT기능] 전산정보실=전산일반·기록물/일반보안·개인정보보호·해양수산정보센터(도서관) 운영 총괄 / 정보보안팀=정보보안 전담.&lt;br&gt;[IT담당배경] 국책연구기관 특성상 내부 정보화(전산정보실·정보보안팀)와 대외 AI 정책지원(해양수산AI전환지원단)이 분리 편제됨. 해양수산AI전환지원단은 기관 내부 IT 운영조직이 아니라 해양수산 산업 대상 AI 전환 정책연구·지원 단위.&lt;br&gt;[조직이력] 종전 기록(2026-06) 대비 본부 체계 확인 — 부원장 산하 기획조정본부·해양연구본부·수산연구본부·해운물류&amp;middot;해사연구본부·항만연구본부·글로벌전략연구본부·경영지원본부. 정책지원단은 5개로 확대(북극항로·해양수산AI전환·해양경제안보·해양수산에너지전환·수산&amp;middot;어촌협력네트워크).</t>
         </is>
       </c>
     </row>
@@ -13871,17 +13871,17 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>국가특허빅데이터본부 (데이터·플랫폼) / AI전략기획실(원장 직속)</t>
+          <t>국가특허빅데이터본부</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>본부 + 원장 직속 실</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>지능화플랫폼실(국가특허빅데이터본부 산하), 특허전략인프라실</t>
+          <t>국가전략기술특허지원실, 특허동향지원실, 지능화플랫폼실</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -13891,17 +13891,17 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>AI전략기획실 (원장 직속), 지능화플랫폼실(국가특허빅데이터본부 산하)</t>
+          <t>AI전략기획실</t>
         </is>
       </c>
       <c r="K179" s="3" t="inlineStr">
         <is>
-          <t>실(원장 직속) + 본부 산하 실</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="L179" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (국가특허빅데이터본부장/AI전략기획실장 소관 추정)</t>
+          <t>확인불가 — 국가특허빅데이터본부장 소관 추정</t>
         </is>
       </c>
       <c r="M179" s="3" t="inlineStr">
@@ -13911,12 +13911,12 @@
       </c>
       <c r="N179" s="3" t="inlineStr">
         <is>
-          <t>상(공식자료 기반 조직표 + 알리오)</t>
+          <t>상(공식 홈페이지 조직도 직접 확인)</t>
         </is>
       </c>
       <c r="O179" s="3" t="inlineStr">
         <is>
-          <t>원장 직속으로 AI전략기획실을 별도 설치 — AI를 조직 전략의 최상위로 격상. 국가특허빅데이터본부 산하 지능화플랫폼실에서 특허 빅데이터·AI 플랫폼 운영. 특허 빅데이터 기반 R&amp;D 전략 전문기관.</t>
+          <t>IT담당배경: 특허 빅데이터 기반 R&amp;D 전략 전문기관으로, 데이터·플랫폼 기능이 국가특허빅데이터본부에 집중. IT기능: 특허 빅데이터·AI 플랫폼 구축·운영(지능화플랫폼실), 국가전략기술 특허지원·특허동향 분석. 조직이력: 원장 직속으로 AI전략기획실을 별도 설치하여 AI를 조직 전략 최상위로 격상(감사실과 함께 원장 직속 편제). 기타: 5개 본부 체계 — 경영혁신본부(기획예산실·경영지원실·인재경영실), 지식재산전략기획본부(특허성과기획실·표준특허센터·특허전략인프라실·특허심사지원실·상표심사지원실), 지식재산전략지원본부(특허전략사업실·정보통신지원실·화학생명지원실·기계금속지원실·융복합전략지원실), 지식재산전략확산본부(특허전략확산실·특허활용전략실·성장전략지원실·산업전략지원실), 국가특허빅데이터본부. 지식재산전략지원본부의 '정보통신지원실'은 내부 전산이 아닌 정보통신 기술분야 특허전략 지원 조직. 내부 전산운영 전담 조직명은 공식 조직도에서 미확인(경영혁신본부 경영지원실 소관 추정).</t>
         </is>
       </c>
     </row>
@@ -14171,52 +14171,52 @@
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>인재운영처 (경영기획본부 산하) — 정보화·정보보안 기능 보유</t>
+          <t>정보안전팀</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>처(본부 산하)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>정보안전팀 (인재운영처 소속, 정보화·정보보안·개인정보 담당)</t>
+          <t>없음(단일 팀)</t>
         </is>
       </c>
       <c r="I183" s="3" t="inlineStr">
         <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="J183" s="3" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
           <t>확인불가</t>
         </is>
       </c>
-      <c r="J183" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (별도 AI 전담조직 미확인)</t>
-        </is>
-      </c>
-      <c r="K183" s="3" t="inlineStr">
-        <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-      <c r="L183" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (인재운영처장 소관 추정 — 개인정보보호책임자(CPO)도 인재운영처장(정재환))</t>
-        </is>
-      </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 CISO 직위 미표기). 개인정보보호책임자(CPO)=인재운영처장(정재환), 담당부서=인재운영처 정보안전팀. 정보안전팀이 정보보안·접근통제·암호화 등 안전성 확보조치 수행. 개인정보 보호수준 평가 'A'등급(2024)</t>
+          <t>인재운영처장이 개인정보보호책임자(CPO) 겸임, 담당부서는 인재운영처 정보안전팀 (별도 CISO 직위 미표기)</t>
         </is>
       </c>
       <c r="N183" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도(텍스트 확인) + 공식 개인정보처리방침 교차 확인)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O183" s="3" t="inlineStr">
         <is>
-          <t>2023.12 환경보전협회를 모태로 '한국환경보전원(KECI)'으로 새 출범(영문 Korea Environmental Conservation Institute). 조직: 원장 직속 감사실 + 4개 본부/센터(경영기획본부·환경사업본부·환경생태본부·국가환경교육센터) + 4개 지사. 경영기획본부 산하에 기획성과처·인재운영처가 있으며, IT/정보화·정보보안은 인재운영처 '정보안전팀'이 담당(인사운영팀과 병렬). 별도 IT 전담 본부/처는 없음.</t>
+          <t>[IT담당배경] 정보안전팀은 경영기획본부 &gt; 인재운영처 산하 팀으로, 인사운영팀과 병렬. 별도 IT 전담 본부/처 없음. 2026년 '인사조직 내 안전 기능 통합' 정책으로 정보화와 안전 기능이 한 팀에 묶인 구조. [IT기능] 정보시스템 관리, 전자정부 성과관리, 정보·안전 업무, 정보보안·접근통제·암호화 등 안전성 확보조치, 개인정보보호, 고정형 영상정보처리기기 운영·관리. [조직이력] 2023.12 환경보전협회를 모태로 '한국환경보전원(KECI)'으로 새 출범. 현 조직: 원장 직속 감사실 + 4개 본부/센터(경영기획본부·환경사업본부·환경생태본부·국가환경교육센터) + 지사. 2026 정부조직 개편으로 주무부처는 기후에너지환경부. [기타] 개인정보 보호수준 평가 'A'등급(2024). 유사기관 혼동 주의 — 한국환경공단(KECO)·한국환경산업기술원(KEITI)·한국환경연구원(KEI)과 별개, 본 건은 KECI(keci.or.kr).</t>
         </is>
       </c>
     </row>
@@ -14246,17 +14246,17 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>기획조정실(AI데이터팀)·행정관리실(지식정보팀) — 경영부원장 산하</t>
+          <t>AI홍보전략실</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>팀 (실 산하 팀)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>AI데이터팀(기획조정실), 지식정보팀(행정관리실)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -14266,32 +14266,32 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>AI데이터팀(기획조정실 산하), AI융복합연구단·환경데이터지능연구단(융복합환경연구단 내 연구조직)</t>
+          <t>AI홍보전략실, AI융복합 연구단</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>팀(AI데이터팀, 기획조정실 산하) / 연구단(연구조직)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (경영부원장/기획조정실장 계열 추정)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (지식정보팀이 정보시스템·지식정보 관리 수행 추정)</t>
+          <t>개인정보보호책임자(CPO)는 행정관리실장, 분야별책임관은 지식정보팀장 (개인정보처리방침 기준 — 2026 조직개편 전 부서명)</t>
         </is>
       </c>
       <c r="N184" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 직접확인)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O184" s="3" t="inlineStr">
         <is>
-          <t>정부출연 정책연구기관(국무조정실·경제인문사회연구회 산하). 연구부원장(기후대기전략/지속가능발전/국토환경/환경평가 본부 + 적응센터)과 경영부원장(기획조정실, 행정관리실) 이원 체계. 행정 IT는 지식정보팀, 데이터·AI 기획은 기획조정실 'AI데이터팀'이 전담 — AI 전담 팀을 기획 라인에 둔 점이 특징. 연구 측에는 'AI융복합연구단', '환경데이터지능연구단' 등 데이터/AI 연구단 운영.</t>
+          <t>[IT담당배경] 2026년 조직개편으로 경영 라인이 '기획경영 본부' 단일 본부로 통합되고, 그 산하에 기획조정실·연구관리실·인사관리실·AI홍보전략실·경영지원실 5개 실이 배치됨. 종전 기획조정실 산하 'AI데이터팀'과 행정관리실은 조직도상 소멸하고, AI 기능이 실 단위 'AI홍보전략실'로 격상됨. [IT기능] 행정 정보화·정보시스템 운영 및 개인정보보호는 지식정보팀이 수행(개인정보처리방침 기준), AI·데이터 기획 및 대외 홍보전략은 AI홍보전략실이 수행. [조직이력] 2026-08 인사에서 AI홍보전략실장(염정윤) 임명 확인. 연구 라인은 연구부원장 산하 기후대기전략·생활환경·국토환경·환경평가 4개 연구본부와 국가기후위기 적응센터로 재편(종전 '지속가능발전 연구본부' → '생활환경 연구본부'). 융복합환경연구단에 'AI융복합 연구단' 운영(종전 '환경데이터지능연구단'은 현 목록에서 미확인). [기타] 세종국책연구단지 소재, 경제·인문사회연구회 소관 정부출연연구기관. 유사기관 혼동 주의 — 한국환경산업기술원(KEITI)·한국환경공단(KECO)·한국환경보전원(KECI)과 별개, 본 건은 KEI(kei.re.kr).</t>
         </is>
       </c>
     </row>
@@ -15596,17 +15596,17 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>기획조정본부 (정보화 기능: 지식정보팀)</t>
+          <t>기획조정본부</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>팀(본부 산하)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H202" s="3" t="inlineStr">
         <is>
-          <t>지식정보팀 (기획조정본부 산하)</t>
+          <t>지식정보팀, 데이터분석·성과확산센터</t>
         </is>
       </c>
       <c r="I202" s="3" t="inlineStr">
@@ -15616,12 +15616,12 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>AI연구지원단 (특임조직)</t>
+          <t>AI연구지원단</t>
         </is>
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>특임조직(부원장 직속 수준)</t>
+          <t>단</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="O202" s="3" t="inlineStr">
         <is>
-          <t>국무총리 산하 정부출연 연구기관(경제·인문사회연구회 소관). 정보화 전담은 기획조정본부 내 '지식정보팀'. AI 관련은 별도 '특임조직 AI연구지원단'을 부원장 직속 특임조직으로 운영(연구 지원 성격). 데이터분석은 미래인재연구본부 내 '데이터분석·성과확산센터'가 별도 담당. 조직도 최종 업데이트 2026-06-10.</t>
+          <t>IT담당배경: '지식정보팀'(기획조정본부 산하)이 정보화 전담. 연구원 특성상 IT가 본부·처·실이 아닌 팀 단위로 운영됨. 'AI연구지원단'은 부원장 직속 특임조직으로 AI 활용 연구를 지원하는 성격이며 IT 인프라 조직은 아님. '데이터분석·성과확산센터'는 미래인재연구본부 산하로 IT 계통 밖이나 데이터 전담조직이므로 함께 기재. 기타: 국무총리 산하 정부출연 연구기관(경제·인문사회연구회 소관). 별도 정보보안 전담조직은 조직도상 미확인. 조직도 최종 업데이트 2026-06-10.</t>
         </is>
       </c>
     </row>
@@ -15901,12 +15901,12 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>처·실(사장 직속)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H206" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (공식 조직도에 하위부서 미표기)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="I206" s="3" t="inlineStr">
@@ -15921,12 +15921,12 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>사장(이사장) 직속 실</t>
+          <t>실</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (해양AI전략실장이 사실상 정보화·AI 총괄로 추정)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="M206" s="3" t="inlineStr">
@@ -15936,12 +15936,12 @@
       </c>
       <c r="N206" s="3" t="inlineStr">
         <is>
-          <t>상(공식 2출처)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O206" s="3" t="inlineStr">
         <is>
-          <t>사장 직속에 '해양AI전략실'을 별도 신설해 AI·디지털 전환을 전략 기능으로 격상. 본부는 경영기획본부·해양전략본부·해양금융본부 3본부 체계. 해양산업 디지털 전환(DX) 지원 사업 및 별도 AX/DX 포털(kobcax.com) 운영. 정책금융기관 특성상 전통적 '정보화실'보다 AI전략 중심 조직 구성.</t>
+          <t>[IT담당배경] 해양AI전략실은 감사실과 함께 사장 직속 라인에 배치되어 있으며, 3개 본부(경영기획본부·해양전략본부·해양금융본부) 어느 곳에도 속하지 않음. 일반적인 '정보화처/정보화부' 명칭 대신 AI전략 중심으로 조직을 명명·배치. [IT기능] 해양산업 디지털 전환(DX) 지원 사업 운영, 별도 AX/DX 포털(kobcax.com) 운영. [조직이력] 2026-09 조직도 기준 3본부 체계 유지, 해양전략본부에 '북극항로종합지원센터' 편제 확인. [기타] 공식 조직도가 실·부 단위까지만 표기되어 해양AI전략실 하위 부 단위 구성과 CIO/CISO 지정 여부는 확인 불가. 명칭 유사기관(해양수산과학기술진흥원 KIMST, 한국해양수산개발원 KMI)과 혼동 주의 — 본 건은 KOBC(kobc.or.kr).</t>
         </is>
       </c>
     </row>
@@ -18371,52 +18371,52 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>지능정보화센터 (정책본부 산하)</t>
+          <t>한의약미래사업단</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하) — 센터 단위</t>
+          <t>단</t>
         </is>
       </c>
       <c r="H239" s="3" t="inlineStr">
         <is>
-          <t>지능정보화센터 (정보화·정보보안·개인정보보호·공공데이터), 임상정보빅데이터추진단(연구개발혁신본부 산하)</t>
+          <t>한의약디지털혁신팀</t>
         </is>
       </c>
       <c r="I239" s="3" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>한의약AI사업단 (2025-08-19 출범)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K239" s="3" t="inlineStr">
         <is>
-          <t>사업단(독립 업무단) — 기존 지능정보화센터의 한의약 AI·빅데이터 업무를 분리 신설</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L239" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (지능정보화센터 소속 정책본부장 추정)</t>
+          <t>확인불가 (조직도상 CIO 직위 명시 없음)</t>
         </is>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>정책본부장(박상표) = 개인정보보호책임자, 지능정보화센터 정보보안 담당</t>
+          <t>확인불가 (별도 CISO 직제 미확인. 개인정보 고충처리부서는 경영기획본부 산하 운영지원팀)</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 다수 보도자료 교차확인)</t>
+          <t>상 (공식 홈페이지 조직도 라이브 직접 확인 + 개인정보처리방침 교차, 2026-09-19)</t>
         </is>
       </c>
       <c r="O239" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19 '한의약AI사업단'(단장 김상진) 공식 출범 — 지능정보화센터에서 AI·빅데이터 기능 분리·신설, 정부 'AI 3대 강국' 정책 연계 국가대표 AI 조직 지향. 한의약 특화 AI 챗봇 '맥챗', KLIMS(한약실험정보관리시스템), 표준 EMR 프레임워크 운영. 공식 홈페이지 조직도에는 신설 사업단이 아직 미반영(2025.08 신설).</t>
+          <t>[IT기능] 한의약디지털혁신팀(한의약미래사업단 소속)이 한의약 AI·디지털 전환 사업 담당 — 한의약 특화 AI 챗봇 '맥챗', 한약실험정보관리시스템(KLIMS), 표준 EMR 프레임워크 개발·보급, 한의약 데이터 분석 실무 워크숍 운영. 내부 정보화·개인정보 고충처리는 경영기획본부 산하 운영지원팀 소관.&lt;br&gt;[조직이력] 종전 기록(2026-06)에 있던 **지능정보화센터(정책본부 산하)·임상정보빅데이터추진단·연구개발혁신본부가 현 조직도에서 소멸**. 2025-08-19 출범한 '한의약AI사업단'은 TF 성격 조직이었으며 현 공식 조직도에 미존재 — 기능이 한의약미래사업단(한의약디지털혁신팀·한의약글로벌사업팀)으로 재편된 것으로 판단.&lt;br&gt;[기타] 현 조직 체계: 원장 직속 비상임감사·감사팀·대외소통실(대외협력팀·홍보소통팀) + 경영기획본부(기획예산팀·성과평가팀·인재경영팀·운영지원팀) + 정책본부(정책지원팀·공공의료팀·근거분석팀) + 산업진흥본부(한의약기술산업화팀·한약재유통지원팀·천연물소재개발팀·의약품안전생산센터·한약비임상시험센터) + 한의약미래사업단 + 한약조제관리단 + 한의약혁신기술개발사업단(RnD기획팀·한의표준진료지침팀·임상연구지원국).</t>
         </is>
       </c>
     </row>
@@ -19271,17 +19271,17 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>경영혁신본부(기획조정실)</t>
+          <t>경영혁신본부</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>기획조정실(정보화사업·개인정보보호·정보보안 담당)</t>
+          <t>기획조정실</t>
         </is>
       </c>
       <c r="I251" s="3" t="inlineStr">
@@ -19291,12 +19291,12 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>- (상표부정경쟁조사실 내 'AI 모니터링 사업' 운영 — 사업 단위, 전담조직 아님)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L251" s="3" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="O251" s="3" t="inlineStr">
         <is>
-          <t>정보화·정보보안 기능이 경영혁신본부 산하 기획조정실에 통합(전담 IT 본부/처 없음). 별도 AI 전담조직은 미확인이나, 상표부정경쟁조사실에서 'AI 모니터링 사업'을 사업으로 운영(위조상품 온라인 모니터링). 2025.10 주무부처가 특허청→지식재산처로 승격. 본부 구성: 경영혁신본부, 지재권분쟁대응본부 등.</t>
+          <t>IT담당배경: 전담 IT 본부·처가 없고, 경영혁신본부 산하 '기획조정실'이 정보화사업·개인정보보호·정보보안 기능을 겸무. IT기능: 정보화사업, 개인정보보호, 정보보안. 조직이력: 2025.10 주무부처가 특허청→지식재산처로 승격. 기타: 상표부정경쟁조사실에서 위조상품 온라인 'AI 모니터링 사업'을 사업 단위로 운영(전담조직 아님). 본부 구성: 경영혁신본부·지재권분쟁대응본부 등, 부속조직으로 영업비밀보호센터·공익변리사센터 및 해외 지식재산센터 9곳(LA·베이징·도쿄·호치민·워싱턴DC·뉴델리·광저우·프랑크푸르트·방콕·멕시코시티) 운영.</t>
         </is>
       </c>
     </row>
@@ -19796,27 +19796,27 @@
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (기획경영본부 산하) — 별도 정보화 전담 본부·실 없음</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>실(본부 산하)의 일부 기능 / 정보화 전담 단위는 팀 레벨 추정</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>경영지원실이 전산 운영·관리·정보보안, 공공데이터·정보기술아키텍처(EA) 기반 정보화 관리·운영, 개인정보보호 업무 담당. (항공안전 도메인 데이터는 항공안전본부 산하 '항공데이터실'이 별도 수행)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="I258" s="3" t="inlineStr">
         <is>
-          <t>없음 (직제상 AI 전담 본부·실·팀 미확인)</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>해당없음 (단, 'AI 기반 항공안전 생태계' 비전 선포 등 사업 차원 AI 추진 중)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K258" s="3" t="inlineStr">
@@ -19836,12 +19836,12 @@
       </c>
       <c r="N258" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 직원검색·보도 교차)</t>
+          <t>상(공식 홈페이지 조직도 라이브 확인 + 직원검색·보도 교차, 조직도상 경영지원실 하위 팀 세부구성은 미표기)</t>
         </is>
       </c>
       <c r="O258" s="3" t="inlineStr">
         <is>
-          <t>4본부(기획경영본부·항공안전본부·항공인증본부·미래항공본부) 체제. 내부 정보화(전산·보안·EA·개인정보)는 기획경영본부 경영지원실이 담당. '항공데이터실'(항공안전본부 산하)은 항공안전 정보 수집·조사·관리·연구를 수행하는 도메인 데이터 조직으로 내부 IT 운영조직과 구분됨. AI 비전 선포식 개최 등 AI 기반 항공안전 추진(사업 차원). UAM/드론 등 미래항공 분야 다룸.</t>
+          <t>[IT담당배경] 별도 정보화 전담 본부·실 없이 기획경영본부 경영지원실이 내부 정보화를 겸장. [IT기능] 경영지원실 업무분장 — 전산 운영·관리 및 정보보안, 공공데이터 및 정보기술아키텍처(EA) 기반 정보화 관리·운영, 개인정보보호. [기타] 4본부(기획경영본부·항공안전본부·항공인증본부·미래항공본부) 체제. 항공안전본부 산하 '항공데이터실'은 항공안전 정보 수집·조사·관리·연구를 수행하는 도메인 데이터 조직으로 내부 IT 운영조직과 구분. AI 비전 선포식 개최 등 AI 기반 항공안전 추진은 사업 차원이며 직제상 AI 전담 조직은 없음. UAM/드론 등 미래항공 분야 담당.</t>
         </is>
       </c>
     </row>
@@ -20701,12 +20701,12 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>팀 (기획조정본부 &gt; 행정지원실 산하)</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H270" s="3" t="inlineStr">
         <is>
-          <t>전산정보팀 (단일 팀 — 네트워크 구축·운영관리, 전산장비 구입·유지보수 등). 행정지원실 내 형제팀: 인재개발팀, 운영지원팀, 재무회계팀</t>
+          <t>없음(단일 팀)</t>
         </is>
       </c>
       <c r="I270" s="3" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="L270" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 CIO 직위 미확인 — 행정지원실/기획조정본부 라인에서 정보화 총괄 추정)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="M270" s="3" t="inlineStr">
@@ -20736,12 +20736,12 @@
       </c>
       <c r="N270" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 채용사이트 부서소개 교차확인)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O270" s="3" t="inlineStr">
         <is>
-          <t>연구기관 특성상 IT 조직은 '전산정보팀'(행정지원 성격)에 한정. 'AI' 명칭 전담조직은 조직도상 없음. 다만 데이터 분석 성격의 '국정데이터조사센터'를 별도 운영(연구 목적, IT조직 아님). 홈페이지에 '인공지능 챗봇' 서비스 운영.</t>
+          <t>[IT담당배경] 전산정보팀은 기획조정본부 &gt; 행정지원실 산하 팀으로, 형제팀은 인재개발팀·운영지원팀·재무회계팀. 소규모 연구기관 특성상 정보화 기획과 정보보안이 별도 분화되지 않음. [IT기능] 네트워크 구축·운영관리, 전산장비 구입·유지보수, 홈페이지·인공지능 챗봇 서비스 운영. [조직이력] 2026-09 시점에도 기획조정본부-행정지원실-전산정보팀 체계 유지(2026년 행정포커스 제1호에 '기획조정본부 행정지원실 전산정보팀장' 표기). [기타] '국정데이터조사센터'는 국정·여론조사 데이터 연구조직으로 IT 인프라/정보화 조직이 아니어서 IT최상위조직에서 제외. 유사기관 혼동 주의 — '한국지방행정연구원'(krila.re.kr, 행안부 산하)과 별개 기관, 본 건은 KIPA(kipa.re.kr).</t>
         </is>
       </c>
     </row>
@@ -20996,17 +20996,17 @@
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
-          <t>경영지원실 (산하 지식정보팀이 내부 정보화·정보보안 담당) / 데이터·AI는 사법무디지털센터(정보통계팀·AI·법·정책연구팀)가 수행</t>
+          <t>정보·통계실</t>
         </is>
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>팀 (경영지원실 산하 지식정보팀 / 사법무디지털센터 산하 정보통계팀)</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H274" s="3" t="inlineStr">
         <is>
-          <t>지식정보팀(내부 정보화·정보보안·개인정보, 경영지원실 산하), 정보통계팀(기술·개발·내부 통계서비스·AI lab 운영, 사법무디지털센터 산하)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="I274" s="3" t="inlineStr">
@@ -21016,32 +21016,32 @@
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
-          <t>AI·법·정책연구팀 (사법무디지털센터 산하) — 정보통계팀(AI lab)과 병행</t>
+          <t>사법개혁·AI 전략 연구본부, AI법무정책 중점연구단</t>
         </is>
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>팀 (사법무디지털센터 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr">
         <is>
-          <t>경영지원실장 총괄 추정 (내부 정보화 담당이 경영지원실 지식정보팀)</t>
+          <t>확인불가</t>
         </is>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
-          <t>개인정보보호책임자(CPO) 겸 보안 총괄: 경영지원실장 김병규(02-3460-5158, kbg@kicj.re.kr), 보호담당자 경영지원실 지식정보팀장 전태윤(02-3460-5112) — CISO를 경영지원실장이 겸하는 구조</t>
+          <t>범죄·법무동향연구본부장(황지태)이 개인정보 보호책임자(CPO) 겸임, 담당부서는 범죄·법무동향연구본부 정보통계팀</t>
         </is>
       </c>
       <c r="N274" s="3" t="inlineStr">
         <is>
-          <t>상(개인정보처리방침으로 CPO(경영지원실장 김병규)·담당부서(지식정보팀) 확정 + 인터뷰·R&amp;D 자료로 사법무디지털센터·AI·법·정책연구팀 확인. 단 공식 홈페이지(kicj.re.kr)가 WebFetch 403·tavily 일시오류로 직접 트리는 미열람, 검색 스니펫·교차출처로 확정)</t>
+          <t>상</t>
         </is>
       </c>
       <c r="O274" s="3" t="inlineStr">
         <is>
-          <t>형사정책·법무 전문 연구기관(경제·인문사회연구회 소관, 영문약칭 KICJ). 2023년 '사법무디지털센터' 신설 — 산하에 정보통계팀(기술·개발, AI lab 운영)과 AI·법·정책연구팀(생성형 AI 활용 형사·법무 정책연구·빅데이터 분석·융합연구)을 두어 AI 전담 연구 기능 보유. 2024년 'AI 전자감독·재범위험도분석·일탈탐지' 국가 R&amp;D 수행. 형사사법통계(CCJS)·범죄통계 통합DB 등 데이터 자산 보유. 내부 정보화·정보보안은 경영지원실(총무인사팀·지식정보팀·재무회계팀) 산하 지식정보팀이 담당.</t>
+          <t>[IT담당배경] 2026년 조직개편으로 기존 '사법무디지털센터'·'경영지원실 지식정보팀' 체계가 해체되고, 정보화·통계·개인정보 기능이 '범죄·법무동향 연구본부' 산하 '정보·통계실(정보통계팀)'로 통합됨. IT 전담 본부/처는 없음. [IT기능] 형사사법통계(CCJS)·전국범죄피해조사·비교형사법DB·마이크로데이터 등 데이터 자산 운영, 개인정보 권리행사 접수·처리, 정보보안·접근통제·암호화 등 안전성 확보조치 수행. [조직이력] 2026-09 조직도 기준 — 부원장 직속에 'AI법무정책 중점연구단'·성과관리실·홍보담당관 신설, 연구본부가 사법개혁·AI 전략 / 형사법제 / 법무정책혁신 / 범죄예방·교정정책 / 범죄·법무동향 5개 본부로 재편, 기획조정본부(연구기획실·대외협력실·예산실)·경영지원본부(인재개발실·운영지원실·재무회계실)·조사정보센터·현안대응단 구성. 2021년 '한국형사정책연구원'에서 현 명칭으로 개칭(도메인 kic.re.kr → kicj.re.kr). [기타] 2025년 개인정보 보호수준 평가 'B'등급. 연속간행물로 'AI JUSTICE BRIEF' 발간.</t>
         </is>
       </c>
     </row>
@@ -21138,19 +21138,19 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="G3" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
     </row>
@@ -21164,11 +21164,11 @@
         <v>60</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -21198,11 +21198,11 @@
         <v>184</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -21232,27 +21232,27 @@
         <v>273</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
@@ -21294,11 +21294,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>33.7%</t>
         </is>
       </c>
     </row>
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.6%</t>
         </is>
       </c>
     </row>
@@ -21324,11 +21324,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -21339,11 +21339,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -21400,11 +21400,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>40.3%</t>
         </is>
       </c>
     </row>
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
     </row>
@@ -21461,11 +21461,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>91.9%</t>
         </is>
       </c>
     </row>
@@ -21476,11 +21476,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.1%</t>
         </is>
       </c>
     </row>
@@ -21525,7 +21525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -21950,7 +21950,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>한국해양수산연수원</t>
+          <t>선박해양플랜트연구소</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -21964,11 +21964,11 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 개인정보처리방침 2출처로 지능정보화팀·CPO=경영본부장 확인)</t>
+          <t>상(공식 조직도 + 인사 보도 교차)</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -21978,19 +21978,19 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>지능정보화팀 (경영본부 산하)</t>
+          <t>해양공공디지털연구본부, 경영지원본부</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 'AI' 명칭 전담조직 미확인. 정보화는 경영본부 산하 '지능정보화팀'이 담당하나 일반 IT 기능으로 판단)</t>
+          <t>확인불가 (별도 AI 전담조직 미확인. 해양공공디지털연구본부가 디지털·AI 연구 수행 추정)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>선박해양플랜트연구소</t>
+          <t>중소기업기술정보진흥원</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -22004,11 +22004,11 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>312</v>
+        <v>271.3</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 + 인사 보도 교차)</t>
+          <t>상(공식 조직도 전체 트리 라이브 재확인, 2026-09-18)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -22018,19 +22018,19 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>해양공공디지털연구본부, 경영지원본부</t>
+          <t>R&amp;D지원본부</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 AI 전담조직 미확인. 해양공공디지털연구본부가 디지털·AI 연구 수행 추정)</t>
+          <t>확인불가 (별도 AI 전담조직 없음 / '지능정보화실'이 지능정보·정보화 기능 총괄)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>중소기업기술정보진흥원</t>
+          <t>한국보건복지인재원</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -22044,11 +22044,11 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>271.3</v>
+        <v>238.6</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도 전체 트리 라이브 재확인, 2026-09-18)</t>
+          <t>상(공식 개인정보처리방침 + 공공데이터포털 담당부서 표기 + 알리오 교차 확인)</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -22058,19 +22058,19 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>R&amp;D지원본부</t>
+          <t>경영전략본부</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (별도 AI 전담조직 없음 / '지능정보화실'이 지능정보·정보화 기능 총괄)</t>
+          <t>확인불가</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>한국청소년상담복지개발원</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -22084,11 +22084,11 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>239.5</v>
+        <v>232.5</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직 명칭 + 개인정보처리방침(공식) 교차 확인)</t>
+          <t>상(공식 개인정보처리방침 + 알리오 + 보도 교차 확인)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -22098,7 +22098,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>정보화전략부</t>
+          <t>연금사업본부</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -22110,7 +22110,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>한국보건복지인재원</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -22124,11 +22124,11 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>238.6</v>
+        <v>202.3</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침 + 공공데이터포털 담당부서 표기 + 알리오 교차 확인)</t>
+          <t>상(공식 개인정보처리방침(2025.7.10) + 공시 부서별 업무추진계획 + 보도 교차 확인)</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -22138,7 +22138,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>경영전략본부</t>
+          <t>융합기술센터 / 데이터정보화팀</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -22150,7 +22150,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
+          <t>과학기술정책연구원</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -22164,11 +22164,11 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>232.5</v>
+        <v>152</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침 + 알리오 + 보도 교차 확인)</t>
+          <t>상(공식 홈페이지 개인정보처리방침으로 경영지원실·디지털전환팀 소속·CPO 확인 + 2026 개편 보도 다수 교차확인)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -22178,19 +22178,19 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>연금사업본부</t>
+          <t>경영지원실</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>확인불가 (전담 AI 조직 미확인 — 디지털·AI 전환 대응은 디지털전환팀이 수행)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>한국환경보전원</t>
+          <t>한국기상산업기술원</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -22204,11 +22204,11 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>225</v>
+        <v>151.8</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>상(공식 조직도(텍스트 확인) + 공식 개인정보처리방침 교차 확인)</t>
+          <t>상(공식 홈페이지 조직도 + 공공데이터포털 기관조직 데이터 교차확인)</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -22218,130 +22218,10 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>인재운영처 (경영기획본부 산하) — 정보화·정보보안 기능 보유</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>국제방송교류재단</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>202.3</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>상(공식 개인정보처리방침(2025.7.10) + 공시 부서별 업무추진계획 + 보도 교차 확인)</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>융합기술센터 / 데이터정보화팀</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>과학기술정책연구원</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>152</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>상(공식 홈페이지 개인정보처리방침으로 경영지원실·디지털전환팀 소속·CPO 확인 + 2026 개편 보도 다수 교차확인)</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>경영지원실</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (전담 AI 조직 미확인 — 디지털·AI 전환 대응은 디지털전환팀이 수행)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>한국기상산업기술원</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>151.8</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>상(공식 홈페이지 조직도 + 공공데이터포털 기관조직 데이터 교차확인)</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>경영기획본부</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>확인불가 (전담 조직 미확인 — 데이터/AI 업무는 산업육성실 기상기후데이터·빅데이터 사업에서 수행)</t>
         </is>

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>미래부문</t>
+          <t>AI전략본부</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>AI전략본부(AX기획처·AX추진처·디지털관리처·IT운영센터), 정보보안실</t>
+          <t>AX기획처·AX추진처·디지털관리처·IT운영센터</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>중(공식 조직도 페이지는 개편 전 구조 노출 — 실질 근거는 나무위키·언론 보도 교차. 직제규정 시행세칙 원문 미확보)</t>
+          <t>상(나무위키·언론 보도 + 코레일 재직 사용자 직접 확인, 2026-09-23)</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -21461,11 +21461,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>92.3%</t>
         </is>
       </c>
     </row>
@@ -21476,11 +21476,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.7%</t>
         </is>
       </c>
     </row>

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>경영관리본부</t>
+          <t>IT운영처</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>IT운영처, 정보보안처</t>
+          <t>없음(단일 처)</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -1421,17 +1421,17 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>기획전략본부</t>
+          <t>AI디지털처</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>AI디지털처(AI디지털기획부·플랫폼운영부)</t>
+          <t>AI디지털기획부·플랫폼운영부</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>의료관리실</t>
+          <t>전산정보과</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>처·실</t>
+          <t>과(의료관리실 산하)</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>전산정보과(정보시스템·EMR/OCS 운영). 별도 진료정보실(의무기록 — 진료정보실 의무기록팀)은 의료기록 담당으로 IT기획과 구분</t>
+          <t>없음(단일 과)</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>통합 의료정보시스템(EMR) 구축해 '종이없는 디지털병원' 구현. 공식 조직도 확인 결과 원장 직속으로 대외협력홍보실·고객인권지원실·의료관리실(→전산정보과)·의생명연구원·기획조정실(기획예산과)·사무국(총무/물류관리/원무/시설과) 등 편제. 의생명연구원 산하 전북빅데이터센터가 의료 빅데이터 플랫폼·진단치료 보조시스템 개발. 군산전북대학교병원 개원 준비단 운영 중. 1084병상.</t>
+          <t>통합 의료정보시스템(EMR) 구축해 '종이없는 디지털병원' 구현. 공식 조직도 확인 결과 원장 직속으로 대외협력홍보실·고객인권지원실·의료관리실(→전산정보과·의료질향상팀)·의생명연구원·기획조정실(기획예산과)·사무국(총무/물류관리/원무/시설과) 등 편제. 의료관리실 내 병렬조직(비IT): 의료질향상팀. 진료정보실(의무기록)은 의료관리실과 별개의 독립 부서(진료부문 소속). 의생명연구원 산하 전북빅데이터센터가 의료 빅데이터 플랫폼·진단치료 보조시스템 개발. 군산전북대학교병원 개원 준비단 운영 중. 1084병상.</t>
         </is>
       </c>
     </row>
@@ -5171,17 +5171,17 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>비서실</t>
+          <t>정보화실</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>실(원장 직속 비서실 산하)</t>
+          <t>실(비서실 산하)</t>
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr">
         <is>
-          <t>정보화실(정보보호팀), 정보운영팀, 기획조정실(새병원정보화전략팀)</t>
+          <t>정보보호팀·정보운영팀</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>IT기능: 의료정보시스템 운영·정보보안·정보화전략기획(새병원정보화전략팀)&lt;br&gt;기타: AI 기반 응급의료시스템 운영. 2026년 병원정보시스템 AI SaaS 전환 사업 대상. 직원 AI 역량강화 정규교육 운영. 분산 IT: 중앙응급의료센터&gt;재난의료정책실&gt;응급의료정보화팀, 공공보건의료본부&gt;정책통계지원센터&gt;공공의료정보운영팀.</t>
+          <t>IT기능: 의료정보시스템 운영·정보보안(정보화실 산하 정보보호팀·정보운영팀)&lt;br&gt;병렬조직: 비서실 자체는 원장 비서 지원 기능이 본연이며 IT 무관, 정보화실이 그 산하 유일한 실질 IT부서. 기획조정실 산하 '새병원정보화전략팀'은 별개 병렬 IT조직.&lt;br&gt;기타: AI 기반 응급의료시스템 운영. 2026년 병원정보시스템 AI SaaS 전환 사업 대상. 직원 AI 역량강화 정규교육 운영. 분산 IT: 중앙응급의료센터&gt;재난의료정책실&gt;응급의료정보화팀, 공공보건의료본부&gt;정책통계지원센터&gt;공공의료정보운영팀.</t>
         </is>
       </c>
     </row>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>경영본부</t>
+          <t>AI혁신단</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>AI혁신단(AI전환팀·AI인프라팀)</t>
+          <t>AI전환팀·AI인프라팀</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>IT기능: 전사 AI·디지털 전환 총괄. AI·ERP 통합 예측기반 운영체계 구축.&lt;br&gt;조직이력: 2025.2 디지털기획팀 → 디지털전환팀+정보운영팀 분리. 2025.9.26 AI혁신단 신설(AI전환팀·AI인프라팀으로 개편).&lt;br&gt;기타: 비전 'Next GKL: AI 혁신으로 도약하는 카지노의 미래'. 업계 최초 세븐럭 전용앱 개발.</t>
+          <t>IT기능: 전사 AI·디지털 전환 총괄. AI·ERP 통합 예측기반 운영체계 구축.&lt;br&gt;병렬조직(비IT): 경영본부 산하 기획조정실·지속성장실·경영지원실·재무관리실(모두 비IT)&lt;br&gt;조직이력: 2025.2 디지털기획팀 → 디지털전환팀+정보운영팀 분리. 2025.9.26 AI혁신단 신설(AI전환팀·AI인프라팀으로 개편).&lt;br&gt;기타: 비전 'Next GKL: AI 혁신으로 도약하는 카지노의 미래'. 업계 최초 세븐럭 전용앱 개발.</t>
         </is>
       </c>
     </row>
@@ -5546,17 +5546,17 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>ICT전략부·ICT운영부(센터)·AI데이터전략실·정보보안담당관</t>
+          <t>ICT전략부</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>부(部)급 — 상위 통할 본부 미확정, ICT전략부·ICT운영부 병렬 구조</t>
         </is>
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>ICT전략부, ICT운영부(舊 ICT운영센터), AI데이터전략실, 정보보안담당관</t>
+          <t>없음(단일 부, 병렬조직 ICT운영부(舊 ICT운영센터) 있음 — 특이사항 참조)</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>조직이력: 2025.7 '데이터사업전략실'→'AI데이터전략실' 개편(AI 전환 전략 설계·연구). 2026.1 'AI데이터전략실'→'AI데이터전략부' 격상 예정.&lt;br&gt;기타: 중기 분야 최초 AI최고책임자(CAIO) 선임. 2025.10 부산 KT IDC 내 'AI 클라우드 데이터센터' 개소.</t>
+          <t>병렬조직: ICT운영부(舊 ICT운영센터, IT 운영 담당, ICT전략부와 병렬), AI데이터전략실(AI전담조직 — 별도 AI조직명 필드 참조), 정보보안담당관(CISO 기능부서 — 별도 CISO체계 필드 참조). ICT전략부·ICT운영부·AI데이터전략실·정보보안담당관을 통할하는 단일 상위 본부(舊 디지털혁신본부 추정)는 공식 조직도 미확인으로 확정하지 않음.&lt;br&gt;조직이력: 2025.7 '데이터사업전략실'→'AI데이터전략실' 개편(AI 전환 전략 설계·연구). 2026.1 'AI데이터전략실'→'AI데이터전략부' 격상 예정.&lt;br&gt;기타: 중기 분야 최초 AI최고책임자(CAIO) 선임. 2025.10 부산 KT IDC 내 'AI 클라우드 데이터센터' 개소.</t>
         </is>
       </c>
     </row>
@@ -5621,34 +5621,34 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>경영기획처</t>
+          <t>AI정보화기획실</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
+          <t>실(경영기획처 산하)</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>정보화파트·정보보호파트</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>있음(부분) — IT조직 명칭에 'AI' 반영(AI정보화기획실), 독립 AI전담실은 아님</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>AI정보화기획실 (정보화 기능과 AI·데이터 기능 통합)</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
           <t>처·실(본부 산하)</t>
         </is>
       </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>AI정보화기획실</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>있음(부분) — IT조직 명칭에 'AI' 반영(AI정보화기획실), 독립 AI전담실은 아님</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>AI정보화기획실 (정보화 기능과 AI·데이터 기능 통합)</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>처·실(본부 산하)</t>
-        </is>
-      </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
           <t>경영기획처장 소관 (추정)</t>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>IT담당배경: 경영기획처는 경영 전반을 담당하는 처이며, 그 산하 AI정보화기획실이 정보화·정보보안·데이터분석·공공데이터를 총괄함. 부서명에 'AI'를 명시하여 정보화와 AI 기능을 통합 운영.&lt;br&gt;IT기능: 정보화사업, 개인정보보호, 정보보안, 데이터분석, 공공데이터 개방&lt;br&gt;조직이력: (구)경영지원처&gt;재무정보실&gt;정보화센터 편제에서 경영기획처 산하 AI정보화기획실로 개편·승격&lt;br&gt;기타: 2025.12 'AI 대전환 기본계획' 추진 (AI 기반 물류·행정 혁신)</t>
+          <t>IT담당배경: 경영기획처 산하 AI정보화기획실(정보화파트·정보보호파트)이 정보화·정보보안·데이터분석·공공데이터를 총괄함. 부서명에 'AI'를 명시하여 정보화와 AI 기능을 통합 운영. 경영기획처 내 병렬조직(비IT): 혁신성장실·경영지원실·재무성과실·윤리경영노무법무실.&lt;br&gt;IT기능: 정보화사업, 개인정보보호, 정보보안, 데이터분석, 공공데이터 개방&lt;br&gt;조직이력: (구)경영지원처&gt;재무정보실&gt;정보화센터 편제에서 경영기획처 산하 AI정보화기획실로 개편·승격&lt;br&gt;기타: 2025.12 'AI 대전환 기본계획' 추진 (AI 기반 물류·행정 혁신)</t>
         </is>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>경영기획실</t>
+          <t>디지털혁신팀</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신팀</t>
+          <t>없음(단일 팀)</t>
         </is>
       </c>
       <c r="I73" s="3" t="inlineStr">
@@ -6821,29 +6821,29 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>경영본부</t>
+          <t>AI전략실</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>실(경영본부 산하)</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
+          <t>없음(단일 실, 하위 팀 세부명칭 미공개)</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>있음 (경영본부 산하 'AI전략실'이 AI를 명칭에 포함, AI·데이터·정보화·정보보안 통합 총괄)</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
           <t>AI전략실</t>
         </is>
       </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>있음 (경영본부 산하 'AI전략실'이 AI를 명칭에 포함, AI·데이터·정보화·정보보안 통합 총괄)</t>
-        </is>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>AI전략실</t>
-        </is>
-      </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
           <t>실 (경영본부 산하)</t>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>IT기능: AI·데이터·정보화사업·정보보안을 단일 실(AI전략실)에서 통합 운영&lt;br&gt;기타: '국토안전 빅데이터 플랫폼(bigtori)' 운영. LH와 건설사고 예측 AI 공동개발. 2020.12 한국시설안전공단+한국건설관리공사 통합 출범.</t>
+          <t>IT기능: AI·데이터·정보화사업·정보보안을 단일 실(AI전략실)에서 통합 운영&lt;br&gt;병렬조직(비IT): 경영본부 산하 기획조정실·인사노무실·ESG경영실·운영지원실(모두 비IT)&lt;br&gt;기타: '국토안전 빅데이터 플랫폼(bigtori)' 운영. LH와 건설사고 예측 AI 공동개발. 2020.12 한국시설안전공단+한국건설관리공사 통합 출범.</t>
         </is>
       </c>
     </row>
@@ -6896,17 +6896,17 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>기획본부</t>
+          <t>디지털혁신처</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>디지털혁신처(정보보안기획부·데이터사업부·디지털AI운영부)</t>
+          <t>정보보안기획부·데이터사업부·디지털AI운영부</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>경영관리본부</t>
+          <t>AI혁신처</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
@@ -7421,17 +7421,17 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>재생에너지기반본부</t>
+          <t>AI데이터처</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>처·실</t>
+          <t>처</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>AI데이터처</t>
+          <t>없음(단일 처)</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>경영기획처</t>
+          <t>정보화지원실</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>정보화지원실</t>
+          <t>없음(단일 실)</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>경영전략본부</t>
+          <t>정보보안팀</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>정보보안팀, 데이터정책팀</t>
+          <t>없음(단일 팀)</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
@@ -9671,17 +9671,17 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>전략본부</t>
+          <t>AI디지털혁신실</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>처·실</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>AI디지털혁신실(AI기획팀·정보보안팀)</t>
+          <t>AI기획팀·정보보안팀</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
@@ -10796,17 +10796,17 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>경영지원본부</t>
+          <t>디지털정보부</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>처·실</t>
+          <t>부</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>디지털정보부</t>
+          <t>없음 (디지털정보부 단일 부, 팀 하위조직 없음)</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
@@ -11096,17 +11096,17 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>예술협력본부</t>
+          <t>정보전략부</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>부(고객개발본부 산하)</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>정보전략부</t>
+          <t>없음(단일 부)</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>예술협력본부장 겸임 (추정 — 정보전략부가 예술협력본부 산하)</t>
+          <t>고객개발본부장 겸임 (추정 — 정보전략부가 고객개발본부 산하)</t>
         </is>
       </c>
       <c r="M142" s="3" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>IT기능: 정보화 운영, 정보보안, 개인정보보호, 앱·홈페이지 통합관리&lt;br&gt;기타: 경영본부·공연예술본부·예술협력본부 등 본부 체제. AI 전담조직 단서 확인되지 않음.</t>
+          <t>IT기능: 정보화 운영, 정보보안, 개인정보보호, 앱·홈페이지 통합관리&lt;br&gt;병렬조직(비IT): 고객개발본부 산하 마케팅홍보부·대관운영사업부(모두 비IT)&lt;br&gt;⚠조직개편 발견(2026-09-23): 현재 공식 조직도(sac.or.kr) 확인 결과 본부 체제가 경영전략본부·예술사업본부·성장사업본부·고객개발본부로 재편되어 있으며, 기존 기재된 '예술협력본부' 명칭은 현재 조직도에 존재하지 않음. 정보전략부는 현재 '고객개발본부' 산하로 소속 변경 확인. 현원·주무부처 등 타 필드는 본 작업 범위 밖이라 미변경 — 전체 재조사 권장.&lt;br&gt;기타: AI 전담조직 단서 확인되지 않음.</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>경영관리부문</t>
+          <t>정보시스템실</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>정보시스템실, AI혁신실</t>
+          <t>없음(단일 실)</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>경영기획본부</t>
+          <t>정보안전부</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>정보안전부, 정보보호팀, AI데이터혁신부</t>
+          <t>없음 (정보안전부 단일 부)</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="O157" s="3" t="inlineStr">
         <is>
-          <t>IT담당배경: 별도 IT 전담 본부는 없고, 경영기획본부 산하 '정보안전부'가 정보화·전산과 안전 기능을, '정보보호팀'이 정보보호를 담당. IT기능: 정보화·전산 운영, 정보보호. 조직이력: 종전 조사 시점의 '안전정보부'가 현 조직도에서 '정보안전부'로 표기되며, 별도 '정보보호팀'이 경영기획본부 산하에 병렬 편제됨. 정책지원본부 산하 '데이터연구부'는 'AI데이터혁신부'로 개편. 기타: AI데이터혁신부는 정책지원본부(경영기획본부가 아님) 산하로, 정책·평가 데이터와 AI 혁신 기능을 담당하는 조직. 사업 측면에서 'AI 기반 교재교구·환경구성' 디지털 컨설팅 교육 제공. 공식 도메인은 kcpi.or.kr → kicece.or.kr(영문약칭 KICECE).</t>
+          <t>IT담당배경: 별도 IT 전담 본부는 없고, 경영기획본부 산하 '정보안전부'가 정보화·전산과 안전 기능을 담당(IT최상위조직). IT기능: 정보화·전산 운영, 정보보호. 조직이력: 종전 조사 시점의 '안전정보부'가 현 조직도에서 '정보안전부'로 표기되며, 별도 '정보보호팀'이 경영기획본부 산하에 병렬 편제됨. 정책지원본부 산하 '데이터연구부'는 'AI데이터혁신부'로 개편. 병렬조직: '정보보호팀'은 경영기획본부 소속으로 정보안전부와 별도 편제된 정보보호 전담 팀(IT하위부서 아님, 병렬조직). 기타: AI데이터혁신부는 정책지원본부(경영기획본부가 아님) 산하로, 정책·평가 데이터와 AI 혁신 기능을 담당하는 별개 계통 조직. 사업 측면에서 'AI 기반 교재교구·환경구성' 디지털 컨설팅 교육 제공. 공식 도메인은 kcpi.or.kr → kicece.or.kr(영문약칭 KICECE).</t>
         </is>
       </c>
     </row>
@@ -12746,17 +12746,17 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>기획조정본부</t>
+          <t>스포츠정보화부</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>부 (기획조정본부 산하)</t>
+          <t>부(기획조정본부 산하)</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>스포츠정보화부</t>
+          <t>없음(단일 부)</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="O164" s="3" t="inlineStr">
         <is>
-          <t>IT기능: 체육정보화 기본계획·ISP 수립, 전산장비·DB·시스템 보안, 개인정보보호, 국가정보화 평가 대비, 스포츠ICT통합체계, 회원단체 정보화 지원, 데이터기반행정, 디지털혁신위원회 운영&lt;br&gt;기타: 2025년 정보화·공공데이터 분야 평가 '우수' 등급. AI 전담조직 없으나 디지털혁신위원회(스포츠정보화부 운영)로 디지털전환 추진.</t>
+          <t>IT기능: 체육정보화 기본계획·ISP 수립, 전산장비·DB·시스템 보안, 개인정보보호, 국가정보화 평가 대비, 스포츠ICT통합체계, 회원단체 정보화 지원, 데이터기반행정, 디지털혁신위원회 운영&lt;br&gt;병렬조직(비IT): 기획조정본부 산하 전략기획부·예산부·인사총무부·회계부(모두 비IT)&lt;br&gt;기타: 2025년 정보화·공공데이터 분야 평가 '우수' 등급. AI 전담조직 없으나 디지털혁신위원회(스포츠정보화부 운영)로 디지털전환 추진.</t>
         </is>
       </c>
     </row>
@@ -13871,17 +13871,17 @@
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>국가특허빅데이터본부</t>
+          <t>지능화플랫폼실</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>국가전략기술특허지원실, 특허동향지원실, 지능화플랫폼실</t>
+          <t>없음 (지능화플랫폼실 단일 실)</t>
         </is>
       </c>
       <c r="I179" s="3" t="inlineStr">
@@ -14096,7 +14096,7 @@
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>경영혁신본부</t>
+          <t>정보화팀</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>연구지원·정보실(정보화팀), 연구혁신본부(AI융합연구단)</t>
+          <t>없음(단일 팀). 연구혁신본부(AI융합연구단)는 별도 AI 연구조직</t>
         </is>
       </c>
       <c r="I182" s="3" t="inlineStr">
@@ -14321,17 +14321,17 @@
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>관리운영부</t>
+          <t>행정지원팀</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>처·실</t>
+          <t>팀(관리운영부 산하)</t>
         </is>
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>행정지원팀(정보화·정보보안, 전산·정보보안, 공공데이터·정보화 지원 담당)</t>
+          <t>없음(단일 팀, 정보화·정보보안 외 총무 등 업무 겸무)</t>
         </is>
       </c>
       <c r="I185" s="3" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="O185" s="3" t="inlineStr">
         <is>
-          <t>국방부 산하 기타공공기관, 전쟁기념관 운영. 회장 직속 대외협력실·감사부, 사무총장 산하 전략기획부·학예부·전시유물부·관리운영부·어린이박물관·W-아카데미 구성. 정보화/전산/정보보안은 관리운영부 행정지원팀 내 담당업무로 분산 수행하며, IT 전담 부/팀은 없음. 박물관 특성상 IT 조직이 행정지원 기능에 흡수된 전형적 소규모 구조.</t>
+          <t>국방부 산하 기타공공기관, 전쟁기념관 운영. 회장 직속 대외협력실·감사부, 사무총장 산하 전략기획부·학예부·전시유물부·관리운영부·어린이박물관·W-아카데미 구성. 정보화/전산/정보보안은 관리운영부 행정지원팀 내 담당업무(총무 등과 겸무)로 수행. 관리운영부 내 병렬조직(비IT): 시설관리팀·통합운영센터. 박물관 특성상 IT 기능이 행정지원팀의 여러 업무 중 하나로 흡수된 소규모 구조.</t>
         </is>
       </c>
     </row>
@@ -14696,17 +14696,17 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>기획경영본부</t>
+          <t>디지털정보실</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실</t>
         </is>
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
-          <t>디지털정보실(디지털정보팀 — 정보보안 전담, 정보시스템/IT인프라관리, 개인정보보호)</t>
+          <t>디지털정보팀 — 정보보안 전담, 정보시스템/IT인프라관리, 개인정보보호</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
@@ -15071,17 +15071,17 @@
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>경영지원실</t>
+          <t>전산팀</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>팀(본부 산하)</t>
+          <t>팀(경영지원실 산하)</t>
         </is>
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>전산팀, 학술정보팀</t>
+          <t>없음(단일 팀)</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="O195" s="3" t="inlineStr">
         <is>
-          <t>IT담당배경: 정부출연 연구기관 특성상 IT는 경영지원실 산하 전산팀 1개 팀 수준. 데이터/DB는 연구조정실 학술정보팀이 별도 담당.&lt;br&gt;기타: AI는 연구 주제(경제정책 분석)로 다루나 IT 전담 AI조직은 아님.</t>
+          <t>IT담당배경: 정부출연 연구기관 특성상 IT는 경영지원실 산하 전산팀 1개 팀 수준. 경영지원실 내 병렬조직(비IT): 인사팀·총무회계팀. 데이터/DB는 연구조정실 학술정보팀이 별도(비IT최상위조직 계열) 담당.&lt;br&gt;기타: AI는 연구 주제(경제정책 분석)로 다루나 IT 전담 AI조직은 아님.</t>
         </is>
       </c>
     </row>
@@ -15146,17 +15146,17 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>경영지원실</t>
+          <t>전산팀</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>처·실(본부 산하)</t>
+          <t>팀(경영지원실 산하)</t>
         </is>
       </c>
       <c r="H196" s="3" t="inlineStr">
         <is>
-          <t>전산팀</t>
+          <t>없음(단일 팀)</t>
         </is>
       </c>
       <c r="I196" s="3" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="O196" s="3" t="inlineStr">
         <is>
-          <t>IT담당배경: 경영지원실 산하 전산팀이 IT 전산 인프라를 담당하며, 별도 정보화 본부·처는 없음.&lt;br&gt;기타: '산업경제데이터분석실'은 산업데이터 연구·분석 조직으로 일반 정보화 조직과 구분. KIET 50주년(2026 기준, 1976년 전신 설립).</t>
+          <t>IT담당배경: 경영지원실 산하 전산팀이 IT 전산 인프라를 담당하며, 별도 정보화 본부·처는 없음. 경영지원실 내 병렬조직(비IT): 인사팀·총무팀·회계팀.&lt;br&gt;기타: '산업경제데이터분석실'은 산업데이터 연구·분석 조직으로 일반 정보화 조직과 구분. KIET 50주년(2026 기준, 1976년 전신 설립).</t>
         </is>
       </c>
     </row>
@@ -15221,17 +15221,17 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>경영지원실</t>
+          <t>정보기술융합팀</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>처·실</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>정보기술융합팀. 별도 데이터조사관리팀(재정통계연구실 산하 — 데이터 조사·관리)</t>
+          <t>없음(단일 팀). 별도 데이터조사관리팀(재정통계연구실 산하 — 데이터 조사·관리)</t>
         </is>
       </c>
       <c r="I197" s="3" t="inlineStr">
@@ -15371,17 +15371,17 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>정책본부</t>
+          <t>디지털AI실</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>실</t>
         </is>
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>디지털AI실(정보보안팀). 디지털AI실이 정보화·디지털·AI·공공데이터 총괄(공공데이터 제공 책임관=디지털AI실장)</t>
+          <t>정보보안팀. 디지털AI실이 정보화·디지털·AI·공공데이터 총괄(공공데이터 제공 책임관=디지털AI실장)</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
@@ -15671,7 +15671,7 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>사업전략본부</t>
+          <t>AI디지털전환실</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
-          <t>AI디지털전환실</t>
+          <t>없음 (AI디지털전환실 단일 실)</t>
         </is>
       </c>
       <c r="I203" s="3" t="inlineStr">
@@ -15746,7 +15746,7 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>기획경영본부</t>
+          <t>전산정보팀</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -15756,7 +15756,7 @@
       </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>경영지원실(전산정보팀), 수문자료디지털자동화추진단(디지털자동화추진1팀·디지털자동화추진2팀), 한강AI품질팀, 낙동강AI품질팀, 금강AI품질팀, 영산강AI품질팀</t>
+          <t>없음(단일 팀). 수문자료디지털자동화추진단·권역실 AI품질팀들은 수자원본부 소속 별도 현업조직(특이사항 참조)</t>
         </is>
       </c>
       <c r="I204" s="3" t="inlineStr">
@@ -17996,17 +17996,17 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>경영지원실</t>
+          <t>디지털기획부</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>처·실</t>
+          <t>부</t>
         </is>
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>디지털기획부(舊 ICT기획부 — 정보시스템 통합유지관리·인프라·네트워크·공공데이터·정보보안 전략·사이버안전센터 운영)</t>
+          <t>없음(단일 부)</t>
         </is>
       </c>
       <c r="I234" s="3" t="inlineStr">
@@ -18071,17 +18071,17 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>경영지원실</t>
+          <t>정보전산팀</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>처·실</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="H235" s="3" t="inlineStr">
         <is>
-          <t>정보전산팀(전산장비·소프트웨어 운영, 정보보안, 개인정보보호, 홈페이지, 공공데이터·데이터기반행정 통합 담당)</t>
+          <t>없음(단일 팀)</t>
         </is>
       </c>
       <c r="I235" s="3" t="inlineStr">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>경영혁신본부</t>
+          <t>기획조정실</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="H251" s="3" t="inlineStr">
         <is>
-          <t>기획조정실</t>
+          <t>없음 (기획조정실 단일 실)</t>
         </is>
       </c>
       <c r="I251" s="3" t="inlineStr">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>침해대응본부</t>
+          <t>정보기술부</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="H269" s="3" t="inlineStr">
         <is>
-          <t>정보기술부</t>
+          <t>없음 (정보기술부 단일 부)</t>
         </is>
       </c>
       <c r="I269" s="3" t="inlineStr">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>기획경영본부</t>
+          <t>정보화팀</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -20781,7 +20781,7 @@
       </c>
       <c r="H271" s="3" t="inlineStr">
         <is>
-          <t>정보화팀, 의약품통합정보관리팀</t>
+          <t>없음 (정보화팀 단일 팀)</t>
         </is>
       </c>
       <c r="I271" s="3" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="O271" s="3" t="inlineStr">
         <is>
-          <t>IT담당배경: IT 전담 조직은 **기획경영본부** 산하 정보화팀·의약품통합정보관리팀 2개 팀이다(IT하위부서에는 이 2개 팀만 기재). 이와 별개로 **의약품안전정보본부**(기획경영본부와 병렬인 별도 본부) 산하 약물역학빅데이터팀·DUR정보팀이 데이터 분석·DUR 정보를 담당하나, 계층이 다른 본부이므로 IT하위부서에 넣지 않고 본 항목에 기재한다.&lt;br&gt;IT기능: 정보화팀 — 정보화·전산·정보보안 총괄 / 의약품통합정보관리팀 — 의약품통합정보시스템·KAERS 등 핵심 정보시스템 운영 / (의약품안전정보본부) 약물역학빅데이터팀 — 약물역학 데이터 분석·CDM / (의약품안전정보본부) DUR정보팀 — DUR 정보 관리.&lt;br&gt;AI판정근거: 2026-09-19 공식 조직도 라이브 재추출 결과 AI 명칭 조직은 마약류통합정보관리본부 산하 **마약류AI혁신TF** 1건뿐이다. 통일기준(상설 직제가 아닌 위원회·TF·협의체는 AI전담조직으로 계상하지 않음)에 따라 AI전담조직 '없음'을 유지하되, 향후 정규 팀 승격 시 재판정 대상.&lt;br&gt;조직이력: 2026년 9월 현재 공식 조직도 기준 원장 직속 감사팀 + 4본부 14팀 1TF 체계(마약류AI혁신TF 신설 확인). 기획경영본부에 전략기획팀 신설(전략기획팀·혁신경영팀·교육홍보팀·정보화팀·의약품통합정보관리팀), 의약품안전조사본부에 임상시험안전지원팀 신설(의약품부작용피해구제팀·첨단바이오규제과학팀·임상시험안전지원팀). 종전 조사 시 기재된 마약류감사지원TF는 현 조직도에 미표시.&lt;br&gt;기타: 약칭 KIDS, 식약처 산하 국내 유일 약물감시 전담기관(2012 설립). 의약품안전정보본부(안전정보관리팀·약물역학빅데이터팀·DUR정보팀), 마약류통합정보관리본부(마약류시스템운영팀·마약류제도지원팀·마약류정보분석팀). 2025~2028 'AI·빅데이터 기반 능동형 약물감시 전면 개편'(LLM 기반 이상사례 검토 자동화, EMR-CDM 확대, 비정형 데이터 NLP 표준화, K-NASS 마약류 통합감시) 추진 — 조직명에 'AI'가 들어간 전담조직은 없으며 의약품안전정보본부·정보화팀이 본업에 AI 적용.</t>
+          <t>IT담당배경: 기획경영본부 산하는 전략기획팀·혁신경영팀·교육홍보팀·정보화팀·의약품통합정보관리팀 5개 팀으로, 이 중 IT 관련은 정보화팀·의약품통합정보관리팀 2개뿐(혼합기준상 소수) → 정보화·정보보안 총괄부서인 '정보화팀'을 IT최상위조직으로 기재. 병렬조직: 같은 기획경영본부 소속 '의약품통합정보관리팀'(의약품통합정보시스템·KAERS 등 핵심 정보시스템 운영)이 정보화팀과 별도로 병렬 편제(IT하위부서 아님). 이와 별개로 **의약품안전정보본부**(기획경영본부와 병렬인 별도 본부) 산하 약물역학빅데이터팀·DUR정보팀이 데이터 분석·DUR 정보를 담당하나, 계층이 다른 본부이므로 IT하위부서에 넣지 않고 본 항목에 기재한다.&lt;br&gt;IT기능: 정보화팀 — 정보화·전산·정보보안 총괄 / 의약품통합정보관리팀 — 의약품통합정보시스템·KAERS 등 핵심 정보시스템 운영 / (의약품안전정보본부) 약물역학빅데이터팀 — 약물역학 데이터 분석·CDM / (의약품안전정보본부) DUR정보팀 — DUR 정보 관리.&lt;br&gt;AI판정근거: 2026-09-19 공식 조직도 라이브 재추출 결과 AI 명칭 조직은 마약류통합정보관리본부 산하 **마약류AI혁신TF** 1건뿐이다. 통일기준(상설 직제가 아닌 위원회·TF·협의체는 AI전담조직으로 계상하지 않음)에 따라 AI전담조직 '없음'을 유지하되, 향후 정규 팀 승격 시 재판정 대상.&lt;br&gt;조직이력: 2026년 9월 현재 공식 조직도 기준 원장 직속 감사팀 + 4본부 14팀 1TF 체계(마약류AI혁신TF 신설 확인). 기획경영본부에 전략기획팀 신설(전략기획팀·혁신경영팀·교육홍보팀·정보화팀·의약품통합정보관리팀), 의약품안전조사본부에 임상시험안전지원팀 신설(의약품부작용피해구제팀·첨단바이오규제과학팀·임상시험안전지원팀). 종전 조사 시 기재된 마약류감사지원TF는 현 조직도에 미표시.&lt;br&gt;기타: 약칭 KIDS, 식약처 산하 국내 유일 약물감시 전담기관(2012 설립). 의약품안전정보본부(안전정보관리팀·약물역학빅데이터팀·DUR정보팀), 마약류통합정보관리본부(마약류시스템운영팀·마약류제도지원팀·마약류정보분석팀). 2025~2028 'AI·빅데이터 기반 능동형 약물감시 전면 개편'(LLM 기반 이상사례 검토 자동화, EMR-CDM 확대, 비정형 데이터 NLP 표준화, K-NASS 마약류 통합감시) 추진 — 조직명에 'AI'가 들어간 전담조직은 없으며 의약품안전정보본부·정보화팀이 본업에 AI 적용.</t>
         </is>
       </c>
     </row>
@@ -21130,11 +21130,11 @@
         <v>29</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -21164,11 +21164,11 @@
         <v>60</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -21198,11 +21198,11 @@
         <v>184</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -21232,11 +21232,11 @@
         <v>273</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
@@ -21294,11 +21294,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
     </row>
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.2%</t>
         </is>
       </c>
     </row>
@@ -21324,11 +21324,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.6%</t>
         </is>
       </c>
     </row>
@@ -21339,11 +21339,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -11101,7 +11101,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>부(고객개발본부 산하)</t>
+          <t>부</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
@@ -11116,32 +11116,32 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>해당 없음</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr">
         <is>
-          <t>고객개발본부장 겸임 (추정 — 정보전략부가 고객개발본부 산하)</t>
+          <t>확인불가 (고객개발본부장이 정보전략부 소관 본부장으로서 총괄 추정, 전담 CIO 명문 표기 없음)</t>
         </is>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>정보전략부 (정보보안·개인정보보호 담당). 전담 CISO 임원 직제 확인불가</t>
+          <t>개인정보보호책임자=고객개발본부장 박거일, 개인정보보호담당자=정보전략부 주임 이지연(개인정보처리방침 명시). 전담 임원급 CISO 직제는 별도 확인불가</t>
         </is>
       </c>
       <c r="N142" s="3" t="inlineStr">
         <is>
-          <t>상(공식 홈페이지 조직도 + 임직원 페이지 2출처)</t>
+          <t>상(공식 조직도+주요 임직원+개인정보처리방침 3출처 교차, 라이브 재검증 2026-09-23)</t>
         </is>
       </c>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>IT기능: 정보화 운영, 정보보안, 개인정보보호, 앱·홈페이지 통합관리&lt;br&gt;병렬조직(비IT): 고객개발본부 산하 마케팅홍보부·대관운영사업부(모두 비IT)&lt;br&gt;⚠조직개편 발견(2026-09-23): 현재 공식 조직도(sac.or.kr) 확인 결과 본부 체제가 경영전략본부·예술사업본부·성장사업본부·고객개발본부로 재편되어 있으며, 기존 기재된 '예술협력본부' 명칭은 현재 조직도에 존재하지 않음. 정보전략부는 현재 '고객개발본부' 산하로 소속 변경 확인. 현원·주무부처 등 타 필드는 본 작업 범위 밖이라 미변경 — 전체 재조사 권장.&lt;br&gt;기타: AI 전담조직 단서 확인되지 않음.</t>
+          <t>[조직체계] 사장(대표자 장한나) 직속 감사실·기획전략실·문화협력실 + 4개 본부(경영전략본부·예술사업본부·성장사업본부·고객개발본부). 경영전략본부(재무전략부·인사관리부·시설관리부·재난안전부), 예술사업본부(무대예술사업부·음악사업부·전시사업부·무대운영부), 성장사업본부(야외사업부·교육사업부·영상사업부), 고객개발본부(정보전략부·마케팅홍보부·대관운영사업부).&lt;br&gt;[IT기능] 정보전략부 — 정보화사업 전개, 홈페이지, 정보화 운영, 정보보안 및 개인정보보호, 기관 앱 통합관리.&lt;br&gt;[조직이력] 종전(2026-06) 기재된 '경영본부·공연예술본부·예술협력본부' 체제는 현재 조직도에 없음 — '경영전략본부·예술사업본부·성장사업본부·고객개발본부' 체제로 전면 개편 확인(개편 시점 불명, 최소 2026-09-23 이전). 舊 '예술협력본부' 산하였던 정보전략부는 현재 '고객개발본부' 산하로 소속 변경.&lt;br&gt;[승격규칙] 고객개발본부 산하 3개 부(정보전략부·마케팅홍보부·대관운영사업부) 중 IT 관련은 정보전략부 1개뿐 → 혼합기준상 비승격, 실무조직 '정보전략부'를 IT최상위조직으로 유지.&lt;br&gt;[기타] 전체 조직도·임직원 명단 어디에도 'AI' 명칭 조직 없음 — AI전담조직 '없음' 재확인.</t>
         </is>
       </c>
     </row>
@@ -21324,11 +21324,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.0%</t>
         </is>
       </c>
     </row>
@@ -21339,11 +21339,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
     </row>

--- a/IT조직_비교표_공공기관274.xlsx
+++ b/IT조직_비교표_공공기관274.xlsx
@@ -1951,7 +1951,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>본부(본부 산하)</t>
+          <t>본부</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
@@ -8636,17 +8636,17 @@
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>있음(지능정보 기능 중심)</t>
+          <t>없음 — 지능정보 명칭만 존재(AI/AX/인공지능 명시 조직 아님, 계상기준)</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>지능생태정보실 (산하 지능정보전략팀)</t>
+          <t>해당없음 (IT: 지능생태정보실)</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>실 (원장 직속)</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L109" s="3" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
@@ -10201,7 +10201,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
@@ -10361,17 +10361,17 @@
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>없음 — 지능정보 명칭만 존재(AI/AX/인공지능 명시 조직 아님, 계상기준)</t>
         </is>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>지능정보화센터 (지능정보전략실·지능정보기술실·지능정보데이터실)</t>
+          <t>해당없음 (IT: 지능정보화센터)</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>센터</t>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H139" s="3" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>없음 (정보화 직제 기준). 단, 연구사업 조직에 AI 관련 연구팀 존재</t>
+          <t>있음 — 연구사업 AI 조직(통일기준 소급: 연구/사업 불문)</t>
         </is>
       </c>
       <c r="J146" s="3" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>부 (경영본부 산하)</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
@@ -13351,7 +13351,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H175" s="3" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H177" s="3" t="inlineStr">
@@ -13736,17 +13736,17 @@
       </c>
       <c r="I177" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>있음 — 의료AI교육팀(교육 사업조직, 통일기준 소급)</t>
         </is>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담 부서는 아니나 보건인재양성본부 바이오헬스교육실 산하 '의료AI교육팀' 확인 — 교육과정 운영 조직)</t>
+          <t>의료AI교육팀</t>
         </is>
       </c>
       <c r="K177" s="3" t="inlineStr">
         <is>
-          <t>확인불가</t>
+          <t>팀</t>
         </is>
       </c>
       <c r="L177" s="3" t="inlineStr">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H188" s="3" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H194" s="3" t="inlineStr">
@@ -15301,7 +15301,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H198" s="3" t="inlineStr">
@@ -16351,7 +16351,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H212" s="3" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H214" s="3" t="inlineStr">
@@ -16726,7 +16726,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>확인불가 — 전담 IT조직 없음(인사노무처 담당자 배치)</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H218" s="3" t="inlineStr">
@@ -16961,12 +16961,12 @@
       </c>
       <c r="I220" s="3" t="inlineStr">
         <is>
-          <t>확인불가 (전담 AI 조직 미확인 — 디지털·AI 전환 대응은 디지털전환팀이 수행)</t>
+          <t>있음 — 디지털전환팀(DAX팀) AX 명시(통일기준 소급)</t>
         </is>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>디지털전환팀</t>
+          <t>디지털전환팀(DAX팀)</t>
         </is>
       </c>
       <c r="K220" s="3" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H221" s="3" t="inlineStr">
@@ -18151,7 +18151,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H236" s="3" t="inlineStr">
@@ -18301,7 +18301,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>처·실(본부 산하)</t>
         </is>
       </c>
       <c r="H238" s="3" t="inlineStr">
@@ -18601,7 +18601,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H242" s="3" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H259" s="3" t="inlineStr">
@@ -20026,7 +20026,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>본부</t>
+          <t>팀(본부 산하)</t>
         </is>
       </c>
       <c r="H261" s="3" t="inlineStr">
@@ -21130,11 +21130,11 @@
         <v>29</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -21164,19 +21164,19 @@
         <v>60</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="G4" s="5" t="n">
@@ -21198,27 +21198,27 @@
         <v>184</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -21232,27 +21232,27 @@
         <v>273</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>11.0%</t>
         </is>
       </c>
     </row>
@@ -21294,11 +21294,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -21309,11 +21309,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -21324,11 +21324,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -21339,11 +21339,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
     </row>
@@ -21385,11 +21385,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.6%</t>
         </is>
       </c>
     </row>
@@ -21400,11 +21400,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
     </row>
@@ -21415,11 +21415,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>4.8%</t>
         </is>
       </c>
     </row>
@@ -21525,7 +21525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -22030,7 +22030,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>한국보건복지인재원</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -22044,11 +22044,11 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>238.6</v>
+        <v>232.5</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침 + 공공데이터포털 담당부서 표기 + 알리오 교차 확인)</t>
+          <t>상(공식 개인정보처리방침 + 알리오 + 보도 교차 확인)</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -22058,7 +22058,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>경영전략본부</t>
+          <t>연금사업본부</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -22070,7 +22070,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>사립학교교직원연금공단</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -22084,11 +22084,11 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>232.5</v>
+        <v>202.3</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침 + 알리오 + 보도 교차 확인)</t>
+          <t>상(공식 개인정보처리방침(2025.7.10) + 공시 부서별 업무추진계획 + 보도 교차 확인)</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -22098,7 +22098,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>연금사업본부</t>
+          <t>융합기술센터 / 데이터정보화팀</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -22110,7 +22110,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>국제방송교류재단</t>
+          <t>한국기상산업기술원</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -22124,11 +22124,11 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>202.3</v>
+        <v>151.8</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>상(공식 개인정보처리방침(2025.7.10) + 공시 부서별 업무추진계획 + 보도 교차 확인)</t>
+          <t>상(공식 홈페이지 조직도 + 공공데이터포털 기관조직 데이터 교차확인)</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -22138,90 +22138,10 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>융합기술센터 / 데이터정보화팀</t>
+          <t>경영기획본부</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>확인불가</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>과학기술정책연구원</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>152</v>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>상(공식 홈페이지 개인정보처리방침으로 경영지원실·디지털전환팀 소속·CPO 확인 + 2026 개편 보도 다수 교차확인)</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>경영지원실</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>확인불가 (전담 AI 조직 미확인 — 디지털·AI 전환 대응은 디지털전환팀이 수행)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>한국기상산업기술원</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>기타공공기관</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>151.8</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>상(공식 홈페이지 조직도 + 공공데이터포털 기관조직 데이터 교차확인)</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>AI전담 확인불가</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>경영기획본부</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>확인불가 (전담 조직 미확인 — 데이터/AI 업무는 산업육성실 기상기후데이터·빅데이터 사업에서 수행)</t>
         </is>
